--- a/Result/analyze_4.xlsx
+++ b/Result/analyze_4.xlsx
@@ -682,19 +682,19 @@
         <v>79024.497669</v>
       </c>
       <c r="H6" t="n">
-        <v>85367.476962</v>
+        <v>83502.547507</v>
       </c>
       <c r="I6" t="n">
-        <v>85349.38688400001</v>
+        <v>83166.929366</v>
       </c>
       <c r="J6" t="n">
-        <v>90108.166631</v>
+        <v>87782.524467</v>
       </c>
       <c r="K6" t="n">
-        <v>78267.47951999999</v>
+        <v>76053.04532600001</v>
       </c>
       <c r="L6" t="n">
-        <v>92632.856988</v>
+        <v>88583.42969200001</v>
       </c>
       <c r="M6" t="n">
         <v>91303.38544100001</v>
@@ -790,34 +790,34 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>85194.841172</v>
+        <v>85196.192029</v>
       </c>
       <c r="D9" t="n">
-        <v>70351.61664399999</v>
+        <v>70354.48411600001</v>
       </c>
       <c r="E9" t="n">
-        <v>71132.16093300001</v>
+        <v>71133.84921499999</v>
       </c>
       <c r="F9" t="n">
-        <v>75099.850895</v>
+        <v>75100.920121</v>
       </c>
       <c r="G9" t="n">
-        <v>73253.446033</v>
+        <v>73255.56247200001</v>
       </c>
       <c r="H9" t="n">
-        <v>75968.30987700001</v>
+        <v>75969.98527799999</v>
       </c>
       <c r="I9" t="n">
-        <v>72076.00026099999</v>
+        <v>72078.454633</v>
       </c>
       <c r="J9" t="n">
-        <v>74069.22224425001</v>
+        <v>74070.71950825</v>
       </c>
       <c r="K9" t="n">
-        <v>58132.49851333334</v>
+        <v>58133.61134633334</v>
       </c>
       <c r="L9" t="n">
-        <v>70772.28312750001</v>
+        <v>70773.7442645</v>
       </c>
       <c r="M9" t="n">
         <v>54272.960127</v>
@@ -1690,41 +1690,39 @@
           <t>人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>6512.784052</v>
+        <v>6513.192402</v>
       </c>
       <c r="D31" t="n">
-        <v>7597.565447</v>
+        <v>7598.007797</v>
       </c>
       <c r="E31" t="n">
-        <v>4288.218102</v>
+        <v>4292.720068</v>
       </c>
       <c r="F31" t="n">
-        <v>9445.283126</v>
+        <v>9445.719725999999</v>
       </c>
       <c r="G31" t="n">
-        <v>15992.263185</v>
+        <v>15992.937051</v>
       </c>
       <c r="H31" t="n">
-        <v>15404.957424</v>
+        <v>15405.400974</v>
       </c>
       <c r="I31" t="n">
-        <v>17134.51228366667</v>
+        <v>17134.94443566666</v>
       </c>
       <c r="J31" t="n">
-        <v>19054.707612</v>
+        <v>19055.165762</v>
       </c>
       <c r="K31" t="n">
-        <v>15869.545266</v>
+        <v>15869.923663</v>
       </c>
       <c r="L31" t="n">
-        <v>6586.691708</v>
+        <v>6587.151408</v>
       </c>
       <c r="M31" t="n">
-        <v>7382.643532</v>
+        <v>7383.058642</v>
       </c>
     </row>
     <row r="32">
@@ -1733,39 +1731,41 @@
           <t>休閒車業</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
       <c r="C32" t="n">
-        <v>45984.706118</v>
+        <v>45984.68464</v>
       </c>
       <c r="D32" t="n">
-        <v>24000.580897</v>
+        <v>24000.557848</v>
       </c>
       <c r="E32" t="n">
-        <v>20013.67561</v>
+        <v>20013.65139</v>
       </c>
       <c r="F32" t="n">
-        <v>16638.372498</v>
+        <v>16638.362498</v>
       </c>
       <c r="G32" t="n">
-        <v>14503.403721</v>
+        <v>14503.320006</v>
       </c>
       <c r="H32" t="n">
-        <v>21881.452664</v>
+        <v>21881.431882</v>
       </c>
       <c r="I32" t="n">
-        <v>31847.118301</v>
+        <v>31847.108974</v>
       </c>
       <c r="J32" t="n">
-        <v>18372.43646</v>
+        <v>18372.429192</v>
       </c>
       <c r="K32" t="n">
-        <v>13129.531043</v>
+        <v>13129.52006</v>
       </c>
       <c r="L32" t="n">
-        <v>12908.778483</v>
+        <v>12908.744704</v>
       </c>
       <c r="M32" t="n">
-        <v>9526.674677999999</v>
+        <v>9526.670403</v>
       </c>
     </row>
     <row r="33">
@@ -1856,39 +1856,41 @@
           <t>保健食品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
       <c r="C35" t="n">
-        <v>1490.016545</v>
+        <v>1490.015662</v>
       </c>
       <c r="D35" t="n">
-        <v>2178.069156</v>
+        <v>2178.068418</v>
       </c>
       <c r="E35" t="n">
-        <v>3756.223559</v>
+        <v>3756.222262</v>
       </c>
       <c r="F35" t="n">
-        <v>2797.791879</v>
+        <v>2797.791647</v>
       </c>
       <c r="G35" t="n">
-        <v>1903.256109</v>
+        <v>1903.25528</v>
       </c>
       <c r="H35" t="n">
-        <v>2009.855617</v>
+        <v>2009.849577</v>
       </c>
       <c r="I35" t="n">
-        <v>1378.992722</v>
+        <v>1378.989649</v>
       </c>
       <c r="J35" t="n">
-        <v>1107.814607</v>
+        <v>1107.814458</v>
       </c>
       <c r="K35" t="n">
-        <v>536.77061</v>
+        <v>536.770076</v>
       </c>
       <c r="L35" t="n">
-        <v>570.993468</v>
+        <v>570.992154</v>
       </c>
       <c r="M35" t="n">
-        <v>676.856773</v>
+        <v>676.856394</v>
       </c>
     </row>
     <row r="36">
@@ -2102,41 +2104,39 @@
           <t>傳動元件</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>30460.036334</v>
+        <v>30460.040346</v>
       </c>
       <c r="D41" t="n">
-        <v>15403.481703</v>
+        <v>15403.489362</v>
       </c>
       <c r="E41" t="n">
-        <v>14698.670508</v>
+        <v>14698.674189</v>
       </c>
       <c r="F41" t="n">
-        <v>11292.177166</v>
+        <v>11292.179246</v>
       </c>
       <c r="G41" t="n">
-        <v>10149.69114266667</v>
+        <v>10149.69380766667</v>
       </c>
       <c r="H41" t="n">
-        <v>19453.01710166667</v>
+        <v>19453.02047866667</v>
       </c>
       <c r="I41" t="n">
-        <v>22912.6644405</v>
+        <v>22912.6677555</v>
       </c>
       <c r="J41" t="n">
-        <v>14904.26401875</v>
+        <v>14904.26534975</v>
       </c>
       <c r="K41" t="n">
-        <v>11399.30612808333</v>
+        <v>11399.31037108333</v>
       </c>
       <c r="L41" t="n">
-        <v>14560.88032966667</v>
+        <v>14560.88447166667</v>
       </c>
       <c r="M41" t="n">
-        <v>8460.0064575</v>
+        <v>8460.0084995</v>
       </c>
     </row>
     <row r="42">
@@ -2227,41 +2227,39 @@
           <t>光學鏡片、鏡頭</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>26449.602585</v>
+        <v>26741.200868</v>
       </c>
       <c r="D44" t="n">
-        <v>19418.991422</v>
+        <v>19768.37797</v>
       </c>
       <c r="E44" t="n">
-        <v>18982.651336</v>
+        <v>19624.769793</v>
       </c>
       <c r="F44" t="n">
-        <v>16389.018143</v>
+        <v>16705.970816</v>
       </c>
       <c r="G44" t="n">
-        <v>14731.944132</v>
+        <v>15101.692128</v>
       </c>
       <c r="H44" t="n">
-        <v>13442.938653</v>
+        <v>13680.335716</v>
       </c>
       <c r="I44" t="n">
-        <v>12763.187485</v>
+        <v>12945.082042</v>
       </c>
       <c r="J44" t="n">
-        <v>13857.502465</v>
+        <v>14071.858038</v>
       </c>
       <c r="K44" t="n">
-        <v>9028.91346</v>
+        <v>10726.72899</v>
       </c>
       <c r="L44" t="n">
-        <v>12069.594688</v>
+        <v>13152.352391</v>
       </c>
       <c r="M44" t="n">
-        <v>9933.479633999999</v>
+        <v>10383.890674</v>
       </c>
     </row>
     <row r="45">
@@ -2352,39 +2350,41 @@
           <t>光碟片</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
       <c r="C47" t="n">
-        <v>44.714366</v>
+        <v>40.408114</v>
       </c>
       <c r="D47" t="n">
-        <v>74.509807</v>
+        <v>69.425997</v>
       </c>
       <c r="E47" t="n">
-        <v>56.177821</v>
+        <v>49.803235</v>
       </c>
       <c r="F47" t="n">
-        <v>26.609233</v>
+        <v>23.22163</v>
       </c>
       <c r="G47" t="n">
-        <v>40.066344</v>
+        <v>36.031295</v>
       </c>
       <c r="H47" t="n">
-        <v>57.93039</v>
+        <v>54.191911</v>
       </c>
       <c r="I47" t="n">
-        <v>73.702658</v>
+        <v>70.924609</v>
       </c>
       <c r="J47" t="n">
-        <v>241.125946</v>
+        <v>203.953011</v>
       </c>
       <c r="K47" t="n">
-        <v>425.311037</v>
+        <v>403.765878</v>
       </c>
       <c r="L47" t="n">
-        <v>311.126186</v>
+        <v>303.597329</v>
       </c>
       <c r="M47" t="n">
-        <v>163.438117</v>
+        <v>156.106302</v>
       </c>
     </row>
     <row r="48">
@@ -2520,37 +2520,37 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>47033.2485695</v>
+        <v>47033.2548585</v>
       </c>
       <c r="D51" t="n">
-        <v>31676.44524</v>
+        <v>31676.454858</v>
       </c>
       <c r="E51" t="n">
-        <v>34115.67231541667</v>
+        <v>34115.67992341667</v>
       </c>
       <c r="F51" t="n">
-        <v>36047.41857716667</v>
+        <v>36047.42536816667</v>
       </c>
       <c r="G51" t="n">
-        <v>25393.610897</v>
+        <v>25393.625524</v>
       </c>
       <c r="H51" t="n">
-        <v>44509.93301258334</v>
+        <v>44509.94315558334</v>
       </c>
       <c r="I51" t="n">
-        <v>48209.92709041666</v>
+        <v>48209.94686041666</v>
       </c>
       <c r="J51" t="n">
-        <v>33772.90881575</v>
+        <v>33772.92030075</v>
       </c>
       <c r="K51" t="n">
-        <v>23303.467807</v>
+        <v>23303.470196</v>
       </c>
       <c r="L51" t="n">
-        <v>28133.37567916667</v>
+        <v>28133.38707816667</v>
       </c>
       <c r="M51" t="n">
-        <v>19870.2884835</v>
+        <v>19870.2952005</v>
       </c>
     </row>
     <row r="52">
@@ -2561,37 +2561,37 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>850.917544</v>
+        <v>1083.567993</v>
       </c>
       <c r="D52" t="n">
-        <v>483.120339</v>
+        <v>522.682177</v>
       </c>
       <c r="E52" t="n">
-        <v>950.760301</v>
+        <v>986.570341</v>
       </c>
       <c r="F52" t="n">
-        <v>549.885051</v>
+        <v>569.83836</v>
       </c>
       <c r="G52" t="n">
-        <v>470.45308</v>
+        <v>489.609658</v>
       </c>
       <c r="H52" t="n">
-        <v>499.508679</v>
+        <v>517.295923</v>
       </c>
       <c r="I52" t="n">
-        <v>606.729313</v>
+        <v>620.804759</v>
       </c>
       <c r="J52" t="n">
-        <v>529.679578</v>
+        <v>543.539902</v>
       </c>
       <c r="K52" t="n">
-        <v>403.810574</v>
+        <v>420.807488</v>
       </c>
       <c r="L52" t="n">
-        <v>311.935238</v>
+        <v>327.804768</v>
       </c>
       <c r="M52" t="n">
-        <v>246.767857</v>
+        <v>259.270831</v>
       </c>
     </row>
     <row r="53">
@@ -2600,41 +2600,39 @@
           <t>其他零組件</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>49330.127649</v>
+        <v>49333.678205</v>
       </c>
       <c r="D53" t="n">
-        <v>26393.58628</v>
+        <v>26397.301791</v>
       </c>
       <c r="E53" t="n">
-        <v>21557.122042</v>
+        <v>21561.434505</v>
       </c>
       <c r="F53" t="n">
-        <v>18102.597473</v>
+        <v>18105.260836</v>
       </c>
       <c r="G53" t="n">
-        <v>15942.863506</v>
+        <v>15945.882343</v>
       </c>
       <c r="H53" t="n">
-        <v>23459.243104</v>
+        <v>23464.156393</v>
       </c>
       <c r="I53" t="n">
-        <v>33405.416135</v>
+        <v>33407.949983</v>
       </c>
       <c r="J53" t="n">
-        <v>20063.928003</v>
+        <v>20067.967382</v>
       </c>
       <c r="K53" t="n">
-        <v>14356.310506</v>
+        <v>14361.574585</v>
       </c>
       <c r="L53" t="n">
-        <v>14729.908991</v>
+        <v>14732.670478</v>
       </c>
       <c r="M53" t="n">
-        <v>11541.367832</v>
+        <v>11545.119892</v>
       </c>
     </row>
     <row r="54">
@@ -2725,41 +2723,39 @@
           <t>其他電腦及週邊設備之零組件</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>0</v>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>52388.429196</v>
+        <v>52651.59588</v>
       </c>
       <c r="D56" t="n">
-        <v>23886.7318575</v>
+        <v>24291.1721905</v>
       </c>
       <c r="E56" t="n">
-        <v>19461.460754</v>
+        <v>19680.279914</v>
       </c>
       <c r="F56" t="n">
-        <v>19230.679015</v>
+        <v>19652.564444</v>
       </c>
       <c r="G56" t="n">
-        <v>20892.476165</v>
+        <v>21196.746615</v>
       </c>
       <c r="H56" t="n">
-        <v>13160.932113</v>
+        <v>13243.58567</v>
       </c>
       <c r="I56" t="n">
-        <v>20245.31622</v>
+        <v>20393.705095</v>
       </c>
       <c r="J56" t="n">
-        <v>14150.422163</v>
+        <v>14256.342762</v>
       </c>
       <c r="K56" t="n">
-        <v>12886.59241025</v>
+        <v>12981.83893425</v>
       </c>
       <c r="L56" t="n">
-        <v>12552.70380233333</v>
+        <v>12620.11083233333</v>
       </c>
       <c r="M56" t="n">
-        <v>9603.340627</v>
+        <v>9701.660974</v>
       </c>
     </row>
     <row r="57">
@@ -3301,39 +3297,41 @@
           <t>化妝品</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
       <c r="C70" t="n">
-        <v>21.666071</v>
+        <v>17.95503</v>
       </c>
       <c r="D70" t="n">
-        <v>9.060294000000001</v>
+        <v>5.284859</v>
       </c>
       <c r="E70" t="n">
-        <v>39.56759</v>
+        <v>36.183741</v>
       </c>
       <c r="F70" t="n">
-        <v>14.128363</v>
+        <v>9.746195</v>
       </c>
       <c r="G70" t="n">
-        <v>9.064895999999999</v>
+        <v>7.978753</v>
       </c>
       <c r="H70" t="n">
-        <v>18.569356</v>
+        <v>15.262535</v>
       </c>
       <c r="I70" t="n">
-        <v>10.997686</v>
+        <v>9.191566999999999</v>
       </c>
       <c r="J70" t="n">
-        <v>7.671489</v>
+        <v>5.029509</v>
       </c>
       <c r="K70" t="n">
-        <v>15.747262</v>
+        <v>14.177253</v>
       </c>
       <c r="L70" t="n">
-        <v>16.928357</v>
+        <v>13.971637</v>
       </c>
       <c r="M70" t="n">
-        <v>17.156959</v>
+        <v>13.827422</v>
       </c>
     </row>
     <row r="71">
@@ -3342,41 +3340,39 @@
           <t>化學助劑</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>0</v>
-      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>474.4204215</v>
+        <v>474.8287715</v>
       </c>
       <c r="D71" t="n">
-        <v>748.606107</v>
+        <v>749.048457</v>
       </c>
       <c r="E71" t="n">
-        <v>1536.344274666667</v>
+        <v>1540.846240666667</v>
       </c>
       <c r="F71" t="n">
-        <v>703.4165144999999</v>
+        <v>703.8531144999999</v>
       </c>
       <c r="G71" t="n">
-        <v>537.387782</v>
+        <v>538.061648</v>
       </c>
       <c r="H71" t="n">
-        <v>470.1934165</v>
+        <v>470.6369665</v>
       </c>
       <c r="I71" t="n">
-        <v>388.906953</v>
+        <v>389.339105</v>
       </c>
       <c r="J71" t="n">
-        <v>267.330528</v>
+        <v>267.788678</v>
       </c>
       <c r="K71" t="n">
-        <v>191.308289</v>
+        <v>191.686686</v>
       </c>
       <c r="L71" t="n">
-        <v>327.614721</v>
+        <v>328.074421</v>
       </c>
       <c r="M71" t="n">
-        <v>182.636044</v>
+        <v>183.051154</v>
       </c>
     </row>
     <row r="72">
@@ -3385,39 +3381,41 @@
           <t>化學品</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
       <c r="C72" t="n">
-        <v>1571.013834</v>
+        <v>1453.77269</v>
       </c>
       <c r="D72" t="n">
-        <v>1909.272398</v>
+        <v>1822.598945</v>
       </c>
       <c r="E72" t="n">
-        <v>3545.125341</v>
+        <v>3286.051457</v>
       </c>
       <c r="F72" t="n">
-        <v>2322.650865</v>
+        <v>2156.906603</v>
       </c>
       <c r="G72" t="n">
-        <v>2650.275269</v>
+        <v>2399.519558</v>
       </c>
       <c r="H72" t="n">
-        <v>2230.393096</v>
+        <v>2052.561736</v>
       </c>
       <c r="I72" t="n">
-        <v>2061.16478</v>
+        <v>1861.831628</v>
       </c>
       <c r="J72" t="n">
-        <v>2239.642162</v>
+        <v>2124.768903</v>
       </c>
       <c r="K72" t="n">
-        <v>1324.705185</v>
+        <v>1204.942627</v>
       </c>
       <c r="L72" t="n">
-        <v>1953.52813</v>
+        <v>1808.960986</v>
       </c>
       <c r="M72" t="n">
-        <v>2920.277328</v>
+        <v>2755.030089</v>
       </c>
     </row>
     <row r="73">
@@ -3426,39 +3424,41 @@
           <t>化學品(如光阻劑、靶材等)</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
       <c r="C73" t="n">
-        <v>712.3335520000001</v>
+        <v>595.092408</v>
       </c>
       <c r="D73" t="n">
-        <v>815.324972</v>
+        <v>728.651519</v>
       </c>
       <c r="E73" t="n">
-        <v>1611.616654</v>
+        <v>1352.54277</v>
       </c>
       <c r="F73" t="n">
-        <v>1374.247749</v>
+        <v>1208.503487</v>
       </c>
       <c r="G73" t="n">
-        <v>1892.747094</v>
+        <v>1641.991383</v>
       </c>
       <c r="H73" t="n">
-        <v>1544.791363</v>
+        <v>1366.960003</v>
       </c>
       <c r="I73" t="n">
-        <v>1179.460507</v>
+        <v>980.127355</v>
       </c>
       <c r="J73" t="n">
-        <v>1399.817988</v>
+        <v>1284.944729</v>
       </c>
       <c r="K73" t="n">
-        <v>807.6651900000001</v>
+        <v>687.902632</v>
       </c>
       <c r="L73" t="n">
-        <v>1036.824979</v>
+        <v>892.257835</v>
       </c>
       <c r="M73" t="n">
-        <v>880.199448</v>
+        <v>714.952209</v>
       </c>
     </row>
     <row r="74">
@@ -3510,37 +3510,37 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>1.220551</v>
+        <v>0.024734</v>
       </c>
       <c r="D75" t="n">
-        <v>2.543266</v>
+        <v>0.024566</v>
       </c>
       <c r="E75" t="n">
-        <v>2.561671</v>
+        <v>0.038439</v>
       </c>
       <c r="F75" t="n">
-        <v>4.239002</v>
+        <v>0.02161</v>
       </c>
       <c r="G75" t="n">
-        <v>4.956047</v>
+        <v>0.035423</v>
       </c>
       <c r="H75" t="n">
-        <v>6.585983</v>
+        <v>0.02347</v>
       </c>
       <c r="I75" t="n">
-        <v>5.591823</v>
+        <v>0.016592</v>
       </c>
       <c r="J75" t="n">
-        <v>4.60075</v>
+        <v>0.010826</v>
       </c>
       <c r="K75" t="n">
-        <v>2.088338</v>
+        <v>0.026945</v>
       </c>
       <c r="L75" t="n">
-        <v>1.733048</v>
+        <v>0.017817</v>
       </c>
       <c r="M75" t="n">
-        <v>2.160761</v>
+        <v>0.029985</v>
       </c>
     </row>
     <row r="76">
@@ -3549,41 +3549,39 @@
           <t>印表機、傳真機、掃瞄器、多功能事務機、投影機</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>0</v>
-      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>33729.277752</v>
+        <v>33969.509216</v>
       </c>
       <c r="D76" t="n">
-        <v>18151.798967</v>
+        <v>18421.072729</v>
       </c>
       <c r="E76" t="n">
-        <v>16895.8242</v>
+        <v>17344.904619</v>
       </c>
       <c r="F76" t="n">
-        <v>16108.473661</v>
+        <v>16330.742366</v>
       </c>
       <c r="G76" t="n">
-        <v>14643.14673</v>
+        <v>14950.175494</v>
       </c>
       <c r="H76" t="n">
-        <v>13526.936903</v>
+        <v>13702.158053</v>
       </c>
       <c r="I76" t="n">
-        <v>12890.111388</v>
+        <v>13020.344881</v>
       </c>
       <c r="J76" t="n">
-        <v>13616.595018</v>
+        <v>13767.301876</v>
       </c>
       <c r="K76" t="n">
-        <v>7258.340388</v>
+        <v>8763.175069000001</v>
       </c>
       <c r="L76" t="n">
-        <v>9648.618979999999</v>
+        <v>10195.724281</v>
       </c>
       <c r="M76" t="n">
-        <v>9082.704092</v>
+        <v>9432.602047</v>
       </c>
     </row>
     <row r="77">
@@ -3633,39 +3631,41 @@
           <t>原材料</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
       <c r="C78" t="n">
-        <v>33105.831464</v>
+        <v>32988.59032</v>
       </c>
       <c r="D78" t="n">
-        <v>16849.580731</v>
+        <v>16762.907278</v>
       </c>
       <c r="E78" t="n">
-        <v>16028.275834</v>
+        <v>15769.20195</v>
       </c>
       <c r="F78" t="n">
-        <v>12086.514784</v>
+        <v>11920.770522</v>
       </c>
       <c r="G78" t="n">
-        <v>9601.015362</v>
+        <v>9350.259651</v>
       </c>
       <c r="H78" t="n">
-        <v>7017.52579</v>
+        <v>6839.69443</v>
       </c>
       <c r="I78" t="n">
-        <v>14852.147609</v>
+        <v>14652.814457</v>
       </c>
       <c r="J78" t="n">
-        <v>8444.869672000001</v>
+        <v>8329.996413000001</v>
       </c>
       <c r="K78" t="n">
-        <v>12164.998705</v>
+        <v>12045.236147</v>
       </c>
       <c r="L78" t="n">
-        <v>12443.993615</v>
+        <v>12299.426471</v>
       </c>
       <c r="M78" t="n">
-        <v>7170.731085</v>
+        <v>7005.483846</v>
       </c>
     </row>
     <row r="79">
@@ -3674,39 +3674,41 @@
           <t>原物料</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
       <c r="C79" t="n">
-        <v>1461.355878</v>
+        <v>1461.354593</v>
       </c>
       <c r="D79" t="n">
-        <v>841.223315</v>
+        <v>841.218611</v>
       </c>
       <c r="E79" t="n">
-        <v>1126.999598</v>
+        <v>1126.997198</v>
       </c>
       <c r="F79" t="n">
-        <v>1181.379466</v>
+        <v>1181.377007</v>
       </c>
       <c r="G79" t="n">
-        <v>751.173289</v>
+        <v>751.17048</v>
       </c>
       <c r="H79" t="n">
-        <v>839.4206103333333</v>
+        <v>839.4178763333334</v>
       </c>
       <c r="I79" t="n">
-        <v>862.777126</v>
+        <v>862.774726</v>
       </c>
       <c r="J79" t="n">
-        <v>736.29584</v>
+        <v>736.2940129999999</v>
       </c>
       <c r="K79" t="n">
-        <v>592.7563259999999</v>
+        <v>592.753188</v>
       </c>
       <c r="L79" t="n">
-        <v>587.229593</v>
+        <v>587.2268</v>
       </c>
       <c r="M79" t="n">
-        <v>672.166228</v>
+        <v>672.1637490000001</v>
       </c>
     </row>
     <row r="80">
@@ -3881,37 +3883,37 @@
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>86.69121199999999</v>
+        <v>319.341661</v>
       </c>
       <c r="D84" t="n">
-        <v>42.057296</v>
+        <v>81.619134</v>
       </c>
       <c r="E84" t="n">
-        <v>74.566855</v>
+        <v>110.376895</v>
       </c>
       <c r="F84" t="n">
-        <v>90.048176</v>
+        <v>110.001485</v>
       </c>
       <c r="G84" t="n">
-        <v>73.630757</v>
+        <v>92.787335</v>
       </c>
       <c r="H84" t="n">
-        <v>96.379971</v>
+        <v>114.167215</v>
       </c>
       <c r="I84" t="n">
-        <v>42.949975</v>
+        <v>57.025421</v>
       </c>
       <c r="J84" t="n">
-        <v>45.651944</v>
+        <v>59.512268</v>
       </c>
       <c r="K84" t="n">
-        <v>28.309056</v>
+        <v>45.30597</v>
       </c>
       <c r="L84" t="n">
-        <v>57.673353</v>
+        <v>73.542883</v>
       </c>
       <c r="M84" t="n">
-        <v>28.370516</v>
+        <v>40.87349</v>
       </c>
     </row>
     <row r="85">
@@ -3963,37 +3965,37 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>452.062504</v>
+        <v>452.068793</v>
       </c>
       <c r="D86" t="n">
-        <v>491.468112</v>
+        <v>491.47773</v>
       </c>
       <c r="E86" t="n">
-        <v>1035.999395</v>
+        <v>1036.007003</v>
       </c>
       <c r="F86" t="n">
-        <v>656.6997</v>
+        <v>656.706491</v>
       </c>
       <c r="G86" t="n">
-        <v>512.169752</v>
+        <v>512.184379</v>
       </c>
       <c r="H86" t="n">
-        <v>1482.569302</v>
+        <v>1482.579445</v>
       </c>
       <c r="I86" t="n">
-        <v>2042.754421</v>
+        <v>2042.774191</v>
       </c>
       <c r="J86" t="n">
-        <v>1425.415519</v>
+        <v>1425.427004</v>
       </c>
       <c r="K86" t="n">
-        <v>1250.009062</v>
+        <v>1250.011451</v>
       </c>
       <c r="L86" t="n">
-        <v>2061.761958</v>
+        <v>2061.773357</v>
       </c>
       <c r="M86" t="n">
-        <v>1731.278199</v>
+        <v>1731.284916</v>
       </c>
     </row>
     <row r="87">
@@ -4088,37 +4090,37 @@
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>2999.473238</v>
+        <v>3017.535355</v>
       </c>
       <c r="D89" t="n">
-        <v>2414.734118</v>
+        <v>2427.68657</v>
       </c>
       <c r="E89" t="n">
-        <v>1745.255268</v>
+        <v>1758.785457</v>
       </c>
       <c r="F89" t="n">
-        <v>2947.555818</v>
+        <v>2957.260577</v>
       </c>
       <c r="G89" t="n">
-        <v>2409.469936</v>
+        <v>2418.20587</v>
       </c>
       <c r="H89" t="n">
-        <v>2311.363429</v>
+        <v>2325.910411</v>
       </c>
       <c r="I89" t="n">
-        <v>5132.442673</v>
+        <v>5142.700723</v>
       </c>
       <c r="J89" t="n">
-        <v>4109.780172</v>
+        <v>4124.868012</v>
       </c>
       <c r="K89" t="n">
-        <v>3093.779807</v>
+        <v>3111.850378</v>
       </c>
       <c r="L89" t="n">
-        <v>2030.74325525</v>
+        <v>2043.72038425</v>
       </c>
       <c r="M89" t="n">
-        <v>1758.719191</v>
+        <v>1776.270124</v>
       </c>
     </row>
     <row r="90">
@@ -4129,37 +4131,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>236.429825</v>
+        <v>469.080274</v>
       </c>
       <c r="D90" t="n">
-        <v>149.355643</v>
+        <v>188.917481</v>
       </c>
       <c r="E90" t="n">
-        <v>126.140252</v>
+        <v>161.950292</v>
       </c>
       <c r="F90" t="n">
-        <v>70.13225</v>
+        <v>90.085559</v>
       </c>
       <c r="G90" t="n">
-        <v>111.993447</v>
+        <v>131.150025</v>
       </c>
       <c r="H90" t="n">
-        <v>142.703815</v>
+        <v>160.491059</v>
       </c>
       <c r="I90" t="n">
-        <v>112.885862</v>
+        <v>126.961308</v>
       </c>
       <c r="J90" t="n">
-        <v>64.197191</v>
+        <v>78.057515</v>
       </c>
       <c r="K90" t="n">
-        <v>85.867822</v>
+        <v>102.864736</v>
       </c>
       <c r="L90" t="n">
-        <v>42.363136</v>
+        <v>58.232666</v>
       </c>
       <c r="M90" t="n">
-        <v>51.809616</v>
+        <v>64.31259</v>
       </c>
     </row>
     <row r="91">
@@ -4209,41 +4211,39 @@
           <t>大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>126268.996387</v>
+        <v>126271.351126</v>
       </c>
       <c r="D92" t="n">
-        <v>61628.747527</v>
+        <v>61629.944338</v>
       </c>
       <c r="E92" t="n">
-        <v>51355.931805</v>
+        <v>51357.721036</v>
       </c>
       <c r="F92" t="n">
-        <v>44598.868252</v>
+        <v>44597.314223</v>
       </c>
       <c r="G92" t="n">
-        <v>42090.806633</v>
+        <v>42088.904846</v>
       </c>
       <c r="H92" t="n">
-        <v>46933.378998</v>
+        <v>46931.729774</v>
       </c>
       <c r="I92" t="n">
-        <v>57769.610934</v>
+        <v>57766.569551</v>
       </c>
       <c r="J92" t="n">
-        <v>41027.454077</v>
+        <v>41026.903532</v>
       </c>
       <c r="K92" t="n">
-        <v>30978.599494</v>
+        <v>30981.80218</v>
       </c>
       <c r="L92" t="n">
-        <v>30158.820424</v>
+        <v>30159.86668</v>
       </c>
       <c r="M92" t="n">
-        <v>27362.790467</v>
+        <v>27364.411751</v>
       </c>
     </row>
     <row r="93">
@@ -4336,37 +4336,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>31884.939865</v>
+        <v>32117.590314</v>
       </c>
       <c r="D95" t="n">
-        <v>14232.910833</v>
+        <v>14272.472671</v>
       </c>
       <c r="E95" t="n">
-        <v>16827.807589</v>
+        <v>16863.617629</v>
       </c>
       <c r="F95" t="n">
-        <v>14866.070918</v>
+        <v>14886.024227</v>
       </c>
       <c r="G95" t="n">
-        <v>13233.96965</v>
+        <v>13253.126228</v>
       </c>
       <c r="H95" t="n">
-        <v>22756.174066</v>
+        <v>22773.96131</v>
       </c>
       <c r="I95" t="n">
-        <v>28107.077503</v>
+        <v>28121.152949</v>
       </c>
       <c r="J95" t="n">
-        <v>19722.743973</v>
+        <v>19736.604297</v>
       </c>
       <c r="K95" t="n">
-        <v>13806.591619</v>
+        <v>13823.588533</v>
       </c>
       <c r="L95" t="n">
-        <v>15941.875652</v>
+        <v>15957.745182</v>
       </c>
       <c r="M95" t="n">
-        <v>12526.327737</v>
+        <v>12538.830711</v>
       </c>
     </row>
     <row r="96">
@@ -4375,39 +4375,41 @@
           <t>太陽能電廠</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
       <c r="C96" t="n">
-        <v>20213.831717</v>
+        <v>20209.525465</v>
       </c>
       <c r="D96" t="n">
-        <v>11640.49426</v>
+        <v>11635.41045</v>
       </c>
       <c r="E96" t="n">
-        <v>12979.883616</v>
+        <v>12973.50903</v>
       </c>
       <c r="F96" t="n">
-        <v>10844.499073</v>
+        <v>10841.11147</v>
       </c>
       <c r="G96" t="n">
-        <v>9368.299534</v>
+        <v>9364.264485</v>
       </c>
       <c r="H96" t="n">
-        <v>18541.370987</v>
+        <v>18537.632508</v>
       </c>
       <c r="I96" t="n">
-        <v>21275.318708</v>
+        <v>21272.540659</v>
       </c>
       <c r="J96" t="n">
-        <v>14467.828523</v>
+        <v>14430.655588</v>
       </c>
       <c r="K96" t="n">
-        <v>9066.157479</v>
+        <v>9044.61232</v>
       </c>
       <c r="L96" t="n">
-        <v>11318.684411</v>
+        <v>11311.155554</v>
       </c>
       <c r="M96" t="n">
-        <v>7815.227947</v>
+        <v>7807.896132</v>
       </c>
     </row>
     <row r="97">
@@ -4703,41 +4705,39 @@
           <t>封裝/模組</t>
         </is>
       </c>
-      <c r="B104" t="n">
-        <v>0</v>
-      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
-        <v>6869.422768</v>
+        <v>7010.362369</v>
       </c>
       <c r="D104" t="n">
-        <v>4679.629077</v>
+        <v>4834.55702</v>
       </c>
       <c r="E104" t="n">
-        <v>4309.92153</v>
+        <v>4453.751327</v>
       </c>
       <c r="F104" t="n">
-        <v>2801.195087</v>
+        <v>2957.876997</v>
       </c>
       <c r="G104" t="n">
-        <v>2934.457701</v>
+        <v>3061.044999</v>
       </c>
       <c r="H104" t="n">
-        <v>3015.125519</v>
+        <v>3144.418082</v>
       </c>
       <c r="I104" t="n">
-        <v>2795.74024</v>
+        <v>2955.585132</v>
       </c>
       <c r="J104" t="n">
-        <v>2250.726366</v>
+        <v>2415.930944</v>
       </c>
       <c r="K104" t="n">
-        <v>2901.335255</v>
+        <v>3028.837969</v>
       </c>
       <c r="L104" t="n">
-        <v>2377.587965</v>
+        <v>2460.348425</v>
       </c>
       <c r="M104" t="n">
-        <v>2372.280857</v>
+        <v>2481.481146</v>
       </c>
     </row>
     <row r="105">
@@ -5361,41 +5361,39 @@
           <t>建材原料</t>
         </is>
       </c>
-      <c r="B120" t="n">
-        <v>0</v>
-      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
-        <v>4465.298267</v>
+        <v>4465.298519</v>
       </c>
       <c r="D120" t="n">
-        <v>3566.170346</v>
+        <v>3566.170814</v>
       </c>
       <c r="E120" t="n">
-        <v>2362.15479</v>
+        <v>2362.155367</v>
       </c>
       <c r="F120" t="n">
-        <v>3287.701016</v>
+        <v>3287.701603</v>
       </c>
       <c r="G120" t="n">
-        <v>9074.180855000001</v>
+        <v>9074.18275</v>
       </c>
       <c r="H120" t="n">
-        <v>7740.144227</v>
+        <v>7740.145183</v>
       </c>
       <c r="I120" t="n">
-        <v>10143.494631</v>
+        <v>10143.495737</v>
       </c>
       <c r="J120" t="n">
-        <v>7926.560348</v>
+        <v>7926.560796</v>
       </c>
       <c r="K120" t="n">
-        <v>3524.072694</v>
+        <v>3524.073986</v>
       </c>
       <c r="L120" t="n">
-        <v>3817.45557525</v>
+        <v>3817.45602125</v>
       </c>
       <c r="M120" t="n">
-        <v>9954.92347</v>
+        <v>9954.930122</v>
       </c>
     </row>
     <row r="121">
@@ -5404,41 +5402,39 @@
           <t>建設業</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>0</v>
-      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>4654.358686</v>
+        <v>4654.360417</v>
       </c>
       <c r="D121" t="n">
-        <v>2979.2777125</v>
+        <v>2979.2796395</v>
       </c>
       <c r="E121" t="n">
-        <v>3064.112165</v>
+        <v>3064.114006</v>
       </c>
       <c r="F121" t="n">
-        <v>3391.56724</v>
+        <v>3391.56962</v>
       </c>
       <c r="G121" t="n">
-        <v>2743.49517825</v>
+        <v>2743.49671325</v>
       </c>
       <c r="H121" t="n">
-        <v>2981.465862</v>
+        <v>2981.468547</v>
       </c>
       <c r="I121" t="n">
-        <v>3178.227906166666</v>
+        <v>3178.231927166667</v>
       </c>
       <c r="J121" t="n">
-        <v>2746.688565666666</v>
+        <v>2746.689592666667</v>
       </c>
       <c r="K121" t="n">
-        <v>3232.696078</v>
+        <v>3232.705532</v>
       </c>
       <c r="L121" t="n">
-        <v>2380.209945</v>
+        <v>2380.212061</v>
       </c>
       <c r="M121" t="n">
-        <v>3331.490538</v>
+        <v>3331.495649</v>
       </c>
     </row>
     <row r="122">
@@ -5820,37 +5816,37 @@
         <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>2091.262598</v>
+        <v>2087.974493</v>
       </c>
       <c r="D131" t="n">
-        <v>927.462305</v>
+        <v>924.137028</v>
       </c>
       <c r="E131" t="n">
-        <v>1426.133516</v>
+        <v>1427.260688</v>
       </c>
       <c r="F131" t="n">
-        <v>977.112788</v>
+        <v>973.174661</v>
       </c>
       <c r="G131" t="n">
-        <v>733.324348</v>
+        <v>732.917866</v>
       </c>
       <c r="H131" t="n">
-        <v>772.817775</v>
+        <v>769.961697</v>
       </c>
       <c r="I131" t="n">
-        <v>1118.674713</v>
+        <v>1117.310452</v>
       </c>
       <c r="J131" t="n">
-        <v>1091.233251</v>
+        <v>1089.054075</v>
       </c>
       <c r="K131" t="n">
-        <v>672.653494</v>
+        <v>671.466171</v>
       </c>
       <c r="L131" t="n">
-        <v>1177.595191</v>
+        <v>1175.1047</v>
       </c>
       <c r="M131" t="n">
-        <v>693.076069</v>
+        <v>690.165743</v>
       </c>
     </row>
     <row r="132">
@@ -5859,41 +5855,39 @@
           <t>手工具機</t>
         </is>
       </c>
-      <c r="B132" t="n">
-        <v>0</v>
-      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
-        <v>136.8073</v>
+        <v>139.906364</v>
       </c>
       <c r="D132" t="n">
-        <v>144.293516</v>
+        <v>147.454326</v>
       </c>
       <c r="E132" t="n">
-        <v>155.490425</v>
+        <v>158.007391</v>
       </c>
       <c r="F132" t="n">
-        <v>100.48992</v>
+        <v>103.006512</v>
       </c>
       <c r="G132" t="n">
-        <v>87.74408</v>
+        <v>89.156132</v>
       </c>
       <c r="H132" t="n">
-        <v>80.389109</v>
+        <v>82.23929699999999</v>
       </c>
       <c r="I132" t="n">
-        <v>108.801931</v>
+        <v>163.337163</v>
       </c>
       <c r="J132" t="n">
-        <v>110.033597</v>
+        <v>127.521665</v>
       </c>
       <c r="K132" t="n">
-        <v>153.184639</v>
+        <v>160.157363</v>
       </c>
       <c r="L132" t="n">
-        <v>430.696981</v>
+        <v>435.860725</v>
       </c>
       <c r="M132" t="n">
-        <v>426.605105</v>
+        <v>430.298951</v>
       </c>
     </row>
     <row r="133">
@@ -5943,39 +5937,41 @@
           <t>接著劑(合成樹脂)</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="n">
+        <v>0</v>
+      </c>
       <c r="C134" t="n">
-        <v>490.8274145</v>
+        <v>373.5862705</v>
       </c>
       <c r="D134" t="n">
-        <v>424.12997</v>
+        <v>337.456517</v>
       </c>
       <c r="E134" t="n">
-        <v>619.641123</v>
+        <v>360.567239</v>
       </c>
       <c r="F134" t="n">
-        <v>515.035659</v>
+        <v>349.291397</v>
       </c>
       <c r="G134" t="n">
-        <v>752.2060320000001</v>
+        <v>501.450321</v>
       </c>
       <c r="H134" t="n">
-        <v>571.337853</v>
+        <v>393.506493</v>
       </c>
       <c r="I134" t="n">
-        <v>746.207036</v>
+        <v>546.873884</v>
       </c>
       <c r="J134" t="n">
-        <v>849.23024</v>
+        <v>734.356981</v>
       </c>
       <c r="K134" t="n">
-        <v>427.744281</v>
+        <v>307.981723</v>
       </c>
       <c r="L134" t="n">
-        <v>403.689147</v>
+        <v>259.122003</v>
       </c>
       <c r="M134" t="n">
-        <v>619.5821570000001</v>
+        <v>454.334918</v>
       </c>
     </row>
     <row r="135">
@@ -6845,39 +6841,41 @@
           <t>材料</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
+      <c r="B156" t="n">
+        <v>0</v>
+      </c>
       <c r="C156" t="n">
-        <v>29328.164656</v>
+        <v>29210.923512</v>
       </c>
       <c r="D156" t="n">
-        <v>14738.318487</v>
+        <v>14651.645034</v>
       </c>
       <c r="E156" t="n">
-        <v>9364.638279000001</v>
+        <v>9105.564394999999</v>
       </c>
       <c r="F156" t="n">
-        <v>8182.536906</v>
+        <v>8016.792644</v>
       </c>
       <c r="G156" t="n">
-        <v>7085.279556</v>
+        <v>6834.523845</v>
       </c>
       <c r="H156" t="n">
-        <v>5348.549016</v>
+        <v>5170.717656</v>
       </c>
       <c r="I156" t="n">
-        <v>12266.405506</v>
+        <v>12067.072354</v>
       </c>
       <c r="J156" t="n">
-        <v>6436.977846</v>
+        <v>6322.104587</v>
       </c>
       <c r="K156" t="n">
-        <v>6536.538242</v>
+        <v>6416.775684</v>
       </c>
       <c r="L156" t="n">
-        <v>3368.058668</v>
+        <v>3223.491524</v>
       </c>
       <c r="M156" t="n">
-        <v>4026.640006</v>
+        <v>3861.392767</v>
       </c>
     </row>
     <row r="157">
@@ -6886,41 +6884,39 @@
           <t>染整</t>
         </is>
       </c>
-      <c r="B157" t="n">
-        <v>0</v>
-      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
-        <v>6605.306728</v>
+        <v>6605.715078</v>
       </c>
       <c r="D157" t="n">
-        <v>7781.121709</v>
+        <v>7781.564059</v>
       </c>
       <c r="E157" t="n">
-        <v>4249.74035</v>
+        <v>4254.242316</v>
       </c>
       <c r="F157" t="n">
-        <v>9401.006708000001</v>
+        <v>9401.443308</v>
       </c>
       <c r="G157" t="n">
-        <v>15812.418997</v>
+        <v>15813.092863</v>
       </c>
       <c r="H157" t="n">
-        <v>15307.436776</v>
+        <v>15307.880326</v>
       </c>
       <c r="I157" t="n">
-        <v>17044.491714</v>
+        <v>17044.923866</v>
       </c>
       <c r="J157" t="n">
-        <v>19037.683565</v>
+        <v>19038.141715</v>
       </c>
       <c r="K157" t="n">
-        <v>15855.82752525</v>
+        <v>15856.20592225</v>
       </c>
       <c r="L157" t="n">
-        <v>6540.087872333333</v>
+        <v>6540.547572333333</v>
       </c>
       <c r="M157" t="n">
-        <v>7353.736958</v>
+        <v>7354.152068</v>
       </c>
     </row>
     <row r="158">
@@ -6970,41 +6966,39 @@
           <t>棒鋼盤元(捲狀條鋼)</t>
         </is>
       </c>
-      <c r="B159" t="n">
-        <v>0</v>
-      </c>
+      <c r="B159" t="inlineStr"/>
       <c r="C159" t="n">
-        <v>1106.881421</v>
+        <v>1107.714975</v>
       </c>
       <c r="D159" t="n">
-        <v>453.6014576666667</v>
+        <v>454.1331976666667</v>
       </c>
       <c r="E159" t="n">
-        <v>592.4836986666667</v>
+        <v>595.6679786666666</v>
       </c>
       <c r="F159" t="n">
-        <v>348.302903</v>
+        <v>349.204805</v>
       </c>
       <c r="G159" t="n">
-        <v>413.335561</v>
+        <v>414.344069</v>
       </c>
       <c r="H159" t="n">
-        <v>690.467809</v>
+        <v>692.019138</v>
       </c>
       <c r="I159" t="n">
-        <v>553.71615975</v>
+        <v>555.18324075</v>
       </c>
       <c r="J159" t="n">
-        <v>825.1641969999999</v>
+        <v>826.339504</v>
       </c>
       <c r="K159" t="n">
-        <v>454.354632</v>
+        <v>454.883113</v>
       </c>
       <c r="L159" t="n">
-        <v>340.837151</v>
+        <v>341.495452</v>
       </c>
       <c r="M159" t="n">
-        <v>413.572523</v>
+        <v>414.056169</v>
       </c>
     </row>
     <row r="160">
@@ -7382,39 +7376,41 @@
           <t>水泥成品</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr"/>
+      <c r="B169" t="n">
+        <v>0</v>
+      </c>
       <c r="C169" t="n">
-        <v>1001.570309</v>
+        <v>966.426331</v>
       </c>
       <c r="D169" t="n">
-        <v>538.898002</v>
+        <v>503.217922</v>
       </c>
       <c r="E169" t="n">
-        <v>741.220129</v>
+        <v>685.3915490000001</v>
       </c>
       <c r="F169" t="n">
-        <v>558.4603530000001</v>
+        <v>545.091435</v>
       </c>
       <c r="G169" t="n">
-        <v>1227.680434</v>
+        <v>1213.270385</v>
       </c>
       <c r="H169" t="n">
-        <v>873.866664</v>
+        <v>856.157641</v>
       </c>
       <c r="I169" t="n">
-        <v>544.340496</v>
+        <v>524.819676</v>
       </c>
       <c r="J169" t="n">
-        <v>456.325253</v>
+        <v>445.478397</v>
       </c>
       <c r="K169" t="n">
-        <v>569.246266</v>
+        <v>547.550838</v>
       </c>
       <c r="L169" t="n">
-        <v>553.519626</v>
+        <v>536.057065</v>
       </c>
       <c r="M169" t="n">
-        <v>393.405883</v>
+        <v>360.243962</v>
       </c>
     </row>
     <row r="170">
@@ -7669,39 +7665,41 @@
           <t>清潔用品</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr"/>
+      <c r="B176" t="n">
+        <v>0</v>
+      </c>
       <c r="C176" t="n">
-        <v>25.468044</v>
+        <v>21.757003</v>
       </c>
       <c r="D176" t="n">
-        <v>10.586576</v>
+        <v>6.811141</v>
       </c>
       <c r="E176" t="n">
-        <v>17.416085</v>
+        <v>14.032236</v>
       </c>
       <c r="F176" t="n">
-        <v>15.86653</v>
+        <v>11.484362</v>
       </c>
       <c r="G176" t="n">
-        <v>8.417373</v>
+        <v>7.33123</v>
       </c>
       <c r="H176" t="n">
-        <v>22.61408</v>
+        <v>19.307259</v>
       </c>
       <c r="I176" t="n">
-        <v>10.565709</v>
+        <v>8.759589999999999</v>
       </c>
       <c r="J176" t="n">
-        <v>8.705496999999999</v>
+        <v>6.063517</v>
       </c>
       <c r="K176" t="n">
-        <v>8.471752</v>
+        <v>6.901743</v>
       </c>
       <c r="L176" t="n">
-        <v>11.783777</v>
+        <v>8.827057</v>
       </c>
       <c r="M176" t="n">
-        <v>19.291392</v>
+        <v>15.961855</v>
       </c>
     </row>
     <row r="177">
@@ -7809,19 +7807,19 @@
         <v>30001.282984</v>
       </c>
       <c r="H179" t="n">
-        <v>39062.350486</v>
+        <v>39062.351365</v>
       </c>
       <c r="I179" t="n">
-        <v>39405.758536</v>
+        <v>39405.758855</v>
       </c>
       <c r="J179" t="n">
-        <v>34320.581614</v>
+        <v>34320.582438</v>
       </c>
       <c r="K179" t="n">
-        <v>21547.698909</v>
+        <v>21547.699943</v>
       </c>
       <c r="L179" t="n">
-        <v>26146.290079</v>
+        <v>26146.290328</v>
       </c>
       <c r="M179" t="n">
         <v>22282.328627</v>
@@ -7876,37 +7874,37 @@
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
-        <v>24522.579767</v>
+        <v>24661.068063</v>
       </c>
       <c r="D181" t="n">
-        <v>14738.10045</v>
+        <v>14890.577917</v>
       </c>
       <c r="E181" t="n">
-        <v>15699.731792</v>
+        <v>15837.073943</v>
       </c>
       <c r="F181" t="n">
-        <v>11429.713974</v>
+        <v>11582.866191</v>
       </c>
       <c r="G181" t="n">
-        <v>10497.454818</v>
+        <v>10620.4593</v>
       </c>
       <c r="H181" t="n">
-        <v>20183.297967</v>
+        <v>20309.865937</v>
       </c>
       <c r="I181" t="n">
-        <v>23115.814278</v>
+        <v>23273.490706</v>
       </c>
       <c r="J181" t="n">
-        <v>15136.03327</v>
+        <v>15297.884963</v>
       </c>
       <c r="K181" t="n">
-        <v>9576.723055</v>
+        <v>9692.794945</v>
       </c>
       <c r="L181" t="n">
-        <v>12229.320742</v>
+        <v>12308.990479</v>
       </c>
       <c r="M181" t="n">
-        <v>7989.73667</v>
+        <v>8094.82044</v>
       </c>
     </row>
     <row r="182">
@@ -8489,39 +8487,41 @@
           <t>生產製程、檢測設備及原物料</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
+      <c r="B196" t="n">
+        <v>0</v>
+      </c>
       <c r="C196" t="n">
-        <v>32966.892586</v>
+        <v>32966.884213</v>
       </c>
       <c r="D196" t="n">
-        <v>7239.420683</v>
+        <v>7239.391414</v>
       </c>
       <c r="E196" t="n">
-        <v>5252.198391</v>
+        <v>5252.178725</v>
       </c>
       <c r="F196" t="n">
-        <v>3030.294721</v>
+        <v>3030.271186</v>
       </c>
       <c r="G196" t="n">
-        <v>5892.253499</v>
+        <v>5892.231674</v>
       </c>
       <c r="H196" t="n">
-        <v>5100.659319</v>
+        <v>5100.643297</v>
       </c>
       <c r="I196" t="n">
-        <v>5985.733166</v>
+        <v>5985.719583</v>
       </c>
       <c r="J196" t="n">
-        <v>5485.271429</v>
+        <v>5485.232898</v>
       </c>
       <c r="K196" t="n">
-        <v>5815.165614</v>
+        <v>5815.145668</v>
       </c>
       <c r="L196" t="n">
-        <v>3436.582992</v>
+        <v>3436.550944</v>
       </c>
       <c r="M196" t="n">
-        <v>4230.005289</v>
+        <v>4229.975428</v>
       </c>
     </row>
     <row r="197">
@@ -8530,39 +8530,41 @@
           <t>生產製程及檢測設備</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="n">
+        <v>0</v>
+      </c>
       <c r="C197" t="n">
-        <v>88295.471686</v>
+        <v>88295.45494</v>
       </c>
       <c r="D197" t="n">
-        <v>30913.2159</v>
+        <v>30913.157362</v>
       </c>
       <c r="E197" t="n">
-        <v>28989.887657</v>
+        <v>28989.848325</v>
       </c>
       <c r="F197" t="n">
-        <v>20387.215555</v>
+        <v>20387.168485</v>
       </c>
       <c r="G197" t="n">
-        <v>29835.853161</v>
+        <v>29835.809511</v>
       </c>
       <c r="H197" t="n">
-        <v>36830.445081</v>
+        <v>36830.413037</v>
       </c>
       <c r="I197" t="n">
-        <v>45448.18639</v>
+        <v>45448.159224</v>
       </c>
       <c r="J197" t="n">
-        <v>34018.589151</v>
+        <v>34018.512089</v>
       </c>
       <c r="K197" t="n">
-        <v>27551.3808285</v>
+        <v>27551.3409365</v>
       </c>
       <c r="L197" t="n">
-        <v>23276.99305633333</v>
+        <v>23276.92896033333</v>
       </c>
       <c r="M197" t="n">
-        <v>27785.750775</v>
+        <v>27785.691053</v>
       </c>
     </row>
     <row r="198">
@@ -8817,39 +8819,41 @@
           <t>石化中間原料(例如乙烯、丙烯、丁二烯、苯、酚等)</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr"/>
+      <c r="B204" t="n">
+        <v>0</v>
+      </c>
       <c r="C204" t="n">
-        <v>2694.794283</v>
+        <v>2577.553139</v>
       </c>
       <c r="D204" t="n">
-        <v>2149.959291</v>
+        <v>2063.285838</v>
       </c>
       <c r="E204" t="n">
-        <v>2923.93787</v>
+        <v>2664.863986</v>
       </c>
       <c r="F204" t="n">
-        <v>2318.566767</v>
+        <v>2152.822505</v>
       </c>
       <c r="G204" t="n">
-        <v>2311.469189</v>
+        <v>2060.713478</v>
       </c>
       <c r="H204" t="n">
-        <v>2108.901898</v>
+        <v>1931.070538</v>
       </c>
       <c r="I204" t="n">
-        <v>3496.75812</v>
+        <v>3297.424968</v>
       </c>
       <c r="J204" t="n">
-        <v>3300.193622</v>
+        <v>3185.320363</v>
       </c>
       <c r="K204" t="n">
-        <v>1957.364347</v>
+        <v>1837.601789</v>
       </c>
       <c r="L204" t="n">
-        <v>1659.088323</v>
+        <v>1514.521179</v>
       </c>
       <c r="M204" t="n">
-        <v>1656.166702</v>
+        <v>1490.919463</v>
       </c>
     </row>
     <row r="205">
@@ -8942,37 +8946,37 @@
       </c>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="n">
-        <v>7180.66134</v>
+        <v>7171.453191</v>
       </c>
       <c r="D207" t="n">
-        <v>1218.117457</v>
+        <v>1215.712683</v>
       </c>
       <c r="E207" t="n">
-        <v>1166.040256</v>
+        <v>1162.256175</v>
       </c>
       <c r="F207" t="n">
-        <v>1150.295152</v>
+        <v>1147.052025</v>
       </c>
       <c r="G207" t="n">
-        <v>1468.208137</v>
+        <v>1464.351565</v>
       </c>
       <c r="H207" t="n">
-        <v>1159.815056</v>
+        <v>1157.272046</v>
       </c>
       <c r="I207" t="n">
-        <v>1171.559992</v>
+        <v>1168.334091</v>
       </c>
       <c r="J207" t="n">
-        <v>1286.641841</v>
+        <v>1282.921069</v>
       </c>
       <c r="K207" t="n">
-        <v>991.5034900000001</v>
+        <v>981.326399</v>
       </c>
       <c r="L207" t="n">
-        <v>948.725539</v>
+        <v>945.763679</v>
       </c>
       <c r="M207" t="n">
-        <v>895.167299</v>
+        <v>892.6709090000001</v>
       </c>
     </row>
     <row r="208">
@@ -8983,37 +8987,37 @@
       </c>
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="n">
-        <v>41924.118783</v>
+        <v>41922.922966</v>
       </c>
       <c r="D208" t="n">
-        <v>39462.752788</v>
+        <v>39460.234088</v>
       </c>
       <c r="E208" t="n">
-        <v>53223.733344</v>
+        <v>53221.210112</v>
       </c>
       <c r="F208" t="n">
-        <v>49202.438798</v>
+        <v>49198.221406</v>
       </c>
       <c r="G208" t="n">
-        <v>30931.857392</v>
+        <v>30926.936768</v>
       </c>
       <c r="H208" t="n">
-        <v>43185.27803</v>
+        <v>43178.715517</v>
       </c>
       <c r="I208" t="n">
-        <v>38261.649362</v>
+        <v>38256.074131</v>
       </c>
       <c r="J208" t="n">
-        <v>32749.062261</v>
+        <v>32744.472337</v>
       </c>
       <c r="K208" t="n">
-        <v>21718.214387</v>
+        <v>21716.152994</v>
       </c>
       <c r="L208" t="n">
-        <v>34170.779957</v>
+        <v>34169.064726</v>
       </c>
       <c r="M208" t="n">
-        <v>28239.616255</v>
+        <v>28237.485479</v>
       </c>
     </row>
     <row r="209">
@@ -9680,37 +9684,37 @@
       </c>
       <c r="B225" t="inlineStr"/>
       <c r="C225" t="n">
-        <v>332.093667</v>
+        <v>564.744116</v>
       </c>
       <c r="D225" t="n">
-        <v>156.257204</v>
+        <v>195.819042</v>
       </c>
       <c r="E225" t="n">
-        <v>233.54675</v>
+        <v>269.35679</v>
       </c>
       <c r="F225" t="n">
-        <v>250.33613</v>
+        <v>270.289439</v>
       </c>
       <c r="G225" t="n">
-        <v>183.070496</v>
+        <v>202.227074</v>
       </c>
       <c r="H225" t="n">
-        <v>210.524697</v>
+        <v>228.311941</v>
       </c>
       <c r="I225" t="n">
-        <v>134.714386</v>
+        <v>148.789832</v>
       </c>
       <c r="J225" t="n">
-        <v>142.570236</v>
+        <v>156.43056</v>
       </c>
       <c r="K225" t="n">
-        <v>106.278401</v>
+        <v>123.275315</v>
       </c>
       <c r="L225" t="n">
-        <v>180.196553</v>
+        <v>196.066083</v>
       </c>
       <c r="M225" t="n">
-        <v>175.283928</v>
+        <v>187.786902</v>
       </c>
     </row>
     <row r="226">
@@ -9885,37 +9889,37 @@
       </c>
       <c r="B230" t="inlineStr"/>
       <c r="C230" t="n">
-        <v>58120.316703</v>
+        <v>58120.316499</v>
       </c>
       <c r="D230" t="n">
-        <v>39946.528115</v>
+        <v>39946.527737</v>
       </c>
       <c r="E230" t="n">
-        <v>39044.966942</v>
+        <v>39044.966527</v>
       </c>
       <c r="F230" t="n">
-        <v>38003.568794</v>
+        <v>38003.568389</v>
       </c>
       <c r="G230" t="n">
-        <v>33077.919842</v>
+        <v>33077.919352</v>
       </c>
       <c r="H230" t="n">
-        <v>44737.556387</v>
+        <v>44737.555691</v>
       </c>
       <c r="I230" t="n">
-        <v>45223.903192</v>
+        <v>45223.90232</v>
       </c>
       <c r="J230" t="n">
-        <v>39043.40597</v>
+        <v>39043.405474</v>
       </c>
       <c r="K230" t="n">
-        <v>23589.446744</v>
+        <v>23589.446407</v>
       </c>
       <c r="L230" t="n">
-        <v>27760.651304</v>
+        <v>27760.650944</v>
       </c>
       <c r="M230" t="n">
-        <v>23648.529792</v>
+        <v>23648.529596</v>
       </c>
     </row>
     <row r="231">
@@ -10047,41 +10051,39 @@
           <t>線材盤元</t>
         </is>
       </c>
-      <c r="B234" t="n">
-        <v>0</v>
-      </c>
+      <c r="B234" t="inlineStr"/>
       <c r="C234" t="n">
-        <v>1070.112055</v>
+        <v>1070.945609</v>
       </c>
       <c r="D234" t="n">
-        <v>427.4496756666667</v>
+        <v>427.9814156666667</v>
       </c>
       <c r="E234" t="n">
-        <v>572.8522246666666</v>
+        <v>576.0365046666666</v>
       </c>
       <c r="F234" t="n">
-        <v>329.217075</v>
+        <v>330.118977</v>
       </c>
       <c r="G234" t="n">
-        <v>384.268971</v>
+        <v>385.277479</v>
       </c>
       <c r="H234" t="n">
-        <v>658.765573</v>
+        <v>660.316902</v>
       </c>
       <c r="I234" t="n">
-        <v>525.36839975</v>
+        <v>526.83548075</v>
       </c>
       <c r="J234" t="n">
-        <v>808.709792</v>
+        <v>809.885099</v>
       </c>
       <c r="K234" t="n">
-        <v>425.428918</v>
+        <v>425.957399</v>
       </c>
       <c r="L234" t="n">
-        <v>321.432564</v>
+        <v>322.090865</v>
       </c>
       <c r="M234" t="n">
-        <v>386.846308</v>
+        <v>387.329954</v>
       </c>
     </row>
     <row r="235">
@@ -10090,41 +10092,39 @@
           <t>織布</t>
         </is>
       </c>
-      <c r="B235" t="n">
-        <v>0</v>
-      </c>
+      <c r="B235" t="inlineStr"/>
       <c r="C235" t="n">
-        <v>1434.368029</v>
+        <v>1434.776379</v>
       </c>
       <c r="D235" t="n">
-        <v>1171.736506</v>
+        <v>1172.178856</v>
       </c>
       <c r="E235" t="n">
-        <v>807.41211</v>
+        <v>811.914076</v>
       </c>
       <c r="F235" t="n">
-        <v>1160.360339</v>
+        <v>1160.796939</v>
       </c>
       <c r="G235" t="n">
-        <v>956.649758</v>
+        <v>957.323624</v>
       </c>
       <c r="H235" t="n">
-        <v>848.200956</v>
+        <v>848.644506</v>
       </c>
       <c r="I235" t="n">
-        <v>1953.602168</v>
+        <v>1954.03432</v>
       </c>
       <c r="J235" t="n">
-        <v>1524.599213</v>
+        <v>1525.057363</v>
       </c>
       <c r="K235" t="n">
-        <v>1016.873223</v>
+        <v>1017.25162</v>
       </c>
       <c r="L235" t="n">
-        <v>1082.734642</v>
+        <v>1083.194342</v>
       </c>
       <c r="M235" t="n">
-        <v>596.0541030000001</v>
+        <v>596.469213</v>
       </c>
     </row>
     <row r="236">
@@ -10215,41 +10215,39 @@
           <t>背光源(發光二極體、冷陰極管)</t>
         </is>
       </c>
-      <c r="B238" t="n">
-        <v>0</v>
-      </c>
+      <c r="B238" t="inlineStr"/>
       <c r="C238" t="n">
-        <v>2476.791345</v>
+        <v>2617.730946</v>
       </c>
       <c r="D238" t="n">
-        <v>1882.700922</v>
+        <v>2037.628865</v>
       </c>
       <c r="E238" t="n">
-        <v>2101.552566</v>
+        <v>2245.382363</v>
       </c>
       <c r="F238" t="n">
-        <v>1634.402763</v>
+        <v>1791.084673</v>
       </c>
       <c r="G238" t="n">
-        <v>3929.87352</v>
+        <v>4056.460818</v>
       </c>
       <c r="H238" t="n">
-        <v>2903.837706</v>
+        <v>3033.130269</v>
       </c>
       <c r="I238" t="n">
-        <v>1417.843847</v>
+        <v>1577.688739</v>
       </c>
       <c r="J238" t="n">
-        <v>1204.838844</v>
+        <v>1370.043422</v>
       </c>
       <c r="K238" t="n">
-        <v>826.7367829999999</v>
+        <v>954.239497</v>
       </c>
       <c r="L238" t="n">
-        <v>919.779208</v>
+        <v>1002.539668</v>
       </c>
       <c r="M238" t="n">
-        <v>2933.057535</v>
+        <v>3042.257824</v>
       </c>
     </row>
     <row r="239">
@@ -10299,39 +10297,41 @@
           <t>膠材</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr"/>
+      <c r="B240" t="n">
+        <v>0</v>
+      </c>
       <c r="C240" t="n">
-        <v>466.63542</v>
+        <v>349.394276</v>
       </c>
       <c r="D240" t="n">
-        <v>383.633154</v>
+        <v>296.959701</v>
       </c>
       <c r="E240" t="n">
-        <v>567.446557</v>
+        <v>308.372673</v>
       </c>
       <c r="F240" t="n">
-        <v>589.99838175</v>
+        <v>424.25411975</v>
       </c>
       <c r="G240" t="n">
-        <v>699.771581</v>
+        <v>449.01587</v>
       </c>
       <c r="H240" t="n">
-        <v>625.162826</v>
+        <v>447.331466</v>
       </c>
       <c r="I240" t="n">
-        <v>808.660609</v>
+        <v>609.327457</v>
       </c>
       <c r="J240" t="n">
-        <v>1011.758176</v>
+        <v>896.884917</v>
       </c>
       <c r="K240" t="n">
-        <v>447.616881</v>
+        <v>327.854323</v>
       </c>
       <c r="L240" t="n">
-        <v>623.67733</v>
+        <v>479.110186</v>
       </c>
       <c r="M240" t="n">
-        <v>540.487141</v>
+        <v>375.239902</v>
       </c>
     </row>
     <row r="241">
@@ -10916,37 +10916,37 @@
       </c>
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="n">
-        <v>62.333918</v>
+        <v>294.984367</v>
       </c>
       <c r="D255" t="n">
-        <v>48.169238</v>
+        <v>87.731076</v>
       </c>
       <c r="E255" t="n">
-        <v>175.779184</v>
+        <v>211.589224</v>
       </c>
       <c r="F255" t="n">
-        <v>66.34115</v>
+        <v>86.294459</v>
       </c>
       <c r="G255" t="n">
-        <v>62.630677</v>
+        <v>81.787255</v>
       </c>
       <c r="H255" t="n">
-        <v>111.699732</v>
+        <v>129.486976</v>
       </c>
       <c r="I255" t="n">
-        <v>52.587968</v>
+        <v>66.663414</v>
       </c>
       <c r="J255" t="n">
-        <v>42.922284</v>
+        <v>56.782608</v>
       </c>
       <c r="K255" t="n">
-        <v>62.50864</v>
+        <v>79.505554</v>
       </c>
       <c r="L255" t="n">
-        <v>53.772083</v>
+        <v>69.64161300000001</v>
       </c>
       <c r="M255" t="n">
-        <v>51.72482</v>
+        <v>64.227794</v>
       </c>
     </row>
     <row r="256">
@@ -12636,41 +12636,39 @@
           <t>農藥</t>
         </is>
       </c>
-      <c r="B297" t="n">
-        <v>0</v>
-      </c>
+      <c r="B297" t="inlineStr"/>
       <c r="C297" t="n">
-        <v>4.641608</v>
+        <v>22.706778</v>
       </c>
       <c r="D297" t="n">
-        <v>40.100746</v>
+        <v>53.059548</v>
       </c>
       <c r="E297" t="n">
-        <v>33.707633</v>
+        <v>47.255255</v>
       </c>
       <c r="F297" t="n">
-        <v>86.04933800000001</v>
+        <v>95.773991</v>
       </c>
       <c r="G297" t="n">
-        <v>295.387734</v>
+        <v>304.129928</v>
       </c>
       <c r="H297" t="n">
-        <v>16.271405</v>
+        <v>30.823617</v>
       </c>
       <c r="I297" t="n">
-        <v>10.836866</v>
+        <v>21.098843</v>
       </c>
       <c r="J297" t="n">
-        <v>6.511222</v>
+        <v>21.603888</v>
       </c>
       <c r="K297" t="n">
-        <v>12.839363</v>
+        <v>30.915362</v>
       </c>
       <c r="L297" t="n">
-        <v>9.121689999999999</v>
+        <v>22.106973</v>
       </c>
       <c r="M297" t="n">
-        <v>16.207273</v>
+        <v>33.764641</v>
       </c>
     </row>
     <row r="298">
@@ -12886,34 +12884,34 @@
       </c>
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="n">
-        <v>29467.80437</v>
+        <v>29468.904746</v>
       </c>
       <c r="D303" t="n">
-        <v>14902.388455</v>
+        <v>14905.092596</v>
       </c>
       <c r="E303" t="n">
-        <v>9368.270109999999</v>
+        <v>9373.682510000001</v>
       </c>
       <c r="F303" t="n">
-        <v>8147.564795</v>
+        <v>8149.565079</v>
       </c>
       <c r="G303" t="n">
-        <v>6770.526942</v>
+        <v>6774.102335</v>
       </c>
       <c r="H303" t="n">
-        <v>5198.044504</v>
+        <v>5202.490894</v>
       </c>
       <c r="I303" t="n">
-        <v>11994.342822</v>
+        <v>11997.132495</v>
       </c>
       <c r="J303" t="n">
-        <v>5915.815098</v>
+        <v>5920.747125</v>
       </c>
       <c r="K303" t="n">
-        <v>6771.982785</v>
+        <v>6775.785728</v>
       </c>
       <c r="L303" t="n">
-        <v>3540.569913</v>
+        <v>3544.300938</v>
       </c>
       <c r="M303" t="n">
         <v>3965.201481</v>
@@ -13294,39 +13292,41 @@
           <t>醫療器材代理銷售及通路</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr"/>
+      <c r="B313" t="n">
+        <v>0</v>
+      </c>
       <c r="C313" t="n">
-        <v>18060.132209</v>
+        <v>18060.131326</v>
       </c>
       <c r="D313" t="n">
-        <v>10751.355109</v>
+        <v>10751.354371</v>
       </c>
       <c r="E313" t="n">
-        <v>12343.55937</v>
+        <v>12343.558073</v>
       </c>
       <c r="F313" t="n">
-        <v>9917.387999</v>
+        <v>9917.387767</v>
       </c>
       <c r="G313" t="n">
-        <v>9497.034495</v>
+        <v>9497.033665999999</v>
       </c>
       <c r="H313" t="n">
-        <v>19138.592622</v>
+        <v>19138.586582</v>
       </c>
       <c r="I313" t="n">
-        <v>22883.51906</v>
+        <v>22883.515987</v>
       </c>
       <c r="J313" t="n">
-        <v>14712.832359</v>
+        <v>14712.83221</v>
       </c>
       <c r="K313" t="n">
-        <v>8723.142519000001</v>
+        <v>8723.141985</v>
       </c>
       <c r="L313" t="n">
-        <v>12655.329744</v>
+        <v>12655.32843</v>
       </c>
       <c r="M313" t="n">
-        <v>8226.621268999999</v>
+        <v>8226.62089</v>
       </c>
     </row>
     <row r="314">
@@ -13335,39 +13335,41 @@
           <t>醫療器材研發、設計、製造</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr"/>
+      <c r="B314" t="n">
+        <v>0</v>
+      </c>
       <c r="C314" t="n">
-        <v>23072.621548</v>
+        <v>23068.90937</v>
       </c>
       <c r="D314" t="n">
-        <v>13948.062549</v>
+        <v>13944.285925</v>
       </c>
       <c r="E314" t="n">
-        <v>15208.019947</v>
+        <v>15204.635217</v>
       </c>
       <c r="F314" t="n">
-        <v>10859.276336</v>
+        <v>10854.893871</v>
       </c>
       <c r="G314" t="n">
-        <v>10037.4800205</v>
+        <v>10036.3926655</v>
       </c>
       <c r="H314" t="n">
-        <v>20331.4362905</v>
+        <v>20328.1282075</v>
       </c>
       <c r="I314" t="n">
-        <v>23916.22608266667</v>
+        <v>23914.41921366667</v>
       </c>
       <c r="J314" t="n">
-        <v>15665.535326</v>
+        <v>15662.892715</v>
       </c>
       <c r="K314" t="n">
-        <v>10093.49352</v>
+        <v>10091.921714</v>
       </c>
       <c r="L314" t="n">
-        <v>14124.23305</v>
+        <v>14121.276268</v>
       </c>
       <c r="M314" t="n">
-        <v>9518.569566</v>
+        <v>9515.239129</v>
       </c>
     </row>
     <row r="315">
@@ -13622,41 +13624,39 @@
           <t>金控業/銀行業/保險業</t>
         </is>
       </c>
-      <c r="B321" t="n">
-        <v>0</v>
-      </c>
+      <c r="B321" t="inlineStr"/>
       <c r="C321" t="n">
-        <v>32961.078737</v>
+        <v>35351.542307</v>
       </c>
       <c r="D321" t="n">
-        <v>17212.422624</v>
+        <v>18588.02795</v>
       </c>
       <c r="E321" t="n">
-        <v>13490.167325</v>
+        <v>14711.969845</v>
       </c>
       <c r="F321" t="n">
-        <v>12588.100903</v>
+        <v>14390.076471</v>
       </c>
       <c r="G321" t="n">
-        <v>11269.232743</v>
+        <v>13167.725989</v>
       </c>
       <c r="H321" t="n">
-        <v>8878.823284</v>
+        <v>10337.655452</v>
       </c>
       <c r="I321" t="n">
-        <v>13246.808311</v>
+        <v>15989.591272</v>
       </c>
       <c r="J321" t="n">
-        <v>8932.827678</v>
+        <v>11233.221395</v>
       </c>
       <c r="K321" t="n">
-        <v>11735.540331</v>
+        <v>14414.900269</v>
       </c>
       <c r="L321" t="n">
-        <v>7600.768209</v>
+        <v>8824.348504</v>
       </c>
       <c r="M321" t="n">
-        <v>14198.493671</v>
+        <v>15352.32767</v>
       </c>
     </row>
     <row r="322">
@@ -13952,39 +13952,41 @@
           <t>鋰電池材料</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr"/>
+      <c r="B329" t="n">
+        <v>0</v>
+      </c>
       <c r="C329" t="n">
-        <v>18987.434123</v>
+        <v>18870.192979</v>
       </c>
       <c r="D329" t="n">
-        <v>11515.607026</v>
+        <v>11428.933573</v>
       </c>
       <c r="E329" t="n">
-        <v>12961.083939</v>
+        <v>12702.010055</v>
       </c>
       <c r="F329" t="n">
-        <v>10839.396709</v>
+        <v>10673.652447</v>
       </c>
       <c r="G329" t="n">
-        <v>10570.495762</v>
+        <v>10319.740051</v>
       </c>
       <c r="H329" t="n">
-        <v>19453.56362</v>
+        <v>19275.73226</v>
       </c>
       <c r="I329" t="n">
-        <v>23004.961871</v>
+        <v>22805.628719</v>
       </c>
       <c r="J329" t="n">
-        <v>15059.972812</v>
+        <v>14945.099553</v>
       </c>
       <c r="K329" t="n">
-        <v>9878.709225000001</v>
+        <v>9758.946667</v>
       </c>
       <c r="L329" t="n">
-        <v>11666.194955</v>
+        <v>11521.627811</v>
       </c>
       <c r="M329" t="n">
-        <v>9012.599752</v>
+        <v>8847.352513</v>
       </c>
     </row>
     <row r="330">
@@ -13995,37 +13997,37 @@
       </c>
       <c r="B330" t="inlineStr"/>
       <c r="C330" t="n">
-        <v>1.116507</v>
+        <v>233.766956</v>
       </c>
       <c r="D330" t="n">
-        <v>1.19925</v>
+        <v>40.761088</v>
       </c>
       <c r="E330" t="n">
-        <v>1.874587</v>
+        <v>37.684627</v>
       </c>
       <c r="F330" t="n">
-        <v>9.485416000000001</v>
+        <v>29.438725</v>
       </c>
       <c r="G330" t="n">
-        <v>4.771976</v>
+        <v>23.928554</v>
       </c>
       <c r="H330" t="n">
-        <v>6.552199</v>
+        <v>24.339443</v>
       </c>
       <c r="I330" t="n">
-        <v>4.122118</v>
+        <v>18.197564</v>
       </c>
       <c r="J330" t="n">
-        <v>1.747189</v>
+        <v>15.607513</v>
       </c>
       <c r="K330" t="n">
-        <v>2.036587</v>
+        <v>19.033501</v>
       </c>
       <c r="L330" t="n">
-        <v>3.16852</v>
+        <v>19.03805</v>
       </c>
       <c r="M330" t="n">
-        <v>1.994332</v>
+        <v>14.497306</v>
       </c>
     </row>
     <row r="331">
@@ -14034,41 +14036,39 @@
           <t>鋼筋</t>
         </is>
       </c>
-      <c r="B331" t="n">
-        <v>0</v>
-      </c>
+      <c r="B331" t="inlineStr"/>
       <c r="C331" t="n">
-        <v>469.169149</v>
+        <v>470.002703</v>
       </c>
       <c r="D331" t="n">
-        <v>521.0687766666667</v>
+        <v>521.6005166666666</v>
       </c>
       <c r="E331" t="n">
-        <v>181.0015226666667</v>
+        <v>184.1858026666667</v>
       </c>
       <c r="F331" t="n">
-        <v>228.441433</v>
+        <v>229.343335</v>
       </c>
       <c r="G331" t="n">
-        <v>260.343228</v>
+        <v>261.351736</v>
       </c>
       <c r="H331" t="n">
-        <v>353.636724</v>
+        <v>355.188053</v>
       </c>
       <c r="I331" t="n">
-        <v>200.555774</v>
+        <v>202.022855</v>
       </c>
       <c r="J331" t="n">
-        <v>303.950513</v>
+        <v>305.12582</v>
       </c>
       <c r="K331" t="n">
-        <v>269.117639</v>
+        <v>269.64612</v>
       </c>
       <c r="L331" t="n">
-        <v>205.505761</v>
+        <v>206.164062</v>
       </c>
       <c r="M331" t="n">
-        <v>229.627163</v>
+        <v>230.110809</v>
       </c>
     </row>
     <row r="332">
@@ -14118,41 +14118,39 @@
           <t>鋼胚</t>
         </is>
       </c>
-      <c r="B333" t="n">
-        <v>0</v>
-      </c>
+      <c r="B333" t="inlineStr"/>
       <c r="C333" t="n">
-        <v>1529.225574</v>
+        <v>1530.059128</v>
       </c>
       <c r="D333" t="n">
-        <v>938.279547</v>
+        <v>938.811287</v>
       </c>
       <c r="E333" t="n">
-        <v>720.5837299999999</v>
+        <v>723.76801</v>
       </c>
       <c r="F333" t="n">
-        <v>541.919193</v>
+        <v>542.821095</v>
       </c>
       <c r="G333" t="n">
-        <v>630.87351</v>
+        <v>631.882018</v>
       </c>
       <c r="H333" t="n">
-        <v>990.304764</v>
+        <v>991.856093</v>
       </c>
       <c r="I333" t="n">
-        <v>708.88476</v>
+        <v>710.351841</v>
       </c>
       <c r="J333" t="n">
-        <v>1101.296326</v>
+        <v>1102.471633</v>
       </c>
       <c r="K333" t="n">
-        <v>683.204369</v>
+        <v>683.73285</v>
       </c>
       <c r="L333" t="n">
-        <v>513.746172</v>
+        <v>514.4044730000001</v>
       </c>
       <c r="M333" t="n">
-        <v>604.551198</v>
+        <v>605.034844</v>
       </c>
     </row>
     <row r="334">
@@ -14448,39 +14446,41 @@
           <t>雲端應用服務</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr"/>
+      <c r="B341" t="n">
+        <v>0</v>
+      </c>
       <c r="C341" t="n">
-        <v>25326.490674</v>
+        <v>25326.489791</v>
       </c>
       <c r="D341" t="n">
-        <v>15500.70141</v>
+        <v>15500.700672</v>
       </c>
       <c r="E341" t="n">
-        <v>15326.664063</v>
+        <v>15326.662766</v>
       </c>
       <c r="F341" t="n">
-        <v>11690.392723</v>
+        <v>11690.392491</v>
       </c>
       <c r="G341" t="n">
-        <v>10718.099846</v>
+        <v>10718.099017</v>
       </c>
       <c r="H341" t="n">
-        <v>19951.941781</v>
+        <v>19951.935741</v>
       </c>
       <c r="I341" t="n">
-        <v>22825.459873</v>
+        <v>22825.4568</v>
       </c>
       <c r="J341" t="n">
-        <v>15268.48264</v>
+        <v>15268.482491</v>
       </c>
       <c r="K341" t="n">
-        <v>9617.177535000001</v>
+        <v>9617.177001</v>
       </c>
       <c r="L341" t="n">
-        <v>12513.97442</v>
+        <v>12513.973106</v>
       </c>
       <c r="M341" t="n">
-        <v>8275.59844</v>
+        <v>8275.598061000001</v>
       </c>
     </row>
     <row r="342">
@@ -14489,39 +14489,41 @@
           <t>零售通路</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr"/>
+      <c r="B342" t="n">
+        <v>0</v>
+      </c>
       <c r="C342" t="n">
-        <v>2510.460821</v>
+        <v>2510.460812</v>
       </c>
       <c r="D342" t="n">
-        <v>1638.860051</v>
+        <v>1638.859966</v>
       </c>
       <c r="E342" t="n">
-        <v>1448.1130865</v>
+        <v>1448.1123635</v>
       </c>
       <c r="F342" t="n">
-        <v>1323.71394</v>
+        <v>1323.713468</v>
       </c>
       <c r="G342" t="n">
-        <v>1614.621991</v>
+        <v>1614.621258</v>
       </c>
       <c r="H342" t="n">
-        <v>1207.28756</v>
+        <v>1207.287388</v>
       </c>
       <c r="I342" t="n">
-        <v>1293.402619</v>
+        <v>1293.402389</v>
       </c>
       <c r="J342" t="n">
-        <v>895.863446</v>
+        <v>895.863187</v>
       </c>
       <c r="K342" t="n">
-        <v>810.412334</v>
+        <v>810.41233</v>
       </c>
       <c r="L342" t="n">
-        <v>1021.206702</v>
+        <v>1021.206511</v>
       </c>
       <c r="M342" t="n">
-        <v>1504.77444225</v>
+        <v>1504.77427125</v>
       </c>
     </row>
     <row r="343">
@@ -14735,39 +14737,41 @@
           <t>電動汽車、電動機車、電動自行車</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr"/>
+      <c r="B348" t="n">
+        <v>0</v>
+      </c>
       <c r="C348" t="n">
-        <v>18007.278816</v>
+        <v>18007.257338</v>
       </c>
       <c r="D348" t="n">
-        <v>10049.994387</v>
+        <v>10049.971338</v>
       </c>
       <c r="E348" t="n">
-        <v>11237.717581</v>
+        <v>11237.693361</v>
       </c>
       <c r="F348" t="n">
-        <v>9062.923543999999</v>
+        <v>9062.913543999999</v>
       </c>
       <c r="G348" t="n">
-        <v>8485.788549000001</v>
+        <v>8485.704834</v>
       </c>
       <c r="H348" t="n">
-        <v>17499.116705</v>
+        <v>17499.095923</v>
       </c>
       <c r="I348" t="n">
-        <v>20561.990475</v>
+        <v>20561.981148</v>
       </c>
       <c r="J348" t="n">
-        <v>13093.529707</v>
+        <v>13093.522439</v>
       </c>
       <c r="K348" t="n">
-        <v>7238.628236</v>
+        <v>7238.617253</v>
       </c>
       <c r="L348" t="n">
-        <v>10020.787164</v>
+        <v>10020.753385</v>
       </c>
       <c r="M348" t="n">
-        <v>6195.629083</v>
+        <v>6195.624808</v>
       </c>
     </row>
     <row r="349">
@@ -15145,41 +15149,39 @@
           <t>電池模組</t>
         </is>
       </c>
-      <c r="B358" t="n">
-        <v>0</v>
-      </c>
+      <c r="B358" t="inlineStr"/>
       <c r="C358" t="n">
-        <v>49843.340087</v>
+        <v>49843.340339</v>
       </c>
       <c r="D358" t="n">
-        <v>16440.816504</v>
+        <v>16440.816972</v>
       </c>
       <c r="E358" t="n">
-        <v>14952.022667</v>
+        <v>14952.023244</v>
       </c>
       <c r="F358" t="n">
-        <v>10908.847922</v>
+        <v>10908.848509</v>
       </c>
       <c r="G358" t="n">
-        <v>12781.839446</v>
+        <v>12781.841341</v>
       </c>
       <c r="H358" t="n">
-        <v>21066.438228</v>
+        <v>21066.439184</v>
       </c>
       <c r="I358" t="n">
-        <v>25334.773787</v>
+        <v>25334.774893</v>
       </c>
       <c r="J358" t="n">
-        <v>16123.217966</v>
+        <v>16123.218414</v>
       </c>
       <c r="K358" t="n">
-        <v>9620.146299</v>
+        <v>9620.147591000001</v>
       </c>
       <c r="L358" t="n">
-        <v>11748.681928</v>
+        <v>11748.682374</v>
       </c>
       <c r="M358" t="n">
-        <v>7658.05731</v>
+        <v>7658.063962</v>
       </c>
     </row>
     <row r="359">
@@ -15229,41 +15231,39 @@
           <t>電源供應器</t>
         </is>
       </c>
-      <c r="B360" t="n">
-        <v>0</v>
-      </c>
+      <c r="B360" t="inlineStr"/>
       <c r="C360" t="n">
-        <v>57432.892929</v>
+        <v>57436.507954</v>
       </c>
       <c r="D360" t="n">
-        <v>21997.657367</v>
+        <v>22001.4164</v>
       </c>
       <c r="E360" t="n">
-        <v>20743.277947</v>
+        <v>20747.641104</v>
       </c>
       <c r="F360" t="n">
-        <v>14055.965225</v>
+        <v>14058.665449</v>
       </c>
       <c r="G360" t="n">
-        <v>15967.448527</v>
+        <v>15970.522585</v>
       </c>
       <c r="H360" t="n">
-        <v>24037.135762</v>
+        <v>24042.118714</v>
       </c>
       <c r="I360" t="n">
-        <v>28063.245898</v>
+        <v>28065.855434</v>
       </c>
       <c r="J360" t="n">
-        <v>18786.42457</v>
+        <v>18790.522114</v>
       </c>
       <c r="K360" t="n">
-        <v>12440.168515</v>
+        <v>12445.511245</v>
       </c>
       <c r="L360" t="n">
-        <v>14523.986478</v>
+        <v>14526.842595</v>
       </c>
       <c r="M360" t="n">
-        <v>10664.140287</v>
+        <v>10667.939013</v>
       </c>
     </row>
     <row r="361">
@@ -15682,39 +15682,41 @@
           <t>預拌混凝土</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr"/>
+      <c r="B371" t="n">
+        <v>0</v>
+      </c>
       <c r="C371" t="n">
-        <v>1058.338506</v>
+        <v>1023.194528</v>
       </c>
       <c r="D371" t="n">
-        <v>626.089653</v>
+        <v>590.409573</v>
       </c>
       <c r="E371" t="n">
-        <v>822.941501</v>
+        <v>767.112921</v>
       </c>
       <c r="F371" t="n">
-        <v>594.46546</v>
+        <v>581.096542</v>
       </c>
       <c r="G371" t="n">
-        <v>1265.789838</v>
+        <v>1251.379789</v>
       </c>
       <c r="H371" t="n">
-        <v>949.945689</v>
+        <v>932.236666</v>
       </c>
       <c r="I371" t="n">
-        <v>595.544579</v>
+        <v>576.023759</v>
       </c>
       <c r="J371" t="n">
-        <v>486.412044</v>
+        <v>475.565188</v>
       </c>
       <c r="K371" t="n">
-        <v>637.210422</v>
+        <v>615.514994</v>
       </c>
       <c r="L371" t="n">
-        <v>598.476617</v>
+        <v>581.014056</v>
       </c>
       <c r="M371" t="n">
-        <v>444.705477</v>
+        <v>411.543556</v>
       </c>
     </row>
     <row r="372">
@@ -15971,37 +15973,37 @@
       </c>
       <c r="B378" t="inlineStr"/>
       <c r="C378" t="n">
-        <v>2948.999332</v>
+        <v>3087.487628</v>
       </c>
       <c r="D378" t="n">
-        <v>1866.253937</v>
+        <v>2018.731404</v>
       </c>
       <c r="E378" t="n">
-        <v>2094.702483</v>
+        <v>2232.044634</v>
       </c>
       <c r="F378" t="n">
-        <v>2131.555614</v>
+        <v>2284.707831</v>
       </c>
       <c r="G378" t="n">
-        <v>3291.8456</v>
+        <v>3414.850082</v>
       </c>
       <c r="H378" t="n">
-        <v>4123.222584</v>
+        <v>4249.790554</v>
       </c>
       <c r="I378" t="n">
-        <v>2437.996762</v>
+        <v>2595.67319</v>
       </c>
       <c r="J378" t="n">
-        <v>1859.788286</v>
+        <v>2021.639979</v>
       </c>
       <c r="K378" t="n">
-        <v>1619.695367</v>
+        <v>1735.767257</v>
       </c>
       <c r="L378" t="n">
-        <v>1468.785935</v>
+        <v>1548.455672</v>
       </c>
       <c r="M378" t="n">
-        <v>2010.97831</v>
+        <v>2116.06208</v>
       </c>
     </row>
     <row r="379">
@@ -16174,39 +16176,41 @@
           <t>餐飲連鎖</t>
         </is>
       </c>
-      <c r="B383" t="inlineStr"/>
+      <c r="B383" t="n">
+        <v>0</v>
+      </c>
       <c r="C383" t="n">
-        <v>323.851856</v>
+        <v>323.851731</v>
       </c>
       <c r="D383" t="n">
-        <v>233.828348</v>
+        <v>233.828222</v>
       </c>
       <c r="E383" t="n">
-        <v>198.09925</v>
+        <v>198.099243</v>
       </c>
       <c r="F383" t="n">
-        <v>124.864137</v>
+        <v>124.86367</v>
       </c>
       <c r="G383" t="n">
-        <v>165.530922</v>
+        <v>165.530427</v>
       </c>
       <c r="H383" t="n">
-        <v>185.260036</v>
+        <v>185.25989</v>
       </c>
       <c r="I383" t="n">
-        <v>190.514171</v>
+        <v>190.514054</v>
       </c>
       <c r="J383" t="n">
-        <v>139.802721</v>
+        <v>139.80253</v>
       </c>
       <c r="K383" t="n">
-        <v>146.842199</v>
+        <v>146.842196</v>
       </c>
       <c r="L383" t="n">
-        <v>141.72008</v>
+        <v>141.720012</v>
       </c>
       <c r="M383" t="n">
-        <v>107.282014</v>
+        <v>107.281011</v>
       </c>
     </row>
     <row r="384">

--- a/Result/analyze_4.xlsx
+++ b/Result/analyze_4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L389"/>
+  <dimension ref="A1:M389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -487,6 +487,11 @@
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
         </is>
       </c>
     </row>
@@ -496,9 +501,7 @@
           <t>AGV及AMR</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0.162621</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0.108556</v>
       </c>
@@ -529,6 +532,9 @@
       <c r="L2" t="n">
         <v>0.905517</v>
       </c>
+      <c r="M2" t="n">
+        <v>0.310954</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -536,9 +542,7 @@
           <t>BIOS(嵌入式軟體)</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2595.882365</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>2111.836964</v>
       </c>
@@ -569,6 +573,9 @@
       <c r="L3" t="n">
         <v>2239.850971</v>
       </c>
+      <c r="M3" t="n">
+        <v>1600.355016</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -576,9 +583,7 @@
           <t>BaaS</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>30.996195</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>23.262423</v>
       </c>
@@ -609,6 +614,9 @@
       <c r="L4" t="n">
         <v>32.775686</v>
       </c>
+      <c r="M4" t="n">
+        <v>25.805276</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -616,9 +624,7 @@
           <t>HMI</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0.020915</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0.012743</v>
       </c>
@@ -649,6 +655,9 @@
       <c r="L5" t="n">
         <v>0.007063</v>
       </c>
+      <c r="M5" t="n">
+        <v>0.010031</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -656,9 +665,7 @@
           <t>IC/晶圓製造</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>108751.965788</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>141044.240782</v>
       </c>
@@ -689,6 +696,9 @@
       <c r="L6" t="n">
         <v>165236.275583</v>
       </c>
+      <c r="M6" t="n">
+        <v>229575.051674</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -696,9 +706,7 @@
           <t>IC封裝測試</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>46865.091493</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>52977.960832</v>
       </c>
@@ -727,7 +735,10 @@
         <v>67374.15689</v>
       </c>
       <c r="L7" t="n">
-        <v>38985.541139</v>
+        <v>41991.125087</v>
+      </c>
+      <c r="M7" t="n">
+        <v>61334.673194</v>
       </c>
     </row>
     <row r="8">
@@ -736,9 +747,7 @@
           <t>IC模組</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>27586.598093</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>17953.836699</v>
       </c>
@@ -769,6 +778,9 @@
       <c r="L8" t="n">
         <v>21815.10294</v>
       </c>
+      <c r="M8" t="n">
+        <v>20915.851836</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -776,9 +788,7 @@
           <t>IC設計</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>52124.292671</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>51771.84454875</v>
       </c>
@@ -807,7 +817,10 @@
         <v>171569.766576</v>
       </c>
       <c r="L9" t="n">
-        <v>127882.612438</v>
+        <v>127912.286462</v>
+      </c>
+      <c r="M9" t="n">
+        <v>196758.361546</v>
       </c>
     </row>
     <row r="10">
@@ -816,9 +829,7 @@
           <t>IC通路</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>22120.341692</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>14412.906692</v>
       </c>
@@ -849,6 +860,9 @@
       <c r="L10" t="n">
         <v>22384.519273</v>
       </c>
+      <c r="M10" t="n">
+        <v>21460.330725</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -856,9 +870,7 @@
           <t>IP設計/IC設計代工服務</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>21608.1277</v>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>13763.186433</v>
       </c>
@@ -889,6 +901,9 @@
       <c r="L11" t="n">
         <v>21112.091722</v>
       </c>
+      <c r="M11" t="n">
+        <v>20600.186286</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -896,9 +911,7 @@
           <t>ITO導電基板</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>137.570252</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>190.431241</v>
       </c>
@@ -929,6 +942,9 @@
       <c r="L12" t="n">
         <v>57.88361</v>
       </c>
+      <c r="M12" t="n">
+        <v>46.579051</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -936,9 +952,7 @@
           <t>ITO導電玻璃</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0.016279</v>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0.019162</v>
       </c>
@@ -969,6 +983,9 @@
       <c r="L13" t="n">
         <v>0.019452</v>
       </c>
+      <c r="M13" t="n">
+        <v>0.008855</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -976,9 +993,7 @@
           <t>ITO導電薄膜</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>29.140615</v>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>30.996466</v>
       </c>
@@ -1009,6 +1024,9 @@
       <c r="L14" t="n">
         <v>11.293432</v>
       </c>
+      <c r="M14" t="n">
+        <v>12.386614</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1016,9 +1034,7 @@
           <t>ITO靶材</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0.82595</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0.374981</v>
       </c>
@@ -1049,6 +1065,9 @@
       <c r="L15" t="n">
         <v>0.7698430000000001</v>
       </c>
+      <c r="M15" t="n">
+        <v>0.398214</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1056,9 +1075,7 @@
           <t>PET膜</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>0.007874000000000001</v>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0.010217</v>
       </c>
@@ -1089,6 +1106,9 @@
       <c r="L16" t="n">
         <v>0.008704999999999999</v>
       </c>
+      <c r="M16" t="n">
+        <v>0.006674</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1096,9 +1116,7 @@
           <t>一般零售</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>108.647785</v>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>102.161426</v>
       </c>
@@ -1129,6 +1147,9 @@
       <c r="L17" t="n">
         <v>88.09882666666667</v>
       </c>
+      <c r="M17" t="n">
+        <v>46.34622066666667</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1136,9 +1157,7 @@
           <t>不鏽鋼型鋼</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>40.365518</v>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>35.348198</v>
       </c>
@@ -1169,6 +1188,9 @@
       <c r="L18" t="n">
         <v>151.313254</v>
       </c>
+      <c r="M18" t="n">
+        <v>59.348241</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1176,9 +1198,7 @@
           <t>不鏽鋼棒線</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>7164.35059</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>5826.915129</v>
       </c>
@@ -1209,6 +1229,9 @@
       <c r="L19" t="n">
         <v>7410.941393</v>
       </c>
+      <c r="M19" t="n">
+        <v>7981.88049525</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1216,9 +1239,7 @@
           <t>不鏽鋼胚</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>7127.386728</v>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>5800.938414</v>
       </c>
@@ -1249,6 +1270,9 @@
       <c r="L20" t="n">
         <v>7329.27059</v>
       </c>
+      <c r="M20" t="n">
+        <v>7924.392416</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1256,9 +1280,7 @@
           <t>中、西藥製劑</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>3902.907539</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>2028.29029</v>
       </c>
@@ -1289,6 +1311,9 @@
       <c r="L21" t="n">
         <v>3534.125313</v>
       </c>
+      <c r="M21" t="n">
+        <v>3421.960167</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1296,9 +1321,7 @@
           <t>中央處理器</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>418.205794</v>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>259.460722</v>
       </c>
@@ -1329,6 +1352,9 @@
       <c r="L22" t="n">
         <v>128.339665</v>
       </c>
+      <c r="M22" t="n">
+        <v>98.193259</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1336,9 +1362,7 @@
           <t>中藥材、西藥原料藥</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>537.162835</v>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>403.830938</v>
       </c>
@@ -1369,6 +1393,9 @@
       <c r="L23" t="n">
         <v>303.54309</v>
       </c>
+      <c r="M23" t="n">
+        <v>409.466229</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1376,9 +1403,7 @@
           <t>主/被動元件</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>2673.100288</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>4226.437105</v>
       </c>
@@ -1409,6 +1434,9 @@
       <c r="L24" t="n">
         <v>1659.32796</v>
       </c>
+      <c r="M24" t="n">
+        <v>1488.734087</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1416,9 +1444,7 @@
           <t>主機板</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>28006.932924</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>24735.146113</v>
       </c>
@@ -1449,6 +1475,9 @@
       <c r="L25" t="n">
         <v>19376.614304</v>
       </c>
+      <c r="M25" t="n">
+        <v>14837.049776</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1456,9 +1485,7 @@
           <t>乳製品</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>763.531605</v>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>686.315249</v>
       </c>
@@ -1489,6 +1516,9 @@
       <c r="L26" t="n">
         <v>531.592914</v>
       </c>
+      <c r="M26" t="n">
+        <v>455.67413</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1496,38 +1526,39 @@
           <t>五金元件及零配件</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>1913.974884</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>1255.569656</v>
+        <v>1255.602784</v>
       </c>
       <c r="D27" t="n">
-        <v>1552.793197</v>
+        <v>1552.833757</v>
       </c>
       <c r="E27" t="n">
-        <v>1987.518676</v>
+        <v>1987.545945</v>
       </c>
       <c r="F27" t="n">
-        <v>1476.3047</v>
+        <v>1476.325786</v>
       </c>
       <c r="G27" t="n">
-        <v>1643.514518</v>
+        <v>1643.536807</v>
       </c>
       <c r="H27" t="n">
-        <v>1686.954434</v>
+        <v>1686.97274</v>
       </c>
       <c r="I27" t="n">
-        <v>1397.79856</v>
+        <v>1397.808755</v>
       </c>
       <c r="J27" t="n">
-        <v>3372.100627</v>
+        <v>3372.13649</v>
       </c>
       <c r="K27" t="n">
-        <v>4568.858846</v>
+        <v>4568.899852</v>
       </c>
       <c r="L27" t="n">
-        <v>3655.916065</v>
+        <v>3655.970646</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3851.610308</v>
       </c>
     </row>
     <row r="28">
@@ -1536,9 +1567,7 @@
           <t>交易平台</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>124.751201</v>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>60.391623</v>
       </c>
@@ -1569,6 +1598,9 @@
       <c r="L28" t="n">
         <v>73.112775</v>
       </c>
+      <c r="M28" t="n">
+        <v>59.921262</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -1576,9 +1608,7 @@
           <t>交易撮(媒)合</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>7.873085</v>
-      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>7.445474</v>
       </c>
@@ -1609,6 +1639,9 @@
       <c r="L29" t="n">
         <v>5.877635</v>
       </c>
+      <c r="M29" t="n">
+        <v>4.531687</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -1616,9 +1649,7 @@
           <t>人造纖維</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>30644.479032</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>19423.931436</v>
       </c>
@@ -1649,6 +1680,9 @@
       <c r="L30" t="n">
         <v>8665.269434</v>
       </c>
+      <c r="M30" t="n">
+        <v>6901.231692</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -1656,9 +1690,7 @@
           <t>人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>29558.965025</v>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>18577.456108</v>
       </c>
@@ -1689,6 +1721,9 @@
       <c r="L31" t="n">
         <v>6837.343146</v>
       </c>
+      <c r="M31" t="n">
+        <v>5828.508016</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -1696,9 +1731,7 @@
           <t>休閒車業</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>22273.534632</v>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>12169.141085</v>
       </c>
@@ -1729,6 +1762,9 @@
       <c r="L32" t="n">
         <v>19771.644463</v>
       </c>
+      <c r="M32" t="n">
+        <v>19311.681177</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -1736,9 +1772,7 @@
           <t>伺服器</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>39768.460744</v>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>42785.302982</v>
       </c>
@@ -1769,6 +1803,9 @@
       <c r="L33" t="n">
         <v>34966.746429</v>
       </c>
+      <c r="M33" t="n">
+        <v>26356.753324</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1776,9 +1813,7 @@
           <t>低壓AMI</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>9378.081587999999</v>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>15711.710519</v>
       </c>
@@ -1809,6 +1844,9 @@
       <c r="L34" t="n">
         <v>2569.111029</v>
       </c>
+      <c r="M34" t="n">
+        <v>2061.571616</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1816,9 +1854,7 @@
           <t>保健食品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>3643.179001</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>1700.92416</v>
       </c>
@@ -1847,7 +1883,10 @@
         <v>2937.34369</v>
       </c>
       <c r="L35" t="n">
-        <v>2356.228955</v>
+        <v>2342.259111</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2603.798406</v>
       </c>
     </row>
     <row r="36">
@@ -1856,9 +1895,7 @@
           <t>保險</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>143.372639</v>
-      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>85.38433999999999</v>
       </c>
@@ -1889,6 +1926,9 @@
       <c r="L36" t="n">
         <v>112.634765</v>
       </c>
+      <c r="M36" t="n">
+        <v>109.634154</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1896,9 +1936,7 @@
           <t>保險桿</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>909.916094</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>627.762851</v>
       </c>
@@ -1929,6 +1967,9 @@
       <c r="L37" t="n">
         <v>218.204579</v>
       </c>
+      <c r="M37" t="n">
+        <v>268.529879</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1936,9 +1977,7 @@
           <t>個人、民間企業、政府機構</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>102.773479</v>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>444.613608</v>
       </c>
@@ -1969,6 +2008,9 @@
       <c r="L38" t="n">
         <v>144.605124</v>
       </c>
+      <c r="M38" t="n">
+        <v>271.12265</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -1976,9 +2018,7 @@
           <t>健身器材</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>186.950688</v>
-      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>101.572872</v>
       </c>
@@ -2009,6 +2049,9 @@
       <c r="L39" t="n">
         <v>100.167478</v>
       </c>
+      <c r="M39" t="n">
+        <v>43.641611</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -2016,9 +2059,7 @@
           <t>健身平台/APP</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>2647.919019</v>
-      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>2867.926065</v>
       </c>
@@ -2049,6 +2090,9 @@
       <c r="L40" t="n">
         <v>2127.889756</v>
       </c>
+      <c r="M40" t="n">
+        <v>1196.967315</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -2056,9 +2100,7 @@
           <t>傳動元件</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>25722.816404</v>
-      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
         <v>17303.645964</v>
       </c>
@@ -2087,7 +2129,10 @@
         <v>25585.074735</v>
       </c>
       <c r="L41" t="n">
-        <v>25745.03778075</v>
+        <v>25701.68533375</v>
+      </c>
+      <c r="M41" t="n">
+        <v>22638.301837</v>
       </c>
     </row>
     <row r="42">
@@ -2096,9 +2141,7 @@
           <t>儲存處理</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>925.660681</v>
-      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
         <v>778.841195</v>
       </c>
@@ -2129,6 +2172,9 @@
       <c r="L42" t="n">
         <v>438.8765073333333</v>
       </c>
+      <c r="M42" t="n">
+        <v>360.20895</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -2136,9 +2182,7 @@
           <t>元件裝置</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>480.053158</v>
-      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
         <v>429.309019</v>
       </c>
@@ -2169,6 +2213,9 @@
       <c r="L43" t="n">
         <v>162.371764</v>
       </c>
+      <c r="M43" t="n">
+        <v>183.720068</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -2176,9 +2223,7 @@
           <t>光學鏡片、鏡頭</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>17112.778346</v>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
         <v>21269.016316</v>
       </c>
@@ -2209,6 +2254,9 @@
       <c r="L44" t="n">
         <v>22294.394877</v>
       </c>
+      <c r="M44" t="n">
+        <v>15003.784019</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -2216,9 +2264,7 @@
           <t>光源/磊晶</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>784.346229</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
         <v>1373.420539</v>
       </c>
@@ -2249,6 +2295,9 @@
       <c r="L45" t="n">
         <v>1295.096401</v>
       </c>
+      <c r="M45" t="n">
+        <v>1266.398031</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -2256,9 +2305,7 @@
           <t>光碟機</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>2595.797194</v>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
         <v>2111.741231</v>
       </c>
@@ -2289,6 +2336,9 @@
       <c r="L46" t="n">
         <v>2239.706383</v>
       </c>
+      <c r="M46" t="n">
+        <v>1600.281085</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -2296,9 +2346,7 @@
           <t>光碟片</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>480.962351</v>
-      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
         <v>345.411775</v>
       </c>
@@ -2329,6 +2377,9 @@
       <c r="L47" t="n">
         <v>191.602496</v>
       </c>
+      <c r="M47" t="n">
+        <v>154.932944</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -2336,9 +2387,7 @@
           <t>光罩</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>238.608755</v>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
         <v>112.236784</v>
       </c>
@@ -2369,6 +2418,9 @@
       <c r="L48" t="n">
         <v>78.12115300000001</v>
       </c>
+      <c r="M48" t="n">
+        <v>45.19852</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -2376,9 +2428,7 @@
           <t>光通訊設備(如光纖電纜、光傳輸設備)</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>21725.375425</v>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
         <v>16427.302688</v>
       </c>
@@ -2409,6 +2459,9 @@
       <c r="L49" t="n">
         <v>25138.332784</v>
       </c>
+      <c r="M49" t="n">
+        <v>29384.521702</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -2416,9 +2469,7 @@
           <t>公共資訊查詢站(Kiosk)</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>0.005662</v>
-      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
         <v>0.002407</v>
       </c>
@@ -2449,6 +2500,9 @@
       <c r="L50" t="n">
         <v>0.001474</v>
       </c>
+      <c r="M50" t="n">
+        <v>0.004047</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -2456,38 +2510,39 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>44170.378812</v>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>33752.6354375</v>
+        <v>33752.6685655</v>
       </c>
       <c r="D51" t="n">
-        <v>64936.07705308333</v>
+        <v>64936.11761308333</v>
       </c>
       <c r="E51" t="n">
-        <v>79036.602134</v>
+        <v>79036.629403</v>
       </c>
       <c r="F51" t="n">
-        <v>77870.40196050001</v>
+        <v>77870.4230465</v>
       </c>
       <c r="G51" t="n">
-        <v>47440.67318375</v>
+        <v>47440.69547275</v>
       </c>
       <c r="H51" t="n">
-        <v>35623.225809</v>
+        <v>35623.244115</v>
       </c>
       <c r="I51" t="n">
-        <v>46861.017949</v>
+        <v>46861.028144</v>
       </c>
       <c r="J51" t="n">
-        <v>55541.6623525</v>
+        <v>55541.6982155</v>
       </c>
       <c r="K51" t="n">
-        <v>42963.778404</v>
+        <v>42963.81941</v>
       </c>
       <c r="L51" t="n">
-        <v>44560.3456</v>
+        <v>44392.683661</v>
+      </c>
+      <c r="M51" t="n">
+        <v>37769.966151</v>
       </c>
     </row>
     <row r="52">
@@ -2496,9 +2551,7 @@
           <t>其他配件</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>969.92585</v>
-      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
         <v>646.704925</v>
       </c>
@@ -2529,6 +2582,9 @@
       <c r="L52" t="n">
         <v>1291.424843</v>
       </c>
+      <c r="M52" t="n">
+        <v>852.747721</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -2536,9 +2592,7 @@
           <t>其他零組件</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>32736.827508</v>
-      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
         <v>24789.031337</v>
       </c>
@@ -2567,7 +2621,10 @@
         <v>29341.99179</v>
       </c>
       <c r="L53" t="n">
-        <v>26842.863111</v>
+        <v>26859.113189</v>
+      </c>
+      <c r="M53" t="n">
+        <v>24470.228429</v>
       </c>
     </row>
     <row r="54">
@@ -2576,9 +2633,7 @@
           <t>其他電子產品及電子服務產業</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>39910.154914</v>
-      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
         <v>39414.334272</v>
       </c>
@@ -2607,7 +2662,10 @@
         <v>27123.768856</v>
       </c>
       <c r="L54" t="n">
-        <v>18397.815452</v>
+        <v>18374.017528</v>
+      </c>
+      <c r="M54" t="n">
+        <v>21305.835673</v>
       </c>
     </row>
     <row r="55">
@@ -2616,9 +2674,7 @@
           <t>其他電腦及週邊設備</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>48698.650035</v>
-      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
         <v>46691.154578</v>
       </c>
@@ -2649,6 +2705,9 @@
       <c r="L55" t="n">
         <v>36745.803329</v>
       </c>
+      <c r="M55" t="n">
+        <v>26955.830554</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -2656,9 +2715,7 @@
           <t>其他電腦及週邊設備之零組件</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>28412.399007</v>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
         <v>26946.587169</v>
       </c>
@@ -2687,7 +2744,10 @@
         <v>21750.850145</v>
       </c>
       <c r="L56" t="n">
-        <v>14833.314285</v>
+        <v>14697.478558</v>
+      </c>
+      <c r="M56" t="n">
+        <v>17138.5044935</v>
       </c>
     </row>
     <row r="57">
@@ -2696,9 +2756,7 @@
           <t>冷凍、罐頭、脫水、醃漬食品</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>1101.72867</v>
-      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
         <v>974.264738</v>
       </c>
@@ -2729,6 +2787,9 @@
       <c r="L57" t="n">
         <v>802.8847510000001</v>
       </c>
+      <c r="M57" t="n">
+        <v>667.421923</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -2736,9 +2797,7 @@
           <t>冷凍空調設備及零件</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>18004.502491</v>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
         <v>23571.752017</v>
       </c>
@@ -2769,6 +2828,9 @@
       <c r="L58" t="n">
         <v>5663.772176</v>
       </c>
+      <c r="M58" t="n">
+        <v>4083.352064</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -2776,9 +2838,7 @@
           <t>冷卻設備</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>17174.716211</v>
-      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
         <v>10625.36662</v>
       </c>
@@ -2809,6 +2869,9 @@
       <c r="L59" t="n">
         <v>19021.602928</v>
       </c>
+      <c r="M59" t="n">
+        <v>17839.701305</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -2816,9 +2879,7 @@
           <t>冷熱軋不鏽鋼板捲</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>7224.260429</v>
-      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
         <v>5877.443437</v>
       </c>
@@ -2849,6 +2910,9 @@
       <c r="L60" t="n">
         <v>7582.397355</v>
       </c>
+      <c r="M60" t="n">
+        <v>8075.693845</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -2856,9 +2920,7 @@
           <t>冷熱軋鋼板捲</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>2146.9837185</v>
-      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
         <v>1606.23889</v>
       </c>
@@ -2889,6 +2951,9 @@
       <c r="L61" t="n">
         <v>6985.023056</v>
       </c>
+      <c r="M61" t="n">
+        <v>3381.898235</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -2896,9 +2961,7 @@
           <t>出版產業</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>2e-05</v>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
         <v>5.2e-05</v>
       </c>
@@ -2929,6 +2992,9 @@
       <c r="L62" t="n">
         <v>0.000145</v>
       </c>
+      <c r="M62" t="n">
+        <v>1e-06</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -2936,9 +3002,7 @@
           <t>分析工具</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>313.191171</v>
-      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
         <v>238.918593</v>
       </c>
@@ -2969,6 +3033,9 @@
       <c r="L63" t="n">
         <v>199.9375563333333</v>
       </c>
+      <c r="M63" t="n">
+        <v>186.046662</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -2976,9 +3043,7 @@
           <t>創意生活產業</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>0.001385</v>
-      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
         <v>0.001022</v>
       </c>
@@ -3009,6 +3074,9 @@
       <c r="L64" t="n">
         <v>0.000624</v>
       </c>
+      <c r="M64" t="n">
+        <v>0.0004033333333333333</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -3016,9 +3084,7 @@
           <t>創投</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>30.996195</v>
-      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
         <v>23.262423</v>
       </c>
@@ -3049,6 +3115,9 @@
       <c r="L65" t="n">
         <v>32.775686</v>
       </c>
+      <c r="M65" t="n">
+        <v>25.805276</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -3056,9 +3125,7 @@
           <t>加密資產</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>30.996195</v>
-      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
         <v>23.262423</v>
       </c>
@@ -3089,6 +3156,9 @@
       <c r="L66" t="n">
         <v>32.775686</v>
       </c>
+      <c r="M66" t="n">
+        <v>25.805276</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -3096,9 +3166,7 @@
           <t>加工製成品</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>2902.36611</v>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
         <v>1483.20651</v>
       </c>
@@ -3127,7 +3195,10 @@
         <v>2801.7467</v>
       </c>
       <c r="L67" t="n">
-        <v>2162.455206</v>
+        <v>2148.485362</v>
+      </c>
+      <c r="M67" t="n">
+        <v>2495.341772</v>
       </c>
     </row>
     <row r="68">
@@ -3136,9 +3207,7 @@
           <t>加工食品</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>1327.287968</v>
-      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
         <v>1112.000063</v>
       </c>
@@ -3169,6 +3238,9 @@
       <c r="L68" t="n">
         <v>1025.23809</v>
       </c>
+      <c r="M68" t="n">
+        <v>797.123972</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -3176,9 +3248,7 @@
           <t>加油站</t>
         </is>
       </c>
-      <c r="B69" t="n">
-        <v>744.283085</v>
-      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
         <v>763.43701</v>
       </c>
@@ -3209,6 +3279,9 @@
       <c r="L69" t="n">
         <v>808.049657</v>
       </c>
+      <c r="M69" t="n">
+        <v>508.460619</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -3216,9 +3289,7 @@
           <t>化妝品</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>14.302963</v>
-      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
         <v>7.870314</v>
       </c>
@@ -3249,6 +3320,9 @@
       <c r="L70" t="n">
         <v>97.635293</v>
       </c>
+      <c r="M70" t="n">
+        <v>44.791612</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -3256,9 +3330,7 @@
           <t>化學助劑</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>869.1392489999999</v>
-      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
         <v>811.041374</v>
       </c>
@@ -3289,6 +3361,9 @@
       <c r="L71" t="n">
         <v>376.408236</v>
       </c>
+      <c r="M71" t="n">
+        <v>277.133991</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -3296,9 +3371,7 @@
           <t>化學品</t>
         </is>
       </c>
-      <c r="B72" t="n">
-        <v>9946.081059</v>
-      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
         <v>6458.920383</v>
       </c>
@@ -3329,6 +3402,9 @@
       <c r="L72" t="n">
         <v>4192.453569</v>
       </c>
+      <c r="M72" t="n">
+        <v>3467.659234</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -3336,9 +3412,7 @@
           <t>化學品(如光阻劑、靶材等)</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>7472.164881</v>
-      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
         <v>5021.317555</v>
       </c>
@@ -3369,6 +3443,9 @@
       <c r="L73" t="n">
         <v>3097.541423</v>
       </c>
+      <c r="M73" t="n">
+        <v>2592.469183</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -3376,9 +3453,7 @@
           <t>印刷材料</t>
         </is>
       </c>
-      <c r="B74" t="n">
-        <v>0.035151</v>
-      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
         <v>0.03952</v>
       </c>
@@ -3409,6 +3484,9 @@
       <c r="L74" t="n">
         <v>0.013634</v>
       </c>
+      <c r="M74" t="n">
+        <v>0.01356</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -3416,9 +3494,7 @@
           <t>印刷電路板</t>
         </is>
       </c>
-      <c r="B75" t="n">
-        <v>1.415005</v>
-      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
         <v>0.774035</v>
       </c>
@@ -3449,6 +3525,9 @@
       <c r="L75" t="n">
         <v>1.019171</v>
       </c>
+      <c r="M75" t="n">
+        <v>0.8439759999999999</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -3456,9 +3535,7 @@
           <t>印表機、傳真機、掃瞄器、多功能事務機、投影機</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>28059.702247</v>
-      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
         <v>28012.410239</v>
       </c>
@@ -3489,6 +3566,9 @@
       <c r="L76" t="n">
         <v>25254.676145</v>
       </c>
+      <c r="M76" t="n">
+        <v>17026.134888</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -3496,9 +3576,7 @@
           <t>原料</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>23.904539</v>
-      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
         <v>13.352082</v>
       </c>
@@ -3529,6 +3607,9 @@
       <c r="L77" t="n">
         <v>7.964373</v>
       </c>
+      <c r="M77" t="n">
+        <v>10.405875</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -3536,9 +3617,7 @@
           <t>原材料</t>
         </is>
       </c>
-      <c r="B78" t="n">
-        <v>15208.338555</v>
-      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
         <v>7874.262525</v>
       </c>
@@ -3569,6 +3648,9 @@
       <c r="L78" t="n">
         <v>10763.531786</v>
       </c>
+      <c r="M78" t="n">
+        <v>8873.126963999999</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -3576,9 +3658,7 @@
           <t>原物料</t>
         </is>
       </c>
-      <c r="B79" t="n">
-        <v>1129.973396</v>
-      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
         <v>973.694196</v>
       </c>
@@ -3609,6 +3689,9 @@
       <c r="L79" t="n">
         <v>803.768674</v>
       </c>
+      <c r="M79" t="n">
+        <v>668.339252</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -3616,9 +3699,7 @@
           <t>商業應用</t>
         </is>
       </c>
-      <c r="B80" t="n">
-        <v>456.866254</v>
-      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
         <v>330.400525</v>
       </c>
@@ -3649,6 +3730,9 @@
       <c r="L80" t="n">
         <v>429.367816</v>
       </c>
+      <c r="M80" t="n">
+        <v>290.79284</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -3656,9 +3740,7 @@
           <t>垂直應用方案</t>
         </is>
       </c>
-      <c r="B81" t="n">
-        <v>0.756432</v>
-      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
         <v>2.71476</v>
       </c>
@@ -3689,6 +3771,9 @@
       <c r="L81" t="n">
         <v>0.818609</v>
       </c>
+      <c r="M81" t="n">
+        <v>0.438579</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -3696,9 +3781,7 @@
           <t>基板</t>
         </is>
       </c>
-      <c r="B82" t="n">
-        <v>15092.240235</v>
-      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
         <v>21811.154994</v>
       </c>
@@ -3729,6 +3812,9 @@
       <c r="L82" t="n">
         <v>12073.637318</v>
       </c>
+      <c r="M82" t="n">
+        <v>18671.239998</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -3736,9 +3822,7 @@
           <t>基板組裝加工及相關製造</t>
         </is>
       </c>
-      <c r="B83" t="n">
-        <v>20315.716698</v>
-      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
         <v>15272.630022</v>
       </c>
@@ -3769,6 +3853,9 @@
       <c r="L83" t="n">
         <v>25846.735158</v>
       </c>
+      <c r="M83" t="n">
+        <v>29895.903815</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -3776,9 +3863,7 @@
           <t>基礎工程</t>
         </is>
       </c>
-      <c r="B84" t="n">
-        <v>123.037318</v>
-      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
         <v>93.551508</v>
       </c>
@@ -3809,6 +3894,9 @@
       <c r="L84" t="n">
         <v>81.39923</v>
       </c>
+      <c r="M84" t="n">
+        <v>67.84872</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -3816,9 +3904,7 @@
           <t>塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="B85" t="n">
-        <v>42.712907</v>
-      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
         <v>48.324991</v>
       </c>
@@ -3849,6 +3935,9 @@
       <c r="L85" t="n">
         <v>69.225334</v>
       </c>
+      <c r="M85" t="n">
+        <v>34.919916</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -3856,38 +3945,39 @@
           <t>塑膠/金屬機殼</t>
         </is>
       </c>
-      <c r="B86" t="n">
-        <v>779.7610089999999</v>
-      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>534.342192</v>
+        <v>534.37532</v>
       </c>
       <c r="D86" t="n">
-        <v>418.567226</v>
+        <v>418.607786</v>
       </c>
       <c r="E86" t="n">
-        <v>332.045446</v>
+        <v>332.072715</v>
       </c>
       <c r="F86" t="n">
-        <v>316.596745</v>
+        <v>316.617831</v>
       </c>
       <c r="G86" t="n">
-        <v>263.589713</v>
+        <v>263.612002</v>
       </c>
       <c r="H86" t="n">
-        <v>349.214855</v>
+        <v>349.233161</v>
       </c>
       <c r="I86" t="n">
-        <v>319.733512</v>
+        <v>319.743707</v>
       </c>
       <c r="J86" t="n">
-        <v>510.897726</v>
+        <v>510.933589</v>
       </c>
       <c r="K86" t="n">
-        <v>400.700062</v>
+        <v>400.741068</v>
       </c>
       <c r="L86" t="n">
-        <v>342.983386</v>
+        <v>163.327007</v>
+      </c>
+      <c r="M86" t="n">
+        <v>71.128767</v>
       </c>
     </row>
     <row r="87">
@@ -3896,9 +3986,7 @@
           <t>塑膠材料</t>
         </is>
       </c>
-      <c r="B87" t="n">
-        <v>7434.378676</v>
-      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
         <v>3677.4244</v>
       </c>
@@ -3929,6 +4017,9 @@
       <c r="L87" t="n">
         <v>3986.982092</v>
       </c>
+      <c r="M87" t="n">
+        <v>5427.363896</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -3936,9 +4027,7 @@
           <t>塑膠框</t>
         </is>
       </c>
-      <c r="B88" t="n">
-        <v>5470.784751</v>
-      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
         <v>7742.038383</v>
       </c>
@@ -3969,6 +4058,9 @@
       <c r="L88" t="n">
         <v>1163.11061</v>
       </c>
+      <c r="M88" t="n">
+        <v>881.808991</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -3976,38 +4068,39 @@
           <t>塑膠製品</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>4404.307656</v>
-      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>3372.507916</v>
+        <v>3381.075316</v>
       </c>
       <c r="D89" t="n">
-        <v>3456.725133</v>
+        <v>3461.574756</v>
       </c>
       <c r="E89" t="n">
-        <v>4136.326706</v>
+        <v>4139.212197</v>
       </c>
       <c r="F89" t="n">
-        <v>4383.864738</v>
+        <v>4387.310369</v>
       </c>
       <c r="G89" t="n">
-        <v>8037.706226</v>
+        <v>8041.633375</v>
       </c>
       <c r="H89" t="n">
-        <v>17693.484045</v>
+        <v>17697.055228</v>
       </c>
       <c r="I89" t="n">
-        <v>11995.490385</v>
+        <v>12002.829735</v>
       </c>
       <c r="J89" t="n">
-        <v>9104.467406</v>
+        <v>9108.175635</v>
       </c>
       <c r="K89" t="n">
-        <v>7377.34557</v>
+        <v>7381.549742</v>
       </c>
       <c r="L89" t="n">
-        <v>5079.522501</v>
+        <v>5088.530042</v>
+      </c>
+      <c r="M89" t="n">
+        <v>3271.590657</v>
       </c>
     </row>
     <row r="90">
@@ -4016,9 +4109,7 @@
           <t>塔架</t>
         </is>
       </c>
-      <c r="B90" t="n">
-        <v>385.397022</v>
-      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
         <v>297.240328</v>
       </c>
@@ -4049,6 +4140,9 @@
       <c r="L90" t="n">
         <v>252.391267</v>
       </c>
+      <c r="M90" t="n">
+        <v>206.970962</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -4056,9 +4150,7 @@
           <t>多功能視訊卡</t>
         </is>
       </c>
-      <c r="B91" t="n">
-        <v>38.970276</v>
-      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
         <v>25.496627</v>
       </c>
@@ -4089,6 +4181,9 @@
       <c r="L91" t="n">
         <v>27.934521</v>
       </c>
+      <c r="M91" t="n">
+        <v>18.50839</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -4096,38 +4191,39 @@
           <t>大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>81005.564803</v>
-      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>78856.478791</v>
+        <v>78856.511919</v>
       </c>
       <c r="D92" t="n">
-        <v>97567.700706</v>
+        <v>97567.741266</v>
       </c>
       <c r="E92" t="n">
-        <v>100250.305086</v>
+        <v>100250.332355</v>
       </c>
       <c r="F92" t="n">
-        <v>82117.18085600001</v>
+        <v>82117.201942</v>
       </c>
       <c r="G92" t="n">
-        <v>57036.435752</v>
+        <v>57036.458041</v>
       </c>
       <c r="H92" t="n">
-        <v>50693.398281</v>
+        <v>50693.416587</v>
       </c>
       <c r="I92" t="n">
-        <v>70804.304153</v>
+        <v>70804.314348</v>
       </c>
       <c r="J92" t="n">
-        <v>72346.00616</v>
+        <v>72346.042023</v>
       </c>
       <c r="K92" t="n">
-        <v>74072.31755000001</v>
+        <v>74072.35855600001</v>
       </c>
       <c r="L92" t="n">
-        <v>58838.204083</v>
+        <v>58838.490702</v>
+      </c>
+      <c r="M92" t="n">
+        <v>55332.389235</v>
       </c>
     </row>
     <row r="93">
@@ -4136,9 +4232,7 @@
           <t>天然瓦斯供應</t>
         </is>
       </c>
-      <c r="B93" t="n">
-        <v>10.409536</v>
-      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
         <v>5.696466</v>
       </c>
@@ -4169,6 +4263,9 @@
       <c r="L93" t="n">
         <v>6.04139</v>
       </c>
+      <c r="M93" t="n">
+        <v>5.675508</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -4176,9 +4273,7 @@
           <t>天然纖維產品(例如純棉、純羊毛等)</t>
         </is>
       </c>
-      <c r="B94" t="n">
-        <v>1.321753</v>
-      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
         <v>0.57272</v>
       </c>
@@ -4209,6 +4304,9 @@
       <c r="L94" t="n">
         <v>1.350904</v>
       </c>
+      <c r="M94" t="n">
+        <v>0.394212</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -4216,9 +4314,7 @@
           <t>太陽能發電設備/系統及系統工程</t>
         </is>
       </c>
-      <c r="B95" t="n">
-        <v>35155.483226</v>
-      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
         <v>34310.036107</v>
       </c>
@@ -4247,7 +4343,10 @@
         <v>39659.490035</v>
       </c>
       <c r="L95" t="n">
-        <v>28935.622095</v>
+        <v>28755.911135</v>
+      </c>
+      <c r="M95" t="n">
+        <v>26450.143996</v>
       </c>
     </row>
     <row r="96">
@@ -4256,9 +4355,7 @@
           <t>太陽能電廠</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>25298.942942</v>
-      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
         <v>26056.306342</v>
       </c>
@@ -4289,6 +4386,9 @@
       <c r="L96" t="n">
         <v>28586.215829</v>
       </c>
+      <c r="M96" t="n">
+        <v>25858.710798</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -4296,9 +4396,7 @@
           <t>太陽能電池</t>
         </is>
       </c>
-      <c r="B97" t="n">
-        <v>5033.967052</v>
-      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
         <v>6197.984133</v>
       </c>
@@ -4329,6 +4427,9 @@
       <c r="L97" t="n">
         <v>10283.692867</v>
       </c>
+      <c r="M97" t="n">
+        <v>10073.837106</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -4336,9 +4437,7 @@
           <t>太陽能電池模組</t>
         </is>
       </c>
-      <c r="B98" t="n">
-        <v>5527.741924</v>
-      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
         <v>6646.360161</v>
       </c>
@@ -4369,6 +4468,9 @@
       <c r="L98" t="n">
         <v>10656.50116</v>
       </c>
+      <c r="M98" t="n">
+        <v>10404.597238</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -4376,9 +4478,7 @@
           <t>娛樂服務業</t>
         </is>
       </c>
-      <c r="B99" t="n">
-        <v>81.56818</v>
-      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
         <v>71.732596</v>
       </c>
@@ -4409,6 +4509,9 @@
       <c r="L99" t="n">
         <v>58.177966</v>
       </c>
+      <c r="M99" t="n">
+        <v>47.668423</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -4416,9 +4519,7 @@
           <t>媒體推廣</t>
         </is>
       </c>
-      <c r="B100" t="n">
-        <v>30.996195</v>
-      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
         <v>23.262423</v>
       </c>
@@ -4449,6 +4550,9 @@
       <c r="L100" t="n">
         <v>32.775686</v>
       </c>
+      <c r="M100" t="n">
+        <v>25.805276</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -4456,9 +4560,7 @@
           <t>安全營運與事件回應</t>
         </is>
       </c>
-      <c r="B101" t="n">
-        <v>252.685573</v>
-      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
         <v>170.29867</v>
       </c>
@@ -4489,6 +4591,9 @@
       <c r="L101" t="n">
         <v>154.650078</v>
       </c>
+      <c r="M101" t="n">
+        <v>139.848324</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -4496,9 +4601,7 @@
           <t>安全監控系統</t>
         </is>
       </c>
-      <c r="B102" t="n">
-        <v>38119.054282</v>
-      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
         <v>39252.121355</v>
       </c>
@@ -4529,6 +4632,9 @@
       <c r="L102" t="n">
         <v>35668.912728</v>
       </c>
+      <c r="M102" t="n">
+        <v>28827.42482</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -4536,9 +4642,7 @@
           <t>家庭用紙</t>
         </is>
       </c>
-      <c r="B103" t="n">
-        <v>52.423094</v>
-      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
         <v>55.308211</v>
       </c>
@@ -4569,6 +4673,9 @@
       <c r="L103" t="n">
         <v>44.593953</v>
       </c>
+      <c r="M103" t="n">
+        <v>37.959684</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -4576,9 +4683,7 @@
           <t>封裝/模組</t>
         </is>
       </c>
-      <c r="B104" t="n">
-        <v>9167.590768</v>
-      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
         <v>11846.883493</v>
       </c>
@@ -4609,6 +4714,9 @@
       <c r="L104" t="n">
         <v>5697.702176</v>
       </c>
+      <c r="M104" t="n">
+        <v>6284.695592</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -4616,9 +4724,7 @@
           <t>專用機械(如紡織成衣生產用機械、食品飲料生產用機械、農林用機械等)</t>
         </is>
       </c>
-      <c r="B105" t="n">
-        <v>16541.257319</v>
-      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
         <v>11836.290906</v>
       </c>
@@ -4649,6 +4755,9 @@
       <c r="L105" t="n">
         <v>16573.58454</v>
       </c>
+      <c r="M105" t="n">
+        <v>14326.504162</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -4656,9 +4765,7 @@
           <t>導線架</t>
         </is>
       </c>
-      <c r="B106" t="n">
-        <v>4630.457194</v>
-      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
         <v>4569.407042</v>
       </c>
@@ -4689,6 +4796,9 @@
       <c r="L106" t="n">
         <v>6645.101739</v>
       </c>
+      <c r="M106" t="n">
+        <v>10087.56711</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -4696,9 +4806,7 @@
           <t>導航定位</t>
         </is>
       </c>
-      <c r="B107" t="n">
-        <v>30.996438</v>
-      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
         <v>23.262675</v>
       </c>
@@ -4729,6 +4837,9 @@
       <c r="L107" t="n">
         <v>32.776186</v>
       </c>
+      <c r="M107" t="n">
+        <v>25.80542</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -4736,9 +4847,7 @@
           <t>工業型機器人</t>
         </is>
       </c>
-      <c r="B108" t="n">
-        <v>2983.287043</v>
-      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
         <v>1938.243632</v>
       </c>
@@ -4769,6 +4878,9 @@
       <c r="L108" t="n">
         <v>2021.297564</v>
       </c>
+      <c r="M108" t="n">
+        <v>1142.458594</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -4776,9 +4888,7 @@
           <t>工業用紙</t>
         </is>
       </c>
-      <c r="B109" t="n">
-        <v>90.38271899999999</v>
-      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
         <v>62.798605</v>
       </c>
@@ -4809,6 +4919,9 @@
       <c r="L109" t="n">
         <v>79.84119800000001</v>
       </c>
+      <c r="M109" t="n">
+        <v>44.865708</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -4816,9 +4929,7 @@
           <t>工業用設備</t>
         </is>
       </c>
-      <c r="B110" t="n">
-        <v>1.145416</v>
-      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
         <v>0.5793199999999999</v>
       </c>
@@ -4849,6 +4960,9 @@
       <c r="L110" t="n">
         <v>0.842079</v>
       </c>
+      <c r="M110" t="n">
+        <v>1.936195</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -4856,9 +4970,7 @@
           <t>工業電腦</t>
         </is>
       </c>
-      <c r="B111" t="n">
-        <v>7809.68687</v>
-      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
         <v>8099.620694</v>
       </c>
@@ -4889,6 +5001,9 @@
       <c r="L111" t="n">
         <v>6981.671158</v>
       </c>
+      <c r="M111" t="n">
+        <v>5593.822</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -4896,9 +5011,7 @@
           <t>工程承攬</t>
         </is>
       </c>
-      <c r="B112" t="n">
-        <v>1188.200519</v>
-      </c>
+      <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
         <v>847.799357</v>
       </c>
@@ -4929,6 +5042,9 @@
       <c r="L112" t="n">
         <v>757.787735</v>
       </c>
+      <c r="M112" t="n">
+        <v>514.201599</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -4936,9 +5052,7 @@
           <t>工程設計</t>
         </is>
       </c>
-      <c r="B113" t="n">
-        <v>219.399861</v>
-      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
         <v>191.528544</v>
       </c>
@@ -4969,6 +5083,9 @@
       <c r="L113" t="n">
         <v>250.752473</v>
       </c>
+      <c r="M113" t="n">
+        <v>358.070407</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -4976,9 +5093,7 @@
           <t>工藝產業</t>
         </is>
       </c>
-      <c r="B114" t="n">
-        <v>0.003287</v>
-      </c>
+      <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
         <v>0.002299</v>
       </c>
@@ -5009,6 +5124,9 @@
       <c r="L114" t="n">
         <v>0.001596</v>
       </c>
+      <c r="M114" t="n">
+        <v>0.000904</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -5016,9 +5134,7 @@
           <t>幹細胞收集儲存</t>
         </is>
       </c>
-      <c r="B115" t="n">
-        <v>26.672685</v>
-      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
         <v>13.458433</v>
       </c>
@@ -5049,6 +5165,9 @@
       <c r="L115" t="n">
         <v>8.807117999999999</v>
       </c>
+      <c r="M115" t="n">
+        <v>16.07497</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -5056,9 +5175,7 @@
           <t>幹細胞開發</t>
         </is>
       </c>
-      <c r="B116" t="n">
-        <v>26.672685</v>
-      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
         <v>13.458433</v>
       </c>
@@ -5089,6 +5206,9 @@
       <c r="L116" t="n">
         <v>8.807117999999999</v>
       </c>
+      <c r="M116" t="n">
+        <v>16.07497</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -5096,9 +5216,7 @@
           <t>底層平台</t>
         </is>
       </c>
-      <c r="B117" t="n">
-        <v>30.996195</v>
-      </c>
+      <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
         <v>23.262423</v>
       </c>
@@ -5129,6 +5247,9 @@
       <c r="L117" t="n">
         <v>32.775686</v>
       </c>
+      <c r="M117" t="n">
+        <v>25.805276</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -5136,9 +5257,7 @@
           <t>店點開設管理</t>
         </is>
       </c>
-      <c r="B118" t="n">
-        <v>108.651352</v>
-      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
         <v>102.151773</v>
       </c>
@@ -5169,6 +5288,9 @@
       <c r="L118" t="n">
         <v>88.040333</v>
       </c>
+      <c r="M118" t="n">
+        <v>46.292824</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -5176,9 +5298,7 @@
           <t>廣播電視/電影產業</t>
         </is>
       </c>
-      <c r="B119" t="n">
-        <v>450.711786</v>
-      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
         <v>380.062004</v>
       </c>
@@ -5209,6 +5329,9 @@
       <c r="L119" t="n">
         <v>448.8946516666667</v>
       </c>
+      <c r="M119" t="n">
+        <v>281.9185366666667</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -5216,9 +5339,7 @@
           <t>建材原料</t>
         </is>
       </c>
-      <c r="B120" t="n">
-        <v>8865.385299</v>
-      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
         <v>23757.004645</v>
       </c>
@@ -5249,6 +5370,9 @@
       <c r="L120" t="n">
         <v>2000.900158</v>
       </c>
+      <c r="M120" t="n">
+        <v>2447.470267</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -5256,9 +5380,7 @@
           <t>建設業</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>12907.521231</v>
-      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
         <v>15217.457664</v>
       </c>
@@ -5287,7 +5409,10 @@
         <v>20030.068914</v>
       </c>
       <c r="L121" t="n">
-        <v>10246.312039</v>
+        <v>10244.104142</v>
+      </c>
+      <c r="M121" t="n">
+        <v>10407.31914225</v>
       </c>
     </row>
     <row r="122">
@@ -5296,9 +5421,7 @@
           <t>引擎蓋</t>
         </is>
       </c>
-      <c r="B122" t="n">
-        <v>895.6701</v>
-      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
         <v>618.11849</v>
       </c>
@@ -5329,6 +5452,9 @@
       <c r="L122" t="n">
         <v>215.408461</v>
       </c>
+      <c r="M122" t="n">
+        <v>262.833123</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -5336,9 +5462,7 @@
           <t>影像遙測</t>
         </is>
       </c>
-      <c r="B123" t="n">
-        <v>30.996195</v>
-      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
         <v>23.262423</v>
       </c>
@@ -5369,6 +5493,9 @@
       <c r="L123" t="n">
         <v>32.775686</v>
       </c>
+      <c r="M123" t="n">
+        <v>25.805276</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -5376,9 +5503,7 @@
           <t>微處理器</t>
         </is>
       </c>
-      <c r="B124" t="n">
-        <v>0.483932</v>
-      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
         <v>0.244448</v>
       </c>
@@ -5409,6 +5534,9 @@
       <c r="L124" t="n">
         <v>3.9945</v>
       </c>
+      <c r="M124" t="n">
+        <v>0.525842</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -5416,9 +5544,7 @@
           <t>感測器</t>
         </is>
       </c>
-      <c r="B125" t="n">
-        <v>0.020915</v>
-      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
         <v>0.012743</v>
       </c>
@@ -5449,6 +5575,9 @@
       <c r="L125" t="n">
         <v>0.007063</v>
       </c>
+      <c r="M125" t="n">
+        <v>0.010031</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -5456,9 +5585,7 @@
           <t>感測器/模組</t>
         </is>
       </c>
-      <c r="B126" t="n">
-        <v>2789.849639</v>
-      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
         <v>2666.511662</v>
       </c>
@@ -5489,6 +5616,9 @@
       <c r="L126" t="n">
         <v>3745.726906</v>
       </c>
+      <c r="M126" t="n">
+        <v>4661.372136</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -5496,9 +5626,7 @@
           <t>感測裝置</t>
         </is>
       </c>
-      <c r="B127" t="n">
-        <v>141.365098</v>
-      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
         <v>195.592369</v>
       </c>
@@ -5529,6 +5657,9 @@
       <c r="L127" t="n">
         <v>64.34693900000001</v>
       </c>
+      <c r="M127" t="n">
+        <v>52.122358</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -5536,9 +5667,7 @@
           <t>應用/系統軟體設計開發</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>20085.560227</v>
-      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
         <v>16354.474866</v>
       </c>
@@ -5569,6 +5698,9 @@
       <c r="L128" t="n">
         <v>17419.843036</v>
       </c>
+      <c r="M128" t="n">
+        <v>14761.523537</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -5576,9 +5708,7 @@
           <t>應用軟體</t>
         </is>
       </c>
-      <c r="B129" t="n">
-        <v>503.046916</v>
-      </c>
+      <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
         <v>354.697267</v>
       </c>
@@ -5609,6 +5739,9 @@
       <c r="L129" t="n">
         <v>339.9422463333333</v>
       </c>
+      <c r="M129" t="n">
+        <v>268.030191</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -5616,9 +5749,7 @@
           <t>應用軟體/內容</t>
         </is>
       </c>
-      <c r="B130" t="n">
-        <v>341.138424</v>
-      </c>
+      <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
         <v>278.311185</v>
       </c>
@@ -5649,6 +5780,9 @@
       <c r="L130" t="n">
         <v>363.538041</v>
       </c>
+      <c r="M130" t="n">
+        <v>236.964239</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -5656,9 +5790,7 @@
           <t>成衣及其它家居紡織類品</t>
         </is>
       </c>
-      <c r="B131" t="n">
-        <v>1350.364563</v>
-      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
         <v>984.12505</v>
       </c>
@@ -5689,6 +5821,9 @@
       <c r="L131" t="n">
         <v>748.127598</v>
       </c>
+      <c r="M131" t="n">
+        <v>754.0771580000001</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -5696,9 +5831,7 @@
           <t>手工具機</t>
         </is>
       </c>
-      <c r="B132" t="n">
-        <v>532.605487</v>
-      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
         <v>311.076449</v>
       </c>
@@ -5729,6 +5862,9 @@
       <c r="L132" t="n">
         <v>247.843054</v>
       </c>
+      <c r="M132" t="n">
+        <v>148.504434</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -5736,9 +5872,7 @@
           <t>技術標準/聯盟</t>
         </is>
       </c>
-      <c r="B133" t="n">
-        <v>332.115053</v>
-      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
         <v>270.008902</v>
       </c>
@@ -5769,6 +5903,9 @@
       <c r="L133" t="n">
         <v>356.255041</v>
       </c>
+      <c r="M133" t="n">
+        <v>230.871578</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -5776,9 +5913,7 @@
           <t>接著劑(合成樹脂)</t>
         </is>
       </c>
-      <c r="B134" t="n">
-        <v>7690.133355</v>
-      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
         <v>4865.282096</v>
       </c>
@@ -5809,6 +5944,9 @@
       <c r="L134" t="n">
         <v>2917.662774</v>
       </c>
+      <c r="M134" t="n">
+        <v>2390.319473</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -5816,9 +5954,7 @@
           <t>控制IC</t>
         </is>
       </c>
-      <c r="B135" t="n">
-        <v>211.753002</v>
-      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
         <v>217.715227</v>
       </c>
@@ -5849,6 +5985,9 @@
       <c r="L135" t="n">
         <v>189.389523</v>
       </c>
+      <c r="M135" t="n">
+        <v>183.722692</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
@@ -5856,9 +5995,7 @@
           <t>控制器</t>
         </is>
       </c>
-      <c r="B136" t="n">
-        <v>0.183536</v>
-      </c>
+      <c r="B136" t="inlineStr"/>
       <c r="C136" t="n">
         <v>0.121299</v>
       </c>
@@ -5889,6 +6026,9 @@
       <c r="L136" t="n">
         <v>0.9125799999999999</v>
       </c>
+      <c r="M136" t="n">
+        <v>0.320985</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
@@ -5896,9 +6036,7 @@
           <t>擴散膜、增亮膜、導光板</t>
         </is>
       </c>
-      <c r="B137" t="n">
-        <v>11278.853082</v>
-      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
         <v>11792.068564</v>
       </c>
@@ -5929,6 +6067,9 @@
       <c r="L137" t="n">
         <v>3484.621372</v>
       </c>
+      <c r="M137" t="n">
+        <v>2405.006668</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
@@ -5936,9 +6077,7 @@
           <t>支付</t>
         </is>
       </c>
-      <c r="B138" t="n">
-        <v>114.927609</v>
-      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
         <v>156.362261</v>
       </c>
@@ -5969,6 +6108,9 @@
       <c r="L138" t="n">
         <v>137.05258</v>
       </c>
+      <c r="M138" t="n">
+        <v>120.266583</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
@@ -5976,9 +6118,7 @@
           <t>支援服務</t>
         </is>
       </c>
-      <c r="B139" t="n">
-        <v>7.808222</v>
-      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
         <v>7.363299</v>
       </c>
@@ -6009,6 +6149,9 @@
       <c r="L139" t="n">
         <v>5.850662</v>
       </c>
+      <c r="M139" t="n">
+        <v>4.508811</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
@@ -6016,9 +6159,7 @@
           <t>散熱片、風扇馬達、散熱模組</t>
         </is>
       </c>
-      <c r="B140" t="n">
-        <v>29352.744744</v>
-      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
         <v>16579.223072</v>
       </c>
@@ -6049,6 +6190,9 @@
       <c r="L140" t="n">
         <v>27886.330068</v>
       </c>
+      <c r="M140" t="n">
+        <v>39054.270745</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
@@ -6056,9 +6200,7 @@
           <t>散裝航運</t>
         </is>
       </c>
-      <c r="B141" t="n">
-        <v>1049.446795</v>
-      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
         <v>1056.995175</v>
       </c>
@@ -6089,6 +6231,9 @@
       <c r="L141" t="n">
         <v>1936.664031</v>
       </c>
+      <c r="M141" t="n">
+        <v>915.238212</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
@@ -6096,9 +6241,7 @@
           <t>整車組裝、修理及技術服務</t>
         </is>
       </c>
-      <c r="B142" t="n">
-        <v>540.208242</v>
-      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
         <v>354.211393</v>
       </c>
@@ -6129,6 +6272,9 @@
       <c r="L142" t="n">
         <v>281.092618</v>
       </c>
+      <c r="M142" t="n">
+        <v>324.799712</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
@@ -6136,9 +6282,7 @@
           <t>整體解決方案</t>
         </is>
       </c>
-      <c r="B143" t="n">
-        <v>0.835033</v>
-      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
         <v>2.951202</v>
       </c>
@@ -6169,6 +6313,9 @@
       <c r="L143" t="n">
         <v>0.965817</v>
       </c>
+      <c r="M143" t="n">
+        <v>0.539083</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
@@ -6176,9 +6323,7 @@
           <t>數位內容</t>
         </is>
       </c>
-      <c r="B144" t="n">
-        <v>332.115098</v>
-      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
         <v>270.00898</v>
       </c>
@@ -6209,6 +6354,9 @@
       <c r="L144" t="n">
         <v>356.255194</v>
       </c>
+      <c r="M144" t="n">
+        <v>230.8716</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
@@ -6216,9 +6364,7 @@
           <t>數位內容產業</t>
         </is>
       </c>
-      <c r="B145" t="n">
-        <v>333.595417</v>
-      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
         <v>271.122711</v>
       </c>
@@ -6249,6 +6395,9 @@
       <c r="L145" t="n">
         <v>357.849869</v>
       </c>
+      <c r="M145" t="n">
+        <v>232.5806553333333</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
@@ -6256,9 +6405,7 @@
           <t>數位身分</t>
         </is>
       </c>
-      <c r="B146" t="n">
-        <v>124.804411</v>
-      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
         <v>60.547553</v>
       </c>
@@ -6289,6 +6436,9 @@
       <c r="L146" t="n">
         <v>73.126947</v>
       </c>
+      <c r="M146" t="n">
+        <v>59.934614</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
@@ -6296,9 +6446,7 @@
           <t>數位銀行</t>
         </is>
       </c>
-      <c r="B147" t="n">
-        <v>38.964419</v>
-      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
         <v>30.685261</v>
       </c>
@@ -6329,6 +6477,9 @@
       <c r="L147" t="n">
         <v>38.698824</v>
       </c>
+      <c r="M147" t="n">
+        <v>30.359963</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
@@ -6336,9 +6487,7 @@
           <t>數據分析</t>
         </is>
       </c>
-      <c r="B148" t="n">
-        <v>132.645838</v>
-      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
         <v>67.924847</v>
       </c>
@@ -6369,6 +6518,9 @@
       <c r="L148" t="n">
         <v>78.99762699999999</v>
       </c>
+      <c r="M148" t="n">
+        <v>64.46114300000001</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
@@ -6376,9 +6528,7 @@
           <t>文化印刷業</t>
         </is>
       </c>
-      <c r="B149" t="n">
-        <v>245.160573</v>
-      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
         <v>87.543212</v>
       </c>
@@ -6409,6 +6559,9 @@
       <c r="L149" t="n">
         <v>600.91730025</v>
       </c>
+      <c r="M149" t="n">
+        <v>170.294588</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -6416,9 +6569,7 @@
           <t>文化用紙</t>
         </is>
       </c>
-      <c r="B150" t="n">
-        <v>102.623961</v>
-      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
         <v>82.03993199999999</v>
       </c>
@@ -6449,6 +6600,9 @@
       <c r="L150" t="n">
         <v>66.08777000000001</v>
       </c>
+      <c r="M150" t="n">
+        <v>51.640512</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
@@ -6456,9 +6610,7 @@
           <t>旅遊服務業</t>
         </is>
       </c>
-      <c r="B151" t="n">
-        <v>130.934386</v>
-      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
         <v>93.738489</v>
       </c>
@@ -6489,6 +6641,9 @@
       <c r="L151" t="n">
         <v>103.073733</v>
       </c>
+      <c r="M151" t="n">
+        <v>71.11221</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
@@ -6496,9 +6651,7 @@
           <t>旅館服務業</t>
         </is>
       </c>
-      <c r="B152" t="n">
-        <v>95.489605</v>
-      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
         <v>75.28268975</v>
       </c>
@@ -6529,6 +6682,9 @@
       <c r="L152" t="n">
         <v>54.78402575</v>
       </c>
+      <c r="M152" t="n">
+        <v>45.17676</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
@@ -6536,9 +6692,7 @@
           <t>晶片組</t>
         </is>
       </c>
-      <c r="B153" t="n">
-        <v>457.7083</v>
-      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
         <v>292.522339</v>
       </c>
@@ -6569,6 +6723,9 @@
       <c r="L153" t="n">
         <v>360.353274</v>
       </c>
+      <c r="M153" t="n">
+        <v>613.106529</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
@@ -6576,9 +6733,7 @@
           <t>智慧設備</t>
         </is>
       </c>
-      <c r="B154" t="n">
-        <v>17388.800972</v>
-      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
         <v>10797.87725</v>
       </c>
@@ -6609,6 +6764,9 @@
       <c r="L154" t="n">
         <v>18530.71278333333</v>
       </c>
+      <c r="M154" t="n">
+        <v>15644.036932</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
@@ -6616,9 +6774,7 @@
           <t>有線通訊設備(如電話機、傳真機)</t>
         </is>
       </c>
-      <c r="B155" t="n">
-        <v>5307.879531</v>
-      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="n">
         <v>8095.598378</v>
       </c>
@@ -6649,6 +6805,9 @@
       <c r="L155" t="n">
         <v>1046.418287</v>
       </c>
+      <c r="M155" t="n">
+        <v>749.378102</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
@@ -6656,9 +6815,7 @@
           <t>期貨業</t>
         </is>
       </c>
-      <c r="B156" t="n">
-        <v>15.120137</v>
-      </c>
+      <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
         <v>16.118956</v>
       </c>
@@ -6689,6 +6846,9 @@
       <c r="L156" t="n">
         <v>22.272824</v>
       </c>
+      <c r="M156" t="n">
+        <v>12.84421</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
@@ -6696,9 +6856,7 @@
           <t>材料</t>
         </is>
       </c>
-      <c r="B157" t="n">
-        <v>13567.848348</v>
-      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
         <v>7376.934616</v>
       </c>
@@ -6729,6 +6887,9 @@
       <c r="L157" t="n">
         <v>6359.599714</v>
       </c>
+      <c r="M157" t="n">
+        <v>7440.632202</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
@@ -6736,9 +6897,7 @@
           <t>染整</t>
         </is>
       </c>
-      <c r="B158" t="n">
-        <v>29619.73714733333</v>
-      </c>
+      <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
         <v>18627.47118733333</v>
       </c>
@@ -6769,6 +6928,9 @@
       <c r="L158" t="n">
         <v>6878.110793666667</v>
       </c>
+      <c r="M158" t="n">
+        <v>5866.251966</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
@@ -6776,9 +6938,7 @@
           <t>桌上型電腦</t>
         </is>
       </c>
-      <c r="B159" t="n">
-        <v>55468.557848</v>
-      </c>
+      <c r="B159" t="inlineStr"/>
       <c r="C159" t="n">
         <v>48044.472821</v>
       </c>
@@ -6809,6 +6969,9 @@
       <c r="L159" t="n">
         <v>45106.192003</v>
       </c>
+      <c r="M159" t="n">
+        <v>33534.700988</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
@@ -6816,9 +6979,7 @@
           <t>棒鋼盤元(捲狀條鋼)</t>
         </is>
       </c>
-      <c r="B160" t="n">
-        <v>1569.7754725</v>
-      </c>
+      <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
         <v>1201.147451</v>
       </c>
@@ -6849,6 +7010,9 @@
       <c r="L160" t="n">
         <v>4206.30041</v>
       </c>
+      <c r="M160" t="n">
+        <v>2204.48563725</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
@@ -6856,9 +7020,7 @@
           <t>模具</t>
         </is>
       </c>
-      <c r="B161" t="n">
-        <v>415.90735</v>
-      </c>
+      <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
         <v>542.589248</v>
       </c>
@@ -6889,6 +7051,9 @@
       <c r="L161" t="n">
         <v>460.19671</v>
       </c>
+      <c r="M161" t="n">
+        <v>472.384795</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
@@ -6896,9 +7061,7 @@
           <t>樹酯</t>
         </is>
       </c>
-      <c r="B162" t="n">
-        <v>477.253821</v>
-      </c>
+      <c r="B162" t="inlineStr"/>
       <c r="C162" t="n">
         <v>242.419267</v>
       </c>
@@ -6929,6 +7092,9 @@
       <c r="L162" t="n">
         <v>136.326798</v>
       </c>
+      <c r="M162" t="n">
+        <v>93.80111100000001</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
@@ -6936,9 +7102,7 @@
           <t>機器學習</t>
         </is>
       </c>
-      <c r="B163" t="n">
-        <v>15742.785283</v>
-      </c>
+      <c r="B163" t="inlineStr"/>
       <c r="C163" t="n">
         <v>9371.788608000001</v>
       </c>
@@ -6969,6 +7133,9 @@
       <c r="L163" t="n">
         <v>16915.37491633333</v>
       </c>
+      <c r="M163" t="n">
+        <v>14509.308014</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
@@ -6976,9 +7143,7 @@
           <t>機械設備之沖壓零組件</t>
         </is>
       </c>
-      <c r="B164" t="n">
-        <v>33318.313405</v>
-      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
         <v>25235.144516</v>
       </c>
@@ -7009,6 +7174,9 @@
       <c r="L164" t="n">
         <v>5870.917469</v>
       </c>
+      <c r="M164" t="n">
+        <v>5254.566698</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
@@ -7016,9 +7184,7 @@
           <t>機構樞紐</t>
         </is>
       </c>
-      <c r="B165" t="n">
-        <v>4191.612076</v>
-      </c>
+      <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
         <v>5214.742237</v>
       </c>
@@ -7049,6 +7215,9 @@
       <c r="L165" t="n">
         <v>3203.386858</v>
       </c>
+      <c r="M165" t="n">
+        <v>7097.824601</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
@@ -7056,38 +7225,39 @@
           <t>機殼</t>
         </is>
       </c>
-      <c r="B166" t="n">
-        <v>20582.941554</v>
-      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
-        <v>25186.310315</v>
+        <v>25186.343443</v>
       </c>
       <c r="D166" t="n">
-        <v>27974.274791</v>
+        <v>27974.315351</v>
       </c>
       <c r="E166" t="n">
-        <v>27726.605256</v>
+        <v>27726.632525</v>
       </c>
       <c r="F166" t="n">
-        <v>28879.789622</v>
+        <v>28879.810708</v>
       </c>
       <c r="G166" t="n">
-        <v>21730.572894</v>
+        <v>21730.595183</v>
       </c>
       <c r="H166" t="n">
-        <v>20913.521588</v>
+        <v>20913.539894</v>
       </c>
       <c r="I166" t="n">
-        <v>30163.99827</v>
+        <v>30164.008465</v>
       </c>
       <c r="J166" t="n">
-        <v>22254.718454</v>
+        <v>22254.754317</v>
       </c>
       <c r="K166" t="n">
-        <v>25015.735738</v>
+        <v>25015.776744</v>
       </c>
       <c r="L166" t="n">
-        <v>21558.463622</v>
+        <v>21558.518203</v>
+      </c>
+      <c r="M166" t="n">
+        <v>18187.560179</v>
       </c>
     </row>
     <row r="167">
@@ -7096,9 +7266,7 @@
           <t>機電工程</t>
         </is>
       </c>
-      <c r="B167" t="n">
-        <v>28538.766927</v>
-      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
         <v>24201.099254</v>
       </c>
@@ -7129,6 +7297,9 @@
       <c r="L167" t="n">
         <v>20271.860825</v>
       </c>
+      <c r="M167" t="n">
+        <v>16817.717093</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
@@ -7136,9 +7307,7 @@
           <t>機電系統工程</t>
         </is>
       </c>
-      <c r="B168" t="n">
-        <v>31538.300209</v>
-      </c>
+      <c r="B168" t="inlineStr"/>
       <c r="C168" t="n">
         <v>37359.657291</v>
       </c>
@@ -7169,6 +7338,9 @@
       <c r="L168" t="n">
         <v>10311.743967</v>
       </c>
+      <c r="M168" t="n">
+        <v>11455.637329</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
@@ -7176,9 +7348,7 @@
           <t>橡膠製品</t>
         </is>
       </c>
-      <c r="B169" t="n">
-        <v>560.869042</v>
-      </c>
+      <c r="B169" t="inlineStr"/>
       <c r="C169" t="n">
         <v>481.635466</v>
       </c>
@@ -7209,6 +7379,9 @@
       <c r="L169" t="n">
         <v>424.916001</v>
       </c>
+      <c r="M169" t="n">
+        <v>476.855958</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
@@ -7216,9 +7389,7 @@
           <t>水泥成品</t>
         </is>
       </c>
-      <c r="B170" t="n">
-        <v>2126.73069</v>
-      </c>
+      <c r="B170" t="inlineStr"/>
       <c r="C170" t="n">
         <v>1457.319182</v>
       </c>
@@ -7249,6 +7420,9 @@
       <c r="L170" t="n">
         <v>1281.962524</v>
       </c>
+      <c r="M170" t="n">
+        <v>877.560384</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
@@ -7256,9 +7430,7 @@
           <t>水泥熟料</t>
         </is>
       </c>
-      <c r="B171" t="n">
-        <v>2476.059415</v>
-      </c>
+      <c r="B171" t="inlineStr"/>
       <c r="C171" t="n">
         <v>1961.118883</v>
       </c>
@@ -7289,6 +7461,9 @@
       <c r="L171" t="n">
         <v>1614.196619</v>
       </c>
+      <c r="M171" t="n">
+        <v>1095.935686</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
@@ -7296,9 +7471,7 @@
           <t>水泥生料</t>
         </is>
       </c>
-      <c r="B172" t="n">
-        <v>2104.707862</v>
-      </c>
+      <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
         <v>1442.740303</v>
       </c>
@@ -7329,6 +7502,9 @@
       <c r="L172" t="n">
         <v>1254.598794</v>
       </c>
+      <c r="M172" t="n">
+        <v>862.3374669999999</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
@@ -7336,9 +7512,7 @@
           <t>油空壓元件</t>
         </is>
       </c>
-      <c r="B173" t="n">
-        <v>864.3205</v>
-      </c>
+      <c r="B173" t="inlineStr"/>
       <c r="C173" t="n">
         <v>434.61868</v>
       </c>
@@ -7369,6 +7543,9 @@
       <c r="L173" t="n">
         <v>4309.02438475</v>
       </c>
+      <c r="M173" t="n">
+        <v>4217.690621</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
@@ -7376,9 +7553,7 @@
           <t>流行音樂及文化內容產業</t>
         </is>
       </c>
-      <c r="B174" t="n">
-        <v>373.848085</v>
-      </c>
+      <c r="B174" t="inlineStr"/>
       <c r="C174" t="n">
         <v>292.112944</v>
       </c>
@@ -7409,6 +7584,9 @@
       <c r="L174" t="n">
         <v>386.7588616666667</v>
       </c>
+      <c r="M174" t="n">
+        <v>259.0107146666667</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
@@ -7416,9 +7594,7 @@
           <t>海陸空大眾運輸</t>
         </is>
       </c>
-      <c r="B175" t="n">
-        <v>2901.399981</v>
-      </c>
+      <c r="B175" t="inlineStr"/>
       <c r="C175" t="n">
         <v>6793.255297</v>
       </c>
@@ -7449,6 +7625,9 @@
       <c r="L175" t="n">
         <v>2383.461392</v>
       </c>
+      <c r="M175" t="n">
+        <v>2742.247468</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -7456,9 +7635,7 @@
           <t>海陸空貨運承攬</t>
         </is>
       </c>
-      <c r="B176" t="n">
-        <v>175.531059</v>
-      </c>
+      <c r="B176" t="inlineStr"/>
       <c r="C176" t="n">
         <v>248.07971</v>
       </c>
@@ -7489,6 +7666,9 @@
       <c r="L176" t="n">
         <v>345.192702</v>
       </c>
+      <c r="M176" t="n">
+        <v>179.40048575</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
@@ -7496,9 +7676,7 @@
           <t>清潔用品</t>
         </is>
       </c>
-      <c r="B177" t="n">
-        <v>30.850258</v>
-      </c>
+      <c r="B177" t="inlineStr"/>
       <c r="C177" t="n">
         <v>19.523144</v>
       </c>
@@ -7529,6 +7707,9 @@
       <c r="L177" t="n">
         <v>192.622413</v>
       </c>
+      <c r="M177" t="n">
+        <v>48.720924</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
@@ -7537,37 +7718,40 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>38306.676969</v>
+        <v>0</v>
       </c>
       <c r="C178" t="n">
-        <v>23439.106738</v>
+        <v>23439.100927</v>
       </c>
       <c r="D178" t="n">
-        <v>22325.890429</v>
+        <v>22325.88761</v>
       </c>
       <c r="E178" t="n">
-        <v>26619.613949</v>
+        <v>26619.61147</v>
       </c>
       <c r="F178" t="n">
-        <v>22506.482396</v>
+        <v>22506.478089</v>
       </c>
       <c r="G178" t="n">
-        <v>10673.56522</v>
+        <v>10673.563644</v>
       </c>
       <c r="H178" t="n">
-        <v>11409.037431</v>
+        <v>11409.034822</v>
       </c>
       <c r="I178" t="n">
-        <v>16825.470781</v>
+        <v>16825.469238</v>
       </c>
       <c r="J178" t="n">
-        <v>13866.480808</v>
+        <v>13866.477937</v>
       </c>
       <c r="K178" t="n">
-        <v>8969.613944000001</v>
+        <v>8969.610973000001</v>
       </c>
       <c r="L178" t="n">
-        <v>12802.543808</v>
+        <v>12680.371594</v>
+      </c>
+      <c r="M178" t="n">
+        <v>6845.043985</v>
       </c>
     </row>
     <row r="179">
@@ -7576,9 +7760,7 @@
           <t>濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)</t>
         </is>
       </c>
-      <c r="B179" t="n">
-        <v>125.464919</v>
-      </c>
+      <c r="B179" t="inlineStr"/>
       <c r="C179" t="n">
         <v>299.560084</v>
       </c>
@@ -7609,6 +7791,9 @@
       <c r="L179" t="n">
         <v>67.370689</v>
       </c>
+      <c r="M179" t="n">
+        <v>73.047281</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
@@ -7616,9 +7801,7 @@
           <t>無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)</t>
         </is>
       </c>
-      <c r="B180" t="n">
-        <v>51147.409778</v>
-      </c>
+      <c r="B180" t="inlineStr"/>
       <c r="C180" t="n">
         <v>43005.269376</v>
       </c>
@@ -7647,7 +7830,10 @@
         <v>50680.792667</v>
       </c>
       <c r="L180" t="n">
-        <v>51846.022202</v>
+        <v>51843.941929</v>
+      </c>
+      <c r="M180" t="n">
+        <v>47085.396088</v>
       </c>
     </row>
     <row r="181">
@@ -7656,9 +7842,7 @@
           <t>煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼</t>
         </is>
       </c>
-      <c r="B181" t="n">
-        <v>7127.276622</v>
-      </c>
+      <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
         <v>5800.847007</v>
       </c>
@@ -7689,6 +7873,9 @@
       <c r="L181" t="n">
         <v>7329.143832</v>
       </c>
+      <c r="M181" t="n">
+        <v>7924.311492</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
@@ -7696,9 +7883,7 @@
           <t>燈具/應用</t>
         </is>
       </c>
-      <c r="B182" t="n">
-        <v>19053.917108</v>
-      </c>
+      <c r="B182" t="inlineStr"/>
       <c r="C182" t="n">
         <v>12340.85822</v>
       </c>
@@ -7729,6 +7914,9 @@
       <c r="L182" t="n">
         <v>21177.289339</v>
       </c>
+      <c r="M182" t="n">
+        <v>19344.641404</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
@@ -7736,9 +7924,7 @@
           <t>營造業</t>
         </is>
       </c>
-      <c r="B183" t="n">
-        <v>841.647955</v>
-      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" t="n">
         <v>706.547899</v>
       </c>
@@ -7769,6 +7955,9 @@
       <c r="L183" t="n">
         <v>664.923129</v>
       </c>
+      <c r="M183" t="n">
+        <v>701.008777</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
@@ -7776,9 +7965,7 @@
           <t>營造設置</t>
         </is>
       </c>
-      <c r="B184" t="n">
-        <v>342.669489</v>
-      </c>
+      <c r="B184" t="inlineStr"/>
       <c r="C184" t="n">
         <v>173.037339</v>
       </c>
@@ -7809,6 +7996,9 @@
       <c r="L184" t="n">
         <v>152.641605</v>
       </c>
+      <c r="M184" t="n">
+        <v>98.547904</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
@@ -7816,9 +8006,7 @@
           <t>營運管理軟體</t>
         </is>
       </c>
-      <c r="B185" t="n">
-        <v>238.823228</v>
-      </c>
+      <c r="B185" t="inlineStr"/>
       <c r="C185" t="n">
         <v>153.16183</v>
       </c>
@@ -7849,6 +8037,9 @@
       <c r="L185" t="n">
         <v>187.8162843333333</v>
       </c>
+      <c r="M185" t="n">
+        <v>135.31329</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
@@ -7856,9 +8047,7 @@
           <t>營養食品</t>
         </is>
       </c>
-      <c r="B186" t="n">
-        <v>31.139354</v>
-      </c>
+      <c r="B186" t="inlineStr"/>
       <c r="C186" t="n">
         <v>39.494226</v>
       </c>
@@ -7889,6 +8078,9 @@
       <c r="L186" t="n">
         <v>39.03679</v>
       </c>
+      <c r="M186" t="n">
+        <v>21.282977</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
@@ -7896,9 +8088,7 @@
           <t>物業管理</t>
         </is>
       </c>
-      <c r="B187" t="n">
-        <v>9372.231924</v>
-      </c>
+      <c r="B187" t="inlineStr"/>
       <c r="C187" t="n">
         <v>15716.106438</v>
       </c>
@@ -7929,6 +8119,9 @@
       <c r="L187" t="n">
         <v>2641.551439</v>
       </c>
+      <c r="M187" t="n">
+        <v>2288.550111</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
@@ -7936,9 +8129,7 @@
           <t>物流倉儲服務</t>
         </is>
       </c>
-      <c r="B188" t="n">
-        <v>108.628947</v>
-      </c>
+      <c r="B188" t="inlineStr"/>
       <c r="C188" t="n">
         <v>102.142557</v>
       </c>
@@ -7969,6 +8160,9 @@
       <c r="L188" t="n">
         <v>88.02397000000001</v>
       </c>
+      <c r="M188" t="n">
+        <v>46.275669</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
@@ -7976,9 +8170,7 @@
           <t>物聯網安全</t>
         </is>
       </c>
-      <c r="B189" t="n">
-        <v>317.078524</v>
-      </c>
+      <c r="B189" t="inlineStr"/>
       <c r="C189" t="n">
         <v>234.209638</v>
       </c>
@@ -8009,6 +8201,9 @@
       <c r="L189" t="n">
         <v>240.997538</v>
       </c>
+      <c r="M189" t="n">
+        <v>183.108413</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
@@ -8016,9 +8211,7 @@
           <t>特殊照明業</t>
         </is>
       </c>
-      <c r="B190" t="n">
-        <v>14773.107039</v>
-      </c>
+      <c r="B190" t="inlineStr"/>
       <c r="C190" t="n">
         <v>8570.568304</v>
       </c>
@@ -8049,6 +8242,9 @@
       <c r="L190" t="n">
         <v>16400.95679</v>
       </c>
+      <c r="M190" t="n">
+        <v>13850.718687</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
@@ -8056,9 +8252,7 @@
           <t>玻/碳纖</t>
         </is>
       </c>
-      <c r="B191" t="n">
-        <v>477.253821</v>
-      </c>
+      <c r="B191" t="inlineStr"/>
       <c r="C191" t="n">
         <v>242.419267</v>
       </c>
@@ -8089,6 +8283,9 @@
       <c r="L191" t="n">
         <v>136.326798</v>
       </c>
+      <c r="M191" t="n">
+        <v>93.80111100000001</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
@@ -8096,9 +8293,7 @@
           <t>玻璃基板</t>
         </is>
       </c>
-      <c r="B192" t="n">
-        <v>1406.368966</v>
-      </c>
+      <c r="B192" t="inlineStr"/>
       <c r="C192" t="n">
         <v>1536.360365</v>
       </c>
@@ -8129,6 +8324,9 @@
       <c r="L192" t="n">
         <v>470.826224</v>
       </c>
+      <c r="M192" t="n">
+        <v>418.641696</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
@@ -8136,9 +8334,7 @@
           <t>玻璃纖維/玻纖布</t>
         </is>
       </c>
-      <c r="B193" t="n">
-        <v>35074.713342</v>
-      </c>
+      <c r="B193" t="inlineStr"/>
       <c r="C193" t="n">
         <v>38586.469489</v>
       </c>
@@ -8169,6 +8365,9 @@
       <c r="L193" t="n">
         <v>6066.745791</v>
       </c>
+      <c r="M193" t="n">
+        <v>6222.645978</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
@@ -8176,9 +8375,7 @@
           <t>理財投資</t>
         </is>
       </c>
-      <c r="B194" t="n">
-        <v>31.019026</v>
-      </c>
+      <c r="B194" t="inlineStr"/>
       <c r="C194" t="n">
         <v>23.264321</v>
       </c>
@@ -8209,6 +8406,9 @@
       <c r="L194" t="n">
         <v>32.776536</v>
       </c>
+      <c r="M194" t="n">
+        <v>25.80657</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
@@ -8216,9 +8416,7 @@
           <t>環保潔能服務產業</t>
         </is>
       </c>
-      <c r="B195" t="n">
-        <v>23248.372977</v>
-      </c>
+      <c r="B195" t="inlineStr"/>
       <c r="C195" t="n">
         <v>14266.911316</v>
       </c>
@@ -8249,6 +8447,9 @@
       <c r="L195" t="n">
         <v>3238.582944</v>
       </c>
+      <c r="M195" t="n">
+        <v>2512.659935</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
@@ -8256,9 +8457,7 @@
           <t>環氧樹脂</t>
         </is>
       </c>
-      <c r="B196" t="n">
-        <v>34414.654603</v>
-      </c>
+      <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
         <v>21583.13457</v>
       </c>
@@ -8289,6 +8488,9 @@
       <c r="L196" t="n">
         <v>7427.268952</v>
       </c>
+      <c r="M196" t="n">
+        <v>6320.663876</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
@@ -8296,9 +8498,7 @@
           <t>生產製程、檢測設備及原物料</t>
         </is>
       </c>
-      <c r="B197" t="n">
-        <v>6854.985221</v>
-      </c>
+      <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
         <v>8461.565471</v>
       </c>
@@ -8329,6 +8529,9 @@
       <c r="L197" t="n">
         <v>4831.996146</v>
       </c>
+      <c r="M197" t="n">
+        <v>5839.83144</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
@@ -8336,9 +8539,7 @@
           <t>生產製程及檢測設備</t>
         </is>
       </c>
-      <c r="B198" t="n">
-        <v>41987.242919</v>
-      </c>
+      <c r="B198" t="inlineStr"/>
       <c r="C198" t="n">
         <v>41682.862446</v>
       </c>
@@ -8367,7 +8568,10 @@
         <v>36035.740276</v>
       </c>
       <c r="L198" t="n">
-        <v>36746.930172</v>
+        <v>37332.121455</v>
+      </c>
+      <c r="M198" t="n">
+        <v>45206.326493</v>
       </c>
     </row>
     <row r="199">
@@ -8376,9 +8580,7 @@
           <t>發電營運</t>
         </is>
       </c>
-      <c r="B199" t="n">
-        <v>1826.229337</v>
-      </c>
+      <c r="B199" t="inlineStr"/>
       <c r="C199" t="n">
         <v>1740.61111</v>
       </c>
@@ -8409,6 +8611,9 @@
       <c r="L199" t="n">
         <v>729.4397</v>
       </c>
+      <c r="M199" t="n">
+        <v>535.148209</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
@@ -8416,9 +8621,7 @@
           <t>監控管理</t>
         </is>
       </c>
-      <c r="B200" t="n">
-        <v>36.900698</v>
-      </c>
+      <c r="B200" t="inlineStr"/>
       <c r="C200" t="n">
         <v>28.74591</v>
       </c>
@@ -8449,6 +8652,9 @@
       <c r="L200" t="n">
         <v>45.041273</v>
       </c>
+      <c r="M200" t="n">
+        <v>39.574654</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
@@ -8456,9 +8662,7 @@
           <t>監控系統</t>
         </is>
       </c>
-      <c r="B201" t="n">
-        <v>20218.216076</v>
-      </c>
+      <c r="B201" t="inlineStr"/>
       <c r="C201" t="n">
         <v>13223.963367</v>
       </c>
@@ -8489,6 +8693,9 @@
       <c r="L201" t="n">
         <v>17668.280674</v>
       </c>
+      <c r="M201" t="n">
+        <v>14753.123642</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
@@ -8496,9 +8703,7 @@
           <t>監理法遵</t>
         </is>
       </c>
-      <c r="B202" t="n">
-        <v>54.423776</v>
-      </c>
+      <c r="B202" t="inlineStr"/>
       <c r="C202" t="n">
         <v>38.068334</v>
       </c>
@@ -8529,6 +8734,9 @@
       <c r="L202" t="n">
         <v>49.20428</v>
       </c>
+      <c r="M202" t="n">
+        <v>34.189653</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
@@ -8536,9 +8744,7 @@
           <t>監視器/顯示器</t>
         </is>
       </c>
-      <c r="B203" t="n">
-        <v>5689.35682</v>
-      </c>
+      <c r="B203" t="inlineStr"/>
       <c r="C203" t="n">
         <v>8746.51836</v>
       </c>
@@ -8569,6 +8775,9 @@
       <c r="L203" t="n">
         <v>1205.996277</v>
       </c>
+      <c r="M203" t="n">
+        <v>823.854024</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
@@ -8576,9 +8785,7 @@
           <t>石化上游原料及相關鑽探設備</t>
         </is>
       </c>
-      <c r="B204" t="n">
-        <v>28863.71006</v>
-      </c>
+      <c r="B204" t="inlineStr"/>
       <c r="C204" t="n">
         <v>18416.220779</v>
       </c>
@@ -8609,6 +8816,9 @@
       <c r="L204" t="n">
         <v>5692.897326</v>
       </c>
+      <c r="M204" t="n">
+        <v>5100.505315</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
@@ -8616,9 +8826,7 @@
           <t>石化中間原料(例如乙烯、丙烯、丁二烯、苯、酚等)</t>
         </is>
       </c>
-      <c r="B205" t="n">
-        <v>9544.925574999999</v>
-      </c>
+      <c r="B205" t="inlineStr"/>
       <c r="C205" t="n">
         <v>6653.83852</v>
       </c>
@@ -8649,6 +8857,9 @@
       <c r="L205" t="n">
         <v>5405.504065</v>
       </c>
+      <c r="M205" t="n">
+        <v>4007.836843</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
@@ -8656,9 +8867,7 @@
           <t>石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等)</t>
         </is>
       </c>
-      <c r="B206" t="n">
-        <v>31149.491863</v>
-      </c>
+      <c r="B206" t="inlineStr"/>
       <c r="C206" t="n">
         <v>19726.080715</v>
       </c>
@@ -8689,6 +8898,9 @@
       <c r="L206" t="n">
         <v>9042.837455000001</v>
       </c>
+      <c r="M206" t="n">
+        <v>7141.882389</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
@@ -8696,9 +8908,7 @@
           <t>石灰石</t>
         </is>
       </c>
-      <c r="B207" t="n">
-        <v>2100.559595</v>
-      </c>
+      <c r="B207" t="inlineStr"/>
       <c r="C207" t="n">
         <v>1440.916592</v>
       </c>
@@ -8729,6 +8939,9 @@
       <c r="L207" t="n">
         <v>1252.421625</v>
       </c>
+      <c r="M207" t="n">
+        <v>860.811334</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
@@ -8736,9 +8949,7 @@
           <t>矽晶圓/矽晶片</t>
         </is>
       </c>
-      <c r="B208" t="n">
-        <v>13240.531043</v>
-      </c>
+      <c r="B208" t="inlineStr"/>
       <c r="C208" t="n">
         <v>18266.673811</v>
       </c>
@@ -8769,6 +8980,9 @@
       <c r="L208" t="n">
         <v>2537.855924</v>
       </c>
+      <c r="M208" t="n">
+        <v>2201.544643</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
@@ -8776,9 +8990,7 @@
           <t>硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="B209" t="n">
-        <v>76838.70734399999</v>
-      </c>
+      <c r="B209" t="inlineStr"/>
       <c r="C209" t="n">
         <v>87896.89446700001</v>
       </c>
@@ -8807,7 +9019,10 @@
         <v>80700.106344</v>
       </c>
       <c r="L209" t="n">
-        <v>89834.404083</v>
+        <v>82964.705793</v>
+      </c>
+      <c r="M209" t="n">
+        <v>80780.660806</v>
       </c>
     </row>
     <row r="210">
@@ -8816,9 +9031,7 @@
           <t>硬碟機</t>
         </is>
       </c>
-      <c r="B210" t="n">
-        <v>11013.151086</v>
-      </c>
+      <c r="B210" t="inlineStr"/>
       <c r="C210" t="n">
         <v>3351.739665</v>
       </c>
@@ -8849,6 +9062,9 @@
       <c r="L210" t="n">
         <v>2621.87736</v>
       </c>
+      <c r="M210" t="n">
+        <v>3115.981568</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
@@ -8856,9 +9072,7 @@
           <t>硬體開發工具</t>
         </is>
       </c>
-      <c r="B211" t="n">
-        <v>332.115053</v>
-      </c>
+      <c r="B211" t="inlineStr"/>
       <c r="C211" t="n">
         <v>270.008902</v>
       </c>
@@ -8889,6 +9103,9 @@
       <c r="L211" t="n">
         <v>356.255041</v>
       </c>
+      <c r="M211" t="n">
+        <v>230.871578</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
@@ -8896,9 +9113,7 @@
           <t>磁碟儲存系統</t>
         </is>
       </c>
-      <c r="B212" t="n">
-        <v>3217.734836</v>
-      </c>
+      <c r="B212" t="inlineStr"/>
       <c r="C212" t="n">
         <v>2665.921477</v>
       </c>
@@ -8929,6 +9144,9 @@
       <c r="L212" t="n">
         <v>2488.079645</v>
       </c>
+      <c r="M212" t="n">
+        <v>1781.44226</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
@@ -8936,9 +9154,7 @@
           <t>票券銷售</t>
         </is>
       </c>
-      <c r="B213" t="n">
-        <v>192.409925</v>
-      </c>
+      <c r="B213" t="inlineStr"/>
       <c r="C213" t="n">
         <v>235.164189</v>
       </c>
@@ -8969,6 +9185,9 @@
       <c r="L213" t="n">
         <v>192.153839</v>
       </c>
+      <c r="M213" t="n">
+        <v>140.662798</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
@@ -8976,9 +9195,7 @@
           <t>租賃業</t>
         </is>
       </c>
-      <c r="B214" t="n">
-        <v>1511.956985</v>
-      </c>
+      <c r="B214" t="inlineStr"/>
       <c r="C214" t="n">
         <v>1201.641329</v>
       </c>
@@ -9009,6 +9226,9 @@
       <c r="L214" t="n">
         <v>1301.707405</v>
       </c>
+      <c r="M214" t="n">
+        <v>774.154144</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
@@ -9016,9 +9236,7 @@
           <t>移動控制</t>
         </is>
       </c>
-      <c r="B215" t="n">
-        <v>8343.319074999999</v>
-      </c>
+      <c r="B215" t="inlineStr"/>
       <c r="C215" t="n">
         <v>6887.175634</v>
       </c>
@@ -9049,6 +9267,9 @@
       <c r="L215" t="n">
         <v>4169.312817333333</v>
       </c>
+      <c r="M215" t="n">
+        <v>2698.842141</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
@@ -9056,9 +9277,7 @@
           <t>稜鏡片</t>
         </is>
       </c>
-      <c r="B216" t="n">
-        <v>33.390554</v>
-      </c>
+      <c r="B216" t="inlineStr"/>
       <c r="C216" t="n">
         <v>17.554199</v>
       </c>
@@ -9089,6 +9308,9 @@
       <c r="L216" t="n">
         <v>11.671033</v>
       </c>
+      <c r="M216" t="n">
+        <v>15.175221</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
@@ -9096,9 +9318,7 @@
           <t>穿戴式裝置</t>
         </is>
       </c>
-      <c r="B217" t="n">
-        <v>17328.227629</v>
-      </c>
+      <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
         <v>14946.875354</v>
       </c>
@@ -9129,6 +9349,9 @@
       <c r="L217" t="n">
         <v>18413.009785</v>
       </c>
+      <c r="M217" t="n">
+        <v>13649.384081</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
@@ -9136,9 +9359,7 @@
           <t>端點安全防護</t>
         </is>
       </c>
-      <c r="B218" t="n">
-        <v>332.792945</v>
-      </c>
+      <c r="B218" t="inlineStr"/>
       <c r="C218" t="n">
         <v>241.72181</v>
       </c>
@@ -9169,6 +9390,9 @@
       <c r="L218" t="n">
         <v>251.739566</v>
       </c>
+      <c r="M218" t="n">
+        <v>187.059646</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
@@ -9176,9 +9400,7 @@
           <t>筆記型電腦</t>
         </is>
       </c>
-      <c r="B219" t="n">
-        <v>69505.00745200001</v>
-      </c>
+      <c r="B219" t="inlineStr"/>
       <c r="C219" t="n">
         <v>63512.529545</v>
       </c>
@@ -9209,6 +9431,9 @@
       <c r="L219" t="n">
         <v>54113.54832</v>
       </c>
+      <c r="M219" t="n">
+        <v>40771.287929</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
@@ -9216,9 +9441,7 @@
           <t>精簡型電腦</t>
         </is>
       </c>
-      <c r="B220" t="n">
-        <v>18592.369308</v>
-      </c>
+      <c r="B220" t="inlineStr"/>
       <c r="C220" t="n">
         <v>11674.032952</v>
       </c>
@@ -9249,6 +9472,9 @@
       <c r="L220" t="n">
         <v>18980.909708</v>
       </c>
+      <c r="M220" t="n">
+        <v>16095.456465</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
@@ -9256,9 +9482,7 @@
           <t>系統整合</t>
         </is>
       </c>
-      <c r="B221" t="n">
-        <v>49542.547714</v>
-      </c>
+      <c r="B221" t="inlineStr"/>
       <c r="C221" t="n">
         <v>30202.008831</v>
       </c>
@@ -9289,6 +9513,9 @@
       <c r="L221" t="n">
         <v>52671.125257</v>
       </c>
+      <c r="M221" t="n">
+        <v>46662.692503</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
@@ -9296,9 +9523,7 @@
           <t>系統整合服務</t>
         </is>
       </c>
-      <c r="B222" t="n">
-        <v>30183.904336</v>
-      </c>
+      <c r="B222" t="inlineStr"/>
       <c r="C222" t="n">
         <v>31738.410911</v>
       </c>
@@ -9329,6 +9554,9 @@
       <c r="L222" t="n">
         <v>24038.323103</v>
       </c>
+      <c r="M222" t="n">
+        <v>21796.461511</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
@@ -9336,9 +9564,7 @@
           <t>紙漿、紙類原料</t>
         </is>
       </c>
-      <c r="B223" t="n">
-        <v>119.335742</v>
-      </c>
+      <c r="B223" t="inlineStr"/>
       <c r="C223" t="n">
         <v>76.716099</v>
       </c>
@@ -9369,6 +9595,9 @@
       <c r="L223" t="n">
         <v>64.462007</v>
       </c>
+      <c r="M223" t="n">
+        <v>58.242372</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
@@ -9376,9 +9605,7 @@
           <t>紡紗</t>
         </is>
       </c>
-      <c r="B224" t="n">
-        <v>1024.239961</v>
-      </c>
+      <c r="B224" t="inlineStr"/>
       <c r="C224" t="n">
         <v>650.058525</v>
       </c>
@@ -9409,6 +9636,9 @@
       <c r="L224" t="n">
         <v>1703.480191</v>
       </c>
+      <c r="M224" t="n">
+        <v>1145.8478</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
@@ -9416,9 +9646,7 @@
           <t>組裝廠</t>
         </is>
       </c>
-      <c r="B225" t="n">
-        <v>157.319929</v>
-      </c>
+      <c r="B225" t="inlineStr"/>
       <c r="C225" t="n">
         <v>102.116413</v>
       </c>
@@ -9449,6 +9677,9 @@
       <c r="L225" t="n">
         <v>38.164092</v>
       </c>
+      <c r="M225" t="n">
+        <v>27.511775</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
@@ -9456,9 +9687,7 @@
           <t>結構工程</t>
         </is>
       </c>
-      <c r="B226" t="n">
-        <v>279.412992</v>
-      </c>
+      <c r="B226" t="inlineStr"/>
       <c r="C226" t="n">
         <v>267.678125</v>
       </c>
@@ -9489,6 +9718,9 @@
       <c r="L226" t="n">
         <v>371.543524</v>
       </c>
+      <c r="M226" t="n">
+        <v>456.537878</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
@@ -9496,9 +9728,7 @@
           <t>網路IC</t>
         </is>
       </c>
-      <c r="B227" t="n">
-        <v>3.986214</v>
-      </c>
+      <c r="B227" t="inlineStr"/>
       <c r="C227" t="n">
         <v>5.070769</v>
       </c>
@@ -9529,6 +9759,9 @@
       <c r="L227" t="n">
         <v>10.022573</v>
       </c>
+      <c r="M227" t="n">
+        <v>5.766451</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
@@ -9536,9 +9769,7 @@
           <t>網路卡</t>
         </is>
       </c>
-      <c r="B228" t="n">
-        <v>2595.880082</v>
-      </c>
+      <c r="B228" t="inlineStr"/>
       <c r="C228" t="n">
         <v>2111.829362</v>
       </c>
@@ -9569,6 +9800,9 @@
       <c r="L228" t="n">
         <v>2239.779687</v>
       </c>
+      <c r="M228" t="n">
+        <v>1600.375555</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
@@ -9576,9 +9810,7 @@
           <t>網路基礎設施</t>
         </is>
       </c>
-      <c r="B229" t="n">
-        <v>708.159342</v>
-      </c>
+      <c r="B229" t="inlineStr"/>
       <c r="C229" t="n">
         <v>930.347615</v>
       </c>
@@ -9609,6 +9841,9 @@
       <c r="L229" t="n">
         <v>498.429727</v>
       </c>
+      <c r="M229" t="n">
+        <v>395.890875</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
@@ -9616,9 +9851,7 @@
           <t>網路安全防護</t>
         </is>
       </c>
-      <c r="B230" t="n">
-        <v>522.302478</v>
-      </c>
+      <c r="B230" t="inlineStr"/>
       <c r="C230" t="n">
         <v>815.785106</v>
       </c>
@@ -9649,6 +9882,9 @@
       <c r="L230" t="n">
         <v>368.631109</v>
       </c>
+      <c r="M230" t="n">
+        <v>327.359482</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
@@ -9656,9 +9892,7 @@
           <t>網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
         </is>
       </c>
-      <c r="B231" t="n">
-        <v>52644.957877</v>
-      </c>
+      <c r="B231" t="inlineStr"/>
       <c r="C231" t="n">
         <v>53653.573687</v>
       </c>
@@ -9689,6 +9923,9 @@
       <c r="L231" t="n">
         <v>57133.698243</v>
       </c>
+      <c r="M231" t="n">
+        <v>52595.138142</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
@@ -9696,9 +9933,7 @@
           <t>網頁內容安全</t>
         </is>
       </c>
-      <c r="B232" t="n">
-        <v>264.123921</v>
-      </c>
+      <c r="B232" t="inlineStr"/>
       <c r="C232" t="n">
         <v>181.722119</v>
       </c>
@@ -9729,6 +9964,9 @@
       <c r="L232" t="n">
         <v>166.181665</v>
       </c>
+      <c r="M232" t="n">
+        <v>156.460913</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
@@ -9736,9 +9974,7 @@
           <t>線上遊戲業</t>
         </is>
       </c>
-      <c r="B233" t="n">
-        <v>48.031635</v>
-      </c>
+      <c r="B233" t="inlineStr"/>
       <c r="C233" t="n">
         <v>31.575513</v>
       </c>
@@ -9769,6 +10005,9 @@
       <c r="L233" t="n">
         <v>19.129845</v>
       </c>
+      <c r="M233" t="n">
+        <v>12.706736</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
@@ -9776,9 +10015,7 @@
           <t>線材</t>
         </is>
       </c>
-      <c r="B234" t="n">
-        <v>7630.409636</v>
-      </c>
+      <c r="B234" t="inlineStr"/>
       <c r="C234" t="n">
         <v>3918.389613</v>
       </c>
@@ -9809,6 +10046,9 @@
       <c r="L234" t="n">
         <v>4951.610138</v>
       </c>
+      <c r="M234" t="n">
+        <v>6071.10889</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
@@ -9816,9 +10056,7 @@
           <t>線材盤元</t>
         </is>
       </c>
-      <c r="B235" t="n">
-        <v>1534.4335555</v>
-      </c>
+      <c r="B235" t="inlineStr"/>
       <c r="C235" t="n">
         <v>1180.980697</v>
       </c>
@@ -9849,6 +10087,9 @@
       <c r="L235" t="n">
         <v>4141.141641</v>
       </c>
+      <c r="M235" t="n">
+        <v>2150.54629225</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
@@ -9856,9 +10097,7 @@
           <t>織布</t>
         </is>
       </c>
-      <c r="B236" t="n">
-        <v>1444.261656</v>
-      </c>
+      <c r="B236" t="inlineStr"/>
       <c r="C236" t="n">
         <v>967.286305</v>
       </c>
@@ -9889,6 +10128,9 @@
       <c r="L236" t="n">
         <v>1852.181955</v>
       </c>
+      <c r="M236" t="n">
+        <v>1388.800741</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
@@ -9896,9 +10138,7 @@
           <t>聚亞醯胺樹脂</t>
         </is>
       </c>
-      <c r="B237" t="n">
-        <v>6689.285291</v>
-      </c>
+      <c r="B237" t="inlineStr"/>
       <c r="C237" t="n">
         <v>4515.511476</v>
       </c>
@@ -9929,6 +10169,9 @@
       <c r="L237" t="n">
         <v>2645.456752</v>
       </c>
+      <c r="M237" t="n">
+        <v>1984.285904</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
@@ -9936,9 +10179,7 @@
           <t>背光模組</t>
         </is>
       </c>
-      <c r="B238" t="n">
-        <v>5501.588152</v>
-      </c>
+      <c r="B238" t="inlineStr"/>
       <c r="C238" t="n">
         <v>7913.555186666667</v>
       </c>
@@ -9969,6 +10210,9 @@
       <c r="L238" t="n">
         <v>1340.745812</v>
       </c>
+      <c r="M238" t="n">
+        <v>906.58915</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
@@ -9976,9 +10220,7 @@
           <t>背光源(發光二極體、冷陰極管)</t>
         </is>
       </c>
-      <c r="B239" t="n">
-        <v>1732.564836</v>
-      </c>
+      <c r="B239" t="inlineStr"/>
       <c r="C239" t="n">
         <v>1403.397714</v>
       </c>
@@ -10009,6 +10251,9 @@
       <c r="L239" t="n">
         <v>1365.544754</v>
       </c>
+      <c r="M239" t="n">
+        <v>1066.875085</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
@@ -10016,9 +10261,7 @@
           <t>能源管理服務</t>
         </is>
       </c>
-      <c r="B240" t="n">
-        <v>26196.463868</v>
-      </c>
+      <c r="B240" t="inlineStr"/>
       <c r="C240" t="n">
         <v>25645.616946</v>
       </c>
@@ -10049,6 +10292,9 @@
       <c r="L240" t="n">
         <v>20102.800553</v>
       </c>
+      <c r="M240" t="n">
+        <v>17262.980236</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
@@ -10056,9 +10302,7 @@
           <t>膠材</t>
         </is>
       </c>
-      <c r="B241" t="n">
-        <v>6773.617146</v>
-      </c>
+      <c r="B241" t="inlineStr"/>
       <c r="C241" t="n">
         <v>4359.21096</v>
       </c>
@@ -10089,6 +10333,9 @@
       <c r="L241" t="n">
         <v>2830.844934</v>
       </c>
+      <c r="M241" t="n">
+        <v>2127.856216</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
@@ -10096,9 +10343,7 @@
           <t>臨床實驗、移植技術、疾病治療</t>
         </is>
       </c>
-      <c r="B242" t="n">
-        <v>63.874113</v>
-      </c>
+      <c r="B242" t="inlineStr"/>
       <c r="C242" t="n">
         <v>45.870932</v>
       </c>
@@ -10129,6 +10374,9 @@
       <c r="L242" t="n">
         <v>40.985452</v>
       </c>
+      <c r="M242" t="n">
+        <v>55.92611</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
@@ -10136,9 +10384,7 @@
           <t>自動化機台</t>
         </is>
       </c>
-      <c r="B243" t="n">
-        <v>1.099658</v>
-      </c>
+      <c r="B243" t="inlineStr"/>
       <c r="C243" t="n">
         <v>0.954052</v>
       </c>
@@ -10169,6 +10415,9 @@
       <c r="L243" t="n">
         <v>1.460535</v>
       </c>
+      <c r="M243" t="n">
+        <v>1.225289</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
@@ -10176,9 +10425,7 @@
           <t>自動售票機</t>
         </is>
       </c>
-      <c r="B244" t="n">
-        <v>21.951234</v>
-      </c>
+      <c r="B244" t="inlineStr"/>
       <c r="C244" t="n">
         <v>19.494967</v>
       </c>
@@ -10209,6 +10456,9 @@
       <c r="L244" t="n">
         <v>15.009668</v>
       </c>
+      <c r="M244" t="n">
+        <v>9.200265</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
@@ -10216,9 +10466,7 @@
           <t>自動販賣機</t>
         </is>
       </c>
-      <c r="B245" t="n">
-        <v>20.074041</v>
-      </c>
+      <c r="B245" t="inlineStr"/>
       <c r="C245" t="n">
         <v>6.056005</v>
       </c>
@@ -10249,6 +10497,9 @@
       <c r="L245" t="n">
         <v>2.60754</v>
       </c>
+      <c r="M245" t="n">
+        <v>1.533433</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
@@ -10256,9 +10507,7 @@
           <t>自有產品(服務)銷售</t>
         </is>
       </c>
-      <c r="B246" t="n">
-        <v>13.78538</v>
-      </c>
+      <c r="B246" t="inlineStr"/>
       <c r="C246" t="n">
         <v>12.890028</v>
       </c>
@@ -10289,6 +10538,9 @@
       <c r="L246" t="n">
         <v>18.294366</v>
       </c>
+      <c r="M246" t="n">
+        <v>18.394649</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
@@ -10296,9 +10548,7 @@
           <t>自然語言處理</t>
         </is>
       </c>
-      <c r="B247" t="n">
-        <v>52.033709</v>
-      </c>
+      <c r="B247" t="inlineStr"/>
       <c r="C247" t="n">
         <v>31.387267</v>
       </c>
@@ -10329,6 +10579,9 @@
       <c r="L247" t="n">
         <v>35.97012033333333</v>
       </c>
+      <c r="M247" t="n">
+        <v>32.96358</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
@@ -10336,9 +10589,7 @@
           <t>藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="B248" t="n">
-        <v>5231.492374</v>
-      </c>
+      <c r="B248" t="inlineStr"/>
       <c r="C248" t="n">
         <v>7641.195942</v>
       </c>
@@ -10369,6 +10620,9 @@
       <c r="L248" t="n">
         <v>1119.647913</v>
       </c>
+      <c r="M248" t="n">
+        <v>735.534147</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
@@ -10376,9 +10630,7 @@
           <t>藥品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B249" t="n">
-        <v>887.293283</v>
-      </c>
+      <c r="B249" t="inlineStr"/>
       <c r="C249" t="n">
         <v>475.023269</v>
       </c>
@@ -10409,6 +10661,9 @@
       <c r="L249" t="n">
         <v>1263.430943</v>
       </c>
+      <c r="M249" t="n">
+        <v>908.697346</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
@@ -10416,9 +10671,7 @@
           <t>處理器/IC</t>
         </is>
       </c>
-      <c r="B250" t="n">
-        <v>0.964037</v>
-      </c>
+      <c r="B250" t="inlineStr"/>
       <c r="C250" t="n">
         <v>0.854108</v>
       </c>
@@ -10449,6 +10702,9 @@
       <c r="L250" t="n">
         <v>1.255058</v>
       </c>
+      <c r="M250" t="n">
+        <v>1.331894</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
@@ -10456,9 +10712,7 @@
           <t>虛擬化軟體</t>
         </is>
       </c>
-      <c r="B251" t="n">
-        <v>326.091909</v>
-      </c>
+      <c r="B251" t="inlineStr"/>
       <c r="C251" t="n">
         <v>234.834208</v>
       </c>
@@ -10489,6 +10743,9 @@
       <c r="L251" t="n">
         <v>234.0853753333333</v>
       </c>
+      <c r="M251" t="n">
+        <v>195.893272</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
@@ -10496,9 +10753,7 @@
           <t>螺絲螺帽</t>
         </is>
       </c>
-      <c r="B252" t="n">
-        <v>122.505204</v>
-      </c>
+      <c r="B252" t="inlineStr"/>
       <c r="C252" t="n">
         <v>110.430695</v>
       </c>
@@ -10529,6 +10784,9 @@
       <c r="L252" t="n">
         <v>92.799583</v>
       </c>
+      <c r="M252" t="n">
+        <v>109.739268</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
@@ -10536,9 +10794,7 @@
           <t>行動安全</t>
         </is>
       </c>
-      <c r="B253" t="n">
-        <v>443.997313</v>
-      </c>
+      <c r="B253" t="inlineStr"/>
       <c r="C253" t="n">
         <v>738.880188</v>
       </c>
@@ -10569,6 +10825,9 @@
       <c r="L253" t="n">
         <v>263.185752</v>
       </c>
+      <c r="M253" t="n">
+        <v>265.484922</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
@@ -10576,9 +10835,7 @@
           <t>行銷廣告服務</t>
         </is>
       </c>
-      <c r="B254" t="n">
-        <v>89.618908</v>
-      </c>
+      <c r="B254" t="inlineStr"/>
       <c r="C254" t="n">
         <v>142.351163</v>
       </c>
@@ -10609,6 +10866,9 @@
       <c r="L254" t="n">
         <v>109.19685</v>
       </c>
+      <c r="M254" t="n">
+        <v>97.834431</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
@@ -10616,9 +10876,7 @@
           <t>衛星定位系統</t>
         </is>
       </c>
-      <c r="B255" t="n">
-        <v>0.000243</v>
-      </c>
+      <c r="B255" t="inlineStr"/>
       <c r="C255" t="n">
         <v>0.000252</v>
       </c>
@@ -10649,6 +10907,9 @@
       <c r="L255" t="n">
         <v>0.0005</v>
       </c>
+      <c r="M255" t="n">
+        <v>0.000144</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
@@ -10656,9 +10917,7 @@
           <t>裁剪加工</t>
         </is>
       </c>
-      <c r="B256" t="n">
-        <v>123.546804</v>
-      </c>
+      <c r="B256" t="inlineStr"/>
       <c r="C256" t="n">
         <v>117.488219</v>
       </c>
@@ -10689,6 +10948,9 @@
       <c r="L256" t="n">
         <v>335.164995</v>
       </c>
+      <c r="M256" t="n">
+        <v>211.594841</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
@@ -10696,9 +10958,7 @@
           <t>裝潢業</t>
         </is>
       </c>
-      <c r="B257" t="n">
-        <v>217.977344</v>
-      </c>
+      <c r="B257" t="inlineStr"/>
       <c r="C257" t="n">
         <v>191.547579</v>
       </c>
@@ -10729,6 +10989,9 @@
       <c r="L257" t="n">
         <v>251.066129</v>
       </c>
+      <c r="M257" t="n">
+        <v>357.595166</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
@@ -10736,9 +10999,7 @@
           <t>裝置/器材零組件</t>
         </is>
       </c>
-      <c r="B258" t="n">
-        <v>3.491333</v>
-      </c>
+      <c r="B258" t="inlineStr"/>
       <c r="C258" t="n">
         <v>4.817071</v>
       </c>
@@ -10769,6 +11030,9 @@
       <c r="L258" t="n">
         <v>6.016457</v>
       </c>
+      <c r="M258" t="n">
+        <v>5.230808</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
@@ -10776,9 +11040,7 @@
           <t>裝置/器材顯示器</t>
         </is>
       </c>
-      <c r="B259" t="n">
-        <v>3.487639</v>
-      </c>
+      <c r="B259" t="inlineStr"/>
       <c r="C259" t="n">
         <v>4.816107</v>
       </c>
@@ -10809,6 +11071,9 @@
       <c r="L259" t="n">
         <v>6.015132</v>
       </c>
+      <c r="M259" t="n">
+        <v>5.229814</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
@@ -10816,9 +11081,7 @@
           <t>製管</t>
         </is>
       </c>
-      <c r="B260" t="n">
-        <v>7921.677461</v>
-      </c>
+      <c r="B260" t="inlineStr"/>
       <c r="C260" t="n">
         <v>6697.0424</v>
       </c>
@@ -10849,6 +11112,9 @@
       <c r="L260" t="n">
         <v>11086.111399</v>
       </c>
+      <c r="M260" t="n">
+        <v>9902.584876000001</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
@@ -10856,9 +11122,7 @@
           <t>製造商</t>
         </is>
       </c>
-      <c r="B261" t="n">
-        <v>5121.082738</v>
-      </c>
+      <c r="B261" t="inlineStr"/>
       <c r="C261" t="n">
         <v>7529.549814</v>
       </c>
@@ -10889,6 +11153,9 @@
       <c r="L261" t="n">
         <v>942.7438990000001</v>
       </c>
+      <c r="M261" t="n">
+        <v>626.574979</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
@@ -10896,9 +11163,7 @@
           <t>觸控面板</t>
         </is>
       </c>
-      <c r="B262" t="n">
-        <v>7450.358211</v>
-      </c>
+      <c r="B262" t="inlineStr"/>
       <c r="C262" t="n">
         <v>6193.240157</v>
       </c>
@@ -10927,7 +11192,10 @@
         <v>18393.569229</v>
       </c>
       <c r="L262" t="n">
-        <v>9310.94492</v>
+        <v>9283.063964000001</v>
+      </c>
+      <c r="M262" t="n">
+        <v>6932.704581</v>
       </c>
     </row>
     <row r="263">
@@ -10936,9 +11204,7 @@
           <t>記憶體</t>
         </is>
       </c>
-      <c r="B263" t="n">
-        <v>32176.301533</v>
-      </c>
+      <c r="B263" t="inlineStr"/>
       <c r="C263" t="n">
         <v>32001.615185</v>
       </c>
@@ -10969,6 +11235,9 @@
       <c r="L263" t="n">
         <v>106374.091398</v>
       </c>
+      <c r="M263" t="n">
+        <v>211886.996489</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
@@ -10976,9 +11245,7 @@
           <t>設備安裝服務</t>
         </is>
       </c>
-      <c r="B264" t="n">
-        <v>17103.507431</v>
-      </c>
+      <c r="B264" t="inlineStr"/>
       <c r="C264" t="n">
         <v>10564.930474</v>
       </c>
@@ -11009,6 +11276,9 @@
       <c r="L264" t="n">
         <v>18905.360756</v>
       </c>
+      <c r="M264" t="n">
+        <v>17675.880138</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
@@ -11016,9 +11286,7 @@
           <t>設備管理軟體</t>
         </is>
       </c>
-      <c r="B265" t="n">
-        <v>14836.774999</v>
-      </c>
+      <c r="B265" t="inlineStr"/>
       <c r="C265" t="n">
         <v>8712.535664000001</v>
       </c>
@@ -11049,6 +11317,9 @@
       <c r="L265" t="n">
         <v>16037.365967</v>
       </c>
+      <c r="M265" t="n">
+        <v>13875.957167</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
@@ -11056,9 +11327,7 @@
           <t>設備維護</t>
         </is>
       </c>
-      <c r="B266" t="n">
-        <v>90.593718</v>
-      </c>
+      <c r="B266" t="inlineStr"/>
       <c r="C266" t="n">
         <v>44.432779</v>
       </c>
@@ -11089,6 +11358,9 @@
       <c r="L266" t="n">
         <v>37.282443</v>
       </c>
+      <c r="M266" t="n">
+        <v>22.400085</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
@@ -11096,9 +11368,7 @@
           <t>證券業</t>
         </is>
       </c>
-      <c r="B267" t="n">
-        <v>1306.420836</v>
-      </c>
+      <c r="B267" t="inlineStr"/>
       <c r="C267" t="n">
         <v>1076.4571</v>
       </c>
@@ -11129,6 +11399,9 @@
       <c r="L267" t="n">
         <v>1052.174052</v>
       </c>
+      <c r="M267" t="n">
+        <v>617.02145</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
@@ -11136,9 +11409,7 @@
           <t>變壓器</t>
         </is>
       </c>
-      <c r="B268" t="n">
-        <v>8582.689736</v>
-      </c>
+      <c r="B268" t="inlineStr"/>
       <c r="C268" t="n">
         <v>8852.13817</v>
       </c>
@@ -11169,6 +11440,9 @@
       <c r="L268" t="n">
         <v>3491.647968</v>
       </c>
+      <c r="M268" t="n">
+        <v>5650.105963</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
@@ -11176,9 +11450,7 @@
           <t>貨櫃航運</t>
         </is>
       </c>
-      <c r="B269" t="n">
-        <v>4401.544054</v>
-      </c>
+      <c r="B269" t="inlineStr"/>
       <c r="C269" t="n">
         <v>3665.495578</v>
       </c>
@@ -11209,6 +11481,9 @@
       <c r="L269" t="n">
         <v>2715.705304</v>
       </c>
+      <c r="M269" t="n">
+        <v>2120.132926</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
@@ -11216,9 +11491,7 @@
           <t>貨櫃運輸集散及倉儲</t>
         </is>
       </c>
-      <c r="B270" t="n">
-        <v>315.841665</v>
-      </c>
+      <c r="B270" t="inlineStr"/>
       <c r="C270" t="n">
         <v>768.624454</v>
       </c>
@@ -11249,6 +11522,9 @@
       <c r="L270" t="n">
         <v>424.291263</v>
       </c>
+      <c r="M270" t="n">
+        <v>233.973088</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
@@ -11256,9 +11532,7 @@
           <t>貿易商、代理商、經銷商</t>
         </is>
       </c>
-      <c r="B271" t="n">
-        <v>6352.601821</v>
-      </c>
+      <c r="B271" t="inlineStr"/>
       <c r="C271" t="n">
         <v>9821.342420000001</v>
       </c>
@@ -11289,6 +11563,9 @@
       <c r="L271" t="n">
         <v>1478.966525</v>
       </c>
+      <c r="M271" t="n">
+        <v>1047.938567</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
@@ -11296,9 +11573,7 @@
           <t>資安審計</t>
         </is>
       </c>
-      <c r="B272" t="n">
-        <v>30.996195</v>
-      </c>
+      <c r="B272" t="inlineStr"/>
       <c r="C272" t="n">
         <v>23.262423</v>
       </c>
@@ -11329,6 +11604,9 @@
       <c r="L272" t="n">
         <v>32.775686</v>
       </c>
+      <c r="M272" t="n">
+        <v>25.805276</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
@@ -11336,9 +11614,7 @@
           <t>資安治理</t>
         </is>
       </c>
-      <c r="B273" t="n">
-        <v>151.194995</v>
-      </c>
+      <c r="B273" t="inlineStr"/>
       <c r="C273" t="n">
         <v>75.129958</v>
       </c>
@@ -11369,6 +11645,9 @@
       <c r="L273" t="n">
         <v>86.122602</v>
       </c>
+      <c r="M273" t="n">
+        <v>65.732265</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
@@ -11376,9 +11655,7 @@
           <t>資安營運管理服務</t>
         </is>
       </c>
-      <c r="B274" t="n">
-        <v>399.903095</v>
-      </c>
+      <c r="B274" t="inlineStr"/>
       <c r="C274" t="n">
         <v>303.287728</v>
       </c>
@@ -11409,6 +11686,9 @@
       <c r="L274" t="n">
         <v>331.345709</v>
       </c>
+      <c r="M274" t="n">
+        <v>223.56863</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
@@ -11416,9 +11696,7 @@
           <t>資安防護能力分析與鑑識服務</t>
         </is>
       </c>
-      <c r="B275" t="n">
-        <v>324.855816</v>
-      </c>
+      <c r="B275" t="inlineStr"/>
       <c r="C275" t="n">
         <v>241.555762</v>
       </c>
@@ -11449,6 +11727,9 @@
       <c r="L275" t="n">
         <v>246.831153</v>
       </c>
+      <c r="M275" t="n">
+        <v>187.604734</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
@@ -11456,9 +11737,7 @@
           <t>資安防護軟體</t>
         </is>
       </c>
-      <c r="B276" t="n">
-        <v>291.016875</v>
-      </c>
+      <c r="B276" t="inlineStr"/>
       <c r="C276" t="n">
         <v>210.610299</v>
       </c>
@@ -11489,6 +11768,9 @@
       <c r="L276" t="n">
         <v>178.5190573333333</v>
       </c>
+      <c r="M276" t="n">
+        <v>166.808822</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
@@ -11496,9 +11778,7 @@
           <t>資安顧問服務</t>
         </is>
       </c>
-      <c r="B277" t="n">
-        <v>366.144508</v>
-      </c>
+      <c r="B277" t="inlineStr"/>
       <c r="C277" t="n">
         <v>274.880229</v>
       </c>
@@ -11529,6 +11809,9 @@
       <c r="L277" t="n">
         <v>291.656601</v>
       </c>
+      <c r="M277" t="n">
+        <v>230.102388</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
@@ -11536,9 +11819,7 @@
           <t>資料分析處理服務</t>
         </is>
       </c>
-      <c r="B278" t="n">
-        <v>207.985627</v>
-      </c>
+      <c r="B278" t="inlineStr"/>
       <c r="C278" t="n">
         <v>135.22722</v>
       </c>
@@ -11569,6 +11850,9 @@
       <c r="L278" t="n">
         <v>167.941177</v>
       </c>
+      <c r="M278" t="n">
+        <v>98.712147</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
@@ -11576,9 +11860,7 @@
           <t>資料安全</t>
         </is>
       </c>
-      <c r="B279" t="n">
-        <v>278.449238</v>
-      </c>
+      <c r="B279" t="inlineStr"/>
       <c r="C279" t="n">
         <v>187.712729</v>
       </c>
@@ -11609,6 +11891,9 @@
       <c r="L279" t="n">
         <v>176.383668</v>
       </c>
+      <c r="M279" t="n">
+        <v>160.111885</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
@@ -11616,9 +11901,7 @@
           <t>資料庫</t>
         </is>
       </c>
-      <c r="B280" t="n">
-        <v>226.185144</v>
-      </c>
+      <c r="B280" t="inlineStr"/>
       <c r="C280" t="n">
         <v>149.868537</v>
       </c>
@@ -11649,6 +11932,9 @@
       <c r="L280" t="n">
         <v>142.5598053333333</v>
       </c>
+      <c r="M280" t="n">
+        <v>115.873117</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
@@ -11656,9 +11942,7 @@
           <t>資料聚合</t>
         </is>
       </c>
-      <c r="B281" t="n">
-        <v>124.777106</v>
-      </c>
+      <c r="B281" t="inlineStr"/>
       <c r="C281" t="n">
         <v>60.401816</v>
       </c>
@@ -11689,6 +11973,9 @@
       <c r="L281" t="n">
         <v>73.12916300000001</v>
       </c>
+      <c r="M281" t="n">
+        <v>59.935023</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
@@ -11696,9 +11983,7 @@
           <t>資料處理</t>
         </is>
       </c>
-      <c r="B282" t="n">
-        <v>581.8397200000001</v>
-      </c>
+      <c r="B282" t="inlineStr"/>
       <c r="C282" t="n">
         <v>419.812972</v>
       </c>
@@ -11729,6 +12014,9 @@
       <c r="L282" t="n">
         <v>488.7593693333333</v>
       </c>
+      <c r="M282" t="n">
+        <v>404.649411</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
@@ -11736,9 +12024,7 @@
           <t>資料處理服務</t>
         </is>
       </c>
-      <c r="B283" t="n">
-        <v>5297.971279</v>
-      </c>
+      <c r="B283" t="inlineStr"/>
       <c r="C283" t="n">
         <v>7684.2997</v>
       </c>
@@ -11769,6 +12055,9 @@
       <c r="L283" t="n">
         <v>1151.147472</v>
       </c>
+      <c r="M283" t="n">
+        <v>781.652429</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
@@ -11776,9 +12065,7 @@
           <t>資服</t>
         </is>
       </c>
-      <c r="B284" t="n">
-        <v>7.994039</v>
-      </c>
+      <c r="B284" t="inlineStr"/>
       <c r="C284" t="n">
         <v>7.443175</v>
       </c>
@@ -11809,6 +12096,9 @@
       <c r="L284" t="n">
         <v>6.002757</v>
       </c>
+      <c r="M284" t="n">
+        <v>4.581513</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
@@ -11816,9 +12106,7 @@
           <t>資訊收集設備</t>
         </is>
       </c>
-      <c r="B285" t="n">
-        <v>0.052603</v>
-      </c>
+      <c r="B285" t="inlineStr"/>
       <c r="C285" t="n">
         <v>0.031024</v>
       </c>
@@ -11849,6 +12137,9 @@
       <c r="L285" t="n">
         <v>0.02579</v>
       </c>
+      <c r="M285" t="n">
+        <v>0.013566</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
@@ -11856,9 +12147,7 @@
           <t>資訊系統建置服務</t>
         </is>
       </c>
-      <c r="B286" t="n">
-        <v>200.234877</v>
-      </c>
+      <c r="B286" t="inlineStr"/>
       <c r="C286" t="n">
         <v>127.892105</v>
       </c>
@@ -11889,6 +12178,9 @@
       <c r="L286" t="n">
         <v>162.194131</v>
       </c>
+      <c r="M286" t="n">
+        <v>94.248248</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
@@ -11896,9 +12188,7 @@
           <t>資訊聚合</t>
         </is>
       </c>
-      <c r="B287" t="n">
-        <v>195.773609</v>
-      </c>
+      <c r="B287" t="inlineStr"/>
       <c r="C287" t="n">
         <v>126.486237</v>
       </c>
@@ -11929,6 +12219,9 @@
       <c r="L287" t="n">
         <v>145.306327</v>
       </c>
+      <c r="M287" t="n">
+        <v>85.354704</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
@@ -11936,9 +12229,7 @@
           <t>身分認證與訪問管理</t>
         </is>
       </c>
-      <c r="B288" t="n">
-        <v>260.457309</v>
-      </c>
+      <c r="B288" t="inlineStr"/>
       <c r="C288" t="n">
         <v>177.648074</v>
       </c>
@@ -11969,6 +12260,9 @@
       <c r="L288" t="n">
         <v>159.779892</v>
       </c>
+      <c r="M288" t="n">
+        <v>144.136822</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
@@ -11976,9 +12270,7 @@
           <t>車燈</t>
         </is>
       </c>
-      <c r="B289" t="n">
-        <v>3036.972286</v>
-      </c>
+      <c r="B289" t="inlineStr"/>
       <c r="C289" t="n">
         <v>2372.349218</v>
       </c>
@@ -12009,6 +12301,9 @@
       <c r="L289" t="n">
         <v>3157.927049</v>
       </c>
+      <c r="M289" t="n">
+        <v>3970.662508</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
@@ -12016,9 +12311,7 @@
           <t>車用機械傳動設備及零配件</t>
         </is>
       </c>
-      <c r="B290" t="n">
-        <v>4152.43746</v>
-      </c>
+      <c r="B290" t="inlineStr"/>
       <c r="C290" t="n">
         <v>4050.978517</v>
       </c>
@@ -12049,6 +12342,9 @@
       <c r="L290" t="n">
         <v>4576.652078</v>
       </c>
+      <c r="M290" t="n">
+        <v>4499.323123</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
@@ -12056,9 +12352,7 @@
           <t>軟性電路板</t>
         </is>
       </c>
-      <c r="B291" t="n">
-        <v>0.029388</v>
-      </c>
+      <c r="B291" t="inlineStr"/>
       <c r="C291" t="n">
         <v>0.011044</v>
       </c>
@@ -12089,6 +12383,9 @@
       <c r="L291" t="n">
         <v>0.00617</v>
       </c>
+      <c r="M291" t="n">
+        <v>0.00348</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
@@ -12096,9 +12393,7 @@
           <t>軟體開發</t>
         </is>
       </c>
-      <c r="B292" t="n">
-        <v>615.174307</v>
-      </c>
+      <c r="B292" t="inlineStr"/>
       <c r="C292" t="n">
         <v>1033.692224</v>
       </c>
@@ -12129,6 +12424,9 @@
       <c r="L292" t="n">
         <v>1183.093559</v>
       </c>
+      <c r="M292" t="n">
+        <v>718.317669</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
@@ -12136,9 +12434,7 @@
           <t>軟體開發工具</t>
         </is>
       </c>
-      <c r="B293" t="n">
-        <v>332.115053</v>
-      </c>
+      <c r="B293" t="inlineStr"/>
       <c r="C293" t="n">
         <v>270.008902</v>
       </c>
@@ -12169,6 +12465,9 @@
       <c r="L293" t="n">
         <v>356.255041</v>
       </c>
+      <c r="M293" t="n">
+        <v>230.871578</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
@@ -12176,9 +12475,7 @@
           <t>輪胎</t>
         </is>
       </c>
-      <c r="B294" t="n">
-        <v>144.37445</v>
-      </c>
+      <c r="B294" t="inlineStr"/>
       <c r="C294" t="n">
         <v>95.38425599999999</v>
       </c>
@@ -12209,6 +12506,9 @@
       <c r="L294" t="n">
         <v>93.256123</v>
       </c>
+      <c r="M294" t="n">
+        <v>79.868334</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
@@ -12216,9 +12516,7 @@
           <t>輸出入模組/介面卡</t>
         </is>
       </c>
-      <c r="B295" t="n">
-        <v>3359.870649</v>
-      </c>
+      <c r="B295" t="inlineStr"/>
       <c r="C295" t="n">
         <v>2961.232038</v>
       </c>
@@ -12249,6 +12547,9 @@
       <c r="L295" t="n">
         <v>3096.105434</v>
       </c>
+      <c r="M295" t="n">
+        <v>2308.663432</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
@@ -12256,9 +12557,7 @@
           <t>輸送機械及零配件</t>
         </is>
       </c>
-      <c r="B296" t="n">
-        <v>18293.38964</v>
-      </c>
+      <c r="B296" t="inlineStr"/>
       <c r="C296" t="n">
         <v>12551.556174</v>
       </c>
@@ -12289,6 +12588,9 @@
       <c r="L296" t="n">
         <v>20205.747809</v>
       </c>
+      <c r="M296" t="n">
+        <v>18254.925584</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
@@ -12296,9 +12598,7 @@
           <t>農業科技業</t>
         </is>
       </c>
-      <c r="B297" t="n">
-        <v>617.7325070000001</v>
-      </c>
+      <c r="B297" t="inlineStr"/>
       <c r="C297" t="n">
         <v>229.34773</v>
       </c>
@@ -12329,6 +12629,9 @@
       <c r="L297" t="n">
         <v>756.963339</v>
       </c>
+      <c r="M297" t="n">
+        <v>261.079355</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
@@ -12336,9 +12639,7 @@
           <t>農藥</t>
         </is>
       </c>
-      <c r="B298" t="n">
-        <v>36.524538</v>
-      </c>
+      <c r="B298" t="inlineStr"/>
       <c r="C298" t="n">
         <v>22.558101</v>
       </c>
@@ -12369,6 +12670,9 @@
       <c r="L298" t="n">
         <v>37.370743</v>
       </c>
+      <c r="M298" t="n">
+        <v>21.532111</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
@@ -12376,9 +12680,7 @@
           <t>近眼顯示(Dear-Eye Display)</t>
         </is>
       </c>
-      <c r="B299" t="n">
-        <v>23.238203</v>
-      </c>
+      <c r="B299" t="inlineStr"/>
       <c r="C299" t="n">
         <v>21.028046</v>
       </c>
@@ -12409,6 +12711,9 @@
       <c r="L299" t="n">
         <v>20.168064</v>
       </c>
+      <c r="M299" t="n">
+        <v>12.325518</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
@@ -12416,9 +12721,7 @@
           <t>通訊</t>
         </is>
       </c>
-      <c r="B300" t="n">
-        <v>30.996195</v>
-      </c>
+      <c r="B300" t="inlineStr"/>
       <c r="C300" t="n">
         <v>23.262423</v>
       </c>
@@ -12449,6 +12752,9 @@
       <c r="L300" t="n">
         <v>32.775686</v>
       </c>
+      <c r="M300" t="n">
+        <v>25.805276</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
@@ -12456,9 +12762,7 @@
           <t>通訊服務</t>
         </is>
       </c>
-      <c r="B301" t="n">
-        <v>4.5e-05</v>
-      </c>
+      <c r="B301" t="inlineStr"/>
       <c r="C301" t="n">
         <v>7.8e-05</v>
       </c>
@@ -12489,6 +12793,9 @@
       <c r="L301" t="n">
         <v>0.000153</v>
       </c>
+      <c r="M301" t="n">
+        <v>2.2e-05</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
@@ -12496,9 +12803,7 @@
           <t>通路經銷</t>
         </is>
       </c>
-      <c r="B302" t="n">
-        <v>5394.381835</v>
-      </c>
+      <c r="B302" t="inlineStr"/>
       <c r="C302" t="n">
         <v>7761.314791</v>
       </c>
@@ -12529,6 +12834,9 @@
       <c r="L302" t="n">
         <v>1209.852457333333</v>
       </c>
+      <c r="M302" t="n">
+        <v>849.224473</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
@@ -12536,9 +12844,7 @@
           <t>連接器設計、組裝及製造</t>
         </is>
       </c>
-      <c r="B303" t="n">
-        <v>23238.430701</v>
-      </c>
+      <c r="B303" t="inlineStr"/>
       <c r="C303" t="n">
         <v>23175.171397</v>
       </c>
@@ -12569,6 +12875,9 @@
       <c r="L303" t="n">
         <v>22650.776835</v>
       </c>
+      <c r="M303" t="n">
+        <v>22337.645989</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
@@ -12576,9 +12885,7 @@
           <t>連接線</t>
         </is>
       </c>
-      <c r="B304" t="n">
-        <v>8474.782746000001</v>
-      </c>
+      <c r="B304" t="inlineStr"/>
       <c r="C304" t="n">
         <v>4733.577961</v>
       </c>
@@ -12609,6 +12916,9 @@
       <c r="L304" t="n">
         <v>5102.54494</v>
       </c>
+      <c r="M304" t="n">
+        <v>6216.572908</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
@@ -12616,9 +12926,7 @@
           <t>運動服務/顧問</t>
         </is>
       </c>
-      <c r="B305" t="n">
-        <v>4.5e-05</v>
-      </c>
+      <c r="B305" t="inlineStr"/>
       <c r="C305" t="n">
         <v>7.8e-05</v>
       </c>
@@ -12649,6 +12957,9 @@
       <c r="L305" t="n">
         <v>0.000153</v>
       </c>
+      <c r="M305" t="n">
+        <v>2.2e-05</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
@@ -12656,9 +12967,7 @@
           <t>運動用品</t>
         </is>
       </c>
-      <c r="B306" t="n">
-        <v>50.388033</v>
-      </c>
+      <c r="B306" t="inlineStr"/>
       <c r="C306" t="n">
         <v>34.09521</v>
       </c>
@@ -12689,6 +12998,9 @@
       <c r="L306" t="n">
         <v>16.328138</v>
       </c>
+      <c r="M306" t="n">
+        <v>26.040457</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
@@ -12696,9 +13008,7 @@
           <t>運動行銷/媒體</t>
         </is>
       </c>
-      <c r="B307" t="n">
-        <v>4.5e-05</v>
-      </c>
+      <c r="B307" t="inlineStr"/>
       <c r="C307" t="n">
         <v>7.8e-05</v>
       </c>
@@ -12729,6 +13039,9 @@
       <c r="L307" t="n">
         <v>0.000153</v>
       </c>
+      <c r="M307" t="n">
+        <v>2.2e-05</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
@@ -12736,9 +13049,7 @@
           <t>運算元件與設備</t>
         </is>
       </c>
-      <c r="B308" t="n">
-        <v>15475.832119</v>
-      </c>
+      <c r="B308" t="inlineStr"/>
       <c r="C308" t="n">
         <v>10336.603209</v>
       </c>
@@ -12769,6 +13080,9 @@
       <c r="L308" t="n">
         <v>16467.531498</v>
       </c>
+      <c r="M308" t="n">
+        <v>14449.347683</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
@@ -12776,9 +13090,7 @@
           <t>運算設備</t>
         </is>
       </c>
-      <c r="B309" t="n">
-        <v>26873.031009</v>
-      </c>
+      <c r="B309" t="inlineStr"/>
       <c r="C309" t="n">
         <v>17401.112639</v>
       </c>
@@ -12809,6 +13121,9 @@
       <c r="L309" t="n">
         <v>21002.158983</v>
       </c>
+      <c r="M309" t="n">
+        <v>19510.501187</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
@@ -12816,9 +13131,7 @@
           <t>運輸工具</t>
         </is>
       </c>
-      <c r="B310" t="n">
-        <v>95.583513</v>
-      </c>
+      <c r="B310" t="inlineStr"/>
       <c r="C310" t="n">
         <v>91.75666200000001</v>
       </c>
@@ -12849,6 +13162,9 @@
       <c r="L310" t="n">
         <v>45.058887</v>
       </c>
+      <c r="M310" t="n">
+        <v>47.387771</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
@@ -12856,9 +13172,7 @@
           <t>配電管理設施</t>
         </is>
       </c>
-      <c r="B311" t="n">
-        <v>39890.089834</v>
-      </c>
+      <c r="B311" t="inlineStr"/>
       <c r="C311" t="n">
         <v>41280.649641</v>
       </c>
@@ -12889,6 +13203,9 @@
       <c r="L311" t="n">
         <v>27814.974397</v>
       </c>
+      <c r="M311" t="n">
+        <v>29062.340198</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
@@ -12896,9 +13213,7 @@
           <t>配電系統</t>
         </is>
       </c>
-      <c r="B312" t="n">
-        <v>13051.04149</v>
-      </c>
+      <c r="B312" t="inlineStr"/>
       <c r="C312" t="n">
         <v>13169.817631</v>
       </c>
@@ -12929,6 +13244,9 @@
       <c r="L312" t="n">
         <v>4240.479105</v>
       </c>
+      <c r="M312" t="n">
+        <v>6784.425626</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
@@ -12936,9 +13254,7 @@
           <t>酚醛樹脂</t>
         </is>
       </c>
-      <c r="B313" t="n">
-        <v>34027.818259</v>
-      </c>
+      <c r="B313" t="inlineStr"/>
       <c r="C313" t="n">
         <v>21424.514506</v>
       </c>
@@ -12969,6 +13285,9 @@
       <c r="L313" t="n">
         <v>7251.666655</v>
       </c>
+      <c r="M313" t="n">
+        <v>6211.89235</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
@@ -12976,9 +13295,7 @@
           <t>醫療器材代理銷售及通路</t>
         </is>
       </c>
-      <c r="B314" t="n">
-        <v>20426.668184</v>
-      </c>
+      <c r="B314" t="inlineStr"/>
       <c r="C314" t="n">
         <v>17341.056149</v>
       </c>
@@ -13007,7 +13324,10 @@
         <v>15590.52825</v>
       </c>
       <c r="L314" t="n">
-        <v>17348.591091</v>
+        <v>17168.880131</v>
+      </c>
+      <c r="M314" t="n">
+        <v>14659.56958175</v>
       </c>
     </row>
     <row r="315">
@@ -13016,9 +13336,7 @@
           <t>醫療器材研發、設計、製造</t>
         </is>
       </c>
-      <c r="B315" t="n">
-        <v>18145.837518</v>
-      </c>
+      <c r="B315" t="inlineStr"/>
       <c r="C315" t="n">
         <v>11950.711128</v>
       </c>
@@ -13047,7 +13365,10 @@
         <v>17504.469208</v>
       </c>
       <c r="L315" t="n">
-        <v>20243.376435</v>
+        <v>20247.410084</v>
+      </c>
+      <c r="M315" t="n">
+        <v>19076.291715</v>
       </c>
     </row>
     <row r="316">
@@ -13056,9 +13377,7 @@
           <t>醫療院所</t>
         </is>
       </c>
-      <c r="B316" t="n">
-        <v>50.234876</v>
-      </c>
+      <c r="B316" t="inlineStr"/>
       <c r="C316" t="n">
         <v>32.233037</v>
       </c>
@@ -13089,6 +13408,9 @@
       <c r="L316" t="n">
         <v>26.991676</v>
       </c>
+      <c r="M316" t="n">
+        <v>105.413049</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
@@ -13096,9 +13418,7 @@
           <t>金屬、塑膠模具</t>
         </is>
       </c>
-      <c r="B317" t="n">
-        <v>13099.720304</v>
-      </c>
+      <c r="B317" t="inlineStr"/>
       <c r="C317" t="n">
         <v>18262.887513</v>
       </c>
@@ -13127,7 +13447,10 @@
         <v>16728.448958</v>
       </c>
       <c r="L317" t="n">
-        <v>14581.838051</v>
+        <v>14598.088129</v>
+      </c>
+      <c r="M317" t="n">
+        <v>9682.570436</v>
       </c>
     </row>
     <row r="318">
@@ -13136,9 +13459,7 @@
           <t>金屬加工用機械</t>
         </is>
       </c>
-      <c r="B318" t="n">
-        <v>4888.155294</v>
-      </c>
+      <c r="B318" t="inlineStr"/>
       <c r="C318" t="n">
         <v>8965.192346</v>
       </c>
@@ -13169,6 +13490,9 @@
       <c r="L318" t="n">
         <v>4049.584412</v>
       </c>
+      <c r="M318" t="n">
+        <v>4641.998509</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
@@ -13176,9 +13500,7 @@
           <t>金屬加工處理</t>
         </is>
       </c>
-      <c r="B319" t="n">
-        <v>4686.53342</v>
-      </c>
+      <c r="B319" t="inlineStr"/>
       <c r="C319" t="n">
         <v>8553.376027</v>
       </c>
@@ -13207,7 +13529,10 @@
         <v>5808.800384</v>
       </c>
       <c r="L319" t="n">
-        <v>4275.975885</v>
+        <v>4258.178583</v>
+      </c>
+      <c r="M319" t="n">
+        <v>4339.467403</v>
       </c>
     </row>
     <row r="320">
@@ -13216,9 +13541,7 @@
           <t>金屬材料</t>
         </is>
       </c>
-      <c r="B320" t="n">
-        <v>552.472082</v>
-      </c>
+      <c r="B320" t="inlineStr"/>
       <c r="C320" t="n">
         <v>306.012852</v>
       </c>
@@ -13249,6 +13572,9 @@
       <c r="L320" t="n">
         <v>158.671383</v>
       </c>
+      <c r="M320" t="n">
+        <v>65.736065</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
@@ -13256,9 +13582,7 @@
           <t>金屬製品</t>
         </is>
       </c>
-      <c r="B321" t="n">
-        <v>461.813543</v>
-      </c>
+      <c r="B321" t="inlineStr"/>
       <c r="C321" t="n">
         <v>564.1230870000001</v>
       </c>
@@ -13289,6 +13613,9 @@
       <c r="L321" t="n">
         <v>426.9109855</v>
       </c>
+      <c r="M321" t="n">
+        <v>344.5643</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
@@ -13296,9 +13623,7 @@
           <t>金控業/銀行業/保險業</t>
         </is>
       </c>
-      <c r="B322" t="n">
-        <v>16729.105323</v>
-      </c>
+      <c r="B322" t="inlineStr"/>
       <c r="C322" t="n">
         <v>12757.742272</v>
       </c>
@@ -13329,6 +13654,9 @@
       <c r="L322" t="n">
         <v>13992.859045</v>
       </c>
+      <c r="M322" t="n">
+        <v>10206.63941</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
@@ -13336,9 +13664,7 @@
           <t>金流串接處理服務</t>
         </is>
       </c>
-      <c r="B323" t="n">
-        <v>90.91579299999999</v>
-      </c>
+      <c r="B323" t="inlineStr"/>
       <c r="C323" t="n">
         <v>138.655772</v>
       </c>
@@ -13369,6 +13695,9 @@
       <c r="L323" t="n">
         <v>113.730214</v>
       </c>
+      <c r="M323" t="n">
+        <v>100.434498</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
@@ -13376,9 +13705,7 @@
           <t>金融提款機(ATM)</t>
         </is>
       </c>
-      <c r="B324" t="n">
-        <v>21.951234</v>
-      </c>
+      <c r="B324" t="inlineStr"/>
       <c r="C324" t="n">
         <v>19.494967</v>
       </c>
@@ -13409,6 +13736,9 @@
       <c r="L324" t="n">
         <v>15.009668</v>
       </c>
+      <c r="M324" t="n">
+        <v>9.200265</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
@@ -13416,9 +13746,7 @@
           <t>鈑金</t>
         </is>
       </c>
-      <c r="B325" t="n">
-        <v>1492.726389</v>
-      </c>
+      <c r="B325" t="inlineStr"/>
       <c r="C325" t="n">
         <v>826.666105</v>
       </c>
@@ -13449,6 +13777,9 @@
       <c r="L325" t="n">
         <v>271.606693</v>
       </c>
+      <c r="M325" t="n">
+        <v>312.806351</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
@@ -13456,9 +13787,7 @@
           <t>銅箔</t>
         </is>
       </c>
-      <c r="B326" t="n">
-        <v>29970.379964</v>
-      </c>
+      <c r="B326" t="inlineStr"/>
       <c r="C326" t="n">
         <v>19697.369475</v>
       </c>
@@ -13489,6 +13818,9 @@
       <c r="L326" t="n">
         <v>5398.257591</v>
       </c>
+      <c r="M326" t="n">
+        <v>5239.073752</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
@@ -13496,9 +13828,7 @@
           <t>銅箔基板</t>
         </is>
       </c>
-      <c r="B327" t="n">
-        <v>43505.304184</v>
-      </c>
+      <c r="B327" t="inlineStr"/>
       <c r="C327" t="n">
         <v>29938.724483</v>
       </c>
@@ -13529,6 +13859,9 @@
       <c r="L327" t="n">
         <v>16061.779619</v>
       </c>
+      <c r="M327" t="n">
+        <v>15242.373787</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
@@ -13536,9 +13869,7 @@
           <t>銷售、進出口業務</t>
         </is>
       </c>
-      <c r="B328" t="n">
-        <v>2762.497522</v>
-      </c>
+      <c r="B328" t="inlineStr"/>
       <c r="C328" t="n">
         <v>2217.889333</v>
       </c>
@@ -13569,6 +13900,9 @@
       <c r="L328" t="n">
         <v>3308.971532</v>
       </c>
+      <c r="M328" t="n">
+        <v>4064.407434</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
@@ -13576,9 +13910,7 @@
           <t>鋁合金鋼圈</t>
         </is>
       </c>
-      <c r="B329" t="n">
-        <v>68.75461900000001</v>
-      </c>
+      <c r="B329" t="inlineStr"/>
       <c r="C329" t="n">
         <v>41.375398</v>
       </c>
@@ -13609,6 +13941,9 @@
       <c r="L329" t="n">
         <v>26.977103</v>
       </c>
+      <c r="M329" t="n">
+        <v>24.088963</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
@@ -13616,9 +13951,7 @@
           <t>鋰電池材料</t>
         </is>
       </c>
-      <c r="B330" t="n">
-        <v>27845.135701</v>
-      </c>
+      <c r="B330" t="inlineStr"/>
       <c r="C330" t="n">
         <v>22840.434619</v>
       </c>
@@ -13649,6 +13982,9 @@
       <c r="L330" t="n">
         <v>24895.52817</v>
       </c>
+      <c r="M330" t="n">
+        <v>23053.752017</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
@@ -13656,9 +13992,7 @@
           <t>鋼材</t>
         </is>
       </c>
-      <c r="B331" t="n">
-        <v>31.984887</v>
-      </c>
+      <c r="B331" t="inlineStr"/>
       <c r="C331" t="n">
         <v>43.703895</v>
       </c>
@@ -13689,6 +14023,9 @@
       <c r="L331" t="n">
         <v>45.758272</v>
       </c>
+      <c r="M331" t="n">
+        <v>49.863859</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
@@ -13696,9 +14033,7 @@
           <t>鋼筋</t>
         </is>
       </c>
-      <c r="B332" t="n">
-        <v>205.5851245</v>
-      </c>
+      <c r="B332" t="inlineStr"/>
       <c r="C332" t="n">
         <v>170.775608</v>
       </c>
@@ -13729,6 +14064,9 @@
       <c r="L332" t="n">
         <v>247.467495</v>
       </c>
+      <c r="M332" t="n">
+        <v>143.979723</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
@@ -13736,9 +14074,7 @@
           <t>鋼線鋼纜</t>
         </is>
       </c>
-      <c r="B333" t="n">
-        <v>7142.208854</v>
-      </c>
+      <c r="B333" t="inlineStr"/>
       <c r="C333" t="n">
         <v>5811.113852</v>
       </c>
@@ -13769,6 +14105,9 @@
       <c r="L333" t="n">
         <v>7354.605541</v>
       </c>
+      <c r="M333" t="n">
+        <v>7935.62915</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
@@ -13776,9 +14115,7 @@
           <t>鋼胚</t>
         </is>
       </c>
-      <c r="B334" t="n">
-        <v>1687.256159</v>
-      </c>
+      <c r="B334" t="inlineStr"/>
       <c r="C334" t="n">
         <v>1308.736348</v>
       </c>
@@ -13809,6 +14146,9 @@
       <c r="L334" t="n">
         <v>4168.039888</v>
       </c>
+      <c r="M334" t="n">
+        <v>2204.96159</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
@@ -13816,9 +14156,7 @@
           <t>鋼鑄鐵元件</t>
         </is>
       </c>
-      <c r="B335" t="n">
-        <v>5222.920125</v>
-      </c>
+      <c r="B335" t="inlineStr"/>
       <c r="C335" t="n">
         <v>7585.258584</v>
       </c>
@@ -13849,6 +14187,9 @@
       <c r="L335" t="n">
         <v>957.75424</v>
       </c>
+      <c r="M335" t="n">
+        <v>662.172953</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
@@ -13856,9 +14197,7 @@
           <t>錢包/資產管理</t>
         </is>
       </c>
-      <c r="B336" t="n">
-        <v>30.996195</v>
-      </c>
+      <c r="B336" t="inlineStr"/>
       <c r="C336" t="n">
         <v>23.262423</v>
       </c>
@@ -13889,6 +14228,9 @@
       <c r="L336" t="n">
         <v>32.775686</v>
       </c>
+      <c r="M336" t="n">
+        <v>25.805276</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
@@ -13896,9 +14238,7 @@
           <t>開發工具</t>
         </is>
       </c>
-      <c r="B337" t="n">
-        <v>363.111248</v>
-      </c>
+      <c r="B337" t="inlineStr"/>
       <c r="C337" t="n">
         <v>293.271325</v>
       </c>
@@ -13929,6 +14269,9 @@
       <c r="L337" t="n">
         <v>389.030727</v>
       </c>
+      <c r="M337" t="n">
+        <v>256.676854</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
@@ -13936,9 +14279,7 @@
           <t>隨身碟、記憶卡讀卡機</t>
         </is>
       </c>
-      <c r="B338" t="n">
-        <v>15060.844276</v>
-      </c>
+      <c r="B338" t="inlineStr"/>
       <c r="C338" t="n">
         <v>7422.06972</v>
       </c>
@@ -13969,6 +14310,9 @@
       <c r="L338" t="n">
         <v>9814.051195</v>
       </c>
+      <c r="M338" t="n">
+        <v>10608.266306</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
@@ -13976,9 +14320,7 @@
           <t>雲端作業系統</t>
         </is>
       </c>
-      <c r="B339" t="n">
-        <v>275.703679</v>
-      </c>
+      <c r="B339" t="inlineStr"/>
       <c r="C339" t="n">
         <v>195.798818</v>
       </c>
@@ -14009,6 +14351,9 @@
       <c r="L339" t="n">
         <v>156.8664863333333</v>
       </c>
+      <c r="M339" t="n">
+        <v>153.376246</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
@@ -14016,9 +14361,7 @@
           <t>雲端安全</t>
         </is>
       </c>
-      <c r="B340" t="n">
-        <v>271.933606</v>
-      </c>
+      <c r="B340" t="inlineStr"/>
       <c r="C340" t="n">
         <v>189.085869</v>
       </c>
@@ -14049,6 +14392,9 @@
       <c r="L340" t="n">
         <v>172.033284</v>
       </c>
+      <c r="M340" t="n">
+        <v>160.970279</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
@@ -14056,9 +14402,7 @@
           <t>雲端平台</t>
         </is>
       </c>
-      <c r="B341" t="n">
-        <v>2798.834562</v>
-      </c>
+      <c r="B341" t="inlineStr"/>
       <c r="C341" t="n">
         <v>2104.034024</v>
       </c>
@@ -14089,6 +14433,9 @@
       <c r="L341" t="n">
         <v>2017.462916666667</v>
       </c>
+      <c r="M341" t="n">
+        <v>1756.757851</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
@@ -14096,9 +14443,7 @@
           <t>雲端應用服務</t>
         </is>
       </c>
-      <c r="B342" t="n">
-        <v>18743.036647</v>
-      </c>
+      <c r="B342" t="inlineStr"/>
       <c r="C342" t="n">
         <v>12309.744519</v>
       </c>
@@ -14129,6 +14474,9 @@
       <c r="L342" t="n">
         <v>20994.49928033333</v>
       </c>
+      <c r="M342" t="n">
+        <v>19256.017067</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
@@ -14136,9 +14484,7 @@
           <t>零售通路</t>
         </is>
       </c>
-      <c r="B343" t="n">
-        <v>6151.255678</v>
-      </c>
+      <c r="B343" t="inlineStr"/>
       <c r="C343" t="n">
         <v>8694.33288075</v>
       </c>
@@ -14169,6 +14515,9 @@
       <c r="L343" t="n">
         <v>1531.042148</v>
       </c>
+      <c r="M343" t="n">
+        <v>1236.509877</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
@@ -14176,38 +14525,39 @@
           <t>零組件/材料</t>
         </is>
       </c>
-      <c r="B344" t="n">
-        <v>16694.644026</v>
-      </c>
+      <c r="B344" t="inlineStr"/>
       <c r="C344" t="n">
-        <v>14545.57741</v>
+        <v>14545.610538</v>
       </c>
       <c r="D344" t="n">
-        <v>27076.278181</v>
+        <v>27076.318741</v>
       </c>
       <c r="E344" t="n">
-        <v>30250.954792</v>
+        <v>30250.982061</v>
       </c>
       <c r="F344" t="n">
-        <v>37999.508711</v>
+        <v>37999.529797</v>
       </c>
       <c r="G344" t="n">
-        <v>31968.262291</v>
+        <v>31968.28458</v>
       </c>
       <c r="H344" t="n">
-        <v>19473.513451</v>
+        <v>19473.531757</v>
       </c>
       <c r="I344" t="n">
-        <v>23638.954786</v>
+        <v>23638.964981</v>
       </c>
       <c r="J344" t="n">
-        <v>28412.291053</v>
+        <v>28412.326916</v>
       </c>
       <c r="K344" t="n">
-        <v>25083.489963</v>
+        <v>25083.530969</v>
       </c>
       <c r="L344" t="n">
-        <v>27722.208034</v>
+        <v>27722.262615</v>
+      </c>
+      <c r="M344" t="n">
+        <v>24840.489151</v>
       </c>
     </row>
     <row r="345">
@@ -14216,9 +14566,7 @@
           <t>電信服務業</t>
         </is>
       </c>
-      <c r="B345" t="n">
-        <v>1730.451226</v>
-      </c>
+      <c r="B345" t="inlineStr"/>
       <c r="C345" t="n">
         <v>1357.076152</v>
       </c>
@@ -14249,6 +14597,9 @@
       <c r="L345" t="n">
         <v>2573.377192</v>
       </c>
+      <c r="M345" t="n">
+        <v>2254.418655</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="inlineStr">
@@ -14256,9 +14607,7 @@
           <t>電力系統</t>
         </is>
       </c>
-      <c r="B346" t="n">
-        <v>36263.158366</v>
-      </c>
+      <c r="B346" t="inlineStr"/>
       <c r="C346" t="n">
         <v>29646.618189</v>
       </c>
@@ -14289,6 +14638,9 @@
       <c r="L346" t="n">
         <v>23332.29423</v>
       </c>
+      <c r="M346" t="n">
+        <v>22626.953395</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="inlineStr">
@@ -14296,9 +14648,7 @@
           <t>電力設備</t>
         </is>
       </c>
-      <c r="B347" t="n">
-        <v>16808.96637</v>
-      </c>
+      <c r="B347" t="inlineStr"/>
       <c r="C347" t="n">
         <v>10358.817968</v>
       </c>
@@ -14329,6 +14679,9 @@
       <c r="L347" t="n">
         <v>18717.197622</v>
       </c>
+      <c r="M347" t="n">
+        <v>17509.116258</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="inlineStr">
@@ -14336,9 +14689,7 @@
           <t>電力零售業</t>
         </is>
       </c>
-      <c r="B348" t="n">
-        <v>1536.470674</v>
-      </c>
+      <c r="B348" t="inlineStr"/>
       <c r="C348" t="n">
         <v>816.685523</v>
       </c>
@@ -14369,6 +14720,9 @@
       <c r="L348" t="n">
         <v>582.973827</v>
       </c>
+      <c r="M348" t="n">
+        <v>422.091188</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="inlineStr">
@@ -14376,9 +14730,7 @@
           <t>電動汽車、電動機車、電動自行車</t>
         </is>
       </c>
-      <c r="B349" t="n">
-        <v>16046.560344</v>
-      </c>
+      <c r="B349" t="inlineStr"/>
       <c r="C349" t="n">
         <v>9517.022236000001</v>
       </c>
@@ -14409,6 +14761,9 @@
       <c r="L349" t="n">
         <v>16592.84141</v>
       </c>
+      <c r="M349" t="n">
+        <v>14360.965638</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="inlineStr">
@@ -14416,9 +14771,7 @@
           <t>電子書</t>
         </is>
       </c>
-      <c r="B350" t="n">
-        <v>0.6198399999999999</v>
-      </c>
+      <c r="B350" t="inlineStr"/>
       <c r="C350" t="n">
         <v>1.123504</v>
       </c>
@@ -14449,6 +14802,9 @@
       <c r="L350" t="n">
         <v>0.509023</v>
       </c>
+      <c r="M350" t="n">
+        <v>1.046588</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="inlineStr">
@@ -14456,9 +14812,7 @@
           <t>電子觸控白板</t>
         </is>
       </c>
-      <c r="B351" t="n">
-        <v>0.418728</v>
-      </c>
+      <c r="B351" t="inlineStr"/>
       <c r="C351" t="n">
         <v>0.194151</v>
       </c>
@@ -14489,6 +14843,9 @@
       <c r="L351" t="n">
         <v>0.532725</v>
       </c>
+      <c r="M351" t="n">
+        <v>1.529012</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
@@ -14496,38 +14853,39 @@
           <t>電子零組件、塑膠零件、五金零件</t>
         </is>
       </c>
-      <c r="B352" t="n">
-        <v>22340.978943</v>
-      </c>
+      <c r="B352" t="inlineStr"/>
       <c r="C352" t="n">
-        <v>13196.897767</v>
+        <v>13196.930895</v>
       </c>
       <c r="D352" t="n">
-        <v>28299.766513</v>
+        <v>28299.807073</v>
       </c>
       <c r="E352" t="n">
-        <v>32903.411259</v>
+        <v>32903.438528</v>
       </c>
       <c r="F352" t="n">
-        <v>29148.479499</v>
+        <v>29148.500585</v>
       </c>
       <c r="G352" t="n">
-        <v>19670.866941</v>
+        <v>19670.88923</v>
       </c>
       <c r="H352" t="n">
-        <v>15248.219974</v>
+        <v>15248.23828</v>
       </c>
       <c r="I352" t="n">
-        <v>18046.444419</v>
+        <v>18046.454614</v>
       </c>
       <c r="J352" t="n">
-        <v>23445.652773</v>
+        <v>23445.688636</v>
       </c>
       <c r="K352" t="n">
-        <v>19682.619932</v>
+        <v>19682.660938</v>
       </c>
       <c r="L352" t="n">
-        <v>20096.777947</v>
+        <v>19917.121568</v>
+      </c>
+      <c r="M352" t="n">
+        <v>19191.18453</v>
       </c>
     </row>
     <row r="353">
@@ -14536,9 +14894,7 @@
           <t>電容器</t>
         </is>
       </c>
-      <c r="B353" t="n">
-        <v>56120.855322</v>
-      </c>
+      <c r="B353" t="inlineStr"/>
       <c r="C353" t="n">
         <v>32793.700749</v>
       </c>
@@ -14569,6 +14925,9 @@
       <c r="L353" t="n">
         <v>29446.610858</v>
       </c>
+      <c r="M353" t="n">
+        <v>21552.456895</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="inlineStr">
@@ -14576,9 +14935,7 @@
           <t>電容器材料(如電蝕／化成鋁箔、介面瓷粉)</t>
         </is>
       </c>
-      <c r="B354" t="n">
-        <v>5816.724149</v>
-      </c>
+      <c r="B354" t="inlineStr"/>
       <c r="C354" t="n">
         <v>5564.361051</v>
       </c>
@@ -14609,6 +14966,9 @@
       <c r="L354" t="n">
         <v>1255.131869</v>
       </c>
+      <c r="M354" t="n">
+        <v>800.421575</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
@@ -14616,9 +14976,7 @@
           <t>電感器</t>
         </is>
       </c>
-      <c r="B355" t="n">
-        <v>52130.936566</v>
-      </c>
+      <c r="B355" t="inlineStr"/>
       <c r="C355" t="n">
         <v>31146.438399</v>
       </c>
@@ -14647,7 +15005,10 @@
         <v>22254.495631</v>
       </c>
       <c r="L355" t="n">
-        <v>28529.16849</v>
+        <v>28406.997355</v>
+      </c>
+      <c r="M355" t="n">
+        <v>20521.127118</v>
       </c>
     </row>
     <row r="356">
@@ -14656,9 +15017,7 @@
           <t>電感器材料(如鐵氧體、導電漿墨)</t>
         </is>
       </c>
-      <c r="B356" t="n">
-        <v>1105.233394</v>
-      </c>
+      <c r="B356" t="inlineStr"/>
       <c r="C356" t="n">
         <v>938.085509</v>
       </c>
@@ -14687,7 +15046,10 @@
         <v>277.585131</v>
       </c>
       <c r="L356" t="n">
-        <v>128.691418</v>
+        <v>6.520283</v>
+      </c>
+      <c r="M356" t="n">
+        <v>5.608408</v>
       </c>
     </row>
     <row r="357">
@@ -14696,9 +15058,7 @@
           <t>電控元件</t>
         </is>
       </c>
-      <c r="B357" t="n">
-        <v>48729.623268</v>
-      </c>
+      <c r="B357" t="inlineStr"/>
       <c r="C357" t="n">
         <v>31187.990868</v>
       </c>
@@ -14729,6 +15089,9 @@
       <c r="L357" t="n">
         <v>23454.693585</v>
       </c>
+      <c r="M357" t="n">
+        <v>19877.445133</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="inlineStr">
@@ -14736,9 +15099,7 @@
           <t>電池</t>
         </is>
       </c>
-      <c r="B358" t="n">
-        <v>659.143339</v>
-      </c>
+      <c r="B358" t="inlineStr"/>
       <c r="C358" t="n">
         <v>274.93103</v>
       </c>
@@ -14769,6 +15130,9 @@
       <c r="L358" t="n">
         <v>165.850445</v>
       </c>
+      <c r="M358" t="n">
+        <v>106.377509</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
@@ -14776,9 +15140,7 @@
           <t>電池模組</t>
         </is>
       </c>
-      <c r="B359" t="n">
-        <v>18192.626515</v>
-      </c>
+      <c r="B359" t="inlineStr"/>
       <c r="C359" t="n">
         <v>13596.565918</v>
       </c>
@@ -14809,6 +15171,9 @@
       <c r="L359" t="n">
         <v>18193.45396</v>
       </c>
+      <c r="M359" t="n">
+        <v>17283.994727</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="inlineStr">
@@ -14816,9 +15181,7 @@
           <t>電池芯</t>
         </is>
       </c>
-      <c r="B360" t="n">
-        <v>17424.210888</v>
-      </c>
+      <c r="B360" t="inlineStr"/>
       <c r="C360" t="n">
         <v>13220.880203</v>
       </c>
@@ -14849,6 +15212,9 @@
       <c r="L360" t="n">
         <v>18037.734099</v>
       </c>
+      <c r="M360" t="n">
+        <v>17122.566657</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
@@ -14856,9 +15222,7 @@
           <t>電源供應器</t>
         </is>
       </c>
-      <c r="B361" t="n">
-        <v>31691.629368</v>
-      </c>
+      <c r="B361" t="inlineStr"/>
       <c r="C361" t="n">
         <v>28298.489633</v>
       </c>
@@ -14889,6 +15253,9 @@
       <c r="L361" t="n">
         <v>24858.512605</v>
       </c>
+      <c r="M361" t="n">
+        <v>24208.988059</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="inlineStr">
@@ -14896,9 +15263,7 @@
           <t>電網營造</t>
         </is>
       </c>
-      <c r="B362" t="n">
-        <v>8759.011907</v>
-      </c>
+      <c r="B362" t="inlineStr"/>
       <c r="C362" t="n">
         <v>9016.996552000001</v>
       </c>
@@ -14929,6 +15294,9 @@
       <c r="L362" t="n">
         <v>3716.814715</v>
       </c>
+      <c r="M362" t="n">
+        <v>5791.528664</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
@@ -14936,9 +15304,7 @@
           <t>電網維運</t>
         </is>
       </c>
-      <c r="B363" t="n">
-        <v>176.322171</v>
-      </c>
+      <c r="B363" t="inlineStr"/>
       <c r="C363" t="n">
         <v>164.858382</v>
       </c>
@@ -14969,6 +15335,9 @@
       <c r="L363" t="n">
         <v>225.166747</v>
       </c>
+      <c r="M363" t="n">
+        <v>141.422701</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
@@ -14976,9 +15345,7 @@
           <t>電纜</t>
         </is>
       </c>
-      <c r="B364" t="n">
-        <v>8395.870534</v>
-      </c>
+      <c r="B364" t="inlineStr"/>
       <c r="C364" t="n">
         <v>8107.809038</v>
       </c>
@@ -15009,6 +15376,9 @@
       <c r="L364" t="n">
         <v>8406.261193</v>
       </c>
+      <c r="M364" t="n">
+        <v>8677.70037</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
@@ -15016,9 +15386,7 @@
           <t>電腦視覺</t>
         </is>
       </c>
-      <c r="B365" t="n">
-        <v>15304.157655</v>
-      </c>
+      <c r="B365" t="inlineStr"/>
       <c r="C365" t="n">
         <v>8995.36138</v>
       </c>
@@ -15049,6 +15417,9 @@
       <c r="L365" t="n">
         <v>16471.14020933333</v>
       </c>
+      <c r="M365" t="n">
+        <v>14176.76763</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="inlineStr">
@@ -15056,9 +15427,7 @@
           <t>電腦設備</t>
         </is>
       </c>
-      <c r="B366" t="n">
-        <v>33362.869157</v>
-      </c>
+      <c r="B366" t="inlineStr"/>
       <c r="C366" t="n">
         <v>22728.70888</v>
       </c>
@@ -15089,6 +15458,9 @@
       <c r="L366" t="n">
         <v>27169.63545</v>
       </c>
+      <c r="M366" t="n">
+        <v>25792.534005</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="inlineStr">
@@ -15096,9 +15468,7 @@
           <t>電視</t>
         </is>
       </c>
-      <c r="B367" t="n">
-        <v>8070.326084</v>
-      </c>
+      <c r="B367" t="inlineStr"/>
       <c r="C367" t="n">
         <v>11459.758234</v>
       </c>
@@ -15129,6 +15499,9 @@
       <c r="L367" t="n">
         <v>3175.622826</v>
       </c>
+      <c r="M367" t="n">
+        <v>1910.837545</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
@@ -15136,9 +15509,7 @@
           <t>電鍍材料</t>
         </is>
       </c>
-      <c r="B368" t="n">
-        <v>532.709875</v>
-      </c>
+      <c r="B368" t="inlineStr"/>
       <c r="C368" t="n">
         <v>289.712794</v>
       </c>
@@ -15169,6 +15540,9 @@
       <c r="L368" t="n">
         <v>152.617711</v>
       </c>
+      <c r="M368" t="n">
+        <v>63.463724</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="inlineStr">
@@ -15176,9 +15550,7 @@
           <t>電阻器</t>
         </is>
       </c>
-      <c r="B369" t="n">
-        <v>56737.768188</v>
-      </c>
+      <c r="B369" t="inlineStr"/>
       <c r="C369" t="n">
         <v>37846.20613</v>
       </c>
@@ -15209,6 +15581,9 @@
       <c r="L369" t="n">
         <v>29328.556382</v>
       </c>
+      <c r="M369" t="n">
+        <v>21102.778277</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="inlineStr">
@@ -15216,9 +15591,7 @@
           <t>電阻器材料(氧化鋁陶瓷基板、導電漿墨)</t>
         </is>
       </c>
-      <c r="B370" t="n">
-        <v>285.768388</v>
-      </c>
+      <c r="B370" t="inlineStr"/>
       <c r="C370" t="n">
         <v>273.106091</v>
       </c>
@@ -15249,6 +15622,9 @@
       <c r="L370" t="n">
         <v>204.103008</v>
       </c>
+      <c r="M370" t="n">
+        <v>176.969163</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="inlineStr">
@@ -15256,9 +15632,7 @@
           <t>面板</t>
         </is>
       </c>
-      <c r="B371" t="n">
-        <v>21119.678689</v>
-      </c>
+      <c r="B371" t="inlineStr"/>
       <c r="C371" t="n">
         <v>24261.627864</v>
       </c>
@@ -15287,7 +15661,10 @@
         <v>23204.194807</v>
       </c>
       <c r="L371" t="n">
-        <v>12350.788364</v>
+        <v>12322.907408</v>
+      </c>
+      <c r="M371" t="n">
+        <v>9889.286767</v>
       </c>
     </row>
     <row r="372">
@@ -15296,9 +15673,7 @@
           <t>預拌混凝土</t>
         </is>
       </c>
-      <c r="B372" t="n">
-        <v>2167.648675</v>
-      </c>
+      <c r="B372" t="inlineStr"/>
       <c r="C372" t="n">
         <v>1576.798285</v>
       </c>
@@ -15329,6 +15704,9 @@
       <c r="L372" t="n">
         <v>1309.702257</v>
       </c>
+      <c r="M372" t="n">
+        <v>905.811833</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="inlineStr">
@@ -15336,9 +15714,7 @@
           <t>領域方案</t>
         </is>
       </c>
-      <c r="B373" t="n">
-        <v>30.996195</v>
-      </c>
+      <c r="B373" t="inlineStr"/>
       <c r="C373" t="n">
         <v>23.262423</v>
       </c>
@@ -15369,6 +15745,9 @@
       <c r="L373" t="n">
         <v>32.775686</v>
       </c>
+      <c r="M373" t="n">
+        <v>25.805276</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="inlineStr">
@@ -15376,9 +15755,7 @@
           <t>領域解決方案</t>
         </is>
       </c>
-      <c r="B374" t="n">
-        <v>30457.715437</v>
-      </c>
+      <c r="B374" t="inlineStr"/>
       <c r="C374" t="n">
         <v>17960.15316</v>
       </c>
@@ -15409,6 +15786,9 @@
       <c r="L374" t="n">
         <v>32620.39490766667</v>
       </c>
+      <c r="M374" t="n">
+        <v>28132.638424</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="inlineStr">
@@ -15416,9 +15796,7 @@
           <t>頭顯裝置品牌廠</t>
         </is>
       </c>
-      <c r="B375" t="n">
-        <v>332.826429</v>
-      </c>
+      <c r="B375" t="inlineStr"/>
       <c r="C375" t="n">
         <v>270.586591</v>
       </c>
@@ -15449,6 +15827,9 @@
       <c r="L375" t="n">
         <v>357.115714</v>
       </c>
+      <c r="M375" t="n">
+        <v>231.944493</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="inlineStr">
@@ -15456,9 +15837,7 @@
           <t>顏染料</t>
         </is>
       </c>
-      <c r="B376" t="n">
-        <v>311.880923</v>
-      </c>
+      <c r="B376" t="inlineStr"/>
       <c r="C376" t="n">
         <v>173.078416</v>
       </c>
@@ -15489,6 +15868,9 @@
       <c r="L376" t="n">
         <v>74.18924</v>
       </c>
+      <c r="M376" t="n">
+        <v>232.979874</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="inlineStr">
@@ -15496,9 +15878,7 @@
           <t>顧問諮詢</t>
         </is>
       </c>
-      <c r="B377" t="n">
-        <v>46859.101485</v>
-      </c>
+      <c r="B377" t="inlineStr"/>
       <c r="C377" t="n">
         <v>28039.910955</v>
       </c>
@@ -15529,6 +15909,9 @@
       <c r="L377" t="n">
         <v>51015.623059</v>
       </c>
+      <c r="M377" t="n">
+        <v>45553.214423</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="inlineStr">
@@ -15536,9 +15919,7 @@
           <t>顯示卡</t>
         </is>
       </c>
-      <c r="B378" t="n">
-        <v>5112.91115</v>
-      </c>
+      <c r="B378" t="inlineStr"/>
       <c r="C378" t="n">
         <v>4034.218264</v>
       </c>
@@ -15569,6 +15950,9 @@
       <c r="L378" t="n">
         <v>4083.549874</v>
       </c>
+      <c r="M378" t="n">
+        <v>3158.036425</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="inlineStr">
@@ -15576,9 +15960,7 @@
           <t>顯示器模組</t>
         </is>
       </c>
-      <c r="B379" t="n">
-        <v>10834.346893</v>
-      </c>
+      <c r="B379" t="inlineStr"/>
       <c r="C379" t="n">
         <v>9624.475633</v>
       </c>
@@ -15607,7 +15989,10 @@
         <v>4894.149979</v>
       </c>
       <c r="L379" t="n">
-        <v>3542.935117</v>
+        <v>3515.054161</v>
+      </c>
+      <c r="M379" t="n">
+        <v>6361.772737</v>
       </c>
     </row>
     <row r="380">
@@ -15616,9 +16001,7 @@
           <t>風場營造</t>
         </is>
       </c>
-      <c r="B380" t="n">
-        <v>4442.928177</v>
-      </c>
+      <c r="B380" t="inlineStr"/>
       <c r="C380" t="n">
         <v>9066.852843000001</v>
       </c>
@@ -15649,6 +16032,9 @@
       <c r="L380" t="n">
         <v>1778.43081</v>
       </c>
+      <c r="M380" t="n">
+        <v>1542.804108</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="inlineStr">
@@ -15656,9 +16042,7 @@
           <t>風場規劃</t>
         </is>
       </c>
-      <c r="B381" t="n">
-        <v>4321.239981</v>
-      </c>
+      <c r="B381" t="inlineStr"/>
       <c r="C381" t="n">
         <v>8665.336945999999</v>
       </c>
@@ -15689,6 +16073,9 @@
       <c r="L381" t="n">
         <v>1561.352572</v>
       </c>
+      <c r="M381" t="n">
+        <v>1387.790376</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="inlineStr">
@@ -15696,9 +16083,7 @@
           <t>風場開發</t>
         </is>
       </c>
-      <c r="B382" t="n">
-        <v>1847.152064</v>
-      </c>
+      <c r="B382" t="inlineStr"/>
       <c r="C382" t="n">
         <v>1734.479322</v>
       </c>
@@ -15729,6 +16114,9 @@
       <c r="L382" t="n">
         <v>691.331111</v>
       </c>
+      <c r="M382" t="n">
+        <v>537.080619</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="inlineStr">
@@ -15736,9 +16124,7 @@
           <t>風機維護</t>
         </is>
       </c>
-      <c r="B383" t="n">
-        <v>252.185244</v>
-      </c>
+      <c r="B383" t="inlineStr"/>
       <c r="C383" t="n">
         <v>672.869729</v>
       </c>
@@ -15769,6 +16155,9 @@
       <c r="L383" t="n">
         <v>148.036229</v>
       </c>
+      <c r="M383" t="n">
+        <v>96.96392899999999</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="inlineStr">
@@ -15776,9 +16165,7 @@
           <t>餐飲連鎖</t>
         </is>
       </c>
-      <c r="B384" t="n">
-        <v>240.73373</v>
-      </c>
+      <c r="B384" t="inlineStr"/>
       <c r="C384" t="n">
         <v>192.121532</v>
       </c>
@@ -15809,6 +16196,9 @@
       <c r="L384" t="n">
         <v>268.071678</v>
       </c>
+      <c r="M384" t="n">
+        <v>163.997719</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="inlineStr">
@@ -15816,9 +16206,7 @@
           <t>驅動IC</t>
         </is>
       </c>
-      <c r="B385" t="n">
-        <v>137.411544</v>
-      </c>
+      <c r="B385" t="inlineStr"/>
       <c r="C385" t="n">
         <v>327.293886</v>
       </c>
@@ -15849,6 +16237,9 @@
       <c r="L385" t="n">
         <v>165.868986</v>
       </c>
+      <c r="M385" t="n">
+        <v>127.163915</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="inlineStr">
@@ -15856,9 +16247,7 @@
           <t>高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="B386" t="n">
-        <v>45417.315565</v>
-      </c>
+      <c r="B386" t="inlineStr"/>
       <c r="C386" t="n">
         <v>46767.448635</v>
       </c>
@@ -15889,6 +16278,9 @@
       <c r="L386" t="n">
         <v>32912.575697</v>
       </c>
+      <c r="M386" t="n">
+        <v>33648.526189</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="inlineStr">
@@ -15896,9 +16288,7 @@
           <t>高壓AMI</t>
         </is>
       </c>
-      <c r="B387" t="n">
-        <v>9351.176251000001</v>
-      </c>
+      <c r="B387" t="inlineStr"/>
       <c r="C387" t="n">
         <v>15674.9287</v>
       </c>
@@ -15929,6 +16319,9 @@
       <c r="L387" t="n">
         <v>2564.500101</v>
       </c>
+      <c r="M387" t="n">
+        <v>2049.080192</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="inlineStr">
@@ -15936,9 +16329,7 @@
           <t>高爾夫球具業</t>
         </is>
       </c>
-      <c r="B388" t="n">
-        <v>105.155391</v>
-      </c>
+      <c r="B388" t="inlineStr"/>
       <c r="C388" t="n">
         <v>71.873036</v>
       </c>
@@ -15969,6 +16360,9 @@
       <c r="L388" t="n">
         <v>80.554063</v>
       </c>
+      <c r="M388" t="n">
+        <v>73.078051</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="inlineStr">
@@ -15976,9 +16370,7 @@
           <t>齒輪箱</t>
         </is>
       </c>
-      <c r="B389" t="n">
-        <v>81.447537</v>
-      </c>
+      <c r="B389" t="inlineStr"/>
       <c r="C389" t="n">
         <v>35.521247</v>
       </c>
@@ -16008,6 +16400,9 @@
       </c>
       <c r="L389" t="n">
         <v>14.243239</v>
+      </c>
+      <c r="M389" t="n">
+        <v>24.459851</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_4.xlsx
+++ b/Result/analyze_4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L389"/>
+  <dimension ref="A1:M389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -487,6 +487,11 @@
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
         </is>
       </c>
     </row>
@@ -496,9 +501,7 @@
           <t>AGV及AMR</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0.129047</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0.277592</v>
       </c>
@@ -529,6 +532,9 @@
       <c r="L2" t="n">
         <v>0.095307</v>
       </c>
+      <c r="M2" t="n">
+        <v>0.153435</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -536,9 +542,7 @@
           <t>BIOS(嵌入式軟體)</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>1518.567344</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>1340.703043</v>
       </c>
@@ -569,6 +573,9 @@
       <c r="L3" t="n">
         <v>2134.184235</v>
       </c>
+      <c r="M3" t="n">
+        <v>2126.853298</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -576,9 +583,7 @@
           <t>BaaS</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>178.035564</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>402.315751</v>
       </c>
@@ -609,6 +614,9 @@
       <c r="L4" t="n">
         <v>34.080571</v>
       </c>
+      <c r="M4" t="n">
+        <v>31.111897</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -616,9 +624,7 @@
           <t>HMI</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0.014905</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0.010707</v>
       </c>
@@ -649,6 +655,9 @@
       <c r="L5" t="n">
         <v>0.012723</v>
       </c>
+      <c r="M5" t="n">
+        <v>0.005844</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -656,9 +665,7 @@
           <t>IC/晶圓製造</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>122219.646463</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>157539.152118</v>
       </c>
@@ -687,7 +694,10 @@
         <v>155225.513463</v>
       </c>
       <c r="L6" t="n">
-        <v>137095.329519</v>
+        <v>138073.718008</v>
+      </c>
+      <c r="M6" t="n">
+        <v>175932.824065</v>
       </c>
     </row>
     <row r="7">
@@ -696,9 +706,7 @@
           <t>IC封裝測試</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>43036.047025</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>45458.327836</v>
       </c>
@@ -729,6 +737,9 @@
       <c r="L7" t="n">
         <v>50524.051913</v>
       </c>
+      <c r="M7" t="n">
+        <v>56015.631059</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -736,9 +747,7 @@
           <t>IC模組</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>33182.34154</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>36561.289772</v>
       </c>
@@ -767,7 +776,10 @@
         <v>14939.098151</v>
       </c>
       <c r="L8" t="n">
-        <v>22370.007741</v>
+        <v>22435.590241</v>
+      </c>
+      <c r="M8" t="n">
+        <v>18927.334664</v>
       </c>
     </row>
     <row r="9">
@@ -777,37 +789,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72461.510671</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>143250.460075</v>
+        <v>143250.459155</v>
       </c>
       <c r="D9" t="n">
-        <v>133152.357809</v>
+        <v>133152.357192</v>
       </c>
       <c r="E9" t="n">
-        <v>140727.794882</v>
+        <v>140727.794386</v>
       </c>
       <c r="F9" t="n">
-        <v>132650.09231675</v>
+        <v>132650.09142975</v>
       </c>
       <c r="G9" t="n">
-        <v>199486.256707</v>
+        <v>199486.256383</v>
       </c>
       <c r="H9" t="n">
-        <v>171569.766576</v>
+        <v>171569.766559</v>
       </c>
       <c r="I9" t="n">
-        <v>127912.286462</v>
+        <v>126663.433105</v>
       </c>
       <c r="J9" t="n">
-        <v>196758.361546</v>
+        <v>195139.500813</v>
       </c>
       <c r="K9" t="n">
-        <v>120480.808533</v>
+        <v>119594.00052</v>
       </c>
       <c r="L9" t="n">
-        <v>123218.513445</v>
+        <v>122274.235823</v>
+      </c>
+      <c r="M9" t="n">
+        <v>123061.684217</v>
       </c>
     </row>
     <row r="10">
@@ -816,9 +831,7 @@
           <t>IC通路</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>30543.775643</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>26321.34255525</v>
       </c>
@@ -838,16 +851,19 @@
         <v>23755.360791</v>
       </c>
       <c r="I10" t="n">
-        <v>22269.859447</v>
+        <v>22384.519273</v>
       </c>
       <c r="J10" t="n">
-        <v>21386.297216</v>
+        <v>21460.330725</v>
       </c>
       <c r="K10" t="n">
-        <v>13325.624012</v>
+        <v>13369.242291</v>
       </c>
       <c r="L10" t="n">
-        <v>21965.568739</v>
+        <v>22080.088132</v>
+      </c>
+      <c r="M10" t="n">
+        <v>16080.302499</v>
       </c>
     </row>
     <row r="11">
@@ -856,9 +872,7 @@
           <t>IP設計/IC設計代工服務</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>15277.873527</v>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>20669.305573</v>
       </c>
@@ -889,6 +903,9 @@
       <c r="L11" t="n">
         <v>19277.466982</v>
       </c>
+      <c r="M11" t="n">
+        <v>16777.407974</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -896,9 +913,7 @@
           <t>ITO導電基板</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>169.826895</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>90.34866599999999</v>
       </c>
@@ -929,6 +944,9 @@
       <c r="L12" t="n">
         <v>33.608822</v>
       </c>
+      <c r="M12" t="n">
+        <v>43.872605</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -936,9 +954,7 @@
           <t>ITO導電玻璃</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0.01944</v>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0.018236</v>
       </c>
@@ -969,6 +985,9 @@
       <c r="L13" t="n">
         <v>0.266328</v>
       </c>
+      <c r="M13" t="n">
+        <v>0.405285</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -976,9 +995,7 @@
           <t>ITO導電薄膜</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>24.588051</v>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>21.287644</v>
       </c>
@@ -1009,6 +1026,9 @@
       <c r="L14" t="n">
         <v>7.912691</v>
       </c>
+      <c r="M14" t="n">
+        <v>7.775203</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1016,9 +1036,7 @@
           <t>ITO靶材</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0.833653</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0.950731</v>
       </c>
@@ -1049,6 +1067,9 @@
       <c r="L15" t="n">
         <v>0.343892</v>
       </c>
+      <c r="M15" t="n">
+        <v>0.279336</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1056,9 +1077,7 @@
           <t>PET膜</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>0.014196</v>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0.008229</v>
       </c>
@@ -1089,6 +1108,9 @@
       <c r="L16" t="n">
         <v>0.003302</v>
       </c>
+      <c r="M16" t="n">
+        <v>0.005687</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1096,9 +1118,7 @@
           <t>一般零售</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>87.55143700000001</v>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>51.247042</v>
       </c>
@@ -1129,6 +1149,9 @@
       <c r="L17" t="n">
         <v>82.370683</v>
       </c>
+      <c r="M17" t="n">
+        <v>113.50059525</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1136,9 +1159,7 @@
           <t>不鏽鋼型鋼</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>28.036351</v>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>49.412101</v>
       </c>
@@ -1169,6 +1190,9 @@
       <c r="L18" t="n">
         <v>33.569296</v>
       </c>
+      <c r="M18" t="n">
+        <v>55.399642</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1176,9 +1200,7 @@
           <t>不鏽鋼棒線</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>4858.922952</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>2627.580208</v>
       </c>
@@ -1209,6 +1231,9 @@
       <c r="L19" t="n">
         <v>2133.958969</v>
       </c>
+      <c r="M19" t="n">
+        <v>3735.461963</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1216,9 +1241,7 @@
           <t>不鏽鋼胚</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>4839.105394</v>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>2605.88079</v>
       </c>
@@ -1249,6 +1272,9 @@
       <c r="L20" t="n">
         <v>2078.083435</v>
       </c>
+      <c r="M20" t="n">
+        <v>3688.666663</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1256,9 +1282,7 @@
           <t>中、西藥製劑</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>2481.57154</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>2875.666183</v>
       </c>
@@ -1289,6 +1313,9 @@
       <c r="L21" t="n">
         <v>2477.524035</v>
       </c>
+      <c r="M21" t="n">
+        <v>2308.545044</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1296,9 +1323,7 @@
           <t>中央處理器</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>572.978487</v>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>289.764337</v>
       </c>
@@ -1329,6 +1354,9 @@
       <c r="L22" t="n">
         <v>99.977057</v>
       </c>
+      <c r="M22" t="n">
+        <v>151.465036</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1336,9 +1364,7 @@
           <t>中藥材、西藥原料藥</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>385.810327</v>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>420.119967</v>
       </c>
@@ -1369,6 +1395,9 @@
       <c r="L23" t="n">
         <v>1303.344746</v>
       </c>
+      <c r="M23" t="n">
+        <v>530.5121</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1376,9 +1405,7 @@
           <t>主/被動元件</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>2806.018519</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>1873.802907</v>
       </c>
@@ -1409,6 +1436,9 @@
       <c r="L24" t="n">
         <v>4714.747923</v>
       </c>
+      <c r="M24" t="n">
+        <v>2538.606962</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1416,9 +1446,7 @@
           <t>主機板</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>18618.985412</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>12964.596014</v>
       </c>
@@ -1449,6 +1477,9 @@
       <c r="L25" t="n">
         <v>14521.536841</v>
       </c>
+      <c r="M25" t="n">
+        <v>17512.698067</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1456,9 +1487,7 @@
           <t>乳製品</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>598.083581</v>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>757.742492</v>
       </c>
@@ -1489,6 +1518,9 @@
       <c r="L26" t="n">
         <v>611.1525339999999</v>
       </c>
+      <c r="M26" t="n">
+        <v>654.626404</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1496,9 +1528,7 @@
           <t>五金元件及零配件</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>1987.545945</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>1476.325786</v>
       </c>
@@ -1529,6 +1559,9 @@
       <c r="L27" t="n">
         <v>1756.323262</v>
       </c>
+      <c r="M27" t="n">
+        <v>1206.630153</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1536,9 +1569,7 @@
           <t>交易平台</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>217.065894</v>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>434.514043</v>
       </c>
@@ -1569,6 +1600,9 @@
       <c r="L28" t="n">
         <v>79.067735</v>
       </c>
+      <c r="M28" t="n">
+        <v>69.96997</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -1576,9 +1610,7 @@
           <t>交易撮(媒)合</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>8.965436</v>
-      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>3.937709</v>
       </c>
@@ -1609,6 +1641,9 @@
       <c r="L29" t="n">
         <v>7.252473</v>
       </c>
+      <c r="M29" t="n">
+        <v>4.518936</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -1616,9 +1651,7 @@
           <t>人造纖維</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>16835.247785</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>12390.964524</v>
       </c>
@@ -1647,7 +1680,10 @@
         <v>8407.839721</v>
       </c>
       <c r="L30" t="n">
-        <v>6493.949313</v>
+        <v>6519.776553</v>
+      </c>
+      <c r="M30" t="n">
+        <v>13899.635485</v>
       </c>
     </row>
     <row r="31">
@@ -1656,9 +1692,7 @@
           <t>人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>15470.775271</v>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>10584.02824</v>
       </c>
@@ -1678,16 +1712,19 @@
         <v>8375.418207999999</v>
       </c>
       <c r="I31" t="n">
-        <v>6837.273316</v>
+        <v>6837.343146</v>
       </c>
       <c r="J31" t="n">
-        <v>5828.418067</v>
+        <v>5828.508016</v>
       </c>
       <c r="K31" t="n">
-        <v>7315.83746</v>
+        <v>7315.92685</v>
       </c>
       <c r="L31" t="n">
-        <v>5607.062016</v>
+        <v>5607.092816</v>
+      </c>
+      <c r="M31" t="n">
+        <v>12507.278914</v>
       </c>
     </row>
     <row r="32">
@@ -1696,9 +1733,7 @@
           <t>休閒車業</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>32255.06698</v>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>27942.279311</v>
       </c>
@@ -1727,7 +1762,10 @@
         <v>13988.875505</v>
       </c>
       <c r="L32" t="n">
-        <v>23374.722659</v>
+        <v>23440.305159</v>
+      </c>
+      <c r="M32" t="n">
+        <v>19024.434734</v>
       </c>
     </row>
     <row r="33">
@@ -1736,9 +1774,7 @@
           <t>伺服器</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>41646.029784</v>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>40279.745925</v>
       </c>
@@ -1769,6 +1805,9 @@
       <c r="L33" t="n">
         <v>25810.45489</v>
       </c>
+      <c r="M33" t="n">
+        <v>26503.374599</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1776,9 +1815,7 @@
           <t>低壓AMI</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>14545.108211</v>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>7244.164113</v>
       </c>
@@ -1809,6 +1846,9 @@
       <c r="L34" t="n">
         <v>1956.693943</v>
       </c>
+      <c r="M34" t="n">
+        <v>1969.053502</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1816,9 +1856,7 @@
           <t>保健食品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>4637.981092</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>4014.543392</v>
       </c>
@@ -1849,6 +1887,9 @@
       <c r="L35" t="n">
         <v>1676.476963</v>
       </c>
+      <c r="M35" t="n">
+        <v>1748.852987</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1856,9 +1897,7 @@
           <t>保險</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>272.43736</v>
-      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>531.1727519999999</v>
       </c>
@@ -1889,6 +1928,9 @@
       <c r="L36" t="n">
         <v>141.360903</v>
       </c>
+      <c r="M36" t="n">
+        <v>110.493284</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1896,9 +1938,7 @@
           <t>保險桿</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>430.746629</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>428.349037</v>
       </c>
@@ -1929,6 +1969,9 @@
       <c r="L37" t="n">
         <v>298.112961</v>
       </c>
+      <c r="M37" t="n">
+        <v>278.770111</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1936,9 +1979,7 @@
           <t>個人、民間企業、政府機構</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>436.697624</v>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>199.477739</v>
       </c>
@@ -1969,6 +2010,9 @@
       <c r="L38" t="n">
         <v>78.193102</v>
       </c>
+      <c r="M38" t="n">
+        <v>75.959507</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -1976,9 +2020,7 @@
           <t>健身器材</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>61.59549</v>
-      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>61.611816</v>
       </c>
@@ -2009,6 +2051,9 @@
       <c r="L39" t="n">
         <v>120.859897</v>
       </c>
+      <c r="M39" t="n">
+        <v>57.443564</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -2016,9 +2061,7 @@
           <t>健身平台/APP</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>2627.052942</v>
-      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>4654.406159</v>
       </c>
@@ -2049,6 +2092,9 @@
       <c r="L40" t="n">
         <v>1186.338408</v>
       </c>
+      <c r="M40" t="n">
+        <v>1093.880364</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -2056,9 +2102,7 @@
           <t>傳動元件</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>37506.60277</v>
-      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
         <v>33541.953679</v>
       </c>
@@ -2087,7 +2131,10 @@
         <v>15441.332618</v>
       </c>
       <c r="L41" t="n">
-        <v>24086.456879</v>
+        <v>24298.867959</v>
+      </c>
+      <c r="M41" t="n">
+        <v>17158.063705</v>
       </c>
     </row>
     <row r="42">
@@ -2096,9 +2143,7 @@
           <t>儲存處理</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>1350.195757</v>
-      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
         <v>1047.160913</v>
       </c>
@@ -2129,6 +2174,9 @@
       <c r="L42" t="n">
         <v>394.987937</v>
       </c>
+      <c r="M42" t="n">
+        <v>368.63247</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -2136,9 +2184,7 @@
           <t>元件裝置</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>420.582932</v>
-      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
         <v>222.924562</v>
       </c>
@@ -2169,6 +2215,9 @@
       <c r="L43" t="n">
         <v>121.424945</v>
       </c>
+      <c r="M43" t="n">
+        <v>190.752158</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -2176,9 +2225,7 @@
           <t>光學鏡片、鏡頭</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>19889.053207</v>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
         <v>14337.873047</v>
       </c>
@@ -2209,6 +2256,9 @@
       <c r="L44" t="n">
         <v>15429.581734</v>
       </c>
+      <c r="M44" t="n">
+        <v>16887.701479</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -2216,9 +2266,7 @@
           <t>光源/磊晶</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>1915.601171</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
         <v>4664.132077</v>
       </c>
@@ -2249,6 +2297,9 @@
       <c r="L45" t="n">
         <v>2291.804149</v>
       </c>
+      <c r="M45" t="n">
+        <v>2557.996264</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -2256,9 +2307,7 @@
           <t>光碟機</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>1518.504415</v>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
         <v>1340.564167</v>
       </c>
@@ -2289,6 +2338,9 @@
       <c r="L46" t="n">
         <v>2134.022734</v>
       </c>
+      <c r="M46" t="n">
+        <v>2126.7208</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -2296,9 +2348,7 @@
           <t>光碟片</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>241.02834</v>
-      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
         <v>246.68278</v>
       </c>
@@ -2329,6 +2379,9 @@
       <c r="L47" t="n">
         <v>305.318549</v>
       </c>
+      <c r="M47" t="n">
+        <v>164.943783</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -2336,9 +2389,7 @@
           <t>光罩</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>208.51006</v>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
         <v>131.6083</v>
       </c>
@@ -2369,6 +2420,9 @@
       <c r="L48" t="n">
         <v>41.015389</v>
       </c>
+      <c r="M48" t="n">
+        <v>59.179976</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -2376,9 +2430,7 @@
           <t>光通訊設備(如光纖電纜、光傳輸設備)</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>32360.9375</v>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
         <v>32845.053113</v>
       </c>
@@ -2407,7 +2459,10 @@
         <v>16959.463699</v>
       </c>
       <c r="L49" t="n">
-        <v>31351.969991</v>
+        <v>31417.552491</v>
+      </c>
+      <c r="M49" t="n">
+        <v>17982.51193175</v>
       </c>
     </row>
     <row r="50">
@@ -2416,9 +2471,7 @@
           <t>公共資訊查詢站(Kiosk)</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>0.004035</v>
-      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
         <v>0.003068</v>
       </c>
@@ -2449,6 +2502,9 @@
       <c r="L50" t="n">
         <v>0.004138</v>
       </c>
+      <c r="M50" t="n">
+        <v>0.003993</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -2456,9 +2512,7 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>79036.629403</v>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
         <v>77870.4230465</v>
       </c>
@@ -2487,7 +2541,10 @@
         <v>28974.604559</v>
       </c>
       <c r="L51" t="n">
-        <v>46477.8290375</v>
+        <v>46608.9940375</v>
+      </c>
+      <c r="M51" t="n">
+        <v>32892.47787208333</v>
       </c>
     </row>
     <row r="52">
@@ -2496,9 +2553,7 @@
           <t>其他配件</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>602.97684</v>
-      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
         <v>676.965239</v>
       </c>
@@ -2529,6 +2584,9 @@
       <c r="L52" t="n">
         <v>967.6794609999999</v>
       </c>
+      <c r="M52" t="n">
+        <v>1059.862894</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -2536,9 +2594,7 @@
           <t>其他零組件</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>45335.662984</v>
-      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
         <v>36821.995347</v>
       </c>
@@ -2567,7 +2623,10 @@
         <v>20347.418488</v>
       </c>
       <c r="L53" t="n">
-        <v>30895.504546</v>
+        <v>30961.087046</v>
+      </c>
+      <c r="M53" t="n">
+        <v>23423.317149</v>
       </c>
     </row>
     <row r="54">
@@ -2576,9 +2635,7 @@
           <t>其他電子產品及電子服務產業</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>43104.58204225</v>
-      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
         <v>38974.604406</v>
       </c>
@@ -2607,7 +2664,10 @@
         <v>20652.98982766667</v>
       </c>
       <c r="L54" t="n">
-        <v>20756.269929</v>
+        <v>20861.383929</v>
+      </c>
+      <c r="M54" t="n">
+        <v>17671.608531</v>
       </c>
     </row>
     <row r="55">
@@ -2616,9 +2676,7 @@
           <t>其他電腦及週邊設備</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>41455.960144</v>
-      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
         <v>41630.079521</v>
       </c>
@@ -2649,6 +2707,9 @@
       <c r="L55" t="n">
         <v>26853.213856</v>
       </c>
+      <c r="M55" t="n">
+        <v>28514.369855</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -2656,9 +2717,7 @@
           <t>其他電腦及週邊設備之零組件</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>25233.291122</v>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
         <v>18801.952122</v>
       </c>
@@ -2689,6 +2748,9 @@
       <c r="L56" t="n">
         <v>16462.961969</v>
       </c>
+      <c r="M56" t="n">
+        <v>18658.036035</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -2696,9 +2758,7 @@
           <t>冷凍、罐頭、脫水、醃漬食品</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>892.713102</v>
-      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
         <v>974.0391990000001</v>
       </c>
@@ -2718,16 +2778,19 @@
         <v>1179.813013</v>
       </c>
       <c r="I57" t="n">
-        <v>794.452771</v>
+        <v>802.8847510000001</v>
       </c>
       <c r="J57" t="n">
-        <v>664.99922</v>
+        <v>667.421923</v>
       </c>
       <c r="K57" t="n">
-        <v>633.208803</v>
+        <v>636.3594849999999</v>
       </c>
       <c r="L57" t="n">
-        <v>798.49108</v>
+        <v>801.344422</v>
+      </c>
+      <c r="M57" t="n">
+        <v>938.484727</v>
       </c>
     </row>
     <row r="58">
@@ -2736,9 +2799,7 @@
           <t>冷凍空調設備及零件</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>24721.146085</v>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
         <v>16891.14216</v>
       </c>
@@ -2769,6 +2830,9 @@
       <c r="L58" t="n">
         <v>3332.578538</v>
       </c>
+      <c r="M58" t="n">
+        <v>3592.456911</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -2776,9 +2840,7 @@
           <t>冷卻設備</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>35454.505101</v>
-      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
         <v>37914.402967</v>
       </c>
@@ -2807,7 +2869,10 @@
         <v>15081.222405</v>
       </c>
       <c r="L59" t="n">
-        <v>22185.799841</v>
+        <v>22251.382341</v>
+      </c>
+      <c r="M59" t="n">
+        <v>14574.633978</v>
       </c>
     </row>
     <row r="60">
@@ -2816,9 +2881,7 @@
           <t>冷熱軋不鏽鋼板捲</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>4898.067639</v>
-      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
         <v>2698.026616</v>
       </c>
@@ -2849,6 +2912,9 @@
       <c r="L60" t="n">
         <v>2179.892111</v>
       </c>
+      <c r="M60" t="n">
+        <v>3802.207755</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -2856,9 +2922,7 @@
           <t>冷熱軋鋼板捲</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>1069.061083</v>
-      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
         <v>967.3634615</v>
       </c>
@@ -2889,6 +2953,9 @@
       <c r="L61" t="n">
         <v>1627.11346</v>
       </c>
+      <c r="M61" t="n">
+        <v>1822.760876333333</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -2896,9 +2963,7 @@
           <t>出版產業</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>4.1e-05</v>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
         <v>3.1e-05</v>
       </c>
@@ -2929,6 +2994,9 @@
       <c r="L62" t="n">
         <v>1e-06</v>
       </c>
+      <c r="M62" t="n">
+        <v>1e-06</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -2936,9 +3004,7 @@
           <t>分析工具</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>351.519051</v>
-      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
         <v>591.942006</v>
       </c>
@@ -2969,6 +3035,9 @@
       <c r="L63" t="n">
         <v>280.223821</v>
       </c>
+      <c r="M63" t="n">
+        <v>248.878267</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -2976,9 +3045,7 @@
           <t>創意生活產業</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>0.001744</v>
-      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
         <v>0.0009879999999999999</v>
       </c>
@@ -3009,6 +3076,9 @@
       <c r="L64" t="n">
         <v>0.000748</v>
       </c>
+      <c r="M64" t="n">
+        <v>0.0001836666666666667</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -3016,9 +3086,7 @@
           <t>創投</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>178.035564</v>
-      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
         <v>402.315751</v>
       </c>
@@ -3049,6 +3117,9 @@
       <c r="L65" t="n">
         <v>34.080571</v>
       </c>
+      <c r="M65" t="n">
+        <v>31.111897</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -3056,9 +3127,7 @@
           <t>加密資產</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>178.035564</v>
-      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
         <v>402.315751</v>
       </c>
@@ -3089,6 +3158,9 @@
       <c r="L66" t="n">
         <v>34.080571</v>
       </c>
+      <c r="M66" t="n">
+        <v>31.111897</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -3096,9 +3168,7 @@
           <t>加工製成品</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>2118.804492</v>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
         <v>1873.647656</v>
       </c>
@@ -3129,6 +3199,9 @@
       <c r="L67" t="n">
         <v>1496.75938</v>
       </c>
+      <c r="M67" t="n">
+        <v>1609.939828</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -3136,9 +3209,7 @@
           <t>加工食品</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>1042.610869</v>
-      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
         <v>1179.89544</v>
       </c>
@@ -3169,6 +3240,9 @@
       <c r="L68" t="n">
         <v>991.67876</v>
       </c>
+      <c r="M68" t="n">
+        <v>1133.744993</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -3176,9 +3250,7 @@
           <t>加油站</t>
         </is>
       </c>
-      <c r="B69" t="n">
-        <v>427.352376</v>
-      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
         <v>246.652668</v>
       </c>
@@ -3209,6 +3281,9 @@
       <c r="L69" t="n">
         <v>344.191218</v>
       </c>
+      <c r="M69" t="n">
+        <v>358.687269</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -3216,9 +3291,7 @@
           <t>化妝品</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>6.295832</v>
-      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
         <v>6.579973</v>
       </c>
@@ -3249,6 +3322,9 @@
       <c r="L70" t="n">
         <v>23.089259</v>
       </c>
+      <c r="M70" t="n">
+        <v>24.34486</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -3256,9 +3332,7 @@
           <t>化學助劑</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>749.400572</v>
-      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
         <v>550.37072</v>
       </c>
@@ -3278,16 +3352,19 @@
         <v>736.004832</v>
       </c>
       <c r="I71" t="n">
-        <v>376.408236</v>
+        <v>258.817196</v>
       </c>
       <c r="J71" t="n">
-        <v>277.133991</v>
+        <v>194.26033</v>
       </c>
       <c r="K71" t="n">
-        <v>351.732462</v>
+        <v>249.06868</v>
       </c>
       <c r="L71" t="n">
-        <v>369.154774</v>
+        <v>315.164027</v>
+      </c>
+      <c r="M71" t="n">
+        <v>209.399063</v>
       </c>
     </row>
     <row r="72">
@@ -3296,9 +3373,7 @@
           <t>化學品</t>
         </is>
       </c>
-      <c r="B72" t="n">
-        <v>7841.79084</v>
-      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
         <v>7515.043518</v>
       </c>
@@ -3318,16 +3393,19 @@
         <v>5513.662994</v>
       </c>
       <c r="I72" t="n">
-        <v>4192.453569</v>
+        <v>4074.862529</v>
       </c>
       <c r="J72" t="n">
-        <v>3467.659234</v>
+        <v>3384.785573</v>
       </c>
       <c r="K72" t="n">
-        <v>5072.228287</v>
+        <v>4969.564505</v>
       </c>
       <c r="L72" t="n">
-        <v>4283.357775</v>
+        <v>4229.367028</v>
+      </c>
+      <c r="M72" t="n">
+        <v>3662.133728</v>
       </c>
     </row>
     <row r="73">
@@ -3336,9 +3414,7 @@
           <t>化學品(如光阻劑、靶材等)</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>6580.72092</v>
-      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
         <v>4221.565965</v>
       </c>
@@ -3369,6 +3445,9 @@
       <c r="L73" t="n">
         <v>3368.131877</v>
       </c>
+      <c r="M73" t="n">
+        <v>2589.544472</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -3376,9 +3455,7 @@
           <t>印刷材料</t>
         </is>
       </c>
-      <c r="B74" t="n">
-        <v>0.022911</v>
-      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
         <v>0.018862</v>
       </c>
@@ -3409,6 +3486,9 @@
       <c r="L74" t="n">
         <v>0.016204</v>
       </c>
+      <c r="M74" t="n">
+        <v>0.012699</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -3416,9 +3496,7 @@
           <t>印刷電路板</t>
         </is>
       </c>
-      <c r="B75" t="n">
-        <v>0.936765</v>
-      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
         <v>1.40725</v>
       </c>
@@ -3449,6 +3527,9 @@
       <c r="L75" t="n">
         <v>0.782779</v>
       </c>
+      <c r="M75" t="n">
+        <v>0.976494</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -3456,9 +3537,7 @@
           <t>印表機、傳真機、掃瞄器、多功能事務機、投影機</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>20730.835604</v>
-      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
         <v>13610.077311</v>
       </c>
@@ -3489,6 +3568,9 @@
       <c r="L76" t="n">
         <v>15928.254981</v>
       </c>
+      <c r="M76" t="n">
+        <v>16647.573732</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -3496,9 +3578,7 @@
           <t>原料</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>36.102787</v>
-      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
         <v>27.593777</v>
       </c>
@@ -3529,6 +3609,9 @@
       <c r="L77" t="n">
         <v>4.402973</v>
       </c>
+      <c r="M77" t="n">
+        <v>5.360127</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -3536,9 +3619,7 @@
           <t>原材料</t>
         </is>
       </c>
-      <c r="B78" t="n">
-        <v>10967.305031</v>
-      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
         <v>11380.660348</v>
       </c>
@@ -3569,6 +3650,9 @@
       <c r="L78" t="n">
         <v>9056.739328</v>
       </c>
+      <c r="M78" t="n">
+        <v>11182.073889</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -3576,9 +3660,7 @@
           <t>原物料</t>
         </is>
       </c>
-      <c r="B79" t="n">
-        <v>1124.99505</v>
-      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
         <v>995.454568</v>
       </c>
@@ -3609,6 +3691,9 @@
       <c r="L79" t="n">
         <v>853.68056</v>
       </c>
+      <c r="M79" t="n">
+        <v>961.57526025</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -3616,9 +3701,7 @@
           <t>商業應用</t>
         </is>
       </c>
-      <c r="B80" t="n">
-        <v>921.439059</v>
-      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
         <v>793.130777</v>
       </c>
@@ -3649,6 +3732,9 @@
       <c r="L80" t="n">
         <v>319.401381</v>
       </c>
+      <c r="M80" t="n">
+        <v>343.230491</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -3656,9 +3742,7 @@
           <t>垂直應用方案</t>
         </is>
       </c>
-      <c r="B81" t="n">
-        <v>7.436752</v>
-      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
         <v>4.784715</v>
       </c>
@@ -3689,6 +3773,9 @@
       <c r="L81" t="n">
         <v>0.474411</v>
       </c>
+      <c r="M81" t="n">
+        <v>0.647088</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -3696,9 +3783,7 @@
           <t>基板</t>
         </is>
       </c>
-      <c r="B82" t="n">
-        <v>8836.556364</v>
-      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
         <v>11936.535624</v>
       </c>
@@ -3729,6 +3814,9 @@
       <c r="L82" t="n">
         <v>17171.076023</v>
       </c>
+      <c r="M82" t="n">
+        <v>12655.593799</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -3736,9 +3824,7 @@
           <t>基板組裝加工及相關製造</t>
         </is>
       </c>
-      <c r="B83" t="n">
-        <v>24867.996311</v>
-      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
         <v>22578.038005</v>
       </c>
@@ -3769,6 +3855,9 @@
       <c r="L83" t="n">
         <v>24320.940354</v>
       </c>
+      <c r="M83" t="n">
+        <v>24119.377579</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -3776,9 +3865,7 @@
           <t>基礎工程</t>
         </is>
       </c>
-      <c r="B84" t="n">
-        <v>55.176824</v>
-      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
         <v>61.245432</v>
       </c>
@@ -3809,6 +3896,9 @@
       <c r="L84" t="n">
         <v>53.751019</v>
       </c>
+      <c r="M84" t="n">
+        <v>72.26036000000001</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -3816,9 +3906,7 @@
           <t>塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="B85" t="n">
-        <v>29.60682</v>
-      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
         <v>20.67004</v>
       </c>
@@ -3849,6 +3937,9 @@
       <c r="L85" t="n">
         <v>21.532283</v>
       </c>
+      <c r="M85" t="n">
+        <v>31.011381</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -3856,9 +3947,7 @@
           <t>塑膠/金屬機殼</t>
         </is>
       </c>
-      <c r="B86" t="n">
-        <v>332.072715</v>
-      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
         <v>316.617831</v>
       </c>
@@ -3889,6 +3978,9 @@
       <c r="L86" t="n">
         <v>335.129035</v>
       </c>
+      <c r="M86" t="n">
+        <v>308.544906</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -3896,9 +3988,7 @@
           <t>塑膠材料</t>
         </is>
       </c>
-      <c r="B87" t="n">
-        <v>6989.558259</v>
-      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
         <v>4864.358558</v>
       </c>
@@ -3929,6 +4019,9 @@
       <c r="L87" t="n">
         <v>5163.857428</v>
       </c>
+      <c r="M87" t="n">
+        <v>6570.983325</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -3936,9 +4029,7 @@
           <t>塑膠框</t>
         </is>
       </c>
-      <c r="B88" t="n">
-        <v>4322.852994</v>
-      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
         <v>2506.107055</v>
       </c>
@@ -3969,6 +4060,9 @@
       <c r="L88" t="n">
         <v>1085.865875</v>
       </c>
+      <c r="M88" t="n">
+        <v>791.8735370000001</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -3976,9 +4070,7 @@
           <t>塑膠製品</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>4139.212197</v>
-      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
         <v>4387.310369</v>
       </c>
@@ -4007,7 +4099,10 @@
         <v>3714.646776</v>
       </c>
       <c r="L89" t="n">
-        <v>3278.731874</v>
+        <v>3304.559114</v>
+      </c>
+      <c r="M89" t="n">
+        <v>4379.535411</v>
       </c>
     </row>
     <row r="90">
@@ -4016,9 +4111,7 @@
           <t>塔架</t>
         </is>
       </c>
-      <c r="B90" t="n">
-        <v>160.972069</v>
-      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
         <v>150.988466</v>
       </c>
@@ -4049,6 +4142,9 @@
       <c r="L90" t="n">
         <v>207.457883</v>
       </c>
+      <c r="M90" t="n">
+        <v>196.472703</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -4056,9 +4152,7 @@
           <t>多功能視訊卡</t>
         </is>
       </c>
-      <c r="B91" t="n">
-        <v>29.498338</v>
-      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
         <v>63.529216</v>
       </c>
@@ -4089,6 +4183,9 @@
       <c r="L91" t="n">
         <v>22.679749</v>
       </c>
+      <c r="M91" t="n">
+        <v>29.181226</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -4096,9 +4193,7 @@
           <t>大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>100250.332355</v>
-      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
         <v>82117.201942</v>
       </c>
@@ -4127,7 +4222,10 @@
         <v>41014.261787</v>
       </c>
       <c r="L92" t="n">
-        <v>51909.47638</v>
+        <v>52080.17288</v>
+      </c>
+      <c r="M92" t="n">
+        <v>49943.207858</v>
       </c>
     </row>
     <row r="93">
@@ -4136,9 +4234,7 @@
           <t>天然瓦斯供應</t>
         </is>
       </c>
-      <c r="B93" t="n">
-        <v>8.783528</v>
-      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
         <v>6.8685145</v>
       </c>
@@ -4169,6 +4265,9 @@
       <c r="L93" t="n">
         <v>4.602615</v>
       </c>
+      <c r="M93" t="n">
+        <v>5.082439</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -4176,9 +4275,7 @@
           <t>天然纖維產品(例如純棉、純羊毛等)</t>
         </is>
       </c>
-      <c r="B94" t="n">
-        <v>0.420903</v>
-      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
         <v>0.685548</v>
       </c>
@@ -4209,6 +4306,9 @@
       <c r="L94" t="n">
         <v>0.546161</v>
       </c>
+      <c r="M94" t="n">
+        <v>2.378145</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -4216,9 +4316,7 @@
           <t>太陽能發電設備/系統及系統工程</t>
         </is>
       </c>
-      <c r="B95" t="n">
-        <v>49047.163884</v>
-      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
         <v>37718.628647</v>
       </c>
@@ -4247,7 +4345,10 @@
         <v>17936.542862</v>
       </c>
       <c r="L95" t="n">
-        <v>27676.62676</v>
+        <v>27742.20926</v>
+      </c>
+      <c r="M95" t="n">
+        <v>23042.382345</v>
       </c>
     </row>
     <row r="96">
@@ -4256,9 +4357,7 @@
           <t>太陽能電廠</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>44581.044746</v>
-      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
         <v>39446.035322</v>
       </c>
@@ -4287,7 +4386,10 @@
         <v>23395.392911</v>
       </c>
       <c r="L96" t="n">
-        <v>27725.081995</v>
+        <v>27790.664495</v>
+      </c>
+      <c r="M96" t="n">
+        <v>20788.01294</v>
       </c>
     </row>
     <row r="97">
@@ -4296,9 +4398,7 @@
           <t>太陽能電池</t>
         </is>
       </c>
-      <c r="B97" t="n">
-        <v>4824.142058</v>
-      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
         <v>7761.296018</v>
       </c>
@@ -4329,6 +4429,9 @@
       <c r="L97" t="n">
         <v>6229.633562</v>
       </c>
+      <c r="M97" t="n">
+        <v>6181.043143</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -4336,9 +4439,7 @@
           <t>太陽能電池模組</t>
         </is>
       </c>
-      <c r="B98" t="n">
-        <v>5206.678315</v>
-      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
         <v>8207.662969999999</v>
       </c>
@@ -4369,6 +4470,9 @@
       <c r="L98" t="n">
         <v>6882.32955</v>
       </c>
+      <c r="M98" t="n">
+        <v>6639.802385</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -4376,9 +4480,7 @@
           <t>娛樂服務業</t>
         </is>
       </c>
-      <c r="B99" t="n">
-        <v>62.966109</v>
-      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
         <v>32.388381</v>
       </c>
@@ -4398,16 +4500,19 @@
         <v>64.707052</v>
       </c>
       <c r="I99" t="n">
-        <v>53.394191</v>
+        <v>58.177966</v>
       </c>
       <c r="J99" t="n">
-        <v>45.493806</v>
+        <v>47.668423</v>
       </c>
       <c r="K99" t="n">
-        <v>46.032638</v>
+        <v>48.277516</v>
       </c>
       <c r="L99" t="n">
-        <v>39.475828</v>
+        <v>41.961644</v>
+      </c>
+      <c r="M99" t="n">
+        <v>60.669087</v>
       </c>
     </row>
     <row r="100">
@@ -4416,9 +4521,7 @@
           <t>媒體推廣</t>
         </is>
       </c>
-      <c r="B100" t="n">
-        <v>178.035564</v>
-      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
         <v>402.315751</v>
       </c>
@@ -4449,6 +4552,9 @@
       <c r="L100" t="n">
         <v>34.080571</v>
       </c>
+      <c r="M100" t="n">
+        <v>31.111897</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -4456,9 +4562,7 @@
           <t>安全營運與事件回應</t>
         </is>
       </c>
-      <c r="B101" t="n">
-        <v>150.374804</v>
-      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
         <v>178.311979</v>
       </c>
@@ -4489,6 +4593,9 @@
       <c r="L101" t="n">
         <v>212.328261</v>
       </c>
+      <c r="M101" t="n">
+        <v>189.476805</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -4496,9 +4603,7 @@
           <t>安全監控系統</t>
         </is>
       </c>
-      <c r="B102" t="n">
-        <v>56062.429082</v>
-      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
         <v>52337.306369</v>
       </c>
@@ -4527,7 +4632,10 @@
         <v>22199.868506</v>
       </c>
       <c r="L102" t="n">
-        <v>33043.725371</v>
+        <v>33109.307871</v>
+      </c>
+      <c r="M102" t="n">
+        <v>27953.965513</v>
       </c>
     </row>
     <row r="103">
@@ -4536,9 +4644,7 @@
           <t>家庭用紙</t>
         </is>
       </c>
-      <c r="B103" t="n">
-        <v>45.402715</v>
-      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
         <v>39.706677</v>
       </c>
@@ -4569,6 +4675,9 @@
       <c r="L103" t="n">
         <v>62.57482</v>
       </c>
+      <c r="M103" t="n">
+        <v>41.997243</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -4576,9 +4685,7 @@
           <t>封裝/模組</t>
         </is>
       </c>
-      <c r="B104" t="n">
-        <v>17194.410501</v>
-      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
         <v>22533.008466</v>
       </c>
@@ -4609,6 +4716,9 @@
       <c r="L104" t="n">
         <v>6829.485953</v>
       </c>
+      <c r="M104" t="n">
+        <v>4919.791178</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -4616,9 +4726,7 @@
           <t>專用機械(如紡織成衣生產用機械、食品飲料生產用機械、農林用機械等)</t>
         </is>
       </c>
-      <c r="B105" t="n">
-        <v>26491.28007</v>
-      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
         <v>24443.293609</v>
       </c>
@@ -4647,7 +4755,10 @@
         <v>9638.762387000001</v>
       </c>
       <c r="L105" t="n">
-        <v>19165.93112</v>
+        <v>19231.51362</v>
+      </c>
+      <c r="M105" t="n">
+        <v>16443.68008</v>
       </c>
     </row>
     <row r="106">
@@ -4656,9 +4767,7 @@
           <t>導線架</t>
         </is>
       </c>
-      <c r="B106" t="n">
-        <v>8395.675622999999</v>
-      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
         <v>16096.453015</v>
       </c>
@@ -4689,6 +4798,9 @@
       <c r="L106" t="n">
         <v>6036.564285</v>
       </c>
+      <c r="M106" t="n">
+        <v>5425.12318</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -4696,9 +4808,7 @@
           <t>導航定位</t>
         </is>
       </c>
-      <c r="B107" t="n">
-        <v>178.035621</v>
-      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
         <v>402.31604</v>
       </c>
@@ -4729,6 +4839,9 @@
       <c r="L107" t="n">
         <v>34.080589</v>
       </c>
+      <c r="M107" t="n">
+        <v>31.111968</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -4736,9 +4849,7 @@
           <t>工業型機器人</t>
         </is>
       </c>
-      <c r="B108" t="n">
-        <v>2137.035944</v>
-      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
         <v>972.13181</v>
       </c>
@@ -4769,6 +4880,9 @@
       <c r="L108" t="n">
         <v>951.0461299999999</v>
       </c>
+      <c r="M108" t="n">
+        <v>1009.643026</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -4776,9 +4890,7 @@
           <t>工業用紙</t>
         </is>
       </c>
-      <c r="B109" t="n">
-        <v>64.490116</v>
-      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
         <v>47.783425</v>
       </c>
@@ -4809,6 +4921,9 @@
       <c r="L109" t="n">
         <v>68.827483</v>
       </c>
+      <c r="M109" t="n">
+        <v>53.214708</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -4816,9 +4931,7 @@
           <t>工業用設備</t>
         </is>
       </c>
-      <c r="B110" t="n">
-        <v>0.49984</v>
-      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
         <v>0.453099</v>
       </c>
@@ -4849,6 +4962,9 @@
       <c r="L110" t="n">
         <v>1.467341</v>
       </c>
+      <c r="M110" t="n">
+        <v>1.762512</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -4856,9 +4972,7 @@
           <t>工業電腦</t>
         </is>
       </c>
-      <c r="B111" t="n">
-        <v>8573.574919000001</v>
-      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
         <v>8973.868028999999</v>
       </c>
@@ -4889,6 +5003,9 @@
       <c r="L111" t="n">
         <v>4425.772244</v>
       </c>
+      <c r="M111" t="n">
+        <v>4995.630401</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -4896,9 +5013,7 @@
           <t>工程承攬</t>
         </is>
       </c>
-      <c r="B112" t="n">
-        <v>672.541457</v>
-      </c>
+      <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
         <v>659.252472</v>
       </c>
@@ -4929,6 +5044,9 @@
       <c r="L112" t="n">
         <v>650.5588</v>
       </c>
+      <c r="M112" t="n">
+        <v>717.8017599999999</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -4936,9 +5054,7 @@
           <t>工程設計</t>
         </is>
       </c>
-      <c r="B113" t="n">
-        <v>121.528192</v>
-      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
         <v>148.837506</v>
       </c>
@@ -4969,6 +5085,9 @@
       <c r="L113" t="n">
         <v>181.528371</v>
       </c>
+      <c r="M113" t="n">
+        <v>146.779437</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -4976,9 +5095,7 @@
           <t>工藝產業</t>
         </is>
       </c>
-      <c r="B114" t="n">
-        <v>0.002656</v>
-      </c>
+      <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
         <v>0.001363</v>
       </c>
@@ -5009,6 +5126,9 @@
       <c r="L114" t="n">
         <v>0.001149</v>
       </c>
+      <c r="M114" t="n">
+        <v>0.001395</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -5016,9 +5136,7 @@
           <t>幹細胞收集儲存</t>
         </is>
       </c>
-      <c r="B115" t="n">
-        <v>42.059637</v>
-      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
         <v>29.674538</v>
       </c>
@@ -5049,6 +5167,9 @@
       <c r="L115" t="n">
         <v>5.745914</v>
       </c>
+      <c r="M115" t="n">
+        <v>5.007934</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -5056,9 +5177,7 @@
           <t>幹細胞開發</t>
         </is>
       </c>
-      <c r="B116" t="n">
-        <v>42.059637</v>
-      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
         <v>29.674538</v>
       </c>
@@ -5089,6 +5208,9 @@
       <c r="L116" t="n">
         <v>5.745914</v>
       </c>
+      <c r="M116" t="n">
+        <v>5.007934</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -5096,9 +5218,7 @@
           <t>底層平台</t>
         </is>
       </c>
-      <c r="B117" t="n">
-        <v>178.035564</v>
-      </c>
+      <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
         <v>402.315751</v>
       </c>
@@ -5129,6 +5249,9 @@
       <c r="L117" t="n">
         <v>34.080571</v>
       </c>
+      <c r="M117" t="n">
+        <v>31.111897</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -5136,9 +5259,7 @@
           <t>店點開設管理</t>
         </is>
       </c>
-      <c r="B118" t="n">
-        <v>87.546876</v>
-      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
         <v>51.240492</v>
       </c>
@@ -5169,6 +5290,9 @@
       <c r="L118" t="n">
         <v>82.330825</v>
       </c>
+      <c r="M118" t="n">
+        <v>113.472688</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -5176,9 +5300,7 @@
           <t>廣播電視/電影產業</t>
         </is>
       </c>
-      <c r="B119" t="n">
-        <v>796.3280099999999</v>
-      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
         <v>412.903464</v>
       </c>
@@ -5209,6 +5331,9 @@
       <c r="L119" t="n">
         <v>324.913326</v>
       </c>
+      <c r="M119" t="n">
+        <v>390.227295</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -5216,9 +5341,7 @@
           <t>建材原料</t>
         </is>
       </c>
-      <c r="B120" t="n">
-        <v>19444.612059</v>
-      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
         <v>5823.505869</v>
       </c>
@@ -5249,6 +5372,9 @@
       <c r="L120" t="n">
         <v>1886.005567</v>
       </c>
+      <c r="M120" t="n">
+        <v>4569.382984</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -5256,9 +5382,7 @@
           <t>建設業</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>15861.932347</v>
-      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
         <v>8137.386396</v>
       </c>
@@ -5289,6 +5413,9 @@
       <c r="L121" t="n">
         <v>4204.041249</v>
       </c>
+      <c r="M121" t="n">
+        <v>5976.849175</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -5296,9 +5423,7 @@
           <t>引擎蓋</t>
         </is>
       </c>
-      <c r="B122" t="n">
-        <v>420.62072</v>
-      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
         <v>423.533898</v>
       </c>
@@ -5329,6 +5454,9 @@
       <c r="L122" t="n">
         <v>291.868958</v>
       </c>
+      <c r="M122" t="n">
+        <v>271.479127</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -5336,9 +5464,7 @@
           <t>影像遙測</t>
         </is>
       </c>
-      <c r="B123" t="n">
-        <v>178.035564</v>
-      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
         <v>402.315751</v>
       </c>
@@ -5369,6 +5495,9 @@
       <c r="L123" t="n">
         <v>34.080571</v>
       </c>
+      <c r="M123" t="n">
+        <v>31.111897</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -5376,9 +5505,7 @@
           <t>微處理器</t>
         </is>
       </c>
-      <c r="B124" t="n">
-        <v>0.217131</v>
-      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
         <v>0.420098</v>
       </c>
@@ -5409,6 +5536,9 @@
       <c r="L124" t="n">
         <v>0.388744</v>
       </c>
+      <c r="M124" t="n">
+        <v>0.412205</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -5416,9 +5546,7 @@
           <t>感測器</t>
         </is>
       </c>
-      <c r="B125" t="n">
-        <v>0.014905</v>
-      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
         <v>0.010707</v>
       </c>
@@ -5449,6 +5577,9 @@
       <c r="L125" t="n">
         <v>0.012723</v>
       </c>
+      <c r="M125" t="n">
+        <v>0.005844</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -5456,9 +5587,7 @@
           <t>感測器/模組</t>
         </is>
       </c>
-      <c r="B126" t="n">
-        <v>11182.215499</v>
-      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
         <v>19018.127225</v>
       </c>
@@ -5489,6 +5618,9 @@
       <c r="L126" t="n">
         <v>4981.000891</v>
       </c>
+      <c r="M126" t="n">
+        <v>3127.309953</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -5496,9 +5628,7 @@
           <t>感測裝置</t>
         </is>
       </c>
-      <c r="B127" t="n">
-        <v>181.928802</v>
-      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
         <v>95.873199</v>
       </c>
@@ -5529,6 +5659,9 @@
       <c r="L127" t="n">
         <v>36.848688</v>
       </c>
+      <c r="M127" t="n">
+        <v>46.931346</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -5536,9 +5669,7 @@
           <t>應用/系統軟體設計開發</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>30083.606812</v>
-      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
         <v>26244.688256</v>
       </c>
@@ -5567,7 +5698,10 @@
         <v>10022.62538</v>
       </c>
       <c r="L128" t="n">
-        <v>19602.0467</v>
+        <v>19667.6292</v>
+      </c>
+      <c r="M128" t="n">
+        <v>13356.521027</v>
       </c>
     </row>
     <row r="129">
@@ -5576,9 +5710,7 @@
           <t>應用軟體</t>
         </is>
       </c>
-      <c r="B129" t="n">
-        <v>518.145166</v>
-      </c>
+      <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
         <v>954.028927</v>
       </c>
@@ -5609,6 +5741,9 @@
       <c r="L129" t="n">
         <v>398.066457</v>
       </c>
+      <c r="M129" t="n">
+        <v>366.152124</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -5616,9 +5751,7 @@
           <t>應用軟體/內容</t>
         </is>
       </c>
-      <c r="B130" t="n">
-        <v>714.35337</v>
-      </c>
+      <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
         <v>363.369868</v>
       </c>
@@ -5649,6 +5782,9 @@
       <c r="L130" t="n">
         <v>249.008594</v>
       </c>
+      <c r="M130" t="n">
+        <v>279.026516</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -5656,9 +5792,7 @@
           <t>成衣及其它家居紡織類品</t>
         </is>
       </c>
-      <c r="B131" t="n">
-        <v>1041.799005</v>
-      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
         <v>1121.52799</v>
       </c>
@@ -5689,6 +5823,9 @@
       <c r="L131" t="n">
         <v>1463.508353</v>
       </c>
+      <c r="M131" t="n">
+        <v>765.8137390000001</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -5696,9 +5833,7 @@
           <t>手工具機</t>
         </is>
       </c>
-      <c r="B132" t="n">
-        <v>320.662151</v>
-      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
         <v>933.157522</v>
       </c>
@@ -5729,6 +5864,9 @@
       <c r="L132" t="n">
         <v>186.836827</v>
       </c>
+      <c r="M132" t="n">
+        <v>175.752733</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -5736,9 +5874,7 @@
           <t>技術標準/聯盟</t>
         </is>
       </c>
-      <c r="B133" t="n">
-        <v>704.373165</v>
-      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
         <v>358.616734</v>
       </c>
@@ -5769,6 +5905,9 @@
       <c r="L133" t="n">
         <v>240.333646</v>
       </c>
+      <c r="M133" t="n">
+        <v>273.260521</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -5776,9 +5915,7 @@
           <t>接著劑(合成樹脂)</t>
         </is>
       </c>
-      <c r="B134" t="n">
-        <v>6370.939572</v>
-      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
         <v>3690.807363</v>
       </c>
@@ -5809,6 +5946,9 @@
       <c r="L134" t="n">
         <v>3284.517918</v>
       </c>
+      <c r="M134" t="n">
+        <v>2412.444932</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -5816,9 +5956,7 @@
           <t>控制IC</t>
         </is>
       </c>
-      <c r="B135" t="n">
-        <v>295.352967</v>
-      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
         <v>323.012376</v>
       </c>
@@ -5849,6 +5987,9 @@
       <c r="L135" t="n">
         <v>366.659798</v>
       </c>
+      <c r="M135" t="n">
+        <v>148.312192</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
@@ -5856,9 +5997,7 @@
           <t>控制器</t>
         </is>
       </c>
-      <c r="B136" t="n">
-        <v>0.143952</v>
-      </c>
+      <c r="B136" t="inlineStr"/>
       <c r="C136" t="n">
         <v>0.288299</v>
       </c>
@@ -5889,6 +6028,9 @@
       <c r="L136" t="n">
         <v>0.10803</v>
       </c>
+      <c r="M136" t="n">
+        <v>0.159279</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
@@ -5896,9 +6038,7 @@
           <t>擴散膜、增亮膜、導光板</t>
         </is>
       </c>
-      <c r="B137" t="n">
-        <v>10030.293938</v>
-      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
         <v>5606.953632</v>
       </c>
@@ -5929,6 +6069,9 @@
       <c r="L137" t="n">
         <v>2146.764509</v>
       </c>
+      <c r="M137" t="n">
+        <v>2109.27161</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
@@ -5936,9 +6079,7 @@
           <t>支付</t>
         </is>
       </c>
-      <c r="B138" t="n">
-        <v>280.503976</v>
-      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
         <v>665.989528</v>
       </c>
@@ -5969,6 +6110,9 @@
       <c r="L138" t="n">
         <v>205.41496</v>
       </c>
+      <c r="M138" t="n">
+        <v>139.711329</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
@@ -5976,9 +6120,7 @@
           <t>支援服務</t>
         </is>
       </c>
-      <c r="B139" t="n">
-        <v>8.927711</v>
-      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
         <v>3.903565</v>
       </c>
@@ -6009,6 +6151,9 @@
       <c r="L139" t="n">
         <v>7.230046</v>
       </c>
+      <c r="M139" t="n">
+        <v>4.489923</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
@@ -6016,9 +6161,7 @@
           <t>散熱片、風扇馬達、散熱模組</t>
         </is>
       </c>
-      <c r="B140" t="n">
-        <v>38519.211751</v>
-      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
         <v>31161.610532</v>
       </c>
@@ -6047,7 +6190,10 @@
         <v>27207.992196</v>
       </c>
       <c r="L140" t="n">
-        <v>31077.414838</v>
+        <v>31142.997338</v>
+      </c>
+      <c r="M140" t="n">
+        <v>24581.527854</v>
       </c>
     </row>
     <row r="141">
@@ -6056,9 +6202,7 @@
           <t>散裝航運</t>
         </is>
       </c>
-      <c r="B141" t="n">
-        <v>1348.130062</v>
-      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
         <v>915.989022</v>
       </c>
@@ -6089,6 +6233,9 @@
       <c r="L141" t="n">
         <v>709.411646</v>
       </c>
+      <c r="M141" t="n">
+        <v>741.160319</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
@@ -6096,9 +6243,7 @@
           <t>整車組裝、修理及技術服務</t>
         </is>
       </c>
-      <c r="B142" t="n">
-        <v>384.202542</v>
-      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
         <v>488.437625</v>
       </c>
@@ -6129,6 +6274,9 @@
       <c r="L142" t="n">
         <v>219.413608</v>
       </c>
+      <c r="M142" t="n">
+        <v>219.27014</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
@@ -6136,9 +6284,7 @@
           <t>整體解決方案</t>
         </is>
       </c>
-      <c r="B143" t="n">
-        <v>7.316722</v>
-      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
         <v>4.841815</v>
       </c>
@@ -6169,6 +6315,9 @@
       <c r="L143" t="n">
         <v>0.554637</v>
       </c>
+      <c r="M143" t="n">
+        <v>0.72435</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
@@ -6176,9 +6325,7 @@
           <t>數位內容</t>
         </is>
       </c>
-      <c r="B144" t="n">
-        <v>704.373657</v>
-      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
         <v>358.616871</v>
       </c>
@@ -6209,6 +6356,9 @@
       <c r="L144" t="n">
         <v>240.333665</v>
       </c>
+      <c r="M144" t="n">
+        <v>273.260867</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
@@ -6216,9 +6366,7 @@
           <t>數位內容產業</t>
         </is>
       </c>
-      <c r="B145" t="n">
-        <v>705.563261</v>
-      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
         <v>359.68112</v>
       </c>
@@ -6249,6 +6397,9 @@
       <c r="L145" t="n">
         <v>241.901091</v>
       </c>
+      <c r="M145" t="n">
+        <v>274.6137746666667</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
@@ -6256,9 +6407,7 @@
           <t>數位身分</t>
         </is>
       </c>
-      <c r="B146" t="n">
-        <v>217.141861</v>
-      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
         <v>434.562333</v>
       </c>
@@ -6289,6 +6438,9 @@
       <c r="L146" t="n">
         <v>79.079418</v>
       </c>
+      <c r="M146" t="n">
+        <v>69.98982700000001</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
@@ -6296,9 +6448,7 @@
           <t>數位銀行</t>
         </is>
       </c>
-      <c r="B147" t="n">
-        <v>187.029007</v>
-      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
         <v>406.415752</v>
       </c>
@@ -6329,6 +6479,9 @@
       <c r="L147" t="n">
         <v>41.362929</v>
       </c>
+      <c r="M147" t="n">
+        <v>35.665354</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
@@ -6336,9 +6489,7 @@
           <t>數據分析</t>
         </is>
       </c>
-      <c r="B148" t="n">
-        <v>226.083092</v>
-      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
         <v>438.482686</v>
       </c>
@@ -6369,6 +6520,9 @@
       <c r="L148" t="n">
         <v>86.323337</v>
       </c>
+      <c r="M148" t="n">
+        <v>74.495547</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
@@ -6376,9 +6530,7 @@
           <t>文化印刷業</t>
         </is>
       </c>
-      <c r="B149" t="n">
-        <v>397.748031</v>
-      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
         <v>91.96123799999999</v>
       </c>
@@ -6409,6 +6561,9 @@
       <c r="L149" t="n">
         <v>76.0770795</v>
       </c>
+      <c r="M149" t="n">
+        <v>55.22002</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -6416,9 +6571,7 @@
           <t>文化用紙</t>
         </is>
       </c>
-      <c r="B150" t="n">
-        <v>64.736626</v>
-      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
         <v>53.200631</v>
       </c>
@@ -6449,6 +6602,9 @@
       <c r="L150" t="n">
         <v>68.803467</v>
       </c>
+      <c r="M150" t="n">
+        <v>56.603999</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
@@ -6456,9 +6612,7 @@
           <t>旅遊服務業</t>
         </is>
       </c>
-      <c r="B151" t="n">
-        <v>93.845406</v>
-      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
         <v>65.452044</v>
       </c>
@@ -6489,6 +6643,9 @@
       <c r="L151" t="n">
         <v>477.247866</v>
       </c>
+      <c r="M151" t="n">
+        <v>570.03332</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
@@ -6496,9 +6653,7 @@
           <t>旅館服務業</t>
         </is>
       </c>
-      <c r="B152" t="n">
-        <v>87.74807800000001</v>
-      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
         <v>57.88296</v>
       </c>
@@ -6529,6 +6684,9 @@
       <c r="L152" t="n">
         <v>108.807572</v>
       </c>
+      <c r="M152" t="n">
+        <v>76.6868855</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
@@ -6536,9 +6694,7 @@
           <t>晶片組</t>
         </is>
       </c>
-      <c r="B153" t="n">
-        <v>607.814454</v>
-      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
         <v>306.253592</v>
       </c>
@@ -6569,6 +6725,9 @@
       <c r="L153" t="n">
         <v>304.104575</v>
       </c>
+      <c r="M153" t="n">
+        <v>402.547334</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
@@ -6576,9 +6735,7 @@
           <t>智慧設備</t>
         </is>
       </c>
-      <c r="B154" t="n">
-        <v>27205.397413</v>
-      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
         <v>25184.815982</v>
       </c>
@@ -6607,7 +6764,10 @@
         <v>11367.872735</v>
       </c>
       <c r="L154" t="n">
-        <v>21624.957054</v>
+        <v>21690.539554</v>
+      </c>
+      <c r="M154" t="n">
+        <v>15296.351704</v>
       </c>
     </row>
     <row r="155">
@@ -6616,9 +6776,7 @@
           <t>有線通訊設備(如電話機、傳真機)</t>
         </is>
       </c>
-      <c r="B155" t="n">
-        <v>5408.06679</v>
-      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="n">
         <v>2663.016606</v>
       </c>
@@ -6649,6 +6807,9 @@
       <c r="L155" t="n">
         <v>995.198516</v>
       </c>
+      <c r="M155" t="n">
+        <v>664.854709</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
@@ -6656,9 +6817,7 @@
           <t>期貨業</t>
         </is>
       </c>
-      <c r="B156" t="n">
-        <v>17.434056</v>
-      </c>
+      <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
         <v>16.979753</v>
       </c>
@@ -6689,6 +6848,9 @@
       <c r="L156" t="n">
         <v>11.238211</v>
       </c>
+      <c r="M156" t="n">
+        <v>13.137075</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
@@ -6696,9 +6858,7 @@
           <t>材料</t>
         </is>
       </c>
-      <c r="B157" t="n">
-        <v>12364.99401</v>
-      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
         <v>8118.061754</v>
       </c>
@@ -6729,6 +6889,9 @@
       <c r="L157" t="n">
         <v>7942.079253</v>
       </c>
+      <c r="M157" t="n">
+        <v>8586.23501</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
@@ -6736,9 +6899,7 @@
           <t>染整</t>
         </is>
       </c>
-      <c r="B158" t="n">
-        <v>15518.983661</v>
-      </c>
+      <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
         <v>10594.52794</v>
       </c>
@@ -6769,6 +6930,9 @@
       <c r="L158" t="n">
         <v>5626.327422</v>
       </c>
+      <c r="M158" t="n">
+        <v>12497.643879</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
@@ -6776,9 +6940,7 @@
           <t>桌上型電腦</t>
         </is>
       </c>
-      <c r="B159" t="n">
-        <v>51259.757061</v>
-      </c>
+      <c r="B159" t="inlineStr"/>
       <c r="C159" t="n">
         <v>41793.237735</v>
       </c>
@@ -6807,7 +6969,10 @@
         <v>22406.001993</v>
       </c>
       <c r="L159" t="n">
-        <v>38465.71727</v>
+        <v>38531.29977</v>
+      </c>
+      <c r="M159" t="n">
+        <v>33779.607327</v>
       </c>
     </row>
     <row r="160">
@@ -6816,9 +6981,7 @@
           <t>棒鋼盤元(捲狀條鋼)</t>
         </is>
       </c>
-      <c r="B160" t="n">
-        <v>550.928861</v>
-      </c>
+      <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
         <v>635.9744015</v>
       </c>
@@ -6849,6 +7012,9 @@
       <c r="L160" t="n">
         <v>1033.473971</v>
       </c>
+      <c r="M160" t="n">
+        <v>1134.449021333333</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
@@ -6856,9 +7022,7 @@
           <t>模具</t>
         </is>
       </c>
-      <c r="B161" t="n">
-        <v>843.890435</v>
-      </c>
+      <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
         <v>639.04463</v>
       </c>
@@ -6889,6 +7053,9 @@
       <c r="L161" t="n">
         <v>410.408391</v>
       </c>
+      <c r="M161" t="n">
+        <v>364.193784</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
@@ -6896,9 +7063,7 @@
           <t>樹酯</t>
         </is>
       </c>
-      <c r="B162" t="n">
-        <v>217.720038</v>
-      </c>
+      <c r="B162" t="inlineStr"/>
       <c r="C162" t="n">
         <v>150.62937</v>
       </c>
@@ -6929,6 +7094,9 @@
       <c r="L162" t="n">
         <v>114.657033</v>
       </c>
+      <c r="M162" t="n">
+        <v>132.539768</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
@@ -6936,9 +7104,7 @@
           <t>機器學習</t>
         </is>
       </c>
-      <c r="B163" t="n">
-        <v>27121.072535</v>
-      </c>
+      <c r="B163" t="inlineStr"/>
       <c r="C163" t="n">
         <v>24729.034774</v>
       </c>
@@ -6967,7 +7133,10 @@
         <v>10570.62473</v>
       </c>
       <c r="L163" t="n">
-        <v>20053.32839</v>
+        <v>20118.91089</v>
+      </c>
+      <c r="M163" t="n">
+        <v>13789.810701</v>
       </c>
     </row>
     <row r="164">
@@ -6976,9 +7145,7 @@
           <t>機械設備之沖壓零組件</t>
         </is>
       </c>
-      <c r="B164" t="n">
-        <v>18655.496524</v>
-      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
         <v>11860.364339</v>
       </c>
@@ -7009,6 +7176,9 @@
       <c r="L164" t="n">
         <v>5151.133718</v>
       </c>
+      <c r="M164" t="n">
+        <v>11121.260231</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
@@ -7016,9 +7186,7 @@
           <t>機構樞紐</t>
         </is>
       </c>
-      <c r="B165" t="n">
-        <v>7965.309766</v>
-      </c>
+      <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
         <v>5513.728483</v>
       </c>
@@ -7049,6 +7217,9 @@
       <c r="L165" t="n">
         <v>5257.845714</v>
       </c>
+      <c r="M165" t="n">
+        <v>4039.9412</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
@@ -7056,9 +7227,7 @@
           <t>機殼</t>
         </is>
       </c>
-      <c r="B166" t="n">
-        <v>27726.632525</v>
-      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
         <v>28879.810708</v>
       </c>
@@ -7089,6 +7258,9 @@
       <c r="L166" t="n">
         <v>23873.482173</v>
       </c>
+      <c r="M166" t="n">
+        <v>20849.489807</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
@@ -7096,9 +7268,7 @@
           <t>機電工程</t>
         </is>
       </c>
-      <c r="B167" t="n">
-        <v>40301.359967</v>
-      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
         <v>35602.668684</v>
       </c>
@@ -7127,7 +7297,10 @@
         <v>10881.452331</v>
       </c>
       <c r="L167" t="n">
-        <v>20780.667967</v>
+        <v>20846.250467</v>
+      </c>
+      <c r="M167" t="n">
+        <v>14859.614466</v>
       </c>
     </row>
     <row r="168">
@@ -7136,9 +7309,7 @@
           <t>機電系統工程</t>
         </is>
       </c>
-      <c r="B168" t="n">
-        <v>44568.030337</v>
-      </c>
+      <c r="B168" t="inlineStr"/>
       <c r="C168" t="n">
         <v>28087.894264</v>
       </c>
@@ -7169,6 +7340,9 @@
       <c r="L168" t="n">
         <v>8403.113341</v>
       </c>
+      <c r="M168" t="n">
+        <v>10247.134894</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
@@ -7176,9 +7350,7 @@
           <t>橡膠製品</t>
         </is>
       </c>
-      <c r="B169" t="n">
-        <v>353.946361</v>
-      </c>
+      <c r="B169" t="inlineStr"/>
       <c r="C169" t="n">
         <v>367.299875</v>
       </c>
@@ -7198,16 +7370,19 @@
         <v>600.32322</v>
       </c>
       <c r="I169" t="n">
-        <v>424.916001</v>
+        <v>422.253137</v>
       </c>
       <c r="J169" t="n">
-        <v>476.855958</v>
+        <v>474.266164</v>
       </c>
       <c r="K169" t="n">
-        <v>287.279225</v>
+        <v>285.798495</v>
       </c>
       <c r="L169" t="n">
-        <v>293.037259</v>
+        <v>290.446678</v>
+      </c>
+      <c r="M169" t="n">
+        <v>318.257681</v>
       </c>
     </row>
     <row r="170">
@@ -7216,9 +7391,7 @@
           <t>水泥成品</t>
         </is>
       </c>
-      <c r="B170" t="n">
-        <v>2354.93241</v>
-      </c>
+      <c r="B170" t="inlineStr"/>
       <c r="C170" t="n">
         <v>986.922461</v>
       </c>
@@ -7249,6 +7422,9 @@
       <c r="L170" t="n">
         <v>730.732924</v>
       </c>
+      <c r="M170" t="n">
+        <v>712.577228</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
@@ -7256,9 +7432,7 @@
           <t>水泥熟料</t>
         </is>
       </c>
-      <c r="B171" t="n">
-        <v>2669.375039</v>
-      </c>
+      <c r="B171" t="inlineStr"/>
       <c r="C171" t="n">
         <v>1408.598362</v>
       </c>
@@ -7289,6 +7463,9 @@
       <c r="L171" t="n">
         <v>927.960121</v>
       </c>
+      <c r="M171" t="n">
+        <v>939.714968</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
@@ -7296,9 +7473,7 @@
           <t>水泥生料</t>
         </is>
       </c>
-      <c r="B172" t="n">
-        <v>2332.403212</v>
-      </c>
+      <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
         <v>973.516995</v>
       </c>
@@ -7329,6 +7504,9 @@
       <c r="L172" t="n">
         <v>716.728211</v>
       </c>
+      <c r="M172" t="n">
+        <v>694.769723</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
@@ -7336,9 +7514,7 @@
           <t>油空壓元件</t>
         </is>
       </c>
-      <c r="B173" t="n">
-        <v>484.569014</v>
-      </c>
+      <c r="B173" t="inlineStr"/>
       <c r="C173" t="n">
         <v>353.373632</v>
       </c>
@@ -7369,6 +7545,9 @@
       <c r="L173" t="n">
         <v>2380.288418</v>
       </c>
+      <c r="M173" t="n">
+        <v>3606.121556</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
@@ -7376,9 +7555,7 @@
           <t>流行音樂及文化內容產業</t>
         </is>
       </c>
-      <c r="B174" t="n">
-        <v>726.53061</v>
-      </c>
+      <c r="B174" t="inlineStr"/>
       <c r="C174" t="n">
         <v>370.921137</v>
       </c>
@@ -7409,6 +7586,9 @@
       <c r="L174" t="n">
         <v>264.558391</v>
       </c>
+      <c r="M174" t="n">
+        <v>295.182089</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
@@ -7416,9 +7596,7 @@
           <t>海陸空大眾運輸</t>
         </is>
       </c>
-      <c r="B175" t="n">
-        <v>8286.659916000001</v>
-      </c>
+      <c r="B175" t="inlineStr"/>
       <c r="C175" t="n">
         <v>3939.130983</v>
       </c>
@@ -7449,6 +7627,9 @@
       <c r="L175" t="n">
         <v>2195.624395</v>
       </c>
+      <c r="M175" t="n">
+        <v>2072.427773</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -7456,9 +7637,7 @@
           <t>海陸空貨運承攬</t>
         </is>
       </c>
-      <c r="B176" t="n">
-        <v>204.905597</v>
-      </c>
+      <c r="B176" t="inlineStr"/>
       <c r="C176" t="n">
         <v>200.47187</v>
       </c>
@@ -7489,6 +7668,9 @@
       <c r="L176" t="n">
         <v>178.0668</v>
       </c>
+      <c r="M176" t="n">
+        <v>235.589542</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
@@ -7496,9 +7678,7 @@
           <t>清潔用品</t>
         </is>
       </c>
-      <c r="B177" t="n">
-        <v>15.744528</v>
-      </c>
+      <c r="B177" t="inlineStr"/>
       <c r="C177" t="n">
         <v>12.758118</v>
       </c>
@@ -7529,6 +7709,9 @@
       <c r="L177" t="n">
         <v>30.554041</v>
       </c>
+      <c r="M177" t="n">
+        <v>23.104748</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
@@ -7536,9 +7719,7 @@
           <t>濾波器、振盪器</t>
         </is>
       </c>
-      <c r="B178" t="n">
-        <v>26619.613949</v>
-      </c>
+      <c r="B178" t="inlineStr"/>
       <c r="C178" t="n">
         <v>22506.482396</v>
       </c>
@@ -7567,7 +7748,10 @@
         <v>4881.65779</v>
       </c>
       <c r="L178" t="n">
-        <v>5913.481901</v>
+        <v>5982.883901</v>
+      </c>
+      <c r="M178" t="n">
+        <v>8462.125636999999</v>
       </c>
     </row>
     <row r="179">
@@ -7576,9 +7760,7 @@
           <t>濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)</t>
         </is>
       </c>
-      <c r="B179" t="n">
-        <v>327.150206</v>
-      </c>
+      <c r="B179" t="inlineStr"/>
       <c r="C179" t="n">
         <v>139.23354</v>
       </c>
@@ -7609,6 +7791,9 @@
       <c r="L179" t="n">
         <v>84.582222</v>
       </c>
+      <c r="M179" t="n">
+        <v>68.740066</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
@@ -7616,9 +7801,7 @@
           <t>無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)</t>
         </is>
       </c>
-      <c r="B180" t="n">
-        <v>60648.526277</v>
-      </c>
+      <c r="B180" t="inlineStr"/>
       <c r="C180" t="n">
         <v>66736.806524</v>
       </c>
@@ -7647,7 +7830,10 @@
         <v>38392.286909</v>
       </c>
       <c r="L180" t="n">
-        <v>52119.123526</v>
+        <v>52184.706026</v>
+      </c>
+      <c r="M180" t="n">
+        <v>43008.477291</v>
       </c>
     </row>
     <row r="181">
@@ -7656,9 +7842,7 @@
           <t>煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼</t>
         </is>
       </c>
-      <c r="B181" t="n">
-        <v>4839.002506</v>
-      </c>
+      <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
         <v>2605.808843</v>
       </c>
@@ -7689,6 +7873,9 @@
       <c r="L181" t="n">
         <v>2077.948424</v>
       </c>
+      <c r="M181" t="n">
+        <v>3688.596296</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
@@ -7696,9 +7883,7 @@
           <t>燈具/應用</t>
         </is>
       </c>
-      <c r="B182" t="n">
-        <v>37908.258174</v>
-      </c>
+      <c r="B182" t="inlineStr"/>
       <c r="C182" t="n">
         <v>40221.358177</v>
       </c>
@@ -7727,7 +7912,10 @@
         <v>17351.639807</v>
       </c>
       <c r="L182" t="n">
-        <v>24763.048636</v>
+        <v>24828.631136</v>
+      </c>
+      <c r="M182" t="n">
+        <v>17295.338461</v>
       </c>
     </row>
     <row r="183">
@@ -7736,9 +7924,7 @@
           <t>營造業</t>
         </is>
       </c>
-      <c r="B183" t="n">
-        <v>894.379987</v>
-      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" t="n">
         <v>885.95512</v>
       </c>
@@ -7769,6 +7955,9 @@
       <c r="L183" t="n">
         <v>501.233505</v>
       </c>
+      <c r="M183" t="n">
+        <v>500.844659</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
@@ -7776,9 +7965,7 @@
           <t>營造設置</t>
         </is>
       </c>
-      <c r="B184" t="n">
-        <v>215.658702</v>
-      </c>
+      <c r="B184" t="inlineStr"/>
       <c r="C184" t="n">
         <v>226.645727</v>
       </c>
@@ -7809,6 +7996,9 @@
       <c r="L184" t="n">
         <v>97.28177100000001</v>
       </c>
+      <c r="M184" t="n">
+        <v>111.310779</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
@@ -7816,9 +8006,7 @@
           <t>營運管理軟體</t>
         </is>
       </c>
-      <c r="B185" t="n">
-        <v>216.546136</v>
-      </c>
+      <c r="B185" t="inlineStr"/>
       <c r="C185" t="n">
         <v>637.014225</v>
       </c>
@@ -7849,6 +8037,9 @@
       <c r="L185" t="n">
         <v>149.006674</v>
       </c>
+      <c r="M185" t="n">
+        <v>144.475117</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
@@ -7856,9 +8047,7 @@
           <t>營養食品</t>
         </is>
       </c>
-      <c r="B186" t="n">
-        <v>23.221413</v>
-      </c>
+      <c r="B186" t="inlineStr"/>
       <c r="C186" t="n">
         <v>14.84592</v>
       </c>
@@ -7889,6 +8078,9 @@
       <c r="L186" t="n">
         <v>20.764808</v>
       </c>
+      <c r="M186" t="n">
+        <v>14.396008</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
@@ -7896,9 +8088,7 @@
           <t>物業管理</t>
         </is>
       </c>
-      <c r="B187" t="n">
-        <v>14214.267707</v>
-      </c>
+      <c r="B187" t="inlineStr"/>
       <c r="C187" t="n">
         <v>6955.544813</v>
       </c>
@@ -7929,6 +8119,9 @@
       <c r="L187" t="n">
         <v>2006.958158</v>
       </c>
+      <c r="M187" t="n">
+        <v>1909.956422</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
@@ -7936,9 +8129,7 @@
           <t>物流倉儲服務</t>
         </is>
       </c>
-      <c r="B188" t="n">
-        <v>87.53761299999999</v>
-      </c>
+      <c r="B188" t="inlineStr"/>
       <c r="C188" t="n">
         <v>51.225506</v>
       </c>
@@ -7969,6 +8160,9 @@
       <c r="L188" t="n">
         <v>82.317126</v>
       </c>
+      <c r="M188" t="n">
+        <v>113.458347</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
@@ -7976,9 +8170,7 @@
           <t>物聯網安全</t>
         </is>
       </c>
-      <c r="B189" t="n">
-        <v>212.477728</v>
-      </c>
+      <c r="B189" t="inlineStr"/>
       <c r="C189" t="n">
         <v>282.383503</v>
       </c>
@@ -8009,6 +8201,9 @@
       <c r="L189" t="n">
         <v>263.233674</v>
       </c>
+      <c r="M189" t="n">
+        <v>284.738327</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
@@ -8016,9 +8211,7 @@
           <t>特殊照明業</t>
         </is>
       </c>
-      <c r="B190" t="n">
-        <v>25824.318747</v>
-      </c>
+      <c r="B190" t="inlineStr"/>
       <c r="C190" t="n">
         <v>23116.831704</v>
       </c>
@@ -8047,7 +8240,10 @@
         <v>8945.266301</v>
       </c>
       <c r="L190" t="n">
-        <v>18296.270885</v>
+        <v>18361.853385</v>
+      </c>
+      <c r="M190" t="n">
+        <v>12316.53182</v>
       </c>
     </row>
     <row r="191">
@@ -8056,9 +8252,7 @@
           <t>玻/碳纖</t>
         </is>
       </c>
-      <c r="B191" t="n">
-        <v>217.720038</v>
-      </c>
+      <c r="B191" t="inlineStr"/>
       <c r="C191" t="n">
         <v>150.62937</v>
       </c>
@@ -8089,6 +8283,9 @@
       <c r="L191" t="n">
         <v>114.657033</v>
       </c>
+      <c r="M191" t="n">
+        <v>132.539768</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
@@ -8096,9 +8293,7 @@
           <t>玻璃基板</t>
         </is>
       </c>
-      <c r="B192" t="n">
-        <v>2120.355225</v>
-      </c>
+      <c r="B192" t="inlineStr"/>
       <c r="C192" t="n">
         <v>2413.157038</v>
       </c>
@@ -8129,6 +8324,9 @@
       <c r="L192" t="n">
         <v>336.153684</v>
       </c>
+      <c r="M192" t="n">
+        <v>393.958359</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
@@ -8136,9 +8334,7 @@
           <t>玻璃纖維/玻纖布</t>
         </is>
       </c>
-      <c r="B193" t="n">
-        <v>30937.846143</v>
-      </c>
+      <c r="B193" t="inlineStr"/>
       <c r="C193" t="n">
         <v>12370.60385</v>
       </c>
@@ -8169,6 +8365,9 @@
       <c r="L193" t="n">
         <v>5558.718884</v>
       </c>
+      <c r="M193" t="n">
+        <v>14440.943762</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
@@ -8176,9 +8375,7 @@
           <t>理財投資</t>
         </is>
       </c>
-      <c r="B194" t="n">
-        <v>178.038222</v>
-      </c>
+      <c r="B194" t="inlineStr"/>
       <c r="C194" t="n">
         <v>402.316918</v>
       </c>
@@ -8209,6 +8406,9 @@
       <c r="L194" t="n">
         <v>34.081738</v>
       </c>
+      <c r="M194" t="n">
+        <v>31.113459</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
@@ -8216,9 +8416,7 @@
           <t>環保潔能服務產業</t>
         </is>
       </c>
-      <c r="B195" t="n">
-        <v>6483.082031</v>
-      </c>
+      <c r="B195" t="inlineStr"/>
       <c r="C195" t="n">
         <v>4840.298138</v>
       </c>
@@ -8249,6 +8447,9 @@
       <c r="L195" t="n">
         <v>1512.392175</v>
       </c>
+      <c r="M195" t="n">
+        <v>1291.564048</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
@@ -8256,9 +8457,7 @@
           <t>環氧樹脂</t>
         </is>
       </c>
-      <c r="B196" t="n">
-        <v>19831.381117</v>
-      </c>
+      <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
         <v>12471.743301</v>
       </c>
@@ -8289,6 +8488,9 @@
       <c r="L196" t="n">
         <v>5630.532338</v>
       </c>
+      <c r="M196" t="n">
+        <v>12009.882023</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
@@ -8296,9 +8498,7 @@
           <t>生產製程、檢測設備及原物料</t>
         </is>
       </c>
-      <c r="B197" t="n">
-        <v>7490.943667</v>
-      </c>
+      <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
         <v>9192.600651000001</v>
       </c>
@@ -8327,7 +8527,10 @@
         <v>5523.282576</v>
       </c>
       <c r="L197" t="n">
-        <v>6347.486367</v>
+        <v>6452.600367</v>
+      </c>
+      <c r="M197" t="n">
+        <v>5090.478428</v>
       </c>
     </row>
     <row r="198">
@@ -8336,9 +8539,7 @@
           <t>生產製程及檢測設備</t>
         </is>
       </c>
-      <c r="B198" t="n">
-        <v>49280.027197</v>
-      </c>
+      <c r="B198" t="inlineStr"/>
       <c r="C198" t="n">
         <v>42285.192792</v>
       </c>
@@ -8358,16 +8559,19 @@
         <v>36035.740276</v>
       </c>
       <c r="I198" t="n">
-        <v>37332.121455</v>
+        <v>35678.201659</v>
       </c>
       <c r="J198" t="n">
-        <v>45206.326493</v>
+        <v>42309.252605</v>
       </c>
       <c r="K198" t="n">
-        <v>36631.697921</v>
+        <v>35818.381967</v>
       </c>
       <c r="L198" t="n">
-        <v>51228.608229</v>
+        <v>49060.693001</v>
+      </c>
+      <c r="M198" t="n">
+        <v>41283.553337</v>
       </c>
     </row>
     <row r="199">
@@ -8376,9 +8580,7 @@
           <t>發電營運</t>
         </is>
       </c>
-      <c r="B199" t="n">
-        <v>1077.533996</v>
-      </c>
+      <c r="B199" t="inlineStr"/>
       <c r="C199" t="n">
         <v>1945.182408</v>
       </c>
@@ -8409,6 +8611,9 @@
       <c r="L199" t="n">
         <v>546.9861979999999</v>
       </c>
+      <c r="M199" t="n">
+        <v>542.8145029999999</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
@@ -8416,9 +8621,7 @@
           <t>監控管理</t>
         </is>
       </c>
-      <c r="B200" t="n">
-        <v>182.215079</v>
-      </c>
+      <c r="B200" t="inlineStr"/>
       <c r="C200" t="n">
         <v>409.009537</v>
       </c>
@@ -8449,6 +8652,9 @@
       <c r="L200" t="n">
         <v>38.936418</v>
       </c>
+      <c r="M200" t="n">
+        <v>39.52318</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
@@ -8456,9 +8662,7 @@
           <t>監控系統</t>
         </is>
       </c>
-      <c r="B201" t="n">
-        <v>31120.424712</v>
-      </c>
+      <c r="B201" t="inlineStr"/>
       <c r="C201" t="n">
         <v>29511.506229</v>
       </c>
@@ -8487,7 +8691,10 @@
         <v>9595.179314999999</v>
       </c>
       <c r="L201" t="n">
-        <v>18994.632217</v>
+        <v>19060.214717</v>
+      </c>
+      <c r="M201" t="n">
+        <v>13463.987717</v>
       </c>
     </row>
     <row r="202">
@@ -8496,9 +8703,7 @@
           <t>監理法遵</t>
         </is>
       </c>
-      <c r="B202" t="n">
-        <v>203.331185</v>
-      </c>
+      <c r="B202" t="inlineStr"/>
       <c r="C202" t="n">
         <v>438.140838</v>
       </c>
@@ -8529,6 +8734,9 @@
       <c r="L202" t="n">
         <v>46.591202</v>
       </c>
+      <c r="M202" t="n">
+        <v>45.925659</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
@@ -8536,9 +8744,7 @@
           <t>監視器/顯示器</t>
         </is>
       </c>
-      <c r="B203" t="n">
-        <v>5125.533039</v>
-      </c>
+      <c r="B203" t="inlineStr"/>
       <c r="C203" t="n">
         <v>4881.354054</v>
       </c>
@@ -8569,6 +8775,9 @@
       <c r="L203" t="n">
         <v>1152.752557</v>
       </c>
+      <c r="M203" t="n">
+        <v>789.702401</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
@@ -8576,9 +8785,7 @@
           <t>石化上游原料及相關鑽探設備</t>
         </is>
       </c>
-      <c r="B204" t="n">
-        <v>14896.003904</v>
-      </c>
+      <c r="B204" t="inlineStr"/>
       <c r="C204" t="n">
         <v>9753.705179</v>
       </c>
@@ -8609,6 +8816,9 @@
       <c r="L204" t="n">
         <v>4612.570738</v>
       </c>
+      <c r="M204" t="n">
+        <v>10871.608162</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
@@ -8616,9 +8826,7 @@
           <t>石化中間原料(例如乙烯、丙烯、丁二烯、苯、酚等)</t>
         </is>
       </c>
-      <c r="B205" t="n">
-        <v>7894.181757</v>
-      </c>
+      <c r="B205" t="inlineStr"/>
       <c r="C205" t="n">
         <v>5066.595461</v>
       </c>
@@ -8638,16 +8846,19 @@
         <v>7631.544262</v>
       </c>
       <c r="I205" t="n">
-        <v>5405.504065</v>
+        <v>5287.913025</v>
       </c>
       <c r="J205" t="n">
-        <v>4007.836843</v>
+        <v>3924.963182</v>
       </c>
       <c r="K205" t="n">
-        <v>5626.300413</v>
+        <v>5523.636631</v>
       </c>
       <c r="L205" t="n">
-        <v>4924.54852</v>
+        <v>4870.557773</v>
+      </c>
+      <c r="M205" t="n">
+        <v>4574.414325</v>
       </c>
     </row>
     <row r="206">
@@ -8656,9 +8867,7 @@
           <t>石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等)</t>
         </is>
       </c>
-      <c r="B206" t="n">
-        <v>17092.916464</v>
-      </c>
+      <c r="B206" t="inlineStr"/>
       <c r="C206" t="n">
         <v>12654.986827</v>
       </c>
@@ -8687,7 +8896,10 @@
         <v>8604.441489999999</v>
       </c>
       <c r="L206" t="n">
-        <v>6822.819678</v>
+        <v>6848.646918</v>
+      </c>
+      <c r="M206" t="n">
+        <v>14270.932875</v>
       </c>
     </row>
     <row r="207">
@@ -8696,9 +8908,7 @@
           <t>石灰石</t>
         </is>
       </c>
-      <c r="B207" t="n">
-        <v>2329.788257</v>
-      </c>
+      <c r="B207" t="inlineStr"/>
       <c r="C207" t="n">
         <v>972.043961</v>
       </c>
@@ -8729,6 +8939,9 @@
       <c r="L207" t="n">
         <v>715.578791</v>
       </c>
+      <c r="M207" t="n">
+        <v>694.036544</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
@@ -8736,9 +8949,7 @@
           <t>矽晶圓/矽晶片</t>
         </is>
       </c>
-      <c r="B208" t="n">
-        <v>9654.731088</v>
-      </c>
+      <c r="B208" t="inlineStr"/>
       <c r="C208" t="n">
         <v>5528.020305</v>
       </c>
@@ -8769,6 +8980,9 @@
       <c r="L208" t="n">
         <v>9944.670695999999</v>
       </c>
+      <c r="M208" t="n">
+        <v>5202.75353</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
@@ -8776,9 +8990,7 @@
           <t>硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="B209" t="n">
-        <v>69983.161335</v>
-      </c>
+      <c r="B209" t="inlineStr"/>
       <c r="C209" t="n">
         <v>75390.94137099999</v>
       </c>
@@ -8807,7 +9019,10 @@
         <v>108782.814066</v>
       </c>
       <c r="L209" t="n">
-        <v>89307.151476</v>
+        <v>89353.030776</v>
+      </c>
+      <c r="M209" t="n">
+        <v>67339.770422</v>
       </c>
     </row>
     <row r="210">
@@ -8816,9 +9031,7 @@
           <t>硬碟機</t>
         </is>
       </c>
-      <c r="B210" t="n">
-        <v>4386.005541</v>
-      </c>
+      <c r="B210" t="inlineStr"/>
       <c r="C210" t="n">
         <v>2713.446314</v>
       </c>
@@ -8849,6 +9062,9 @@
       <c r="L210" t="n">
         <v>3163.229034</v>
       </c>
+      <c r="M210" t="n">
+        <v>2698.946198</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
@@ -8856,9 +9072,7 @@
           <t>硬體開發工具</t>
         </is>
       </c>
-      <c r="B211" t="n">
-        <v>704.373165</v>
-      </c>
+      <c r="B211" t="inlineStr"/>
       <c r="C211" t="n">
         <v>358.616734</v>
       </c>
@@ -8889,6 +9103,9 @@
       <c r="L211" t="n">
         <v>240.333646</v>
       </c>
+      <c r="M211" t="n">
+        <v>273.260521</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
@@ -8896,9 +9113,7 @@
           <t>磁碟儲存系統</t>
         </is>
       </c>
-      <c r="B212" t="n">
-        <v>2525.452225</v>
-      </c>
+      <c r="B212" t="inlineStr"/>
       <c r="C212" t="n">
         <v>1799.815782</v>
       </c>
@@ -8929,6 +9144,9 @@
       <c r="L212" t="n">
         <v>2254.754967</v>
       </c>
+      <c r="M212" t="n">
+        <v>2249.872138</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
@@ -8936,9 +9154,7 @@
           <t>票券銷售</t>
         </is>
       </c>
-      <c r="B213" t="n">
-        <v>189.924497</v>
-      </c>
+      <c r="B213" t="inlineStr"/>
       <c r="C213" t="n">
         <v>314.795897</v>
       </c>
@@ -8969,6 +9185,9 @@
       <c r="L213" t="n">
         <v>253.604375</v>
       </c>
+      <c r="M213" t="n">
+        <v>221.99492525</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
@@ -8976,9 +9195,7 @@
           <t>租賃業</t>
         </is>
       </c>
-      <c r="B214" t="n">
-        <v>995.372472</v>
-      </c>
+      <c r="B214" t="inlineStr"/>
       <c r="C214" t="n">
         <v>859.963492</v>
       </c>
@@ -9009,6 +9226,9 @@
       <c r="L214" t="n">
         <v>774.822891</v>
       </c>
+      <c r="M214" t="n">
+        <v>829.8685410000001</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
@@ -9016,9 +9236,7 @@
           <t>移動控制</t>
         </is>
       </c>
-      <c r="B215" t="n">
-        <v>7311.175276</v>
-      </c>
+      <c r="B215" t="inlineStr"/>
       <c r="C215" t="n">
         <v>8352.780285999999</v>
       </c>
@@ -9049,6 +9267,9 @@
       <c r="L215" t="n">
         <v>2922.078695</v>
       </c>
+      <c r="M215" t="n">
+        <v>3356.570193</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
@@ -9056,9 +9277,7 @@
           <t>稜鏡片</t>
         </is>
       </c>
-      <c r="B216" t="n">
-        <v>32.142169</v>
-      </c>
+      <c r="B216" t="inlineStr"/>
       <c r="C216" t="n">
         <v>94.190871</v>
       </c>
@@ -9089,6 +9308,9 @@
       <c r="L216" t="n">
         <v>6.2366</v>
       </c>
+      <c r="M216" t="n">
+        <v>14.068046</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
@@ -9096,9 +9318,7 @@
           <t>穿戴式裝置</t>
         </is>
       </c>
-      <c r="B217" t="n">
-        <v>32175.045943</v>
-      </c>
+      <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
         <v>28049.202996</v>
       </c>
@@ -9129,6 +9349,9 @@
       <c r="L217" t="n">
         <v>20395.478615</v>
       </c>
+      <c r="M217" t="n">
+        <v>15695.654621</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
@@ -9136,9 +9359,7 @@
           <t>端點安全防護</t>
         </is>
       </c>
-      <c r="B218" t="n">
-        <v>228.932425</v>
-      </c>
+      <c r="B218" t="inlineStr"/>
       <c r="C218" t="n">
         <v>314.383672</v>
       </c>
@@ -9169,6 +9390,9 @@
       <c r="L218" t="n">
         <v>268.66801</v>
       </c>
+      <c r="M218" t="n">
+        <v>295.170918</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
@@ -9176,9 +9400,7 @@
           <t>筆記型電腦</t>
         </is>
       </c>
-      <c r="B219" t="n">
-        <v>70534.74253800001</v>
-      </c>
+      <c r="B219" t="inlineStr"/>
       <c r="C219" t="n">
         <v>62152.560828</v>
       </c>
@@ -9207,7 +9429,10 @@
         <v>27192.875467</v>
       </c>
       <c r="L219" t="n">
-        <v>44651.227728</v>
+        <v>44716.810228</v>
+      </c>
+      <c r="M219" t="n">
+        <v>42314.243774</v>
       </c>
     </row>
     <row r="220">
@@ -9216,9 +9441,7 @@
           <t>精簡型電腦</t>
         </is>
       </c>
-      <c r="B220" t="n">
-        <v>28009.464271</v>
-      </c>
+      <c r="B220" t="inlineStr"/>
       <c r="C220" t="n">
         <v>25209.115962</v>
       </c>
@@ -9247,7 +9470,10 @@
         <v>10847.263607</v>
       </c>
       <c r="L220" t="n">
-        <v>21194.740622</v>
+        <v>21260.323122</v>
+      </c>
+      <c r="M220" t="n">
+        <v>15618.414634</v>
       </c>
     </row>
     <row r="221">
@@ -9256,9 +9482,7 @@
           <t>系統整合</t>
         </is>
       </c>
-      <c r="B221" t="n">
-        <v>90945.419436</v>
-      </c>
+      <c r="B221" t="inlineStr"/>
       <c r="C221" t="n">
         <v>89485.972123</v>
       </c>
@@ -9287,7 +9511,10 @@
         <v>35154.164808</v>
       </c>
       <c r="L221" t="n">
-        <v>61037.912599</v>
+        <v>61234.660099</v>
+      </c>
+      <c r="M221" t="n">
+        <v>41263.385301</v>
       </c>
     </row>
     <row r="222">
@@ -9296,9 +9523,7 @@
           <t>系統整合服務</t>
         </is>
       </c>
-      <c r="B222" t="n">
-        <v>45698.540013</v>
-      </c>
+      <c r="B222" t="inlineStr"/>
       <c r="C222" t="n">
         <v>36025.412241</v>
       </c>
@@ -9327,7 +9552,10 @@
         <v>15473.48016</v>
       </c>
       <c r="L222" t="n">
-        <v>26661.460511</v>
+        <v>26832.157011</v>
+      </c>
+      <c r="M222" t="n">
+        <v>20106.232531</v>
       </c>
     </row>
     <row r="223">
@@ -9336,9 +9564,7 @@
           <t>紙漿、紙類原料</t>
         </is>
       </c>
-      <c r="B223" t="n">
-        <v>61.724295</v>
-      </c>
+      <c r="B223" t="inlineStr"/>
       <c r="C223" t="n">
         <v>52.681878</v>
       </c>
@@ -9369,6 +9595,9 @@
       <c r="L223" t="n">
         <v>45.1665</v>
       </c>
+      <c r="M223" t="n">
+        <v>67.78853100000001</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
@@ -9376,9 +9605,7 @@
           <t>紡紗</t>
         </is>
       </c>
-      <c r="B224" t="n">
-        <v>826.669579</v>
-      </c>
+      <c r="B224" t="inlineStr"/>
       <c r="C224" t="n">
         <v>867.847481</v>
       </c>
@@ -9398,16 +9625,19 @@
         <v>3354.77875</v>
       </c>
       <c r="I224" t="n">
-        <v>1703.410361</v>
+        <v>1703.480191</v>
       </c>
       <c r="J224" t="n">
-        <v>1145.757851</v>
+        <v>1145.8478</v>
       </c>
       <c r="K224" t="n">
-        <v>1396.503906</v>
+        <v>1396.593296</v>
       </c>
       <c r="L224" t="n">
-        <v>1066.012544</v>
+        <v>1066.043344</v>
+      </c>
+      <c r="M224" t="n">
+        <v>1679.940968</v>
       </c>
     </row>
     <row r="225">
@@ -9416,9 +9646,7 @@
           <t>組裝廠</t>
         </is>
       </c>
-      <c r="B225" t="n">
-        <v>71.231807</v>
-      </c>
+      <c r="B225" t="inlineStr"/>
       <c r="C225" t="n">
         <v>148.090535</v>
       </c>
@@ -9449,6 +9677,9 @@
       <c r="L225" t="n">
         <v>56.212809</v>
       </c>
+      <c r="M225" t="n">
+        <v>78.11375700000001</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
@@ -9456,9 +9687,7 @@
           <t>結構工程</t>
         </is>
       </c>
-      <c r="B226" t="n">
-        <v>168.539672</v>
-      </c>
+      <c r="B226" t="inlineStr"/>
       <c r="C226" t="n">
         <v>197.877332</v>
       </c>
@@ -9489,6 +9718,9 @@
       <c r="L226" t="n">
         <v>264.643076</v>
       </c>
+      <c r="M226" t="n">
+        <v>224.002318</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
@@ -9496,9 +9728,7 @@
           <t>網路IC</t>
         </is>
       </c>
-      <c r="B227" t="n">
-        <v>11.970034</v>
-      </c>
+      <c r="B227" t="inlineStr"/>
       <c r="C227" t="n">
         <v>5.054933</v>
       </c>
@@ -9529,6 +9759,9 @@
       <c r="L227" t="n">
         <v>3.54811</v>
       </c>
+      <c r="M227" t="n">
+        <v>3.400565</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
@@ -9536,9 +9769,7 @@
           <t>網路卡</t>
         </is>
       </c>
-      <c r="B228" t="n">
-        <v>1518.629389</v>
-      </c>
+      <c r="B228" t="inlineStr"/>
       <c r="C228" t="n">
         <v>1340.737437</v>
       </c>
@@ -9569,6 +9800,9 @@
       <c r="L228" t="n">
         <v>2134.10536</v>
       </c>
+      <c r="M228" t="n">
+        <v>2126.908767</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
@@ -9576,9 +9810,7 @@
           <t>網路基礎設施</t>
         </is>
       </c>
-      <c r="B229" t="n">
-        <v>1629.539002</v>
-      </c>
+      <c r="B229" t="inlineStr"/>
       <c r="C229" t="n">
         <v>996.020816</v>
       </c>
@@ -9609,6 +9841,9 @@
       <c r="L229" t="n">
         <v>522.313265</v>
       </c>
+      <c r="M229" t="n">
+        <v>476.518983</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
@@ -9616,9 +9851,7 @@
           <t>網路安全防護</t>
         </is>
       </c>
-      <c r="B230" t="n">
-        <v>1469.824951</v>
-      </c>
+      <c r="B230" t="inlineStr"/>
       <c r="C230" t="n">
         <v>644.280611</v>
       </c>
@@ -9649,6 +9882,9 @@
       <c r="L230" t="n">
         <v>403.978975</v>
       </c>
+      <c r="M230" t="n">
+        <v>368.244747</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
@@ -9656,9 +9892,7 @@
           <t>網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
         </is>
       </c>
-      <c r="B231" t="n">
-        <v>69473.99498600001</v>
-      </c>
+      <c r="B231" t="inlineStr"/>
       <c r="C231" t="n">
         <v>72256.16495799999</v>
       </c>
@@ -9687,7 +9921,10 @@
         <v>41644.705993</v>
       </c>
       <c r="L231" t="n">
-        <v>55852.133687</v>
+        <v>55917.716187</v>
+      </c>
+      <c r="M231" t="n">
+        <v>49250.93021275</v>
       </c>
     </row>
     <row r="232">
@@ -9696,9 +9933,7 @@
           <t>網頁內容安全</t>
         </is>
       </c>
-      <c r="B232" t="n">
-        <v>163.5777</v>
-      </c>
+      <c r="B232" t="inlineStr"/>
       <c r="C232" t="n">
         <v>194.709904</v>
       </c>
@@ -9729,6 +9964,9 @@
       <c r="L232" t="n">
         <v>232.587808</v>
       </c>
+      <c r="M232" t="n">
+        <v>215.690611</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
@@ -9736,9 +9974,7 @@
           <t>線上遊戲業</t>
         </is>
       </c>
-      <c r="B233" t="n">
-        <v>19.612939</v>
-      </c>
+      <c r="B233" t="inlineStr"/>
       <c r="C233" t="n">
         <v>20.661198</v>
       </c>
@@ -9758,16 +9994,19 @@
         <v>24.55708</v>
       </c>
       <c r="I233" t="n">
-        <v>17.19605</v>
+        <v>19.129845</v>
       </c>
       <c r="J233" t="n">
-        <v>11.010975</v>
+        <v>12.706736</v>
       </c>
       <c r="K233" t="n">
-        <v>14.439932</v>
+        <v>15.901758</v>
       </c>
       <c r="L233" t="n">
-        <v>27.787042</v>
+        <v>28.910743</v>
+      </c>
+      <c r="M233" t="n">
+        <v>15.990174</v>
       </c>
     </row>
     <row r="234">
@@ -9776,9 +10015,7 @@
           <t>線材</t>
         </is>
       </c>
-      <c r="B234" t="n">
-        <v>8181.908839</v>
-      </c>
+      <c r="B234" t="inlineStr"/>
       <c r="C234" t="n">
         <v>6505.305372</v>
       </c>
@@ -9809,6 +10046,9 @@
       <c r="L234" t="n">
         <v>6416.048064</v>
       </c>
+      <c r="M234" t="n">
+        <v>7494.749275</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
@@ -9816,9 +10056,7 @@
           <t>線材盤元</t>
         </is>
       </c>
-      <c r="B235" t="n">
-        <v>525.352161</v>
-      </c>
+      <c r="B235" t="inlineStr"/>
       <c r="C235" t="n">
         <v>613.4166064999999</v>
       </c>
@@ -9849,6 +10087,9 @@
       <c r="L235" t="n">
         <v>975.542199</v>
       </c>
+      <c r="M235" t="n">
+        <v>1080.414736333333</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
@@ -9856,9 +10097,7 @@
           <t>織布</t>
         </is>
       </c>
-      <c r="B236" t="n">
-        <v>1102.257047</v>
-      </c>
+      <c r="B236" t="inlineStr"/>
       <c r="C236" t="n">
         <v>1208.576585</v>
       </c>
@@ -9889,6 +10128,9 @@
       <c r="L236" t="n">
         <v>1746.163596</v>
       </c>
+      <c r="M236" t="n">
+        <v>1934.117764</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
@@ -9896,9 +10138,7 @@
           <t>聚亞醯胺樹脂</t>
         </is>
       </c>
-      <c r="B237" t="n">
-        <v>5707.65485</v>
-      </c>
+      <c r="B237" t="inlineStr"/>
       <c r="C237" t="n">
         <v>3239.467354</v>
       </c>
@@ -9929,6 +10169,9 @@
       <c r="L237" t="n">
         <v>1463.083412</v>
       </c>
+      <c r="M237" t="n">
+        <v>1570.283729</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
@@ -9936,9 +10179,7 @@
           <t>背光模組</t>
         </is>
       </c>
-      <c r="B238" t="n">
-        <v>4686.558082</v>
-      </c>
+      <c r="B238" t="inlineStr"/>
       <c r="C238" t="n">
         <v>2854.324072</v>
       </c>
@@ -9969,6 +10210,9 @@
       <c r="L238" t="n">
         <v>1197.885504</v>
       </c>
+      <c r="M238" t="n">
+        <v>1058.235202333333</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
@@ -9976,9 +10220,7 @@
           <t>背光源(發光二極體、冷陰極管)</t>
         </is>
       </c>
-      <c r="B239" t="n">
-        <v>2735.331622</v>
-      </c>
+      <c r="B239" t="inlineStr"/>
       <c r="C239" t="n">
         <v>4730.719062</v>
       </c>
@@ -10009,6 +10251,9 @@
       <c r="L239" t="n">
         <v>2401.7457</v>
       </c>
+      <c r="M239" t="n">
+        <v>2055.856681</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
@@ -10016,9 +10261,7 @@
           <t>能源管理服務</t>
         </is>
       </c>
-      <c r="B240" t="n">
-        <v>41339.656417</v>
-      </c>
+      <c r="B240" t="inlineStr"/>
       <c r="C240" t="n">
         <v>32476.982225</v>
       </c>
@@ -10047,7 +10290,10 @@
         <v>12273.365795</v>
       </c>
       <c r="L240" t="n">
-        <v>22576.781061</v>
+        <v>22642.363561</v>
+      </c>
+      <c r="M240" t="n">
+        <v>16502.381123</v>
       </c>
     </row>
     <row r="241">
@@ -10056,9 +10302,7 @@
           <t>膠材</t>
         </is>
       </c>
-      <c r="B241" t="n">
-        <v>6324.644767</v>
-      </c>
+      <c r="B241" t="inlineStr"/>
       <c r="C241" t="n">
         <v>3739.451646</v>
       </c>
@@ -10089,6 +10333,9 @@
       <c r="L241" t="n">
         <v>2110.498596</v>
       </c>
+      <c r="M241" t="n">
+        <v>1989.40288</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
@@ -10096,9 +10343,7 @@
           <t>臨床實驗、移植技術、疾病治療</t>
         </is>
       </c>
-      <c r="B242" t="n">
-        <v>66.423514</v>
-      </c>
+      <c r="B242" t="inlineStr"/>
       <c r="C242" t="n">
         <v>60.223557</v>
       </c>
@@ -10129,6 +10374,9 @@
       <c r="L242" t="n">
         <v>57.644193</v>
       </c>
+      <c r="M242" t="n">
+        <v>49.223435</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
@@ -10136,9 +10384,7 @@
           <t>自動化機台</t>
         </is>
       </c>
-      <c r="B243" t="n">
-        <v>0.645653</v>
-      </c>
+      <c r="B243" t="inlineStr"/>
       <c r="C243" t="n">
         <v>0.83435</v>
       </c>
@@ -10169,6 +10415,9 @@
       <c r="L243" t="n">
         <v>0.67972</v>
       </c>
+      <c r="M243" t="n">
+        <v>0.741302</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
@@ -10176,9 +10425,7 @@
           <t>自動售票機</t>
         </is>
       </c>
-      <c r="B244" t="n">
-        <v>16.832351</v>
-      </c>
+      <c r="B244" t="inlineStr"/>
       <c r="C244" t="n">
         <v>18.047698</v>
       </c>
@@ -10209,6 +10456,9 @@
       <c r="L244" t="n">
         <v>11.755694</v>
       </c>
+      <c r="M244" t="n">
+        <v>28.035732</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
@@ -10216,9 +10466,7 @@
           <t>自動販賣機</t>
         </is>
       </c>
-      <c r="B245" t="n">
-        <v>4.322417</v>
-      </c>
+      <c r="B245" t="inlineStr"/>
       <c r="C245" t="n">
         <v>3.876185</v>
       </c>
@@ -10249,6 +10497,9 @@
       <c r="L245" t="n">
         <v>1.492916</v>
       </c>
+      <c r="M245" t="n">
+        <v>5.074748</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
@@ -10256,9 +10507,7 @@
           <t>自有產品(服務)銷售</t>
         </is>
       </c>
-      <c r="B246" t="n">
-        <v>13.142028</v>
-      </c>
+      <c r="B246" t="inlineStr"/>
       <c r="C246" t="n">
         <v>10.656166</v>
       </c>
@@ -10289,6 +10538,9 @@
       <c r="L246" t="n">
         <v>12.157338</v>
       </c>
+      <c r="M246" t="n">
+        <v>12.97161</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
@@ -10296,9 +10548,7 @@
           <t>自然語言處理</t>
         </is>
       </c>
-      <c r="B247" t="n">
-        <v>37.554455</v>
-      </c>
+      <c r="B247" t="inlineStr"/>
       <c r="C247" t="n">
         <v>49.637052</v>
       </c>
@@ -10329,6 +10579,9 @@
       <c r="L247" t="n">
         <v>27.636419</v>
       </c>
+      <c r="M247" t="n">
+        <v>31.636501</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
@@ -10336,9 +10589,7 @@
           <t>藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="B248" t="n">
-        <v>4323.071168</v>
-      </c>
+      <c r="B248" t="inlineStr"/>
       <c r="C248" t="n">
         <v>2472.895752</v>
       </c>
@@ -10369,6 +10620,9 @@
       <c r="L248" t="n">
         <v>956.003576</v>
       </c>
+      <c r="M248" t="n">
+        <v>813.837991</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
@@ -10376,9 +10630,7 @@
           <t>藥品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B249" t="n">
-        <v>299.532624</v>
-      </c>
+      <c r="B249" t="inlineStr"/>
       <c r="C249" t="n">
         <v>884.334384</v>
       </c>
@@ -10409,6 +10661,9 @@
       <c r="L249" t="n">
         <v>898.9430609999999</v>
       </c>
+      <c r="M249" t="n">
+        <v>576.233248</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
@@ -10416,9 +10671,7 @@
           <t>處理器/IC</t>
         </is>
       </c>
-      <c r="B250" t="n">
-        <v>2.718723</v>
-      </c>
+      <c r="B250" t="inlineStr"/>
       <c r="C250" t="n">
         <v>2.403416</v>
       </c>
@@ -10449,6 +10702,9 @@
       <c r="L250" t="n">
         <v>0.613901</v>
       </c>
+      <c r="M250" t="n">
+        <v>0.862165</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
@@ -10456,9 +10712,7 @@
           <t>虛擬化軟體</t>
         </is>
       </c>
-      <c r="B251" t="n">
-        <v>254.76921</v>
-      </c>
+      <c r="B251" t="inlineStr"/>
       <c r="C251" t="n">
         <v>701.191783</v>
       </c>
@@ -10489,6 +10743,9 @@
       <c r="L251" t="n">
         <v>282.753552</v>
       </c>
+      <c r="M251" t="n">
+        <v>250.466229</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
@@ -10496,9 +10753,7 @@
           <t>螺絲螺帽</t>
         </is>
       </c>
-      <c r="B252" t="n">
-        <v>134.827182</v>
-      </c>
+      <c r="B252" t="inlineStr"/>
       <c r="C252" t="n">
         <v>128.254144</v>
       </c>
@@ -10529,6 +10784,9 @@
       <c r="L252" t="n">
         <v>44.515737</v>
       </c>
+      <c r="M252" t="n">
+        <v>59.49989</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
@@ -10536,9 +10794,7 @@
           <t>行動安全</t>
         </is>
       </c>
-      <c r="B253" t="n">
-        <v>1394.457288</v>
-      </c>
+      <c r="B253" t="inlineStr"/>
       <c r="C253" t="n">
         <v>529.2881630000001</v>
       </c>
@@ -10569,6 +10825,9 @@
       <c r="L253" t="n">
         <v>340.851087</v>
       </c>
+      <c r="M253" t="n">
+        <v>259.91409</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
@@ -10576,9 +10835,7 @@
           <t>行銷廣告服務</t>
         </is>
       </c>
-      <c r="B254" t="n">
-        <v>109.268847</v>
-      </c>
+      <c r="B254" t="inlineStr"/>
       <c r="C254" t="n">
         <v>277.78267</v>
       </c>
@@ -10609,6 +10866,9 @@
       <c r="L254" t="n">
         <v>176.841809</v>
       </c>
+      <c r="M254" t="n">
+        <v>110.919141</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
@@ -10616,9 +10876,7 @@
           <t>衛星定位系統</t>
         </is>
       </c>
-      <c r="B255" t="n">
-        <v>5.7e-05</v>
-      </c>
+      <c r="B255" t="inlineStr"/>
       <c r="C255" t="n">
         <v>0.000289</v>
       </c>
@@ -10649,6 +10907,9 @@
       <c r="L255" t="n">
         <v>1.8e-05</v>
       </c>
+      <c r="M255" t="n">
+        <v>7.1e-05</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
@@ -10656,9 +10917,7 @@
           <t>裁剪加工</t>
         </is>
       </c>
-      <c r="B256" t="n">
-        <v>86.495098</v>
-      </c>
+      <c r="B256" t="inlineStr"/>
       <c r="C256" t="n">
         <v>119.923396</v>
       </c>
@@ -10689,6 +10948,9 @@
       <c r="L256" t="n">
         <v>137.199996</v>
       </c>
+      <c r="M256" t="n">
+        <v>155.728896</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
@@ -10696,9 +10958,7 @@
           <t>裝潢業</t>
         </is>
       </c>
-      <c r="B257" t="n">
-        <v>121.481699</v>
-      </c>
+      <c r="B257" t="inlineStr"/>
       <c r="C257" t="n">
         <v>149.297825</v>
       </c>
@@ -10729,6 +10989,9 @@
       <c r="L257" t="n">
         <v>182.018017</v>
       </c>
+      <c r="M257" t="n">
+        <v>147.286144</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
@@ -10736,9 +10999,7 @@
           <t>裝置/器材零組件</t>
         </is>
       </c>
-      <c r="B258" t="n">
-        <v>11.744287</v>
-      </c>
+      <c r="B258" t="inlineStr"/>
       <c r="C258" t="n">
         <v>4.563522</v>
       </c>
@@ -10769,6 +11030,9 @@
       <c r="L258" t="n">
         <v>3.150428</v>
       </c>
+      <c r="M258" t="n">
+        <v>2.970912</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
@@ -10776,9 +11040,7 @@
           <t>裝置/器材顯示器</t>
         </is>
       </c>
-      <c r="B259" t="n">
-        <v>11.741452</v>
-      </c>
+      <c r="B259" t="inlineStr"/>
       <c r="C259" t="n">
         <v>4.561848</v>
       </c>
@@ -10809,6 +11071,9 @@
       <c r="L259" t="n">
         <v>3.149226</v>
       </c>
+      <c r="M259" t="n">
+        <v>2.970124</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
@@ -10816,9 +11081,7 @@
           <t>製管</t>
         </is>
       </c>
-      <c r="B260" t="n">
-        <v>5232.816965</v>
-      </c>
+      <c r="B260" t="inlineStr"/>
       <c r="C260" t="n">
         <v>3202.054307</v>
       </c>
@@ -10849,6 +11112,9 @@
       <c r="L260" t="n">
         <v>3168.260627</v>
       </c>
+      <c r="M260" t="n">
+        <v>4786.608416</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
@@ -10856,9 +11122,7 @@
           <t>製造商</t>
         </is>
       </c>
-      <c r="B261" t="n">
-        <v>4167.51718</v>
-      </c>
+      <c r="B261" t="inlineStr"/>
       <c r="C261" t="n">
         <v>2314.114018</v>
       </c>
@@ -10889,6 +11153,9 @@
       <c r="L261" t="n">
         <v>843.916824</v>
       </c>
+      <c r="M261" t="n">
+        <v>575.415164</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
@@ -10896,9 +11163,7 @@
           <t>觸控面板</t>
         </is>
       </c>
-      <c r="B262" t="n">
-        <v>23087.664895</v>
-      </c>
+      <c r="B262" t="inlineStr"/>
       <c r="C262" t="n">
         <v>19110.92823</v>
       </c>
@@ -10918,16 +11183,19 @@
         <v>18393.569229</v>
       </c>
       <c r="I262" t="n">
-        <v>9283.063964000001</v>
+        <v>9310.94492</v>
       </c>
       <c r="J262" t="n">
-        <v>6932.704581</v>
+        <v>6953.684465</v>
       </c>
       <c r="K262" t="n">
-        <v>10539.42505</v>
+        <v>10619.982878</v>
       </c>
       <c r="L262" t="n">
-        <v>13746.805977</v>
+        <v>13776.33431</v>
+      </c>
+      <c r="M262" t="n">
+        <v>7167.736233</v>
       </c>
     </row>
     <row r="263">
@@ -10936,9 +11204,7 @@
           <t>記憶體</t>
         </is>
       </c>
-      <c r="B263" t="n">
-        <v>30219.772058</v>
-      </c>
+      <c r="B263" t="inlineStr"/>
       <c r="C263" t="n">
         <v>107781.644232</v>
       </c>
@@ -10969,6 +11235,9 @@
       <c r="L263" t="n">
         <v>83173.30237400001</v>
       </c>
+      <c r="M263" t="n">
+        <v>122593.260708</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
@@ -10976,9 +11245,7 @@
           <t>設備安裝服務</t>
         </is>
       </c>
-      <c r="B264" t="n">
-        <v>35368.078565</v>
-      </c>
+      <c r="B264" t="inlineStr"/>
       <c r="C264" t="n">
         <v>38219.926428</v>
       </c>
@@ -11007,7 +11274,10 @@
         <v>14844.505287</v>
       </c>
       <c r="L264" t="n">
-        <v>21993.980871</v>
+        <v>22059.563371</v>
+      </c>
+      <c r="M264" t="n">
+        <v>14511.2087</v>
       </c>
     </row>
     <row r="265">
@@ -11016,9 +11286,7 @@
           <t>設備管理軟體</t>
         </is>
       </c>
-      <c r="B265" t="n">
-        <v>25663.021887</v>
-      </c>
+      <c r="B265" t="inlineStr"/>
       <c r="C265" t="n">
         <v>23703.134592</v>
       </c>
@@ -11047,7 +11315,10 @@
         <v>9085.63536</v>
       </c>
       <c r="L265" t="n">
-        <v>18515.35314</v>
+        <v>18580.93564</v>
+      </c>
+      <c r="M265" t="n">
+        <v>12498.222426</v>
       </c>
     </row>
     <row r="266">
@@ -11056,9 +11327,7 @@
           <t>設備維護</t>
         </is>
       </c>
-      <c r="B266" t="n">
-        <v>78.80997000000001</v>
-      </c>
+      <c r="B266" t="inlineStr"/>
       <c r="C266" t="n">
         <v>48.015688</v>
       </c>
@@ -11089,6 +11358,9 @@
       <c r="L266" t="n">
         <v>21.492498</v>
       </c>
+      <c r="M266" t="n">
+        <v>30.974408</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
@@ -11096,9 +11368,7 @@
           <t>證券業</t>
         </is>
       </c>
-      <c r="B267" t="n">
-        <v>1382.997961</v>
-      </c>
+      <c r="B267" t="inlineStr"/>
       <c r="C267" t="n">
         <v>1030.740993</v>
       </c>
@@ -11129,6 +11399,9 @@
       <c r="L267" t="n">
         <v>1159.303286</v>
       </c>
+      <c r="M267" t="n">
+        <v>799.1746910000001</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
@@ -11136,9 +11409,7 @@
           <t>變壓器</t>
         </is>
       </c>
-      <c r="B268" t="n">
-        <v>8916.705529999999</v>
-      </c>
+      <c r="B268" t="inlineStr"/>
       <c r="C268" t="n">
         <v>5245.07613</v>
       </c>
@@ -11169,6 +11440,9 @@
       <c r="L268" t="n">
         <v>3932.319009</v>
       </c>
+      <c r="M268" t="n">
+        <v>4448.049216</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
@@ -11176,9 +11450,7 @@
           <t>貨櫃航運</t>
         </is>
       </c>
-      <c r="B269" t="n">
-        <v>2719.086108</v>
-      </c>
+      <c r="B269" t="inlineStr"/>
       <c r="C269" t="n">
         <v>3239.244773</v>
       </c>
@@ -11209,6 +11481,9 @@
       <c r="L269" t="n">
         <v>1529.928867</v>
       </c>
+      <c r="M269" t="n">
+        <v>1660.427581</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
@@ -11216,9 +11491,7 @@
           <t>貨櫃運輸集散及倉儲</t>
         </is>
       </c>
-      <c r="B270" t="n">
-        <v>523.312587</v>
-      </c>
+      <c r="B270" t="inlineStr"/>
       <c r="C270" t="n">
         <v>365.648259</v>
       </c>
@@ -11249,6 +11522,9 @@
       <c r="L270" t="n">
         <v>247.426291</v>
       </c>
+      <c r="M270" t="n">
+        <v>286.987169</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
@@ -11256,9 +11532,7 @@
           <t>貿易商、代理商、經銷商</t>
         </is>
       </c>
-      <c r="B271" t="n">
-        <v>4831.98867</v>
-      </c>
+      <c r="B271" t="inlineStr"/>
       <c r="C271" t="n">
         <v>2869.052645</v>
       </c>
@@ -11289,6 +11563,9 @@
       <c r="L271" t="n">
         <v>1629.423117</v>
       </c>
+      <c r="M271" t="n">
+        <v>1737.050116</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
@@ -11296,9 +11573,7 @@
           <t>資安審計</t>
         </is>
       </c>
-      <c r="B272" t="n">
-        <v>178.035564</v>
-      </c>
+      <c r="B272" t="inlineStr"/>
       <c r="C272" t="n">
         <v>402.315751</v>
       </c>
@@ -11329,6 +11604,9 @@
       <c r="L272" t="n">
         <v>34.080571</v>
       </c>
+      <c r="M272" t="n">
+        <v>31.111897</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
@@ -11336,9 +11614,7 @@
           <t>資安治理</t>
         </is>
       </c>
-      <c r="B273" t="n">
-        <v>89.89055399999999</v>
-      </c>
+      <c r="B273" t="inlineStr"/>
       <c r="C273" t="n">
         <v>95.029821</v>
       </c>
@@ -11369,6 +11645,9 @@
       <c r="L273" t="n">
         <v>70.536647</v>
       </c>
+      <c r="M273" t="n">
+        <v>73.052801</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
@@ -11376,9 +11655,7 @@
           <t>資安營運管理服務</t>
         </is>
       </c>
-      <c r="B274" t="n">
-        <v>328.3978</v>
-      </c>
+      <c r="B274" t="inlineStr"/>
       <c r="C274" t="n">
         <v>591.498468</v>
       </c>
@@ -11409,6 +11686,9 @@
       <c r="L274" t="n">
         <v>327.059576</v>
       </c>
+      <c r="M274" t="n">
+        <v>347.883186</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
@@ -11416,9 +11696,7 @@
           <t>資安防護能力分析與鑑識服務</t>
         </is>
       </c>
-      <c r="B275" t="n">
-        <v>221.394257</v>
-      </c>
+      <c r="B275" t="inlineStr"/>
       <c r="C275" t="n">
         <v>286.274462</v>
       </c>
@@ -11449,6 +11727,9 @@
       <c r="L275" t="n">
         <v>270.453766</v>
       </c>
+      <c r="M275" t="n">
+        <v>289.209064</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
@@ -11456,9 +11737,7 @@
           <t>資安防護軟體</t>
         </is>
       </c>
-      <c r="B276" t="n">
-        <v>184.612732</v>
-      </c>
+      <c r="B276" t="inlineStr"/>
       <c r="C276" t="n">
         <v>202.61183</v>
       </c>
@@ -11489,6 +11768,9 @@
       <c r="L276" t="n">
         <v>244.784198</v>
       </c>
+      <c r="M276" t="n">
+        <v>221.383902</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
@@ -11496,9 +11778,7 @@
           <t>資安顧問服務</t>
         </is>
       </c>
-      <c r="B277" t="n">
-        <v>412.032959</v>
-      </c>
+      <c r="B277" t="inlineStr"/>
       <c r="C277" t="n">
         <v>704.519821</v>
       </c>
@@ -11529,6 +11809,9 @@
       <c r="L277" t="n">
         <v>324.579306</v>
       </c>
+      <c r="M277" t="n">
+        <v>346.418175</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
@@ -11536,9 +11819,7 @@
           <t>資料分析處理服務</t>
         </is>
       </c>
-      <c r="B278" t="n">
-        <v>193.383103</v>
-      </c>
+      <c r="B278" t="inlineStr"/>
       <c r="C278" t="n">
         <v>370.707265</v>
       </c>
@@ -11569,6 +11850,9 @@
       <c r="L278" t="n">
         <v>127.688235</v>
       </c>
+      <c r="M278" t="n">
+        <v>124.980821</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
@@ -11576,9 +11860,7 @@
           <t>資料安全</t>
         </is>
       </c>
-      <c r="B279" t="n">
-        <v>179.224098</v>
-      </c>
+      <c r="B279" t="inlineStr"/>
       <c r="C279" t="n">
         <v>225.931933</v>
       </c>
@@ -11609,6 +11891,9 @@
       <c r="L279" t="n">
         <v>237.565455</v>
       </c>
+      <c r="M279" t="n">
+        <v>225.76346</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
@@ -11616,9 +11901,7 @@
           <t>資料庫</t>
         </is>
       </c>
-      <c r="B280" t="n">
-        <v>306.814947</v>
-      </c>
+      <c r="B280" t="inlineStr"/>
       <c r="C280" t="n">
         <v>540.178978</v>
       </c>
@@ -11649,6 +11932,9 @@
       <c r="L280" t="n">
         <v>143.510859</v>
       </c>
+      <c r="M280" t="n">
+        <v>142.639839</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
@@ -11656,9 +11942,7 @@
           <t>資料聚合</t>
         </is>
       </c>
-      <c r="B281" t="n">
-        <v>217.074934</v>
-      </c>
+      <c r="B281" t="inlineStr"/>
       <c r="C281" t="n">
         <v>434.52851</v>
       </c>
@@ -11689,6 +11973,9 @@
       <c r="L281" t="n">
         <v>79.079792</v>
       </c>
+      <c r="M281" t="n">
+        <v>69.982122</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
@@ -11696,9 +11983,7 @@
           <t>資料處理</t>
         </is>
       </c>
-      <c r="B282" t="n">
-        <v>866.282484</v>
-      </c>
+      <c r="B282" t="inlineStr"/>
       <c r="C282" t="n">
         <v>527.179293</v>
       </c>
@@ -11729,6 +12014,9 @@
       <c r="L282" t="n">
         <v>1374.94406</v>
       </c>
+      <c r="M282" t="n">
+        <v>1015.303418</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
@@ -11736,9 +12024,7 @@
           <t>資料處理服務</t>
         </is>
       </c>
-      <c r="B283" t="n">
-        <v>4478.119245</v>
-      </c>
+      <c r="B283" t="inlineStr"/>
       <c r="C283" t="n">
         <v>2876.684458</v>
       </c>
@@ -11769,6 +12055,9 @@
       <c r="L283" t="n">
         <v>1126.899345</v>
       </c>
+      <c r="M283" t="n">
+        <v>786.6770780000001</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
@@ -11776,9 +12065,7 @@
           <t>資服</t>
         </is>
       </c>
-      <c r="B284" t="n">
-        <v>9.236895000000001</v>
-      </c>
+      <c r="B284" t="inlineStr"/>
       <c r="C284" t="n">
         <v>4.036222</v>
       </c>
@@ -11809,6 +12096,9 @@
       <c r="L284" t="n">
         <v>7.296245</v>
       </c>
+      <c r="M284" t="n">
+        <v>4.64304</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
@@ -11816,9 +12106,7 @@
           <t>資訊收集設備</t>
         </is>
       </c>
-      <c r="B285" t="n">
-        <v>0.06872399999999999</v>
-      </c>
+      <c r="B285" t="inlineStr"/>
       <c r="C285" t="n">
         <v>0.038395</v>
       </c>
@@ -11849,6 +12137,9 @@
       <c r="L285" t="n">
         <v>0.026925</v>
       </c>
+      <c r="M285" t="n">
+        <v>0.027516</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
@@ -11856,9 +12147,7 @@
           <t>資訊系統建置服務</t>
         </is>
       </c>
-      <c r="B286" t="n">
-        <v>184.481315</v>
-      </c>
+      <c r="B286" t="inlineStr"/>
       <c r="C286" t="n">
         <v>366.843006</v>
       </c>
@@ -11889,6 +12178,9 @@
       <c r="L286" t="n">
         <v>120.479114</v>
       </c>
+      <c r="M286" t="n">
+        <v>120.521983</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
@@ -11896,9 +12188,7 @@
           <t>資訊聚合</t>
         </is>
       </c>
-      <c r="B287" t="n">
-        <v>174.485444</v>
-      </c>
+      <c r="B287" t="inlineStr"/>
       <c r="C287" t="n">
         <v>361.719472</v>
       </c>
@@ -11929,6 +12219,9 @@
       <c r="L287" t="n">
         <v>123.439731</v>
       </c>
+      <c r="M287" t="n">
+        <v>112.059259</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
@@ -11936,9 +12229,7 @@
           <t>身分認證與訪問管理</t>
         </is>
       </c>
-      <c r="B288" t="n">
-        <v>159.275218</v>
-      </c>
+      <c r="B288" t="inlineStr"/>
       <c r="C288" t="n">
         <v>182.063309</v>
       </c>
@@ -11969,6 +12260,9 @@
       <c r="L288" t="n">
         <v>219.62725</v>
       </c>
+      <c r="M288" t="n">
+        <v>193.943444</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
@@ -11976,9 +12270,7 @@
           <t>車燈</t>
         </is>
       </c>
-      <c r="B289" t="n">
-        <v>10226.778234</v>
-      </c>
+      <c r="B289" t="inlineStr"/>
       <c r="C289" t="n">
         <v>15025.395173</v>
       </c>
@@ -12009,6 +12301,9 @@
       <c r="L289" t="n">
         <v>3784.932767</v>
       </c>
+      <c r="M289" t="n">
+        <v>2267.662435</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
@@ -12016,9 +12311,7 @@
           <t>車用機械傳動設備及零配件</t>
         </is>
       </c>
-      <c r="B290" t="n">
-        <v>6022.789109</v>
-      </c>
+      <c r="B290" t="inlineStr"/>
       <c r="C290" t="n">
         <v>4553.345102</v>
       </c>
@@ -12049,6 +12342,9 @@
       <c r="L290" t="n">
         <v>2433.135756</v>
       </c>
+      <c r="M290" t="n">
+        <v>1532.7428525</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
@@ -12056,9 +12352,7 @@
           <t>軟性電路板</t>
         </is>
       </c>
-      <c r="B291" t="n">
-        <v>0.00842</v>
-      </c>
+      <c r="B291" t="inlineStr"/>
       <c r="C291" t="n">
         <v>0.011936</v>
       </c>
@@ -12089,6 +12383,9 @@
       <c r="L291" t="n">
         <v>0.002954</v>
       </c>
+      <c r="M291" t="n">
+        <v>0.003707</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
@@ -12096,9 +12393,7 @@
           <t>軟體開發</t>
         </is>
       </c>
-      <c r="B292" t="n">
-        <v>931.6213279999999</v>
-      </c>
+      <c r="B292" t="inlineStr"/>
       <c r="C292" t="n">
         <v>634.598406</v>
       </c>
@@ -12129,6 +12424,9 @@
       <c r="L292" t="n">
         <v>394.453141</v>
       </c>
+      <c r="M292" t="n">
+        <v>554.426507</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
@@ -12136,9 +12434,7 @@
           <t>軟體開發工具</t>
         </is>
       </c>
-      <c r="B293" t="n">
-        <v>704.373165</v>
-      </c>
+      <c r="B293" t="inlineStr"/>
       <c r="C293" t="n">
         <v>358.616734</v>
       </c>
@@ -12169,6 +12465,9 @@
       <c r="L293" t="n">
         <v>240.333646</v>
       </c>
+      <c r="M293" t="n">
+        <v>273.260521</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
@@ -12176,9 +12475,7 @@
           <t>輪胎</t>
         </is>
       </c>
-      <c r="B294" t="n">
-        <v>109.241103</v>
-      </c>
+      <c r="B294" t="inlineStr"/>
       <c r="C294" t="n">
         <v>100.341793</v>
       </c>
@@ -12209,6 +12506,9 @@
       <c r="L294" t="n">
         <v>78.90974300000001</v>
       </c>
+      <c r="M294" t="n">
+        <v>73.18960199999999</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
@@ -12216,9 +12516,7 @@
           <t>輸出入模組/介面卡</t>
         </is>
       </c>
-      <c r="B295" t="n">
-        <v>2195.984987</v>
-      </c>
+      <c r="B295" t="inlineStr"/>
       <c r="C295" t="n">
         <v>1829.935518</v>
       </c>
@@ -12249,6 +12547,9 @@
       <c r="L295" t="n">
         <v>2658.189541</v>
       </c>
+      <c r="M295" t="n">
+        <v>2687.002389</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
@@ -12256,9 +12557,7 @@
           <t>輸送機械及零配件</t>
         </is>
       </c>
-      <c r="B296" t="n">
-        <v>31067.355852</v>
-      </c>
+      <c r="B296" t="inlineStr"/>
       <c r="C296" t="n">
         <v>27667.895639</v>
       </c>
@@ -12287,7 +12586,10 @@
         <v>12433.953631</v>
       </c>
       <c r="L296" t="n">
-        <v>20657.615918</v>
+        <v>20723.198418</v>
+      </c>
+      <c r="M296" t="n">
+        <v>14938.932824</v>
       </c>
     </row>
     <row r="297">
@@ -12296,9 +12598,7 @@
           <t>農業科技業</t>
         </is>
       </c>
-      <c r="B297" t="n">
-        <v>590.1894610000001</v>
-      </c>
+      <c r="B297" t="inlineStr"/>
       <c r="C297" t="n">
         <v>276.273455</v>
       </c>
@@ -12329,6 +12629,9 @@
       <c r="L297" t="n">
         <v>246.598824</v>
       </c>
+      <c r="M297" t="n">
+        <v>162.918779</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
@@ -12336,9 +12639,7 @@
           <t>農藥</t>
         </is>
       </c>
-      <c r="B298" t="n">
-        <v>19.19514</v>
-      </c>
+      <c r="B298" t="inlineStr"/>
       <c r="C298" t="n">
         <v>29.196636</v>
       </c>
@@ -12369,6 +12670,9 @@
       <c r="L298" t="n">
         <v>33.234468</v>
       </c>
+      <c r="M298" t="n">
+        <v>18.279712</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
@@ -12376,9 +12680,7 @@
           <t>近眼顯示(Dear-Eye Display)</t>
         </is>
       </c>
-      <c r="B299" t="n">
-        <v>32.55829</v>
-      </c>
+      <c r="B299" t="inlineStr"/>
       <c r="C299" t="n">
         <v>16.523098</v>
       </c>
@@ -12409,6 +12711,9 @@
       <c r="L299" t="n">
         <v>8.773569</v>
       </c>
+      <c r="M299" t="n">
+        <v>12.822521</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
@@ -12416,9 +12721,7 @@
           <t>通訊</t>
         </is>
       </c>
-      <c r="B300" t="n">
-        <v>178.035564</v>
-      </c>
+      <c r="B300" t="inlineStr"/>
       <c r="C300" t="n">
         <v>402.315751</v>
       </c>
@@ -12449,6 +12752,9 @@
       <c r="L300" t="n">
         <v>34.080571</v>
       </c>
+      <c r="M300" t="n">
+        <v>31.111897</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
@@ -12456,9 +12762,7 @@
           <t>通訊服務</t>
         </is>
       </c>
-      <c r="B301" t="n">
-        <v>0.000492</v>
-      </c>
+      <c r="B301" t="inlineStr"/>
       <c r="C301" t="n">
         <v>0.000137</v>
       </c>
@@ -12489,6 +12793,9 @@
       <c r="L301" t="n">
         <v>1.9e-05</v>
       </c>
+      <c r="M301" t="n">
+        <v>0.000346</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
@@ -12496,9 +12803,7 @@
           <t>通路經銷</t>
         </is>
       </c>
-      <c r="B302" t="n">
-        <v>4527.831443</v>
-      </c>
+      <c r="B302" t="inlineStr"/>
       <c r="C302" t="n">
         <v>2954.322108</v>
       </c>
@@ -12529,6 +12834,9 @@
       <c r="L302" t="n">
         <v>1259.481803</v>
       </c>
+      <c r="M302" t="n">
+        <v>896.538811</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
@@ -12536,9 +12844,7 @@
           <t>連接器設計、組裝及製造</t>
         </is>
       </c>
-      <c r="B303" t="n">
-        <v>22802.57249</v>
-      </c>
+      <c r="B303" t="inlineStr"/>
       <c r="C303" t="n">
         <v>16852.375312</v>
       </c>
@@ -12569,6 +12875,9 @@
       <c r="L303" t="n">
         <v>19982.564281</v>
       </c>
+      <c r="M303" t="n">
+        <v>23031.218557</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
@@ -12576,9 +12885,7 @@
           <t>連接線</t>
         </is>
       </c>
-      <c r="B304" t="n">
-        <v>9048.899291</v>
-      </c>
+      <c r="B304" t="inlineStr"/>
       <c r="C304" t="n">
         <v>7526.45167</v>
       </c>
@@ -12609,6 +12916,9 @@
       <c r="L304" t="n">
         <v>6064.428867</v>
       </c>
+      <c r="M304" t="n">
+        <v>8163.568637</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
@@ -12616,9 +12926,7 @@
           <t>運動服務/顧問</t>
         </is>
       </c>
-      <c r="B305" t="n">
-        <v>0.000492</v>
-      </c>
+      <c r="B305" t="inlineStr"/>
       <c r="C305" t="n">
         <v>0.000137</v>
       </c>
@@ -12649,6 +12957,9 @@
       <c r="L305" t="n">
         <v>1.9e-05</v>
       </c>
+      <c r="M305" t="n">
+        <v>0.000346</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
@@ -12656,9 +12967,7 @@
           <t>運動用品</t>
         </is>
       </c>
-      <c r="B306" t="n">
-        <v>20.548104</v>
-      </c>
+      <c r="B306" t="inlineStr"/>
       <c r="C306" t="n">
         <v>12.206492</v>
       </c>
@@ -12689,6 +12998,9 @@
       <c r="L306" t="n">
         <v>13.736649</v>
       </c>
+      <c r="M306" t="n">
+        <v>7.592965</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
@@ -12696,9 +13008,7 @@
           <t>運動行銷/媒體</t>
         </is>
       </c>
-      <c r="B307" t="n">
-        <v>0.000492</v>
-      </c>
+      <c r="B307" t="inlineStr"/>
       <c r="C307" t="n">
         <v>0.000137</v>
       </c>
@@ -12729,6 +13039,9 @@
       <c r="L307" t="n">
         <v>1.9e-05</v>
       </c>
+      <c r="M307" t="n">
+        <v>0.000346</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
@@ -12736,9 +13049,7 @@
           <t>運算元件與設備</t>
         </is>
       </c>
-      <c r="B308" t="n">
-        <v>27229.137925</v>
-      </c>
+      <c r="B308" t="inlineStr"/>
       <c r="C308" t="n">
         <v>24208.645495</v>
       </c>
@@ -12767,7 +13078,10 @@
         <v>9382.276178</v>
       </c>
       <c r="L308" t="n">
-        <v>18729.466364</v>
+        <v>18795.048864</v>
+      </c>
+      <c r="M308" t="n">
+        <v>12733.523532</v>
       </c>
     </row>
     <row r="309">
@@ -12776,9 +13090,7 @@
           <t>運算設備</t>
         </is>
       </c>
-      <c r="B309" t="n">
-        <v>37050.338374</v>
-      </c>
+      <c r="B309" t="inlineStr"/>
       <c r="C309" t="n">
         <v>30913.882906</v>
       </c>
@@ -12807,7 +13119,10 @@
         <v>15266.005757</v>
       </c>
       <c r="L309" t="n">
-        <v>25024.537417</v>
+        <v>25090.119917</v>
+      </c>
+      <c r="M309" t="n">
+        <v>19212.719993</v>
       </c>
     </row>
     <row r="310">
@@ -12816,9 +13131,7 @@
           <t>運輸工具</t>
         </is>
       </c>
-      <c r="B310" t="n">
-        <v>119.335911</v>
-      </c>
+      <c r="B310" t="inlineStr"/>
       <c r="C310" t="n">
         <v>70.15943</v>
       </c>
@@ -12849,6 +13162,9 @@
       <c r="L310" t="n">
         <v>31.801809</v>
       </c>
+      <c r="M310" t="n">
+        <v>38.460909</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
@@ -12856,9 +13172,7 @@
           <t>配電管理設施</t>
         </is>
       </c>
-      <c r="B311" t="n">
-        <v>67180.41347100001</v>
-      </c>
+      <c r="B311" t="inlineStr"/>
       <c r="C311" t="n">
         <v>54662.311542</v>
       </c>
@@ -12887,7 +13201,10 @@
         <v>23942.798102</v>
       </c>
       <c r="L311" t="n">
-        <v>31494.708797</v>
+        <v>31665.405297</v>
+      </c>
+      <c r="M311" t="n">
+        <v>23589.141858</v>
       </c>
     </row>
     <row r="312">
@@ -12896,9 +13213,7 @@
           <t>配電系統</t>
         </is>
       </c>
-      <c r="B312" t="n">
-        <v>19097.458954</v>
-      </c>
+      <c r="B312" t="inlineStr"/>
       <c r="C312" t="n">
         <v>9403.047243000001</v>
       </c>
@@ -12929,6 +13244,9 @@
       <c r="L312" t="n">
         <v>4409.741722</v>
       </c>
+      <c r="M312" t="n">
+        <v>4993.211193</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
@@ -12936,9 +13254,7 @@
           <t>酚醛樹脂</t>
         </is>
       </c>
-      <c r="B313" t="n">
-        <v>19630.784028</v>
-      </c>
+      <c r="B313" t="inlineStr"/>
       <c r="C313" t="n">
         <v>12283.070701</v>
       </c>
@@ -12969,6 +13285,9 @@
       <c r="L313" t="n">
         <v>5426.936874</v>
       </c>
+      <c r="M313" t="n">
+        <v>11887.19927</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
@@ -12976,9 +13295,7 @@
           <t>醫療器材代理銷售及通路</t>
         </is>
       </c>
-      <c r="B314" t="n">
-        <v>30589.123791</v>
-      </c>
+      <c r="B314" t="inlineStr"/>
       <c r="C314" t="n">
         <v>27112.530644</v>
       </c>
@@ -13007,7 +13324,10 @@
         <v>10024.696714</v>
       </c>
       <c r="L314" t="n">
-        <v>19666.017839</v>
+        <v>19731.600339</v>
+      </c>
+      <c r="M314" t="n">
+        <v>13401.765635</v>
       </c>
     </row>
     <row r="315">
@@ -13016,9 +13336,7 @@
           <t>醫療器材研發、設計、製造</t>
         </is>
       </c>
-      <c r="B315" t="n">
-        <v>36326.249234</v>
-      </c>
+      <c r="B315" t="inlineStr"/>
       <c r="C315" t="n">
         <v>39768.107179</v>
       </c>
@@ -13047,7 +13365,10 @@
         <v>15920.723279</v>
       </c>
       <c r="L315" t="n">
-        <v>23067.254306</v>
+        <v>23132.836806</v>
+      </c>
+      <c r="M315" t="n">
+        <v>15685.205361</v>
       </c>
     </row>
     <row r="316">
@@ -13056,9 +13377,7 @@
           <t>醫療院所</t>
         </is>
       </c>
-      <c r="B316" t="n">
-        <v>51.473311</v>
-      </c>
+      <c r="B316" t="inlineStr"/>
       <c r="C316" t="n">
         <v>34.043181</v>
       </c>
@@ -13089,6 +13408,9 @@
       <c r="L316" t="n">
         <v>20.957309</v>
       </c>
+      <c r="M316" t="n">
+        <v>24.394795</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
@@ -13096,9 +13418,7 @@
           <t>金屬、塑膠模具</t>
         </is>
       </c>
-      <c r="B317" t="n">
-        <v>11620.08781</v>
-      </c>
+      <c r="B317" t="inlineStr"/>
       <c r="C317" t="n">
         <v>8422.314383999999</v>
       </c>
@@ -13129,6 +13449,9 @@
       <c r="L317" t="n">
         <v>9780.323308999999</v>
       </c>
+      <c r="M317" t="n">
+        <v>12543.716988</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
@@ -13136,9 +13459,7 @@
           <t>金屬加工用機械</t>
         </is>
       </c>
-      <c r="B318" t="n">
-        <v>11894.07078</v>
-      </c>
+      <c r="B318" t="inlineStr"/>
       <c r="C318" t="n">
         <v>5805.05507</v>
       </c>
@@ -13158,16 +13479,19 @@
         <v>5096.683787</v>
       </c>
       <c r="I318" t="n">
-        <v>4049.584412</v>
+        <v>4039.038919</v>
       </c>
       <c r="J318" t="n">
-        <v>4641.998509</v>
+        <v>4633.404659</v>
       </c>
       <c r="K318" t="n">
-        <v>3425.572123</v>
+        <v>3418.910764</v>
       </c>
       <c r="L318" t="n">
-        <v>4271.204485</v>
+        <v>4402.86713</v>
+      </c>
+      <c r="M318" t="n">
+        <v>2986.233672</v>
       </c>
     </row>
     <row r="319">
@@ -13176,9 +13500,7 @@
           <t>金屬加工處理</t>
         </is>
       </c>
-      <c r="B319" t="n">
-        <v>10626.514665</v>
-      </c>
+      <c r="B319" t="inlineStr"/>
       <c r="C319" t="n">
         <v>5046.921702</v>
       </c>
@@ -13209,6 +13531,9 @@
       <c r="L319" t="n">
         <v>2167.270313</v>
       </c>
+      <c r="M319" t="n">
+        <v>1671.126339</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
@@ -13216,9 +13541,7 @@
           <t>金屬材料</t>
         </is>
       </c>
-      <c r="B320" t="n">
-        <v>205.762817</v>
-      </c>
+      <c r="B320" t="inlineStr"/>
       <c r="C320" t="n">
         <v>104.178395</v>
       </c>
@@ -13249,6 +13572,9 @@
       <c r="L320" t="n">
         <v>78.61353800000001</v>
       </c>
+      <c r="M320" t="n">
+        <v>106.277025</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
@@ -13256,9 +13582,7 @@
           <t>金屬製品</t>
         </is>
       </c>
-      <c r="B321" t="n">
-        <v>850.782773</v>
-      </c>
+      <c r="B321" t="inlineStr"/>
       <c r="C321" t="n">
         <v>584.909947</v>
       </c>
@@ -13289,6 +13613,9 @@
       <c r="L321" t="n">
         <v>336.198275</v>
       </c>
+      <c r="M321" t="n">
+        <v>353.28653</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
@@ -13296,9 +13623,7 @@
           <t>金控業/銀行業/保險業</t>
         </is>
       </c>
-      <c r="B322" t="n">
-        <v>13301.74364</v>
-      </c>
+      <c r="B322" t="inlineStr"/>
       <c r="C322" t="n">
         <v>11686.54065</v>
       </c>
@@ -13318,16 +13643,19 @@
         <v>18640.328592</v>
       </c>
       <c r="I322" t="n">
-        <v>13590.032372</v>
+        <v>13992.859045</v>
       </c>
       <c r="J322" t="n">
-        <v>9935.430698</v>
+        <v>10206.63941</v>
       </c>
       <c r="K322" t="n">
-        <v>11204.860003</v>
+        <v>11530.236187</v>
       </c>
       <c r="L322" t="n">
-        <v>10855.816268</v>
+        <v>11150.595076</v>
+      </c>
+      <c r="M322" t="n">
+        <v>10413.088541</v>
       </c>
     </row>
     <row r="323">
@@ -13336,9 +13664,7 @@
           <t>金流串接處理服務</t>
         </is>
       </c>
-      <c r="B323" t="n">
-        <v>108.502457</v>
-      </c>
+      <c r="B323" t="inlineStr"/>
       <c r="C323" t="n">
         <v>269.045136</v>
       </c>
@@ -13369,6 +13695,9 @@
       <c r="L323" t="n">
         <v>174.487066</v>
       </c>
+      <c r="M323" t="n">
+        <v>116.318017</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
@@ -13376,9 +13705,7 @@
           <t>金融提款機(ATM)</t>
         </is>
       </c>
-      <c r="B324" t="n">
-        <v>16.832351</v>
-      </c>
+      <c r="B324" t="inlineStr"/>
       <c r="C324" t="n">
         <v>18.047698</v>
       </c>
@@ -13409,6 +13736,9 @@
       <c r="L324" t="n">
         <v>11.755694</v>
       </c>
+      <c r="M324" t="n">
+        <v>28.035732</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
@@ -13416,9 +13746,7 @@
           <t>鈑金</t>
         </is>
       </c>
-      <c r="B325" t="n">
-        <v>565.456734</v>
-      </c>
+      <c r="B325" t="inlineStr"/>
       <c r="C325" t="n">
         <v>549.556478</v>
       </c>
@@ -13449,6 +13777,9 @@
       <c r="L325" t="n">
         <v>333.466802</v>
       </c>
+      <c r="M325" t="n">
+        <v>310.679202</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
@@ -13456,9 +13787,7 @@
           <t>銅箔</t>
         </is>
       </c>
-      <c r="B326" t="n">
-        <v>15265.300082</v>
-      </c>
+      <c r="B326" t="inlineStr"/>
       <c r="C326" t="n">
         <v>10227.272015</v>
       </c>
@@ -13489,6 +13818,9 @@
       <c r="L326" t="n">
         <v>4794.982622</v>
       </c>
+      <c r="M326" t="n">
+        <v>10932.075741</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
@@ -13496,9 +13828,7 @@
           <t>銅箔基板</t>
         </is>
       </c>
-      <c r="B327" t="n">
-        <v>32378.7031</v>
-      </c>
+      <c r="B327" t="inlineStr"/>
       <c r="C327" t="n">
         <v>31877.104689</v>
       </c>
@@ -13529,6 +13859,9 @@
       <c r="L327" t="n">
         <v>22654.268909</v>
       </c>
+      <c r="M327" t="n">
+        <v>26953.515944</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
@@ -13536,9 +13869,7 @@
           <t>銷售、進出口業務</t>
         </is>
       </c>
-      <c r="B328" t="n">
-        <v>10207.992687</v>
-      </c>
+      <c r="B328" t="inlineStr"/>
       <c r="C328" t="n">
         <v>15088.648802</v>
       </c>
@@ -13569,6 +13900,9 @@
       <c r="L328" t="n">
         <v>3819.583547</v>
       </c>
+      <c r="M328" t="n">
+        <v>2323.737886</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
@@ -13576,9 +13910,7 @@
           <t>鋁合金鋼圈</t>
         </is>
       </c>
-      <c r="B329" t="n">
-        <v>53.975645</v>
-      </c>
+      <c r="B329" t="inlineStr"/>
       <c r="C329" t="n">
         <v>49.724223</v>
       </c>
@@ -13609,6 +13941,9 @@
       <c r="L329" t="n">
         <v>23.074347</v>
       </c>
+      <c r="M329" t="n">
+        <v>27.572917</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
@@ -13616,9 +13951,7 @@
           <t>鋰電池材料</t>
         </is>
       </c>
-      <c r="B330" t="n">
-        <v>35783.86282</v>
-      </c>
+      <c r="B330" t="inlineStr"/>
       <c r="C330" t="n">
         <v>29144.496275</v>
       </c>
@@ -13647,7 +13980,10 @@
         <v>13431.921022</v>
       </c>
       <c r="L330" t="n">
-        <v>22510.879449</v>
+        <v>22576.461949</v>
+      </c>
+      <c r="M330" t="n">
+        <v>17521.09945</v>
       </c>
     </row>
     <row r="331">
@@ -13656,9 +13992,7 @@
           <t>鋼材</t>
         </is>
       </c>
-      <c r="B331" t="n">
-        <v>31.684088</v>
-      </c>
+      <c r="B331" t="inlineStr"/>
       <c r="C331" t="n">
         <v>35.99803</v>
       </c>
@@ -13689,6 +14023,9 @@
       <c r="L331" t="n">
         <v>28.249835</v>
       </c>
+      <c r="M331" t="n">
+        <v>33.822041</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
@@ -13696,9 +14033,7 @@
           <t>鋼筋</t>
         </is>
       </c>
-      <c r="B332" t="n">
-        <v>174.605767</v>
-      </c>
+      <c r="B332" t="inlineStr"/>
       <c r="C332" t="n">
         <v>204.5362015</v>
       </c>
@@ -13729,6 +14064,9 @@
       <c r="L332" t="n">
         <v>122.521219</v>
       </c>
+      <c r="M332" t="n">
+        <v>148.1541893333333</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
@@ -13736,9 +14074,7 @@
           <t>鋼線鋼纜</t>
         </is>
       </c>
-      <c r="B333" t="n">
-        <v>4846.765341</v>
-      </c>
+      <c r="B333" t="inlineStr"/>
       <c r="C333" t="n">
         <v>2612.634242</v>
       </c>
@@ -13769,6 +14105,9 @@
       <c r="L333" t="n">
         <v>2082.659385</v>
       </c>
+      <c r="M333" t="n">
+        <v>3698.141614</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
@@ -13776,9 +14115,7 @@
           <t>鋼胚</t>
         </is>
       </c>
-      <c r="B334" t="n">
-        <v>672.711022</v>
-      </c>
+      <c r="B334" t="inlineStr"/>
       <c r="C334" t="n">
         <v>789.823311</v>
       </c>
@@ -13809,6 +14146,9 @@
       <c r="L334" t="n">
         <v>1063.425379</v>
       </c>
+      <c r="M334" t="n">
+        <v>1183.541453</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
@@ -13816,9 +14156,7 @@
           <t>鋼鑄鐵元件</t>
         </is>
       </c>
-      <c r="B335" t="n">
-        <v>4210.11662</v>
-      </c>
+      <c r="B335" t="inlineStr"/>
       <c r="C335" t="n">
         <v>2356.965521</v>
       </c>
@@ -13849,6 +14187,9 @@
       <c r="L335" t="n">
         <v>886.67132</v>
       </c>
+      <c r="M335" t="n">
+        <v>629.842391</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
@@ -13856,9 +14197,7 @@
           <t>錢包/資產管理</t>
         </is>
       </c>
-      <c r="B336" t="n">
-        <v>178.035564</v>
-      </c>
+      <c r="B336" t="inlineStr"/>
       <c r="C336" t="n">
         <v>402.315751</v>
       </c>
@@ -13889,6 +14228,9 @@
       <c r="L336" t="n">
         <v>34.080571</v>
       </c>
+      <c r="M336" t="n">
+        <v>31.111897</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
@@ -13896,9 +14238,7 @@
           <t>開發工具</t>
         </is>
       </c>
-      <c r="B337" t="n">
-        <v>882.408729</v>
-      </c>
+      <c r="B337" t="inlineStr"/>
       <c r="C337" t="n">
         <v>760.932485</v>
       </c>
@@ -13929,6 +14269,9 @@
       <c r="L337" t="n">
         <v>274.414217</v>
       </c>
+      <c r="M337" t="n">
+        <v>304.372418</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
@@ -13936,9 +14279,7 @@
           <t>隨身碟、記憶卡讀卡機</t>
         </is>
       </c>
-      <c r="B338" t="n">
-        <v>6453.245912</v>
-      </c>
+      <c r="B338" t="inlineStr"/>
       <c r="C338" t="n">
         <v>7535.703554</v>
       </c>
@@ -13969,6 +14310,9 @@
       <c r="L338" t="n">
         <v>6573.58327</v>
       </c>
+      <c r="M338" t="n">
+        <v>9644.699369</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
@@ -13976,9 +14320,7 @@
           <t>雲端作業系統</t>
         </is>
       </c>
-      <c r="B339" t="n">
-        <v>161.779081</v>
-      </c>
+      <c r="B339" t="inlineStr"/>
       <c r="C339" t="n">
         <v>183.121488</v>
       </c>
@@ -14009,6 +14351,9 @@
       <c r="L339" t="n">
         <v>236.56605</v>
       </c>
+      <c r="M339" t="n">
+        <v>210.86413</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
@@ -14016,9 +14361,7 @@
           <t>雲端安全</t>
         </is>
       </c>
-      <c r="B340" t="n">
-        <v>172.507441</v>
-      </c>
+      <c r="B340" t="inlineStr"/>
       <c r="C340" t="n">
         <v>198.614514</v>
       </c>
@@ -14049,6 +14392,9 @@
       <c r="L340" t="n">
         <v>239.818986</v>
       </c>
+      <c r="M340" t="n">
+        <v>220.181728</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
@@ -14056,9 +14402,7 @@
           <t>雲端平台</t>
         </is>
       </c>
-      <c r="B341" t="n">
-        <v>3563.213365</v>
-      </c>
+      <c r="B341" t="inlineStr"/>
       <c r="C341" t="n">
         <v>2359.112288</v>
       </c>
@@ -14089,6 +14433,9 @@
       <c r="L341" t="n">
         <v>2607.77847</v>
       </c>
+      <c r="M341" t="n">
+        <v>2278.358275</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
@@ -14096,9 +14443,7 @@
           <t>雲端應用服務</t>
         </is>
       </c>
-      <c r="B342" t="n">
-        <v>37444.005031</v>
-      </c>
+      <c r="B342" t="inlineStr"/>
       <c r="C342" t="n">
         <v>39246.110796</v>
       </c>
@@ -14127,7 +14472,10 @@
         <v>16002.313999</v>
       </c>
       <c r="L342" t="n">
-        <v>22997.490859</v>
+        <v>23063.073359</v>
+      </c>
+      <c r="M342" t="n">
+        <v>15778.828471</v>
       </c>
     </row>
     <row r="343">
@@ -14136,9 +14484,7 @@
           <t>零售通路</t>
         </is>
       </c>
-      <c r="B343" t="n">
-        <v>6058.024644</v>
-      </c>
+      <c r="B343" t="inlineStr"/>
       <c r="C343" t="n">
         <v>3633.159816666666</v>
       </c>
@@ -14169,6 +14515,9 @@
       <c r="L343" t="n">
         <v>1749.86176</v>
       </c>
+      <c r="M343" t="n">
+        <v>1804.87718025</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
@@ -14176,9 +14525,7 @@
           <t>零組件/材料</t>
         </is>
       </c>
-      <c r="B344" t="n">
-        <v>30250.982061</v>
-      </c>
+      <c r="B344" t="inlineStr"/>
       <c r="C344" t="n">
         <v>37999.529797</v>
       </c>
@@ -14207,7 +14554,10 @@
         <v>19749.065531</v>
       </c>
       <c r="L344" t="n">
-        <v>26472.683575</v>
+        <v>26538.266075</v>
+      </c>
+      <c r="M344" t="n">
+        <v>21010.484991</v>
       </c>
     </row>
     <row r="345">
@@ -14216,9 +14566,7 @@
           <t>電信服務業</t>
         </is>
       </c>
-      <c r="B345" t="n">
-        <v>1704.698712</v>
-      </c>
+      <c r="B345" t="inlineStr"/>
       <c r="C345" t="n">
         <v>1674.604263</v>
       </c>
@@ -14249,6 +14597,9 @@
       <c r="L345" t="n">
         <v>2946.536482</v>
       </c>
+      <c r="M345" t="n">
+        <v>2881.633155</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="inlineStr">
@@ -14256,9 +14607,7 @@
           <t>電力系統</t>
         </is>
       </c>
-      <c r="B346" t="n">
-        <v>55118.616123</v>
-      </c>
+      <c r="B346" t="inlineStr"/>
       <c r="C346" t="n">
         <v>42548.716764</v>
       </c>
@@ -14287,7 +14636,10 @@
         <v>14553.143472</v>
       </c>
       <c r="L346" t="n">
-        <v>24170.276967</v>
+        <v>24235.859467</v>
+      </c>
+      <c r="M346" t="n">
+        <v>19136.292869</v>
       </c>
     </row>
     <row r="347">
@@ -14296,9 +14648,7 @@
           <t>電力設備</t>
         </is>
       </c>
-      <c r="B347" t="n">
-        <v>35039.970782</v>
-      </c>
+      <c r="B347" t="inlineStr"/>
       <c r="C347" t="n">
         <v>37643.290497</v>
       </c>
@@ -14327,7 +14677,10 @@
         <v>14703.238202</v>
       </c>
       <c r="L347" t="n">
-        <v>21741.781976</v>
+        <v>21807.364476</v>
+      </c>
+      <c r="M347" t="n">
+        <v>14290.877121</v>
       </c>
     </row>
     <row r="348">
@@ -14336,9 +14689,7 @@
           <t>電力零售業</t>
         </is>
       </c>
-      <c r="B348" t="n">
-        <v>866.743755</v>
-      </c>
+      <c r="B348" t="inlineStr"/>
       <c r="C348" t="n">
         <v>1796.40537</v>
       </c>
@@ -14369,6 +14720,9 @@
       <c r="L348" t="n">
         <v>470.221624</v>
       </c>
+      <c r="M348" t="n">
+        <v>546.779486</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="inlineStr">
@@ -14376,9 +14730,7 @@
           <t>電動汽車、電動機車、電動自行車</t>
         </is>
       </c>
-      <c r="B349" t="n">
-        <v>27229.128754</v>
-      </c>
+      <c r="B349" t="inlineStr"/>
       <c r="C349" t="n">
         <v>24168.786688</v>
       </c>
@@ -14407,7 +14759,10 @@
         <v>9426.667164</v>
       </c>
       <c r="L349" t="n">
-        <v>19219.663374</v>
+        <v>19285.245874</v>
+      </c>
+      <c r="M349" t="n">
+        <v>13071.53185</v>
       </c>
     </row>
     <row r="350">
@@ -14416,9 +14771,7 @@
           <t>電子書</t>
         </is>
       </c>
-      <c r="B350" t="n">
-        <v>1.703098</v>
-      </c>
+      <c r="B350" t="inlineStr"/>
       <c r="C350" t="n">
         <v>1.573242</v>
       </c>
@@ -14449,6 +14802,9 @@
       <c r="L350" t="n">
         <v>0.71021</v>
       </c>
+      <c r="M350" t="n">
+        <v>0.7498050000000001</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="inlineStr">
@@ -14456,9 +14812,7 @@
           <t>電子觸控白板</t>
         </is>
       </c>
-      <c r="B351" t="n">
-        <v>0.082022</v>
-      </c>
+      <c r="B351" t="inlineStr"/>
       <c r="C351" t="n">
         <v>0.063573</v>
       </c>
@@ -14489,6 +14843,9 @@
       <c r="L351" t="n">
         <v>0.448676</v>
       </c>
+      <c r="M351" t="n">
+        <v>0.7771169999999999</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
@@ -14496,9 +14853,7 @@
           <t>電子零組件、塑膠零件、五金零件</t>
         </is>
       </c>
-      <c r="B352" t="n">
-        <v>32903.438528</v>
-      </c>
+      <c r="B352" t="inlineStr"/>
       <c r="C352" t="n">
         <v>29148.500585</v>
       </c>
@@ -14527,7 +14882,10 @@
         <v>14210.488625</v>
       </c>
       <c r="L352" t="n">
-        <v>23692.97114</v>
+        <v>23758.55364</v>
+      </c>
+      <c r="M352" t="n">
+        <v>19085.273014</v>
       </c>
     </row>
     <row r="353">
@@ -14536,9 +14894,7 @@
           <t>電容器</t>
         </is>
       </c>
-      <c r="B353" t="n">
-        <v>55285.312391</v>
-      </c>
+      <c r="B353" t="inlineStr"/>
       <c r="C353" t="n">
         <v>46402.96073</v>
       </c>
@@ -14567,7 +14923,10 @@
         <v>15127.626254</v>
       </c>
       <c r="L353" t="n">
-        <v>24943.416692</v>
+        <v>25078.401192</v>
+      </c>
+      <c r="M353" t="n">
+        <v>21281.221541</v>
       </c>
     </row>
     <row r="354">
@@ -14576,9 +14935,7 @@
           <t>電容器材料(如電蝕／化成鋁箔、介面瓷粉)</t>
         </is>
       </c>
-      <c r="B354" t="n">
-        <v>2429.28572</v>
-      </c>
+      <c r="B354" t="inlineStr"/>
       <c r="C354" t="n">
         <v>8243.115608</v>
       </c>
@@ -14609,6 +14966,9 @@
       <c r="L354" t="n">
         <v>670.451061</v>
       </c>
+      <c r="M354" t="n">
+        <v>644.890149</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
@@ -14616,9 +14976,7 @@
           <t>電感器</t>
         </is>
       </c>
-      <c r="B355" t="n">
-        <v>51127.756076</v>
-      </c>
+      <c r="B355" t="inlineStr"/>
       <c r="C355" t="n">
         <v>44869.90082</v>
       </c>
@@ -14647,7 +15005,10 @@
         <v>13713.227107</v>
       </c>
       <c r="L355" t="n">
-        <v>24125.052366</v>
+        <v>24260.036866</v>
+      </c>
+      <c r="M355" t="n">
+        <v>20625.135484</v>
       </c>
     </row>
     <row r="356">
@@ -14656,9 +15017,7 @@
           <t>電感器材料(如鐵氧體、導電漿墨)</t>
         </is>
       </c>
-      <c r="B356" t="n">
-        <v>526.2676300000001</v>
-      </c>
+      <c r="B356" t="inlineStr"/>
       <c r="C356" t="n">
         <v>767.771988</v>
       </c>
@@ -14689,6 +15048,9 @@
       <c r="L356" t="n">
         <v>101.981909</v>
       </c>
+      <c r="M356" t="n">
+        <v>67.070089</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="inlineStr">
@@ -14696,9 +15058,7 @@
           <t>電控元件</t>
         </is>
       </c>
-      <c r="B357" t="n">
-        <v>45900.819946</v>
-      </c>
+      <c r="B357" t="inlineStr"/>
       <c r="C357" t="n">
         <v>40207.142933</v>
       </c>
@@ -14727,7 +15087,10 @@
         <v>16411.964255</v>
       </c>
       <c r="L357" t="n">
-        <v>24056.461319</v>
+        <v>24122.043819</v>
+      </c>
+      <c r="M357" t="n">
+        <v>25132.22849</v>
       </c>
     </row>
     <row r="358">
@@ -14736,9 +15099,7 @@
           <t>電池</t>
         </is>
       </c>
-      <c r="B358" t="n">
-        <v>793.05706</v>
-      </c>
+      <c r="B358" t="inlineStr"/>
       <c r="C358" t="n">
         <v>368.626646</v>
       </c>
@@ -14769,6 +15130,9 @@
       <c r="L358" t="n">
         <v>83.392167</v>
       </c>
+      <c r="M358" t="n">
+        <v>115.380693</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
@@ -14776,9 +15140,7 @@
           <t>電池模組</t>
         </is>
       </c>
-      <c r="B359" t="n">
-        <v>29439.274411</v>
-      </c>
+      <c r="B359" t="inlineStr"/>
       <c r="C359" t="n">
         <v>25562.864408</v>
       </c>
@@ -14807,7 +15169,10 @@
         <v>11267.939348</v>
       </c>
       <c r="L359" t="n">
-        <v>21536.25228</v>
+        <v>21706.94878</v>
+      </c>
+      <c r="M359" t="n">
+        <v>15090.967393</v>
       </c>
     </row>
     <row r="360">
@@ -14816,9 +15181,7 @@
           <t>電池芯</t>
         </is>
       </c>
-      <c r="B360" t="n">
-        <v>28475.88402</v>
-      </c>
+      <c r="B360" t="inlineStr"/>
       <c r="C360" t="n">
         <v>25190.748862</v>
       </c>
@@ -14847,7 +15210,10 @@
         <v>11121.72772</v>
       </c>
       <c r="L360" t="n">
-        <v>21447.066086</v>
+        <v>21617.762586</v>
+      </c>
+      <c r="M360" t="n">
+        <v>14896.776534</v>
       </c>
     </row>
     <row r="361">
@@ -14856,9 +15222,7 @@
           <t>電源供應器</t>
         </is>
       </c>
-      <c r="B361" t="n">
-        <v>53741.631748</v>
-      </c>
+      <c r="B361" t="inlineStr"/>
       <c r="C361" t="n">
         <v>48730.919347</v>
       </c>
@@ -14887,7 +15251,10 @@
         <v>22551.993665</v>
       </c>
       <c r="L361" t="n">
-        <v>29787.417563</v>
+        <v>29958.114063</v>
+      </c>
+      <c r="M361" t="n">
+        <v>20710.190089</v>
       </c>
     </row>
     <row r="362">
@@ -14896,9 +15263,7 @@
           <t>電網營造</t>
         </is>
       </c>
-      <c r="B362" t="n">
-        <v>9291.034517</v>
-      </c>
+      <c r="B362" t="inlineStr"/>
       <c r="C362" t="n">
         <v>5711.860002</v>
       </c>
@@ -14929,6 +15294,9 @@
       <c r="L362" t="n">
         <v>4085.522918</v>
       </c>
+      <c r="M362" t="n">
+        <v>4711.690946</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
@@ -14936,9 +15304,7 @@
           <t>電網維運</t>
         </is>
       </c>
-      <c r="B363" t="n">
-        <v>374.328987</v>
-      </c>
+      <c r="B363" t="inlineStr"/>
       <c r="C363" t="n">
         <v>466.783872</v>
       </c>
@@ -14969,6 +15335,9 @@
       <c r="L363" t="n">
         <v>153.203909</v>
       </c>
+      <c r="M363" t="n">
+        <v>263.64173</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
@@ -14976,9 +15345,7 @@
           <t>電纜</t>
         </is>
       </c>
-      <c r="B364" t="n">
-        <v>11199.587949</v>
-      </c>
+      <c r="B364" t="inlineStr"/>
       <c r="C364" t="n">
         <v>10801.256709</v>
       </c>
@@ -15009,6 +15376,9 @@
       <c r="L364" t="n">
         <v>2940.310013</v>
       </c>
+      <c r="M364" t="n">
+        <v>4432.513482</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
@@ -15016,9 +15386,7 @@
           <t>電腦視覺</t>
         </is>
       </c>
-      <c r="B365" t="n">
-        <v>26346.468539</v>
-      </c>
+      <c r="B365" t="inlineStr"/>
       <c r="C365" t="n">
         <v>24271.025588</v>
       </c>
@@ -15047,7 +15415,10 @@
         <v>10253.729624</v>
       </c>
       <c r="L365" t="n">
-        <v>19650.588206</v>
+        <v>19716.170706</v>
+      </c>
+      <c r="M365" t="n">
+        <v>13388.068897</v>
       </c>
     </row>
     <row r="366">
@@ -15056,9 +15427,7 @@
           <t>電腦設備</t>
         </is>
       </c>
-      <c r="B366" t="n">
-        <v>44184.051927</v>
-      </c>
+      <c r="B366" t="inlineStr"/>
       <c r="C366" t="n">
         <v>37452.652327</v>
       </c>
@@ -15087,7 +15456,10 @@
         <v>21532.911029</v>
       </c>
       <c r="L366" t="n">
-        <v>35693.317649</v>
+        <v>35758.900149</v>
+      </c>
+      <c r="M366" t="n">
+        <v>27144.500141</v>
       </c>
     </row>
     <row r="367">
@@ -15096,9 +15468,7 @@
           <t>電視</t>
         </is>
       </c>
-      <c r="B367" t="n">
-        <v>7552.934685</v>
-      </c>
+      <c r="B367" t="inlineStr"/>
       <c r="C367" t="n">
         <v>9153.631277</v>
       </c>
@@ -15129,6 +15499,9 @@
       <c r="L367" t="n">
         <v>2190.359267</v>
       </c>
+      <c r="M367" t="n">
+        <v>1754.857976</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
@@ -15136,9 +15509,7 @@
           <t>電鍍材料</t>
         </is>
       </c>
-      <c r="B368" t="n">
-        <v>147.580047</v>
-      </c>
+      <c r="B368" t="inlineStr"/>
       <c r="C368" t="n">
         <v>89.315619</v>
       </c>
@@ -15169,6 +15540,9 @@
       <c r="L368" t="n">
         <v>76.903279</v>
       </c>
+      <c r="M368" t="n">
+        <v>104.630543</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="inlineStr">
@@ -15176,9 +15550,7 @@
           <t>電阻器</t>
         </is>
       </c>
-      <c r="B369" t="n">
-        <v>55202.34744</v>
-      </c>
+      <c r="B369" t="inlineStr"/>
       <c r="C369" t="n">
         <v>46642.867974</v>
       </c>
@@ -15207,7 +15579,10 @@
         <v>14122.328395</v>
       </c>
       <c r="L369" t="n">
-        <v>24814.440474</v>
+        <v>24949.424974</v>
+      </c>
+      <c r="M369" t="n">
+        <v>21063.823428</v>
       </c>
     </row>
     <row r="370">
@@ -15216,9 +15591,7 @@
           <t>電阻器材料(氧化鋁陶瓷基板、導電漿墨)</t>
         </is>
       </c>
-      <c r="B370" t="n">
-        <v>221.873735</v>
-      </c>
+      <c r="B370" t="inlineStr"/>
       <c r="C370" t="n">
         <v>272.586777</v>
       </c>
@@ -15249,6 +15622,9 @@
       <c r="L370" t="n">
         <v>160.171821</v>
       </c>
+      <c r="M370" t="n">
+        <v>184.492428</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="inlineStr">
@@ -15256,9 +15632,7 @@
           <t>面板</t>
         </is>
       </c>
-      <c r="B371" t="n">
-        <v>32471.075248</v>
-      </c>
+      <c r="B371" t="inlineStr"/>
       <c r="C371" t="n">
         <v>24410.590869</v>
       </c>
@@ -15278,16 +15652,19 @@
         <v>23204.194807</v>
       </c>
       <c r="I371" t="n">
-        <v>12322.907408</v>
+        <v>12350.788364</v>
       </c>
       <c r="J371" t="n">
-        <v>9889.286767</v>
+        <v>9910.266651</v>
       </c>
       <c r="K371" t="n">
-        <v>16749.945352</v>
+        <v>16830.50318</v>
       </c>
       <c r="L371" t="n">
-        <v>24283.916779</v>
+        <v>24313.445112</v>
+      </c>
+      <c r="M371" t="n">
+        <v>13106.350545</v>
       </c>
     </row>
     <row r="372">
@@ -15296,9 +15673,7 @@
           <t>預拌混凝土</t>
         </is>
       </c>
-      <c r="B372" t="n">
-        <v>2409.357351</v>
-      </c>
+      <c r="B372" t="inlineStr"/>
       <c r="C372" t="n">
         <v>1060.874931</v>
       </c>
@@ -15329,6 +15704,9 @@
       <c r="L372" t="n">
         <v>755.352673</v>
       </c>
+      <c r="M372" t="n">
+        <v>748.497851</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="inlineStr">
@@ -15336,9 +15714,7 @@
           <t>領域方案</t>
         </is>
       </c>
-      <c r="B373" t="n">
-        <v>178.035564</v>
-      </c>
+      <c r="B373" t="inlineStr"/>
       <c r="C373" t="n">
         <v>402.315751</v>
       </c>
@@ -15369,6 +15745,9 @@
       <c r="L373" t="n">
         <v>34.080571</v>
       </c>
+      <c r="M373" t="n">
+        <v>31.111897</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="inlineStr">
@@ -15376,9 +15755,7 @@
           <t>領域解決方案</t>
         </is>
       </c>
-      <c r="B374" t="n">
-        <v>52992.805917</v>
-      </c>
+      <c r="B374" t="inlineStr"/>
       <c r="C374" t="n">
         <v>48401.076217</v>
       </c>
@@ -15407,7 +15784,10 @@
         <v>19328.275002</v>
       </c>
       <c r="L374" t="n">
-        <v>38282.339349</v>
+        <v>38413.504349</v>
+      </c>
+      <c r="M374" t="n">
+        <v>26024.948405</v>
       </c>
     </row>
     <row r="375">
@@ -15416,9 +15796,7 @@
           <t>頭顯裝置品牌廠</t>
         </is>
       </c>
-      <c r="B375" t="n">
-        <v>706.789028</v>
-      </c>
+      <c r="B375" t="inlineStr"/>
       <c r="C375" t="n">
         <v>360.168759</v>
       </c>
@@ -15449,6 +15827,9 @@
       <c r="L375" t="n">
         <v>240.683547</v>
       </c>
+      <c r="M375" t="n">
+        <v>273.715551</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="inlineStr">
@@ -15456,9 +15837,7 @@
           <t>顏染料</t>
         </is>
       </c>
-      <c r="B376" t="n">
-        <v>154.966135</v>
-      </c>
+      <c r="B376" t="inlineStr"/>
       <c r="C376" t="n">
         <v>123.762337</v>
       </c>
@@ -15489,6 +15868,9 @@
       <c r="L376" t="n">
         <v>1183.285853</v>
       </c>
+      <c r="M376" t="n">
+        <v>382.052585</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="inlineStr">
@@ -15496,9 +15878,7 @@
           <t>顧問諮詢</t>
         </is>
       </c>
-      <c r="B377" t="n">
-        <v>86870.00238200001</v>
-      </c>
+      <c r="B377" t="inlineStr"/>
       <c r="C377" t="n">
         <v>85612.105356</v>
       </c>
@@ -15527,7 +15907,10 @@
         <v>33879.126601</v>
       </c>
       <c r="L377" t="n">
-        <v>60104.773372</v>
+        <v>60301.520872</v>
+      </c>
+      <c r="M377" t="n">
+        <v>40217.397954</v>
       </c>
     </row>
     <row r="378">
@@ -15536,9 +15919,7 @@
           <t>顯示卡</t>
         </is>
       </c>
-      <c r="B378" t="n">
-        <v>3334.129063</v>
-      </c>
+      <c r="B378" t="inlineStr"/>
       <c r="C378" t="n">
         <v>2779.106659</v>
       </c>
@@ -15569,6 +15950,9 @@
       <c r="L378" t="n">
         <v>3495.105709</v>
       </c>
+      <c r="M378" t="n">
+        <v>4041.76303</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="inlineStr">
@@ -15576,9 +15960,7 @@
           <t>顯示器模組</t>
         </is>
       </c>
-      <c r="B379" t="n">
-        <v>6143.334612</v>
-      </c>
+      <c r="B379" t="inlineStr"/>
       <c r="C379" t="n">
         <v>4610.042842</v>
       </c>
@@ -15598,16 +15980,19 @@
         <v>4894.149979</v>
       </c>
       <c r="I379" t="n">
-        <v>3515.054161</v>
+        <v>3542.935117</v>
       </c>
       <c r="J379" t="n">
-        <v>6361.772737</v>
+        <v>6382.752621</v>
       </c>
       <c r="K379" t="n">
-        <v>8210.800348000001</v>
+        <v>8291.358176</v>
       </c>
       <c r="L379" t="n">
-        <v>10665.535972</v>
+        <v>10695.064305</v>
+      </c>
+      <c r="M379" t="n">
+        <v>5621.639392</v>
       </c>
     </row>
     <row r="380">
@@ -15616,9 +16001,7 @@
           <t>風場營造</t>
         </is>
       </c>
-      <c r="B380" t="n">
-        <v>10607.090617</v>
-      </c>
+      <c r="B380" t="inlineStr"/>
       <c r="C380" t="n">
         <v>5425.109931</v>
       </c>
@@ -15649,6 +16032,9 @@
       <c r="L380" t="n">
         <v>1153.215829</v>
       </c>
+      <c r="M380" t="n">
+        <v>1364.565595</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="inlineStr">
@@ -15656,9 +16042,7 @@
           <t>風場規劃</t>
         </is>
       </c>
-      <c r="B381" t="n">
-        <v>10313.287321</v>
-      </c>
+      <c r="B381" t="inlineStr"/>
       <c r="C381" t="n">
         <v>5232.677289</v>
       </c>
@@ -15689,6 +16073,9 @@
       <c r="L381" t="n">
         <v>1064.135022</v>
       </c>
+      <c r="M381" t="n">
+        <v>1261.334311</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="inlineStr">
@@ -15696,9 +16083,7 @@
           <t>風場開發</t>
         </is>
       </c>
-      <c r="B382" t="n">
-        <v>1015.695482</v>
-      </c>
+      <c r="B382" t="inlineStr"/>
       <c r="C382" t="n">
         <v>1842.980015</v>
       </c>
@@ -15729,6 +16114,9 @@
       <c r="L382" t="n">
         <v>535.972686</v>
       </c>
+      <c r="M382" t="n">
+        <v>529.674122</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="inlineStr">
@@ -15736,9 +16124,7 @@
           <t>風機維護</t>
         </is>
       </c>
-      <c r="B383" t="n">
-        <v>416.473037</v>
-      </c>
+      <c r="B383" t="inlineStr"/>
       <c r="C383" t="n">
         <v>809.322497</v>
       </c>
@@ -15769,6 +16155,9 @@
       <c r="L383" t="n">
         <v>100.286557</v>
       </c>
+      <c r="M383" t="n">
+        <v>129.882901</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="inlineStr">
@@ -15776,9 +16165,7 @@
           <t>餐飲連鎖</t>
         </is>
       </c>
-      <c r="B384" t="n">
-        <v>176.410847</v>
-      </c>
+      <c r="B384" t="inlineStr"/>
       <c r="C384" t="n">
         <v>222.80514</v>
       </c>
@@ -15809,6 +16196,9 @@
       <c r="L384" t="n">
         <v>234.10224</v>
       </c>
+      <c r="M384" t="n">
+        <v>197.596271</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="inlineStr">
@@ -15816,9 +16206,7 @@
           <t>驅動IC</t>
         </is>
       </c>
-      <c r="B385" t="n">
-        <v>529.767761</v>
-      </c>
+      <c r="B385" t="inlineStr"/>
       <c r="C385" t="n">
         <v>435.643423</v>
       </c>
@@ -15849,6 +16237,9 @@
       <c r="L385" t="n">
         <v>131.325931</v>
       </c>
+      <c r="M385" t="n">
+        <v>132.327383</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="inlineStr">
@@ -15856,9 +16247,7 @@
           <t>高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="B386" t="n">
-        <v>66896.06574000001</v>
-      </c>
+      <c r="B386" t="inlineStr"/>
       <c r="C386" t="n">
         <v>48756.310639</v>
       </c>
@@ -15887,7 +16276,10 @@
         <v>21537.638193</v>
       </c>
       <c r="L386" t="n">
-        <v>30585.002652</v>
+        <v>30755.699152</v>
+      </c>
+      <c r="M386" t="n">
+        <v>25732.92943</v>
       </c>
     </row>
     <row r="387">
@@ -15896,9 +16288,7 @@
           <t>高壓AMI</t>
         </is>
       </c>
-      <c r="B387" t="n">
-        <v>14426.662492</v>
-      </c>
+      <c r="B387" t="inlineStr"/>
       <c r="C387" t="n">
         <v>7196.659108</v>
       </c>
@@ -15929,6 +16319,9 @@
       <c r="L387" t="n">
         <v>1951.704104</v>
       </c>
+      <c r="M387" t="n">
+        <v>1963.293267</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="inlineStr">
@@ -15936,9 +16329,7 @@
           <t>高爾夫球具業</t>
         </is>
       </c>
-      <c r="B388" t="n">
-        <v>84.368998</v>
-      </c>
+      <c r="B388" t="inlineStr"/>
       <c r="C388" t="n">
         <v>95.626407</v>
       </c>
@@ -15969,6 +16360,9 @@
       <c r="L388" t="n">
         <v>68.630905</v>
       </c>
+      <c r="M388" t="n">
+        <v>73.594961</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="inlineStr">
@@ -15976,9 +16370,7 @@
           <t>齒輪箱</t>
         </is>
       </c>
-      <c r="B389" t="n">
-        <v>30.86009</v>
-      </c>
+      <c r="B389" t="inlineStr"/>
       <c r="C389" t="n">
         <v>36.603791</v>
       </c>
@@ -16008,6 +16400,9 @@
       </c>
       <c r="L389" t="n">
         <v>13.33396</v>
+      </c>
+      <c r="M389" t="n">
+        <v>17.171037</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_4.xlsx
+++ b/Result/analyze_4.xlsx
@@ -708,37 +708,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>64245.36254</v>
+        <v>66369.527139</v>
       </c>
       <c r="D7" t="n">
-        <v>79854.839704</v>
+        <v>81143.59105</v>
       </c>
       <c r="E7" t="n">
-        <v>66565.53916</v>
+        <v>67374.15689</v>
       </c>
       <c r="F7" t="n">
-        <v>41206.522561</v>
+        <v>41991.125087</v>
       </c>
       <c r="G7" t="n">
-        <v>60529.39526</v>
+        <v>61334.673194</v>
       </c>
       <c r="H7" t="n">
-        <v>41028.53099</v>
+        <v>42878.95695</v>
       </c>
       <c r="I7" t="n">
-        <v>49063.97146</v>
+        <v>50524.051913</v>
       </c>
       <c r="J7" t="n">
-        <v>54951.847165</v>
+        <v>56015.631059</v>
       </c>
       <c r="K7" t="n">
-        <v>38331.855087</v>
+        <v>39714.527791</v>
       </c>
       <c r="L7" t="n">
-        <v>54723.141484</v>
+        <v>56355.175161</v>
       </c>
       <c r="M7" t="n">
-        <v>56026.849852</v>
+        <v>56908.140114</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>22860.62056</v>
+        <v>24984.785159</v>
       </c>
       <c r="D8" t="n">
-        <v>27063.128674</v>
+        <v>28351.88002</v>
       </c>
       <c r="E8" t="n">
-        <v>23266.177424</v>
+        <v>24074.795154</v>
       </c>
       <c r="F8" t="n">
-        <v>21030.500414</v>
+        <v>21815.10294</v>
       </c>
       <c r="G8" t="n">
-        <v>20110.573902</v>
+        <v>20915.851836</v>
       </c>
       <c r="H8" t="n">
-        <v>13088.672191</v>
+        <v>14939.098151</v>
       </c>
       <c r="I8" t="n">
-        <v>20975.509788</v>
+        <v>22435.590241</v>
       </c>
       <c r="J8" t="n">
-        <v>17863.55077</v>
+        <v>18927.334664</v>
       </c>
       <c r="K8" t="n">
-        <v>14500.934148</v>
+        <v>15883.606852</v>
       </c>
       <c r="L8" t="n">
-        <v>14109.32662</v>
+        <v>15741.360297</v>
       </c>
       <c r="M8" t="n">
-        <v>22636.38291</v>
+        <v>23517.673172</v>
       </c>
     </row>
     <row r="9">
@@ -829,41 +829,39 @@
           <t>IC通路</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>23167.311184</v>
+        <v>23167.313738</v>
       </c>
       <c r="D10" t="n">
-        <v>26203.527048</v>
+        <v>26203.529447</v>
       </c>
       <c r="E10" t="n">
-        <v>23755.35679</v>
+        <v>23755.360791</v>
       </c>
       <c r="F10" t="n">
-        <v>22384.515448</v>
+        <v>22384.519273</v>
       </c>
       <c r="G10" t="n">
-        <v>21460.329875</v>
+        <v>21460.330725</v>
       </c>
       <c r="H10" t="n">
-        <v>13369.240229</v>
+        <v>13369.242291</v>
       </c>
       <c r="I10" t="n">
-        <v>22080.086604</v>
+        <v>22080.088132</v>
       </c>
       <c r="J10" t="n">
-        <v>16080.300564</v>
+        <v>16080.302499</v>
       </c>
       <c r="K10" t="n">
-        <v>13892.812659</v>
+        <v>13892.814005</v>
       </c>
       <c r="L10" t="n">
-        <v>15735.866928</v>
+        <v>15735.867913</v>
       </c>
       <c r="M10" t="n">
-        <v>25663.9597</v>
+        <v>25663.965957</v>
       </c>
     </row>
     <row r="11">
@@ -2268,37 +2266,37 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>630.037885</v>
+        <v>2754.202484</v>
       </c>
       <c r="D45" t="n">
-        <v>567.533106</v>
+        <v>1856.284452</v>
       </c>
       <c r="E45" t="n">
-        <v>667.56136</v>
+        <v>1476.17909</v>
       </c>
       <c r="F45" t="n">
-        <v>510.493875</v>
+        <v>1295.096401</v>
       </c>
       <c r="G45" t="n">
-        <v>461.120097</v>
+        <v>1266.398031</v>
       </c>
       <c r="H45" t="n">
-        <v>542.611934</v>
+        <v>2393.037894</v>
       </c>
       <c r="I45" t="n">
-        <v>831.723696</v>
+        <v>2291.804149</v>
       </c>
       <c r="J45" t="n">
-        <v>1494.21237</v>
+        <v>2557.996264</v>
       </c>
       <c r="K45" t="n">
-        <v>578.994661</v>
+        <v>1961.667365</v>
       </c>
       <c r="L45" t="n">
-        <v>311.358666</v>
+        <v>1943.392343</v>
       </c>
       <c r="M45" t="n">
-        <v>336.185064</v>
+        <v>1217.475326</v>
       </c>
     </row>
     <row r="46">
@@ -2430,41 +2428,39 @@
           <t>光通訊設備(如光纖電纜、光傳輸設備)</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>21660.176564</v>
+        <v>21660.176578</v>
       </c>
       <c r="D49" t="n">
-        <v>33047.78273</v>
+        <v>33047.782973</v>
       </c>
       <c r="E49" t="n">
-        <v>31031.516617</v>
+        <v>31031.516965</v>
       </c>
       <c r="F49" t="n">
-        <v>25138.33235</v>
+        <v>25138.332784</v>
       </c>
       <c r="G49" t="n">
-        <v>29384.521322</v>
+        <v>29384.521702</v>
       </c>
       <c r="H49" t="n">
-        <v>16959.463258</v>
+        <v>16959.463699</v>
       </c>
       <c r="I49" t="n">
-        <v>31417.552475</v>
+        <v>31417.552491</v>
       </c>
       <c r="J49" t="n">
-        <v>17982.511614</v>
+        <v>17982.51193175</v>
       </c>
       <c r="K49" t="n">
-        <v>16574.467098</v>
+        <v>16574.467611</v>
       </c>
       <c r="L49" t="n">
-        <v>17393.764922</v>
+        <v>17393.765474</v>
       </c>
       <c r="M49" t="n">
-        <v>24012.841422</v>
+        <v>24012.841679</v>
       </c>
     </row>
     <row r="50">
@@ -2516,37 +2512,37 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>46261.678466</v>
+        <v>46861.028144</v>
       </c>
       <c r="D51" t="n">
-        <v>55001.5231445</v>
+        <v>55541.6982155</v>
       </c>
       <c r="E51" t="n">
-        <v>42464.959116</v>
+        <v>42963.81941</v>
       </c>
       <c r="F51" t="n">
-        <v>44196.75907</v>
+        <v>44560.400181</v>
       </c>
       <c r="G51" t="n">
-        <v>37612.103332</v>
+        <v>37873.344935</v>
       </c>
       <c r="H51" t="n">
-        <v>28842.071459</v>
+        <v>28974.604559</v>
       </c>
       <c r="I51" t="n">
-        <v>46362.4274035</v>
+        <v>46608.9940375</v>
       </c>
       <c r="J51" t="n">
-        <v>32612.94230908333</v>
+        <v>32892.47787208333</v>
       </c>
       <c r="K51" t="n">
-        <v>31760.1422915</v>
+        <v>31880.9489705</v>
       </c>
       <c r="L51" t="n">
-        <v>35114.01018025</v>
+        <v>35216.57897425</v>
       </c>
       <c r="M51" t="n">
-        <v>52770.311763</v>
+        <v>52964.838728</v>
       </c>
     </row>
     <row r="52">
@@ -2639,37 +2635,37 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>28721.0820285</v>
+        <v>28721.3575975</v>
       </c>
       <c r="D54" t="n">
-        <v>35624.1863455</v>
+        <v>35624.3518225</v>
       </c>
       <c r="E54" t="n">
-        <v>27123.660269</v>
+        <v>27123.768856</v>
       </c>
       <c r="F54" t="n">
-        <v>18397.67614</v>
+        <v>18397.815452</v>
       </c>
       <c r="G54" t="n">
-        <v>21322.84776</v>
+        <v>21322.946556</v>
       </c>
       <c r="H54" t="n">
-        <v>20652.90732066667</v>
+        <v>20652.98982766667</v>
       </c>
       <c r="I54" t="n">
-        <v>20861.34366</v>
+        <v>20861.383929</v>
       </c>
       <c r="J54" t="n">
-        <v>17671.550591</v>
+        <v>17671.608531</v>
       </c>
       <c r="K54" t="n">
-        <v>20300.1301685</v>
+        <v>20300.1877485</v>
       </c>
       <c r="L54" t="n">
-        <v>23787.396779</v>
+        <v>23787.469895</v>
       </c>
       <c r="M54" t="n">
-        <v>20592.716339</v>
+        <v>20592.83481</v>
       </c>
     </row>
     <row r="55">
@@ -3787,37 +3783,37 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>16740.294212</v>
+        <v>18864.458811</v>
       </c>
       <c r="D82" t="n">
-        <v>10094.117266</v>
+        <v>11382.868612</v>
       </c>
       <c r="E82" t="n">
-        <v>19551.170364</v>
+        <v>20359.788094</v>
       </c>
       <c r="F82" t="n">
-        <v>11289.034792</v>
+        <v>12073.637318</v>
       </c>
       <c r="G82" t="n">
-        <v>17865.962064</v>
+        <v>18671.239998</v>
       </c>
       <c r="H82" t="n">
-        <v>21170.243334</v>
+        <v>23020.669294</v>
       </c>
       <c r="I82" t="n">
-        <v>15710.99557</v>
+        <v>17171.076023</v>
       </c>
       <c r="J82" t="n">
-        <v>11591.809905</v>
+        <v>12655.593799</v>
       </c>
       <c r="K82" t="n">
-        <v>11750.890562</v>
+        <v>13133.563266</v>
       </c>
       <c r="L82" t="n">
-        <v>16381.719759</v>
+        <v>18013.753436</v>
       </c>
       <c r="M82" t="n">
-        <v>10215.737057</v>
+        <v>11097.027319</v>
       </c>
     </row>
     <row r="83">
@@ -4072,39 +4068,41 @@
           <t>塑膠製品</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
       <c r="C89" t="n">
-        <v>12002.829735</v>
+        <v>11885.591801</v>
       </c>
       <c r="D89" t="n">
-        <v>9108.175635</v>
+        <v>9054.18578</v>
       </c>
       <c r="E89" t="n">
-        <v>7381.549742</v>
+        <v>7313.617311</v>
       </c>
       <c r="F89" t="n">
-        <v>5088.530042</v>
+        <v>5030.955231</v>
       </c>
       <c r="G89" t="n">
-        <v>3271.590657</v>
+        <v>3244.487328</v>
       </c>
       <c r="H89" t="n">
-        <v>3714.646776</v>
+        <v>3683.09207</v>
       </c>
       <c r="I89" t="n">
-        <v>3304.559114</v>
+        <v>3290.308271</v>
       </c>
       <c r="J89" t="n">
-        <v>4379.535411</v>
+        <v>4359.502221</v>
       </c>
       <c r="K89" t="n">
-        <v>4087.75251625</v>
+        <v>4058.98156325</v>
       </c>
       <c r="L89" t="n">
-        <v>4662.215163</v>
+        <v>4644.216465</v>
       </c>
       <c r="M89" t="n">
-        <v>4615.015594</v>
+        <v>4591.400699</v>
       </c>
     </row>
     <row r="90">
@@ -4361,37 +4359,37 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>26988.793466</v>
+        <v>27588.143144</v>
       </c>
       <c r="D96" t="n">
-        <v>24301.880293</v>
+        <v>24842.055364</v>
       </c>
       <c r="E96" t="n">
-        <v>20789.206209</v>
+        <v>21288.066503</v>
       </c>
       <c r="F96" t="n">
-        <v>28222.574718</v>
+        <v>28586.215829</v>
       </c>
       <c r="G96" t="n">
-        <v>25597.469195</v>
+        <v>25858.710798</v>
       </c>
       <c r="H96" t="n">
-        <v>23262.859811</v>
+        <v>23395.392911</v>
       </c>
       <c r="I96" t="n">
-        <v>27544.097861</v>
+        <v>27790.664495</v>
       </c>
       <c r="J96" t="n">
-        <v>20508.477377</v>
+        <v>20788.01294</v>
       </c>
       <c r="K96" t="n">
-        <v>17519.412673</v>
+        <v>17640.219352</v>
       </c>
       <c r="L96" t="n">
-        <v>14268.980583</v>
+        <v>14371.549377</v>
       </c>
       <c r="M96" t="n">
-        <v>23844.873978</v>
+        <v>24039.400943</v>
       </c>
     </row>
     <row r="97">
@@ -4689,37 +4687,37 @@
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
-        <v>8290.462055</v>
+        <v>10414.626654</v>
       </c>
       <c r="D104" t="n">
-        <v>6256.360722</v>
+        <v>7545.112068</v>
       </c>
       <c r="E104" t="n">
-        <v>5383.249896</v>
+        <v>6191.867626</v>
       </c>
       <c r="F104" t="n">
-        <v>4913.09965</v>
+        <v>5697.702176</v>
       </c>
       <c r="G104" t="n">
-        <v>5479.417658</v>
+        <v>6284.695592</v>
       </c>
       <c r="H104" t="n">
-        <v>7428.360549</v>
+        <v>9278.786509</v>
       </c>
       <c r="I104" t="n">
-        <v>5369.4055</v>
+        <v>6829.485953</v>
       </c>
       <c r="J104" t="n">
-        <v>3856.007284</v>
+        <v>4919.791178</v>
       </c>
       <c r="K104" t="n">
-        <v>5991.469833</v>
+        <v>7374.142537</v>
       </c>
       <c r="L104" t="n">
-        <v>10618.629776</v>
+        <v>12250.663453</v>
       </c>
       <c r="M104" t="n">
-        <v>7259.438313</v>
+        <v>8140.728575</v>
       </c>
     </row>
     <row r="105">
@@ -5304,37 +5302,37 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>355.53067</v>
+        <v>355.530996</v>
       </c>
       <c r="D119" t="n">
-        <v>473.825315</v>
+        <v>473.825405</v>
       </c>
       <c r="E119" t="n">
-        <v>520.8674140000001</v>
+        <v>520.867665</v>
       </c>
       <c r="F119" t="n">
-        <v>448.8944416666667</v>
+        <v>448.8946516666667</v>
       </c>
       <c r="G119" t="n">
-        <v>281.9185326666667</v>
+        <v>281.9185366666667</v>
       </c>
       <c r="H119" t="n">
-        <v>295.937306</v>
+        <v>295.937312</v>
       </c>
       <c r="I119" t="n">
-        <v>324.912894</v>
+        <v>324.913326</v>
       </c>
       <c r="J119" t="n">
-        <v>390.227216</v>
+        <v>390.227295</v>
       </c>
       <c r="K119" t="n">
-        <v>447.2701183333333</v>
+        <v>447.2703663333333</v>
       </c>
       <c r="L119" t="n">
-        <v>288.292358</v>
+        <v>288.29293</v>
       </c>
       <c r="M119" t="n">
-        <v>255.231478</v>
+        <v>255.232646</v>
       </c>
     </row>
     <row r="120">
@@ -5591,37 +5589,37 @@
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>5005.36506</v>
+        <v>7129.529659</v>
       </c>
       <c r="D126" t="n">
-        <v>3740.476529</v>
+        <v>5029.227875</v>
       </c>
       <c r="E126" t="n">
-        <v>2836.214551</v>
+        <v>3644.832281</v>
       </c>
       <c r="F126" t="n">
-        <v>2961.12438</v>
+        <v>3745.726906</v>
       </c>
       <c r="G126" t="n">
-        <v>3856.094202</v>
+        <v>4661.372136</v>
       </c>
       <c r="H126" t="n">
-        <v>5860.199237</v>
+        <v>7710.625197</v>
       </c>
       <c r="I126" t="n">
-        <v>3520.920438</v>
+        <v>4981.000891</v>
       </c>
       <c r="J126" t="n">
-        <v>2063.526059</v>
+        <v>3127.309953</v>
       </c>
       <c r="K126" t="n">
-        <v>4531.467204</v>
+        <v>5914.139908</v>
       </c>
       <c r="L126" t="n">
-        <v>9358.739234000001</v>
+        <v>10990.772911</v>
       </c>
       <c r="M126" t="n">
-        <v>6099.532686</v>
+        <v>6980.822948</v>
       </c>
     </row>
     <row r="127">
@@ -5671,41 +5669,39 @@
           <t>應用/系統軟體設計開發</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>0</v>
-      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>17106.60963</v>
+        <v>17113.749203</v>
       </c>
       <c r="D128" t="n">
-        <v>20360.033545</v>
+        <v>20366.878697</v>
       </c>
       <c r="E128" t="n">
-        <v>15724.118434</v>
+        <v>15730.64163</v>
       </c>
       <c r="F128" t="n">
-        <v>17409.269992</v>
+        <v>17419.843036</v>
       </c>
       <c r="G128" t="n">
-        <v>14757.653504</v>
+        <v>14761.523537</v>
       </c>
       <c r="H128" t="n">
-        <v>10017.471388</v>
+        <v>10022.62538</v>
       </c>
       <c r="I128" t="n">
-        <v>19662.350505</v>
+        <v>19667.6292</v>
       </c>
       <c r="J128" t="n">
-        <v>13346.201013</v>
+        <v>13356.521027</v>
       </c>
       <c r="K128" t="n">
-        <v>11864.399803</v>
+        <v>11881.58198</v>
       </c>
       <c r="L128" t="n">
-        <v>10651.343184</v>
+        <v>10664.831244</v>
       </c>
       <c r="M128" t="n">
-        <v>19970.980664</v>
+        <v>19985.051344</v>
       </c>
     </row>
     <row r="129">
@@ -8504,37 +8500,37 @@
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
-        <v>5454.774995</v>
+        <v>7578.939594</v>
       </c>
       <c r="D197" t="n">
-        <v>7107.940092</v>
+        <v>8396.691438</v>
       </c>
       <c r="E197" t="n">
-        <v>6568.621346</v>
+        <v>7377.239076</v>
       </c>
       <c r="F197" t="n">
-        <v>4047.39362</v>
+        <v>4831.996146</v>
       </c>
       <c r="G197" t="n">
-        <v>5034.553506</v>
+        <v>5839.83144</v>
       </c>
       <c r="H197" t="n">
-        <v>3672.856616</v>
+        <v>5523.282576</v>
       </c>
       <c r="I197" t="n">
-        <v>4992.519914</v>
+        <v>6452.600367</v>
       </c>
       <c r="J197" t="n">
-        <v>4026.694534</v>
+        <v>5090.478428</v>
       </c>
       <c r="K197" t="n">
-        <v>4341.565028</v>
+        <v>5724.237732</v>
       </c>
       <c r="L197" t="n">
-        <v>3343.938357</v>
+        <v>4975.972034</v>
       </c>
       <c r="M197" t="n">
-        <v>3120.550466</v>
+        <v>4001.840728</v>
       </c>
     </row>
     <row r="198">
@@ -8707,41 +8703,39 @@
           <t>監理法遵</t>
         </is>
       </c>
-      <c r="B202" t="n">
-        <v>0</v>
-      </c>
+      <c r="B202" t="inlineStr"/>
       <c r="C202" t="n">
-        <v>92.033252</v>
+        <v>99.172825</v>
       </c>
       <c r="D202" t="n">
-        <v>89.33705399999999</v>
+        <v>96.18220599999999</v>
       </c>
       <c r="E202" t="n">
-        <v>81.294842</v>
+        <v>87.818038</v>
       </c>
       <c r="F202" t="n">
-        <v>38.631236</v>
+        <v>49.20428</v>
       </c>
       <c r="G202" t="n">
-        <v>30.31962</v>
+        <v>34.189653</v>
       </c>
       <c r="H202" t="n">
-        <v>28.941799</v>
+        <v>34.095791</v>
       </c>
       <c r="I202" t="n">
-        <v>41.312507</v>
+        <v>46.591202</v>
       </c>
       <c r="J202" t="n">
-        <v>35.605645</v>
+        <v>45.925659</v>
       </c>
       <c r="K202" t="n">
-        <v>21.356506</v>
+        <v>38.538683</v>
       </c>
       <c r="L202" t="n">
-        <v>49.572878</v>
+        <v>63.060938</v>
       </c>
       <c r="M202" t="n">
-        <v>32.077407</v>
+        <v>46.148087</v>
       </c>
     </row>
     <row r="203">
@@ -8998,37 +8992,37 @@
       </c>
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="n">
-        <v>63688.60158</v>
+        <v>65812.766179</v>
       </c>
       <c r="D209" t="n">
-        <v>77750.390646</v>
+        <v>79039.141992</v>
       </c>
       <c r="E209" t="n">
-        <v>79891.488614</v>
+        <v>80700.106344</v>
       </c>
       <c r="F209" t="n">
-        <v>89052.42034300001</v>
+        <v>89837.02286899999</v>
       </c>
       <c r="G209" t="n">
-        <v>87942.78604000001</v>
+        <v>88748.063974</v>
       </c>
       <c r="H209" t="n">
-        <v>106932.388106</v>
+        <v>108782.814066</v>
       </c>
       <c r="I209" t="n">
-        <v>87892.950323</v>
+        <v>89353.030776</v>
       </c>
       <c r="J209" t="n">
-        <v>66275.98652799999</v>
+        <v>67339.770422</v>
       </c>
       <c r="K209" t="n">
-        <v>69327.20989899999</v>
+        <v>70709.88260300001</v>
       </c>
       <c r="L209" t="n">
-        <v>73254.846425</v>
+        <v>74886.880102</v>
       </c>
       <c r="M209" t="n">
-        <v>62636.132136</v>
+        <v>63517.422398</v>
       </c>
     </row>
     <row r="210">
@@ -9365,41 +9359,39 @@
           <t>端點安全防護</t>
         </is>
       </c>
-      <c r="B218" t="n">
-        <v>0</v>
-      </c>
+      <c r="B218" t="inlineStr"/>
       <c r="C218" t="n">
-        <v>321.210044</v>
+        <v>328.349617</v>
       </c>
       <c r="D218" t="n">
-        <v>201.478513</v>
+        <v>208.323665</v>
       </c>
       <c r="E218" t="n">
-        <v>333.757947</v>
+        <v>340.281143</v>
       </c>
       <c r="F218" t="n">
-        <v>241.166522</v>
+        <v>251.739566</v>
       </c>
       <c r="G218" t="n">
-        <v>183.189613</v>
+        <v>187.059646</v>
       </c>
       <c r="H218" t="n">
-        <v>149.55895</v>
+        <v>154.712942</v>
       </c>
       <c r="I218" t="n">
-        <v>263.389315</v>
+        <v>268.66801</v>
       </c>
       <c r="J218" t="n">
-        <v>284.850904</v>
+        <v>295.170918</v>
       </c>
       <c r="K218" t="n">
-        <v>248.789124</v>
+        <v>265.971301</v>
       </c>
       <c r="L218" t="n">
-        <v>189.634885</v>
+        <v>203.122945</v>
       </c>
       <c r="M218" t="n">
-        <v>464.640735</v>
+        <v>478.711415</v>
       </c>
     </row>
     <row r="219">
@@ -9449,41 +9441,39 @@
           <t>精簡型電腦</t>
         </is>
       </c>
-      <c r="B220" t="n">
-        <v>0</v>
-      </c>
+      <c r="B220" t="inlineStr"/>
       <c r="C220" t="n">
-        <v>17701.68528</v>
+        <v>17719.364039</v>
       </c>
       <c r="D220" t="n">
-        <v>19702.701665</v>
+        <v>19717.326898</v>
       </c>
       <c r="E220" t="n">
-        <v>17033.227044</v>
+        <v>17053.768333</v>
       </c>
       <c r="F220" t="n">
-        <v>18965.271277</v>
+        <v>18980.909708</v>
       </c>
       <c r="G220" t="n">
-        <v>16086.136515</v>
+        <v>16095.456465</v>
       </c>
       <c r="H220" t="n">
-        <v>10834.821617</v>
+        <v>10847.263607</v>
       </c>
       <c r="I220" t="n">
-        <v>21234.092757</v>
+        <v>21260.323122</v>
       </c>
       <c r="J220" t="n">
-        <v>15605.744513</v>
+        <v>15618.414634</v>
       </c>
       <c r="K220" t="n">
-        <v>13967.30455</v>
+        <v>13976.538617</v>
       </c>
       <c r="L220" t="n">
-        <v>13521.26411</v>
+        <v>13534.66886</v>
       </c>
       <c r="M220" t="n">
-        <v>21815.789122</v>
+        <v>21827.375471</v>
       </c>
     </row>
     <row r="221">
@@ -9492,41 +9482,39 @@
           <t>系統整合</t>
         </is>
       </c>
-      <c r="B221" t="n">
-        <v>0</v>
-      </c>
+      <c r="B221" t="inlineStr"/>
       <c r="C221" t="n">
-        <v>53716.452812</v>
+        <v>53737.871531</v>
       </c>
       <c r="D221" t="n">
-        <v>60572.25377675</v>
+        <v>60592.78923275</v>
       </c>
       <c r="E221" t="n">
-        <v>46740.711059</v>
+        <v>46760.280647</v>
       </c>
       <c r="F221" t="n">
-        <v>52639.406125</v>
+        <v>52671.125257</v>
       </c>
       <c r="G221" t="n">
-        <v>46651.082404</v>
+        <v>46662.692503</v>
       </c>
       <c r="H221" t="n">
-        <v>35138.702832</v>
+        <v>35154.164808</v>
       </c>
       <c r="I221" t="n">
-        <v>61218.824014</v>
+        <v>61234.660099</v>
       </c>
       <c r="J221" t="n">
-        <v>41232.425259</v>
+        <v>41263.385301</v>
       </c>
       <c r="K221" t="n">
-        <v>38792.497906</v>
+        <v>38844.044437</v>
       </c>
       <c r="L221" t="n">
-        <v>40580.053095</v>
+        <v>40620.517275</v>
       </c>
       <c r="M221" t="n">
-        <v>65828.78191400001</v>
+        <v>65870.99395400001</v>
       </c>
     </row>
     <row r="222">
@@ -9535,41 +9523,39 @@
           <t>系統整合服務</t>
         </is>
       </c>
-      <c r="B222" t="n">
-        <v>0</v>
-      </c>
+      <c r="B222" t="inlineStr"/>
       <c r="C222" t="n">
-        <v>28040.562055</v>
+        <v>28047.7169</v>
       </c>
       <c r="D222" t="n">
-        <v>29437.103302</v>
+        <v>29443.95417</v>
       </c>
       <c r="E222" t="n">
-        <v>25809.373384</v>
+        <v>25815.903051</v>
       </c>
       <c r="F222" t="n">
-        <v>24027.744344</v>
+        <v>24038.323103</v>
       </c>
       <c r="G222" t="n">
-        <v>21792.572541</v>
+        <v>21796.461511</v>
       </c>
       <c r="H222" t="n">
-        <v>15468.320478</v>
+        <v>15473.48016</v>
       </c>
       <c r="I222" t="n">
-        <v>26826.87184</v>
+        <v>26832.157011</v>
       </c>
       <c r="J222" t="n">
-        <v>20095.910677</v>
+        <v>20106.232531</v>
       </c>
       <c r="K222" t="n">
-        <v>18422.68964</v>
+        <v>18439.873462</v>
       </c>
       <c r="L222" t="n">
-        <v>15724.474534</v>
+        <v>15737.964597</v>
       </c>
       <c r="M222" t="n">
-        <v>26438.264684</v>
+        <v>26452.338202</v>
       </c>
     </row>
     <row r="223">
@@ -9906,41 +9892,39 @@
           <t>網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
         </is>
       </c>
-      <c r="B231" t="n">
-        <v>0</v>
-      </c>
+      <c r="B231" t="inlineStr"/>
       <c r="C231" t="n">
-        <v>56817.858664</v>
+        <v>56817.858678</v>
       </c>
       <c r="D231" t="n">
-        <v>56040.51869</v>
+        <v>56040.518933</v>
       </c>
       <c r="E231" t="n">
-        <v>55377.269461</v>
+        <v>55377.269809</v>
       </c>
       <c r="F231" t="n">
-        <v>57133.697809</v>
+        <v>57133.698243</v>
       </c>
       <c r="G231" t="n">
-        <v>52595.137762</v>
+        <v>52595.138142</v>
       </c>
       <c r="H231" t="n">
-        <v>41644.705552</v>
+        <v>41644.705993</v>
       </c>
       <c r="I231" t="n">
-        <v>55917.716171</v>
+        <v>55917.716187</v>
       </c>
       <c r="J231" t="n">
-        <v>49250.929895</v>
+        <v>49250.93021275</v>
       </c>
       <c r="K231" t="n">
-        <v>46680.697517</v>
+        <v>46680.69803</v>
       </c>
       <c r="L231" t="n">
-        <v>56939.711475</v>
+        <v>56939.712027</v>
       </c>
       <c r="M231" t="n">
-        <v>61020.908087</v>
+        <v>61020.908344</v>
       </c>
     </row>
     <row r="232">
@@ -9990,41 +9974,39 @@
           <t>線上遊戲業</t>
         </is>
       </c>
-      <c r="B233" t="n">
-        <v>0</v>
-      </c>
+      <c r="B233" t="inlineStr"/>
       <c r="C233" t="n">
-        <v>2.599355</v>
+        <v>20.278114</v>
       </c>
       <c r="D233" t="n">
-        <v>2.476017</v>
+        <v>17.10125</v>
       </c>
       <c r="E233" t="n">
-        <v>4.015791</v>
+        <v>24.55708</v>
       </c>
       <c r="F233" t="n">
-        <v>3.491414</v>
+        <v>19.129845</v>
       </c>
       <c r="G233" t="n">
-        <v>3.386786</v>
+        <v>12.706736</v>
       </c>
       <c r="H233" t="n">
-        <v>3.459768</v>
+        <v>15.901758</v>
       </c>
       <c r="I233" t="n">
-        <v>2.680378</v>
+        <v>28.910743</v>
       </c>
       <c r="J233" t="n">
-        <v>3.320053</v>
+        <v>15.990174</v>
       </c>
       <c r="K233" t="n">
-        <v>1.744362</v>
+        <v>10.978429</v>
       </c>
       <c r="L233" t="n">
-        <v>3.25085</v>
+        <v>16.6556</v>
       </c>
       <c r="M233" t="n">
-        <v>5.003497</v>
+        <v>16.589846</v>
       </c>
     </row>
     <row r="234">
@@ -11878,41 +11860,39 @@
           <t>資料安全</t>
         </is>
       </c>
-      <c r="B279" t="n">
-        <v>0</v>
-      </c>
+      <c r="B279" t="inlineStr"/>
       <c r="C279" t="n">
-        <v>277.215734</v>
+        <v>284.355307</v>
       </c>
       <c r="D279" t="n">
-        <v>170.541978</v>
+        <v>177.38713</v>
       </c>
       <c r="E279" t="n">
-        <v>210.351444</v>
+        <v>216.87464</v>
       </c>
       <c r="F279" t="n">
-        <v>165.810624</v>
+        <v>176.383668</v>
       </c>
       <c r="G279" t="n">
-        <v>156.241852</v>
+        <v>160.111885</v>
       </c>
       <c r="H279" t="n">
-        <v>131.841095</v>
+        <v>136.995087</v>
       </c>
       <c r="I279" t="n">
-        <v>232.28676</v>
+        <v>237.565455</v>
       </c>
       <c r="J279" t="n">
-        <v>215.443446</v>
+        <v>225.76346</v>
       </c>
       <c r="K279" t="n">
-        <v>181.962852</v>
+        <v>199.145029</v>
       </c>
       <c r="L279" t="n">
-        <v>146.448813</v>
+        <v>159.936873</v>
       </c>
       <c r="M279" t="n">
-        <v>416.308613</v>
+        <v>430.379293</v>
       </c>
     </row>
     <row r="280">
@@ -11921,41 +11901,39 @@
           <t>資料庫</t>
         </is>
       </c>
-      <c r="B280" t="n">
-        <v>0</v>
-      </c>
+      <c r="B280" t="inlineStr"/>
       <c r="C280" t="n">
-        <v>221.767453</v>
+        <v>228.907026</v>
       </c>
       <c r="D280" t="n">
-        <v>191.79646925</v>
+        <v>198.64162125</v>
       </c>
       <c r="E280" t="n">
-        <v>224.134318</v>
+        <v>230.657514</v>
       </c>
       <c r="F280" t="n">
-        <v>131.9867613333333</v>
+        <v>142.5598053333333</v>
       </c>
       <c r="G280" t="n">
-        <v>112.003084</v>
+        <v>115.873117</v>
       </c>
       <c r="H280" t="n">
-        <v>95.262811</v>
+        <v>100.416803</v>
       </c>
       <c r="I280" t="n">
-        <v>138.232164</v>
+        <v>143.510859</v>
       </c>
       <c r="J280" t="n">
-        <v>132.319825</v>
+        <v>142.639839</v>
       </c>
       <c r="K280" t="n">
-        <v>97.0951</v>
+        <v>114.277277</v>
       </c>
       <c r="L280" t="n">
-        <v>115.11786</v>
+        <v>128.60592</v>
       </c>
       <c r="M280" t="n">
-        <v>162.790327</v>
+        <v>176.861007</v>
       </c>
     </row>
     <row r="281">
@@ -13358,41 +13336,39 @@
           <t>醫療器材研發、設計、製造</t>
         </is>
       </c>
-      <c r="B315" t="n">
-        <v>0</v>
-      </c>
+      <c r="B315" t="inlineStr"/>
       <c r="C315" t="n">
-        <v>20737.776199</v>
+        <v>20755.454958</v>
       </c>
       <c r="D315" t="n">
-        <v>22044.853396</v>
+        <v>22059.478629</v>
       </c>
       <c r="E315" t="n">
-        <v>17483.927919</v>
+        <v>17504.469208</v>
       </c>
       <c r="F315" t="n">
-        <v>20411.482613</v>
+        <v>20427.121044</v>
       </c>
       <c r="G315" t="n">
-        <v>19384.998605</v>
+        <v>19394.318555</v>
       </c>
       <c r="H315" t="n">
-        <v>15908.281289</v>
+        <v>15920.723279</v>
       </c>
       <c r="I315" t="n">
-        <v>23106.606441</v>
+        <v>23132.836806</v>
       </c>
       <c r="J315" t="n">
-        <v>15672.53524</v>
+        <v>15685.205361</v>
       </c>
       <c r="K315" t="n">
-        <v>16404.89780025</v>
+        <v>16414.13186725</v>
       </c>
       <c r="L315" t="n">
-        <v>19996.373043</v>
+        <v>20009.777793</v>
       </c>
       <c r="M315" t="n">
-        <v>26651.270987</v>
+        <v>26662.857336</v>
       </c>
     </row>
     <row r="316">
@@ -14109,25 +14085,25 @@
         <v>15768.55102325</v>
       </c>
       <c r="F333" t="n">
-        <v>7347.989453</v>
+        <v>7354.605541</v>
       </c>
       <c r="G333" t="n">
-        <v>7932.572324</v>
+        <v>7935.62915</v>
       </c>
       <c r="H333" t="n">
-        <v>3125.089956</v>
+        <v>3128.643384</v>
       </c>
       <c r="I333" t="n">
-        <v>2081.51456</v>
+        <v>2082.659385</v>
       </c>
       <c r="J333" t="n">
-        <v>3695.969266</v>
+        <v>3698.141614</v>
       </c>
       <c r="K333" t="n">
-        <v>2538.838535</v>
+        <v>2539.938102</v>
       </c>
       <c r="L333" t="n">
-        <v>1623.031834</v>
+        <v>1626.719455</v>
       </c>
       <c r="M333" t="n">
         <v>1040.264632</v>
@@ -14551,37 +14527,37 @@
       </c>
       <c r="B344" t="inlineStr"/>
       <c r="C344" t="n">
-        <v>21514.800382</v>
+        <v>23638.964981</v>
       </c>
       <c r="D344" t="n">
-        <v>27123.57557</v>
+        <v>28412.326916</v>
       </c>
       <c r="E344" t="n">
-        <v>24274.913239</v>
+        <v>25083.530969</v>
       </c>
       <c r="F344" t="n">
-        <v>26937.660089</v>
+        <v>27722.262615</v>
       </c>
       <c r="G344" t="n">
-        <v>24035.211217</v>
+        <v>24840.489151</v>
       </c>
       <c r="H344" t="n">
-        <v>17898.639571</v>
+        <v>19749.065531</v>
       </c>
       <c r="I344" t="n">
-        <v>25078.185622</v>
+        <v>26538.266075</v>
       </c>
       <c r="J344" t="n">
-        <v>19946.701097</v>
+        <v>21010.484991</v>
       </c>
       <c r="K344" t="n">
-        <v>17820.438774</v>
+        <v>19203.111478</v>
       </c>
       <c r="L344" t="n">
-        <v>16558.05922</v>
+        <v>18190.092897</v>
       </c>
       <c r="M344" t="n">
-        <v>23103.495319</v>
+        <v>23984.785581</v>
       </c>
     </row>
     <row r="345">
@@ -15371,37 +15347,37 @@
       </c>
       <c r="B364" t="inlineStr"/>
       <c r="C364" t="n">
-        <v>12692.720717</v>
+        <v>13292.070395</v>
       </c>
       <c r="D364" t="n">
-        <v>13657.361192</v>
+        <v>14197.536263</v>
       </c>
       <c r="E364" t="n">
-        <v>16721.065206</v>
+        <v>17219.9255</v>
       </c>
       <c r="F364" t="n">
-        <v>8042.620082</v>
+        <v>8406.261193</v>
       </c>
       <c r="G364" t="n">
-        <v>8416.458767</v>
+        <v>8677.70037</v>
       </c>
       <c r="H364" t="n">
-        <v>3714.150485</v>
+        <v>3846.683585</v>
       </c>
       <c r="I364" t="n">
-        <v>2693.743379</v>
+        <v>2940.310013</v>
       </c>
       <c r="J364" t="n">
-        <v>4152.977919</v>
+        <v>4432.513482</v>
       </c>
       <c r="K364" t="n">
-        <v>2934.191337</v>
+        <v>3054.998016</v>
       </c>
       <c r="L364" t="n">
-        <v>2266.045243</v>
+        <v>2368.614037</v>
       </c>
       <c r="M364" t="n">
-        <v>1518.505128</v>
+        <v>1713.032093</v>
       </c>
     </row>
     <row r="365">
@@ -15943,41 +15919,39 @@
           <t>顯示卡</t>
         </is>
       </c>
-      <c r="B378" t="n">
-        <v>0</v>
-      </c>
+      <c r="B378" t="inlineStr"/>
       <c r="C378" t="n">
-        <v>4333.524657</v>
+        <v>4351.203416</v>
       </c>
       <c r="D378" t="n">
-        <v>3892.294775</v>
+        <v>3906.920008</v>
       </c>
       <c r="E378" t="n">
-        <v>4853.743625</v>
+        <v>4874.284914</v>
       </c>
       <c r="F378" t="n">
-        <v>4067.911443</v>
+        <v>4083.549874</v>
       </c>
       <c r="G378" t="n">
-        <v>3148.716475</v>
+        <v>3158.036425</v>
       </c>
       <c r="H378" t="n">
-        <v>2467.269482</v>
+        <v>2479.711472</v>
       </c>
       <c r="I378" t="n">
-        <v>3468.875344</v>
+        <v>3495.105709</v>
       </c>
       <c r="J378" t="n">
-        <v>4029.092909</v>
+        <v>4041.76303</v>
       </c>
       <c r="K378" t="n">
-        <v>3731.069977</v>
+        <v>3740.304044</v>
       </c>
       <c r="L378" t="n">
-        <v>5067.871205</v>
+        <v>5081.275955</v>
       </c>
       <c r="M378" t="n">
-        <v>3318.346057</v>
+        <v>3329.932406</v>
       </c>
     </row>
     <row r="379">
@@ -16275,37 +16249,37 @@
       </c>
       <c r="B386" t="inlineStr"/>
       <c r="C386" t="n">
-        <v>40266.583663</v>
+        <v>40865.933341</v>
       </c>
       <c r="D386" t="n">
-        <v>42166.52003</v>
+        <v>42706.695101</v>
       </c>
       <c r="E386" t="n">
-        <v>41541.089222</v>
+        <v>42039.949516</v>
       </c>
       <c r="F386" t="n">
-        <v>32548.934586</v>
+        <v>32912.575697</v>
       </c>
       <c r="G386" t="n">
-        <v>33387.284586</v>
+        <v>33648.526189</v>
       </c>
       <c r="H386" t="n">
-        <v>21405.105093</v>
+        <v>21537.638193</v>
       </c>
       <c r="I386" t="n">
-        <v>30509.132518</v>
+        <v>30755.699152</v>
       </c>
       <c r="J386" t="n">
-        <v>25453.393867</v>
+        <v>25732.92943</v>
       </c>
       <c r="K386" t="n">
-        <v>20572.095927</v>
+        <v>20692.902606</v>
       </c>
       <c r="L386" t="n">
-        <v>19506.800781</v>
+        <v>19609.369575</v>
       </c>
       <c r="M386" t="n">
-        <v>27533.26644</v>
+        <v>27727.793405</v>
       </c>
     </row>
     <row r="387">
